--- a/medicoes.xlsx
+++ b/medicoes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,27 +446,2754 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>1657713</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1657713 BMD PARCIAL.pdf</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>45.658,12</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1657713</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1657713 parcial 1.pdf</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>37.609,02</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1658452</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1658452 -BMD -HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>7.792,10</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1658452</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1658452 -FFO -HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1663556</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1663556 - BMD - HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2.470,38</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1663556</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1663556 - FFO - HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1676605</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1676605 - BMD PARCIAL - HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>39.199,95</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1676605</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1676605 - BMD PARCIAL - HAGAP1.pdf</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>39.199,95</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1704476</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1704476 BMD.pdf</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>111,28</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1704476</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1704476 FFO.pdf</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1704891</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1704891 - BMD PARC - HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>100.528,77</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1704968</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1704968 - BMD - HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2.808,15</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1704968</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1704968 - FFO - HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1710937</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1710937 - bmd - hagap.pdf</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>4.234,81</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1710937</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1710937 - ffo - hagap.pdf</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1510407</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>BMD - 1510407 - HAGAP - 26-05-2026.pdf</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>28.642,47</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1712538</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>BMD - 1712538 - HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>387,36</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1713240</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>BMD - 1713240 - HAGAP - 20-05-2026.pdf</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>5.108,11</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1713933</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>BMD - 1713933 - HAGAP - 20-05-2026.pdf</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>5.530,92</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1715878</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>BMD - 1715878 - HAGAP - 20-05-2026.pdf</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1.786,71</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1718435</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>BMD - 1718435 - HAGAP - 20-05-2026.pdf</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>17.153,90</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1520612</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>BMD 1520612 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>53.357,33</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1520615</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>BMD 1520615 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>22.840,59</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>1671139I</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>BMD 1671139I HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>6.138,54</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>1699516</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>BMD 1699516 HAGAP PARCIAL.pdf</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>3.388,62</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>1704525</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>BMD 1704525 HAGAP PARCIAL.pdf</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>15.365,48</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>1710937</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>BMD 1710937 HAGAP PARCIAL.pdf</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>1711525</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>BMD 1711525 HAGAP PARCIAL.pdf</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>1.998,42</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>1712624</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>BMD 1712624 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>3.073,90</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>1713679</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>BMD 1713679 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>3.574,44</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>1713719</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>BMD 1713719 HAGAP PARCIAL.pdf</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>3.385,92</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>1715920</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>BMD 1715920 HAGAP PARCIAL.pdf</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>1.031,94</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>1719097</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>BMD 1719097 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>7.450,28</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>1719155</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>BMD 1719155 HAGAP PARCIAL.pdf</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2.223,15</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>1720920</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>BMD 1720920 HAGAP PARCIAL.pdf</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>555,60</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>1702776C</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>BMD FINAL - 1702776C - HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>1702776I</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>BMD FINAL - 1702776I - HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>18.098,87</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>1713262</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>BMD FINAL-1713262-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>55,90</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>1719135</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>BMD FINAL-1719135-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>47,08</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>1677314</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>BMD PARCIAL - 1677314 - HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>46.760,40</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>1677316</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>BMD</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
         <is>
           <t>BMD PARCIAL - 1677316 HAGAP.pdf</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>51.623,62</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>20/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>1688115C</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>BMD PARCIAL - 1688115C - HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>6,36</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>1688115I</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>BMD PARCIAL - 1688115I - HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>18.752,84</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>1694258</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>BMD PARCIAL - 1694258 - HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>127.751,38</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>1695716</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>BMD PARCIAL - 1695716 - HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>74.647,17</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>1710735</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>BMD PARCIAL - 1710735 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>9.153,35</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>1711384</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>BMD PARCIAL - 1711384 - HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2.127,38</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>1712538</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>BMD PARCIAL - 1712538 - HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>3.568,05</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>1715688</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>BMD PARCIAL - 1715688 - HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>9.669,94</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>1712530</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>BMD PARCIAL -1712530-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>5.393,72</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>1563492</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>BMD PARCIAL CIANORTE - 1563492 - HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>80.240,76</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>1563492</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>BMD PARCIAL JUSSARA - 1563492 - HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>64.923,56</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>1708877I</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>BMD PARCIAL-1708877I-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2.132,72</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>1713226</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>BMD PARCIAL-1713226-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>3.049,11</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>1715668</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>BMD PARCIAL-1715668-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2.070,47</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>1717332</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>BMD PARCIAL-1717332-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2.320,28</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>1718442</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>BMD PARCIAL-1718442-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>3.160,96</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>1718555I</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>BMD PARCIAL-1718555I-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2.781,60</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>1713221</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>BMD parcial - 1713221 - HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>18.794,09</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>1708066</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>BMD-1708066-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>3.419,06</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>1712547</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>BMD-1712547-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>117,63</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>1713044I</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>BMD-1713044II-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>1.528,53</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>1714909</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>BMD-1714909-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>107,93</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>1718442</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>BMD-1718442-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>45,19</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>1719070</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>BMD-1719070-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>333,14</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>1719881</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>BMD-1719881-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>3.239,73</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>1719881H</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>BMD-1719881HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>38.258,42</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>1713044C</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>BMD.-1713044C.-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>21,11</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>1715327</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>BMD.1715327-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>1708877</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>BMDFINAL-1708877-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>3,54</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>1712957</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>BMDFINAL-1712957-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>45,19</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>1717332</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>BMDFINAL-1717332-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>1703223</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>BMDPARCIAL-1703223-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>18.169,34</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1712547</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>BMDPARCIAL-1712547-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>6.951,82</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>1712957</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>BMDPARCIAL-1712957-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2.177,64</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>1713262</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>BMDPARCIAL-1713262-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2.619,71</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>1714909</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>BMDPARCIAL-1714909-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>954,64</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>1715127</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>BMDPARCIAL-1715127-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>4.418,94</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>1715327</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>BMDPARCIAL-1715327-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>5.417,39</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>1719070</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>BMDPARCIAL-1719070-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2.744,71</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>1719135</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>BMDPARCIAL-1719135-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>913,84</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>1720116</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>BMDPARCIAL-1720116-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>1.675,57</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>1719135</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>FFO  -1719135-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>1702776C</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>FFO - 1702776C - HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>1702776I</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>FFO - 1702776I - HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>1712538</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>FFO - 1712538 - HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>1713240</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>FFO - 1713240 - HAGAP - 20-05-2026.pdf</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>1715878</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>FFO - 1715878 - HAGAP - 20-05-2026.pdf</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>1641139I</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>FFO 1641139I HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>1713679</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>FFO 1713679 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>1708877</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>FFO-1708877-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>1712547</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>FFO-1712547-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>1713044C</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>FFO-1713044C.-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>1713044I</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>FFO-1713044II-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>1713262</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>FFO-1713262-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>1714909</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>FFO-1714909-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>1715327</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>FFO-1715327-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>65,98</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>1717332</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>FFO-1717332-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>176,23</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>1719070</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>FFO-1719070-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>1708066</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>FFO.-1708066-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>1712957</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>FFO.-1712957-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>1718442</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>FFO´1718442-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
         </is>
       </c>
     </row>

--- a/medicoes.xlsx
+++ b/medicoes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E103"/>
+  <dimension ref="A1:E111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2039,7 +2039,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1708066</t>
+          <t>1703223</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2049,24 +2049,24 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>BMD-1708066-HAGAP.pdf</t>
+          <t>BMD-1703223-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>3.419,06</t>
+          <t>1.471,15</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1712547</t>
+          <t>1708066</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2076,24 +2076,24 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>BMD-1712547-HAGAP.pdf</t>
+          <t>BMD-1708066-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>117,63</t>
+          <t>3.419,06</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1713044I</t>
+          <t>1712547</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2103,24 +2103,24 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>BMD-1713044II-HAGAP.pdf</t>
+          <t>BMD-1712547-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>1.528,53</t>
+          <t>117,63</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1714909</t>
+          <t>1712766</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2130,24 +2130,24 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>BMD-1714909-HAGAP.pdf</t>
+          <t>BMD-1712766-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>107,93</t>
+          <t>705,45</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1718442</t>
+          <t>1713044I</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2157,24 +2157,24 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>BMD-1718442-HAGAP.pdf</t>
+          <t>BMD-1713044II-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>45,19</t>
+          <t>1.528,53</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1719070</t>
+          <t>1714909</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2184,24 +2184,24 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>BMD-1719070-HAGAP.pdf</t>
+          <t>BMD-1714909-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>333,14</t>
+          <t>107,93</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1719881</t>
+          <t>1718442</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2211,12 +2211,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>BMD-1719881-HAGAP.pdf</t>
+          <t>BMD-1718442-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>3.239,73</t>
+          <t>45,19</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2228,7 +2228,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1719881H</t>
+          <t>1719070</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2238,24 +2238,24 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>BMD-1719881HAGAP.pdf</t>
+          <t>BMD-1719070-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>38.258,42</t>
+          <t>333,14</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1713044C</t>
+          <t>1719881</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2265,24 +2265,24 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>BMD.-1713044C.-HAGAP.pdf</t>
+          <t>BMD-1719881-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>21,11</t>
+          <t>3.239,73</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1715327</t>
+          <t>1719881H</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2292,88 +2292,88 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>BMD.1715327-HAGAP.pdf</t>
+          <t>BMD-1719881HAGAP.pdf</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>38.258,42</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1708877</t>
+          <t>1720116</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>BMDFINAL-1708877-HAGAP.pdf</t>
+          <t>BMD-1720116-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>3,54</t>
+          <t>168,95</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1712957</t>
+          <t>1713044C</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>BMDFINAL-1712957-HAGAP.pdf</t>
+          <t>BMD.-1713044C.-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>45,19</t>
+          <t>21,11</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1717332</t>
+          <t>1715327</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>BMDFINAL-1717332-HAGAP.pdf</t>
+          <t>BMD.1715327-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2390,88 +2390,88 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1703223</t>
+          <t>1708877</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1703223-HAGAP.pdf</t>
+          <t>BMDFINAL-1708877-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>18.169,34</t>
+          <t>3,54</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1712547</t>
+          <t>1712957</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1712547-HAGAP.pdf</t>
+          <t>BMDFINAL-1712957-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>6.951,82</t>
+          <t>45,19</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1712957</t>
+          <t>1717332</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1712957-HAGAP.pdf</t>
+          <t>BMDFINAL-1717332-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2.177,64</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1713262</t>
+          <t>1703223</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2481,24 +2481,24 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1713262-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1703223-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2.619,71</t>
+          <t>18.169,34</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1714909</t>
+          <t>1712547</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2508,24 +2508,24 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1714909-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1712547-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>954,64</t>
+          <t>6.951,82</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1715127</t>
+          <t>1712957</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2535,24 +2535,24 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1715127-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1712957-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>4.418,94</t>
+          <t>2.177,64</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1715327</t>
+          <t>1713262</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1715327-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1713262-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>5.417,39</t>
+          <t>2.619,71</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -2579,7 +2579,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1719070</t>
+          <t>1714909</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2589,24 +2589,24 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1719070-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1714909-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2.744,71</t>
+          <t>954,64</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1719135</t>
+          <t>1715127</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2616,24 +2616,24 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1719135-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1715127-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>913,84</t>
+          <t>4.418,94</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1720116</t>
+          <t>1715327</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1720116-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1715327-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>1.675,57</t>
+          <t>5.417,39</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -2660,49 +2660,49 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1719135</t>
+          <t>1719070</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>FFO  -1719135-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1719070-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.744,71</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1702776C</t>
+          <t>1719135</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>FFO - 1702776C - HAGAP.pdf</t>
+          <t>BMDPARCIAL-1719135-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>913,84</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -2714,22 +2714,22 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1702776I</t>
+          <t>1720116</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>FFO - 1702776I - HAGAP.pdf</t>
+          <t>BMDPARCIAL-1720116-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>1.675,57</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -2741,7 +2741,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1712538</t>
+          <t>1712766</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>FFO - 1712538 - HAGAP.pdf</t>
+          <t>FF0-1712766-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2761,14 +2761,14 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1713240</t>
+          <t>1719135</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>FFO - 1713240 - HAGAP - 20-05-2026.pdf</t>
+          <t>FFO  -1719135-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2788,14 +2788,14 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1715878</t>
+          <t>1702776C</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>FFO - 1715878 - HAGAP - 20-05-2026.pdf</t>
+          <t>FFO - 1702776C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2815,14 +2815,14 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1641139I</t>
+          <t>1702776I</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2832,7 +2832,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>FFO 1641139I HAGAP.pdf</t>
+          <t>FFO - 1702776I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2842,14 +2842,14 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1713679</t>
+          <t>1712538</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>FFO 1713679 HAGAP.pdf</t>
+          <t>FFO - 1712538 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2869,14 +2869,14 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1708877</t>
+          <t>1713240</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>FFO-1708877-HAGAP.pdf</t>
+          <t>FFO - 1713240 - HAGAP - 20-05-2026.pdf</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2896,14 +2896,14 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1712547</t>
+          <t>1715878</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2913,7 +2913,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>FFO-1712547-HAGAP.pdf</t>
+          <t>FFO - 1715878 - HAGAP - 20-05-2026.pdf</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2923,14 +2923,14 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1713044C</t>
+          <t>1641139I</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>FFO-1713044C.-HAGAP.pdf</t>
+          <t>FFO 1641139I HAGAP.pdf</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2950,14 +2950,14 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1713044I</t>
+          <t>1713679</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2967,7 +2967,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>FFO-1713044II-HAGAP.pdf</t>
+          <t>FFO 1713679 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2984,7 +2984,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1713262</t>
+          <t>1703223</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>FFO-1713262-HAGAP.pdf</t>
+          <t>FFO-1703223-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3004,14 +3004,14 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1714909</t>
+          <t>1708877</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>FFO-1714909-HAGAP.pdf</t>
+          <t>FFO-1708877-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3031,14 +3031,14 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1715327</t>
+          <t>1710116</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3048,24 +3048,24 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>FFO-1715327-HAGAP.pdf</t>
+          <t>FFO-1710116-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>65,98</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1717332</t>
+          <t>1712547</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3075,24 +3075,24 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>FFO-1717332-HAGAP.pdf</t>
+          <t>FFO-1712547-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>176,23</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1719070</t>
+          <t>1713044C</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>FFO-1719070-HAGAP.pdf</t>
+          <t>FFO-1713044C.-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3112,14 +3112,14 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1708066</t>
+          <t>1713044I</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3129,7 +3129,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>FFO.-1708066-HAGAP.pdf</t>
+          <t>FFO-1713044II-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3146,7 +3146,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1712957</t>
+          <t>1713262</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>FFO.-1712957-HAGAP.pdf</t>
+          <t>FFO-1713262-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3173,29 +3173,241 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
+          <t>1714909</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>FFO-1714909-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>1715327</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>FFO-1715327-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>65,98</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>1717332</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>FFO-1717332-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>176,23</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>1719070</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>FFO-1719070-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>1719881</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>FFO-1719881-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>1708066</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>FFO.-1708066-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>1712957</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>FFO.-1712957-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
           <t>1718442</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>FFO</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
         <is>
           <t>FFO´1718442-HAGAP.pdf</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
+      <c r="D110" t="inlineStr">
         <is>
           <t>0,00</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
+      <c r="E110" t="inlineStr">
         <is>
           <t>26/05/2026</t>
         </is>
       </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>1703223</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>MULTA-1703223-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/medicoes.xlsx
+++ b/medicoes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E111"/>
+  <dimension ref="A1:E120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,34 +446,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1657713</t>
+          <t>1648254</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1657713 BMD PARCIAL.pdf</t>
+          <t>1648254- FFO - asp.pdf</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>45.658,12</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1657713</t>
+          <t>1657710</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -483,12 +483,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1657713 parcial 1.pdf</t>
+          <t>1657710 BMD PARCIAL ASP.pdf</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>37.609,02</t>
+          <t>59.714,14</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -500,7 +500,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1658452</t>
+          <t>1657713</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -510,51 +510,51 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1658452 -BMD -HAGAP.pdf</t>
+          <t>1657713 BMD PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>7.792,10</t>
+          <t>45.658,12</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1658452</t>
+          <t>1657713</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1658452 -FFO -HAGAP.pdf</t>
+          <t>1657713 parcial 1.pdf</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>37.609,02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1663556</t>
+          <t>1658452</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -564,24 +564,24 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1663556 - BMD - HAGAP.pdf</t>
+          <t>1658452 -BMD -HAGAP.pdf</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.470,38</t>
+          <t>7.792,10</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1663556</t>
+          <t>1658452</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1663556 - FFO - HAGAP.pdf</t>
+          <t>1658452 -FFO -HAGAP.pdf</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -601,14 +601,14 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1676605</t>
+          <t>1663556</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -618,105 +618,105 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1676605 - BMD PARCIAL - HAGAP.pdf</t>
+          <t>1663556 - BMD - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>39.199,95</t>
+          <t>2.470,38</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1676605</t>
+          <t>1663556</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1676605 - BMD PARCIAL - HAGAP1.pdf</t>
+          <t>1663556 - FFO - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>39.199,95</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1704476</t>
+          <t>1667593</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1704476 BMD.pdf</t>
+          <t>1667593 - FFO - asp.pdf</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>111,28</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1704476</t>
+          <t>1676605</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1704476 FFO.pdf</t>
+          <t>1676605 - BMD PARCIAL - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>39.199,95</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1704891</t>
+          <t>1676605</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -726,12 +726,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1704891 - BMD PARC - HAGAP.pdf</t>
+          <t>1676605 - BMD PARCIAL - HAGAP1.pdf</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>100.528,77</t>
+          <t>39.199,95</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -743,7 +743,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1704968</t>
+          <t>1704476</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -753,24 +753,24 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1704968 - BMD - HAGAP.pdf</t>
+          <t>1704476 BMD.pdf</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2.808,15</t>
+          <t>111,28</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1704968</t>
+          <t>1704476</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1704968 - FFO - HAGAP.pdf</t>
+          <t>1704476 FFO.pdf</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -790,14 +790,14 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1710937</t>
+          <t>1704891</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -807,78 +807,78 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1710937 - bmd - hagap.pdf</t>
+          <t>1704891 - BMD PARC - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>4.234,81</t>
+          <t>100.528,77</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1710937</t>
+          <t>1704968</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1710937 - ffo - hagap.pdf</t>
+          <t>1704968 - BMD - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.808,15</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1510407</t>
+          <t>1704968</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BMD - 1510407 - HAGAP - 26-05-2026.pdf</t>
+          <t>1704968 - FFO - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>28.642,47</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1712538</t>
+          <t>1710937</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -888,51 +888,51 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>BMD - 1712538 - HAGAP.pdf</t>
+          <t>1710937 - bmd - hagap.pdf</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>387,36</t>
+          <t>4.234,81</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1713240</t>
+          <t>1710937</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>BMD - 1713240 - HAGAP - 20-05-2026.pdf</t>
+          <t>1710937 - ffo - hagap.pdf</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>5.108,11</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1713933</t>
+          <t>1724341</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -942,24 +942,24 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>BMD - 1713933 - HAGAP - 20-05-2026.pdf</t>
+          <t>1724341 - BMD PARC - ASP.pdf</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>5.530,92</t>
+          <t>40.758,00</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1715878</t>
+          <t>1510407</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -969,24 +969,24 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BMD - 1715878 - HAGAP - 20-05-2026.pdf</t>
+          <t>BMD - 1510407 - HAGAP - 26-05-2026.pdf</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.786,71</t>
+          <t>28.642,47</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1718435</t>
+          <t>1704867</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -996,24 +996,24 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BMD - 1718435 - HAGAP - 20-05-2026.pdf</t>
+          <t>BMD - 1704867 - ASP.pdf</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>17.153,90</t>
+          <t>23.915,48</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1520612</t>
+          <t>1712538</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1023,24 +1023,24 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>BMD 1520612 HAGAP.pdf</t>
+          <t>BMD - 1712538 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>53.357,33</t>
+          <t>387,36</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1520615</t>
+          <t>1713240</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1050,24 +1050,24 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BMD 1520615 HAGAP.pdf</t>
+          <t>BMD - 1713240 - HAGAP - 20-05-2026.pdf</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>22.840,59</t>
+          <t>5.108,11</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1671139I</t>
+          <t>1713933</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1077,24 +1077,24 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BMD 1671139I HAGAP.pdf</t>
+          <t>BMD - 1713933 - HAGAP - 20-05-2026.pdf</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>6.138,54</t>
+          <t>5.530,92</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1699516</t>
+          <t>1715878</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1104,24 +1104,24 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BMD 1699516 HAGAP PARCIAL.pdf</t>
+          <t>BMD - 1715878 - HAGAP - 20-05-2026.pdf</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>3.388,62</t>
+          <t>1.786,71</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1704525</t>
+          <t>1718435</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1131,24 +1131,24 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>BMD 1704525 HAGAP PARCIAL.pdf</t>
+          <t>BMD - 1718435 - HAGAP - 20-05-2026.pdf</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>15.365,48</t>
+          <t>17.153,90</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1710937</t>
+          <t>1520612</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1158,24 +1158,24 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>BMD 1710937 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1520612 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>53.357,33</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1711525</t>
+          <t>1520615</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1185,24 +1185,24 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>BMD 1711525 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1520615 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.998,42</t>
+          <t>22.840,59</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1712624</t>
+          <t>1671139I</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1212,24 +1212,24 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>BMD 1712624 HAGAP.pdf</t>
+          <t>BMD 1671139I HAGAP.pdf</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>3.073,90</t>
+          <t>6.138,54</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1713679</t>
+          <t>1692636</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1239,24 +1239,24 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>BMD 1713679 HAGAP.pdf</t>
+          <t>BMD 1692636 ASP.pdf</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>3.574,44</t>
+          <t>19.387,05</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1713719</t>
+          <t>1699516</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>BMD 1713719 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1699516 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>3.385,92</t>
+          <t>3.388,62</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1715920</t>
+          <t>1704525</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1293,24 +1293,24 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>BMD 1715920 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1704525 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1.031,94</t>
+          <t>15.365,48</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1719097</t>
+          <t>1710937</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1320,24 +1320,24 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>BMD 1719097 HAGAP.pdf</t>
+          <t>BMD 1710937 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>7.450,28</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1719155</t>
+          <t>1711525</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1347,24 +1347,24 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>BMD 1719155 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1711525 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2.223,15</t>
+          <t>1.998,42</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1720920</t>
+          <t>1712624</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1374,132 +1374,132 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>BMD 1720920 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1712624 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>555,60</t>
+          <t>3.073,90</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1702776C</t>
+          <t>1713679</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>BMD FINAL - 1702776C - HAGAP.pdf</t>
+          <t>BMD 1713679 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>3.574,44</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1702776I</t>
+          <t>1713719</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>BMD FINAL - 1702776I - HAGAP.pdf</t>
+          <t>BMD 1713719 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>18.098,87</t>
+          <t>3.385,92</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1713262</t>
+          <t>1715920</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>BMD FINAL-1713262-HAGAP.pdf</t>
+          <t>BMD 1715920 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>55,90</t>
+          <t>1.031,94</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1719135</t>
+          <t>1718803</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>BMD FINAL-1719135-HAGAP.pdf</t>
+          <t>BMD 1718803 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>47,08</t>
+          <t>3.825,18</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1677314</t>
+          <t>1719097</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1677314 - HAGAP.pdf</t>
+          <t>BMD 1719097 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>46.760,40</t>
+          <t>7.450,28</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1526,7 +1526,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1677316</t>
+          <t>1719155</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1536,12 +1536,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1677316 HAGAP.pdf</t>
+          <t>BMD 1719155 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>51.623,62</t>
+          <t>2.223,15</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1553,7 +1553,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1688115C</t>
+          <t>1720920</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1563,132 +1563,132 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1688115C - HAGAP.pdf</t>
+          <t>BMD 1720920 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>6,36</t>
+          <t>555,60</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1688115I</t>
+          <t>1702776C</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1688115I - HAGAP.pdf</t>
+          <t>BMD FINAL - 1702776C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>18.752,84</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1694258</t>
+          <t>1702776I</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1694258 - HAGAP.pdf</t>
+          <t>BMD FINAL - 1702776I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>127.751,38</t>
+          <t>18.098,87</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1695716</t>
+          <t>1713262</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1695716 - HAGAP.pdf</t>
+          <t>BMD FINAL-1713262-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>74.647,17</t>
+          <t>55,90</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1710735</t>
+          <t>1719135</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1710735 HAGAP.pdf</t>
+          <t>BMD FINAL-1719135-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>9.153,35</t>
+          <t>47,08</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1711384</t>
+          <t>1677314</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1698,24 +1698,24 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1711384 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1677314 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2.127,38</t>
+          <t>46.760,40</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1712538</t>
+          <t>1677316</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1725,24 +1725,24 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1712538 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1677316 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>3.568,05</t>
+          <t>51.623,62</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1715688</t>
+          <t>1688115C</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1752,24 +1752,24 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1715688 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1688115C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>9.669,94</t>
+          <t>6,36</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1712530</t>
+          <t>1688115I</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1779,24 +1779,24 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>BMD PARCIAL -1712530-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1688115I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>5.393,72</t>
+          <t>18.752,84</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1563492</t>
+          <t>1694258</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1806,24 +1806,24 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>BMD PARCIAL CIANORTE - 1563492 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1694258 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>80.240,76</t>
+          <t>127.751,38</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1563492</t>
+          <t>1695716</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1833,24 +1833,24 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>BMD PARCIAL JUSSARA - 1563492 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1695716 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>64.923,56</t>
+          <t>74.647,17</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1708877I</t>
+          <t>1710735</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1860,12 +1860,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1708877I-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1710735 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2.132,72</t>
+          <t>9.153,35</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1877,7 +1877,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1713226</t>
+          <t>1711384</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1713226-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1711384 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>3.049,11</t>
+          <t>2.127,38</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -1904,7 +1904,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1715668</t>
+          <t>1712538</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1715668-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1712538 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2.070,47</t>
+          <t>3.568,05</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -1931,7 +1931,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1717332</t>
+          <t>1715688</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1717332-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1715688 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2.320,28</t>
+          <t>9.669,94</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -1958,7 +1958,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1718442</t>
+          <t>1712530</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1968,24 +1968,24 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1718442-HAGAP.pdf</t>
+          <t>BMD PARCIAL -1712530-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>3.160,96</t>
+          <t>5.393,72</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1718555I</t>
+          <t>1563492</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1995,24 +1995,24 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1718555I-HAGAP.pdf</t>
+          <t>BMD PARCIAL CIANORTE - 1563492 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2.781,60</t>
+          <t>80.240,76</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1713221</t>
+          <t>1563492</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2022,24 +2022,24 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>BMD parcial - 1713221 - HAGAP.pdf</t>
+          <t>BMD PARCIAL JUSSARA - 1563492 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>18.794,09</t>
+          <t>64.923,56</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1703223</t>
+          <t>1708877I</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2049,24 +2049,24 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>BMD-1703223-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1708877I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>1.471,15</t>
+          <t>2.132,72</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1708066</t>
+          <t>1713226</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2076,24 +2076,24 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>BMD-1708066-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1713226-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>3.419,06</t>
+          <t>3.049,11</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1712547</t>
+          <t>1715668</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2103,24 +2103,24 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>BMD-1712547-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1715668-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>117,63</t>
+          <t>2.070,47</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1712766</t>
+          <t>1717332</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2130,24 +2130,24 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>BMD-1712766-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1717332-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>705,45</t>
+          <t>2.320,28</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1713044I</t>
+          <t>1718442</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2157,24 +2157,24 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>BMD-1713044II-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1718442-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>1.528,53</t>
+          <t>3.160,96</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1714909</t>
+          <t>1718555I</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2184,24 +2184,24 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>BMD-1714909-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1718555I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>107,93</t>
+          <t>2.781,60</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1718442</t>
+          <t>1713221</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>BMD-1718442-HAGAP.pdf</t>
+          <t>BMD parcial - 1713221 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>45,19</t>
+          <t>18.794,09</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1719070</t>
+          <t>1703223</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2238,24 +2238,24 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>BMD-1719070-HAGAP.pdf</t>
+          <t>BMD-1703223-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>333,14</t>
+          <t>1.471,15</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1719881</t>
+          <t>1708066</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2265,24 +2265,24 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>BMD-1719881-HAGAP.pdf</t>
+          <t>BMD-1708066-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>3.239,73</t>
+          <t>3.419,06</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1719881H</t>
+          <t>1712547</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2292,24 +2292,24 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>BMD-1719881HAGAP.pdf</t>
+          <t>BMD-1712547-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>38.258,42</t>
+          <t>117,63</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1720116</t>
+          <t>1712766</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2319,24 +2319,24 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>BMD-1720116-HAGAP.pdf</t>
+          <t>BMD-1712766-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>168,95</t>
+          <t>705,45</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1713044C</t>
+          <t>1713044I</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2346,24 +2346,24 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>BMD.-1713044C.-HAGAP.pdf</t>
+          <t>BMD-1713044II-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>21,11</t>
+          <t>1.528,53</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1715327</t>
+          <t>1714909</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2373,39 +2373,39 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>BMD.1715327-HAGAP.pdf</t>
+          <t>BMD-1714909-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>107,93</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1708877</t>
+          <t>1718442</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>BMDFINAL-1708877-HAGAP.pdf</t>
+          <t>BMD-1718442-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>3,54</t>
+          <t>45,19</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2417,61 +2417,61 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1712957</t>
+          <t>1719070</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>BMDFINAL-1712957-HAGAP.pdf</t>
+          <t>BMD-1719070-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>45,19</t>
+          <t>333,14</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1717332</t>
+          <t>1719881</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>BMDFINAL-1717332-HAGAP.pdf</t>
+          <t>BMD-1719881-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>3.239,73</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1703223</t>
+          <t>1719881H</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2481,24 +2481,24 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1703223-HAGAP.pdf</t>
+          <t>BMD-1719881HAGAP.pdf</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>18.169,34</t>
+          <t>38.258,42</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1712547</t>
+          <t>1720116</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2508,24 +2508,24 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1712547-HAGAP.pdf</t>
+          <t>BMD-1720116-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>6.951,82</t>
+          <t>168,95</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1712957</t>
+          <t>1713044C</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2535,24 +2535,24 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1712957-HAGAP.pdf</t>
+          <t>BMD.-1713044C.-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2.177,64</t>
+          <t>21,11</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1713262</t>
+          <t>1715327</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2562,105 +2562,105 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1713262-HAGAP.pdf</t>
+          <t>BMD.1715327-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2.619,71</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1714909</t>
+          <t>1708877</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1714909-HAGAP.pdf</t>
+          <t>BMDFINAL-1708877-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>954,64</t>
+          <t>3,54</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1715127</t>
+          <t>1712957</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1715127-HAGAP.pdf</t>
+          <t>BMDFINAL-1712957-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>4.418,94</t>
+          <t>45,19</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1715327</t>
+          <t>1717332</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1715327-HAGAP.pdf</t>
+          <t>BMDFINAL-1717332-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>5.417,39</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1719070</t>
+          <t>1703223</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2670,24 +2670,24 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1719070-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1703223-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2.744,71</t>
+          <t>18.169,34</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1719135</t>
+          <t>1712547</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2697,24 +2697,24 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1719135-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1712547-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>913,84</t>
+          <t>6.951,82</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1720116</t>
+          <t>1712957</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2724,12 +2724,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1720116-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1712957-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>1.675,57</t>
+          <t>2.177,64</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -2741,103 +2741,103 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1712766</t>
+          <t>1713262</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>FF0-1712766-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1713262-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.619,71</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1719135</t>
+          <t>1714909</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>FFO  -1719135-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1714909-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>954,64</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1702776C</t>
+          <t>1715127</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>FFO - 1702776C - HAGAP.pdf</t>
+          <t>BMDPARCIAL-1715127-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>4.418,94</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1702776I</t>
+          <t>1715327</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>FFO - 1702776I - HAGAP.pdf</t>
+          <t>BMDPARCIAL-1715327-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>5.417,39</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -2849,88 +2849,88 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1712538</t>
+          <t>1719070</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>FFO - 1712538 - HAGAP.pdf</t>
+          <t>BMDPARCIAL-1719070-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.744,71</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1713240</t>
+          <t>1719135</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>FFO - 1713240 - HAGAP - 20-05-2026.pdf</t>
+          <t>BMDPARCIAL-1719135-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>913,84</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1715878</t>
+          <t>1720116</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>FFO - 1715878 - HAGAP - 20-05-2026.pdf</t>
+          <t>BMDPARCIAL-1720116-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>1.675,57</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1641139I</t>
+          <t>1712766</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>FFO 1641139I HAGAP.pdf</t>
+          <t>FF0-1712766-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2950,14 +2950,14 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1713679</t>
+          <t>1719135</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2967,7 +2967,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>FFO 1713679 HAGAP.pdf</t>
+          <t>FFO  -1719135-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2977,14 +2977,14 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1703223</t>
+          <t>1702776C</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>FFO-1703223-HAGAP.pdf</t>
+          <t>FFO - 1702776C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3004,14 +3004,14 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1708877</t>
+          <t>1702776I</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>FFO-1708877-HAGAP.pdf</t>
+          <t>FFO - 1702776I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3031,14 +3031,14 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1710116</t>
+          <t>1704867</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>FFO-1710116-HAGAP.pdf</t>
+          <t>FFO - 1704867 - ASP.pdf</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3058,14 +3058,14 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1712547</t>
+          <t>1712538</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>FFO-1712547-HAGAP.pdf</t>
+          <t>FFO - 1712538 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3092,7 +3092,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1713044C</t>
+          <t>1713240</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>FFO-1713044C.-HAGAP.pdf</t>
+          <t>FFO - 1713240 - HAGAP - 20-05-2026.pdf</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3119,7 +3119,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1713044I</t>
+          <t>1715878</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3129,7 +3129,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>FFO-1713044II-HAGAP.pdf</t>
+          <t>FFO - 1715878 - HAGAP - 20-05-2026.pdf</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3146,7 +3146,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1713262</t>
+          <t>1641139I</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>FFO-1713262-HAGAP.pdf</t>
+          <t>FFO 1641139I HAGAP.pdf</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3173,7 +3173,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1714909</t>
+          <t>1713679</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>FFO-1714909-HAGAP.pdf</t>
+          <t>FFO 1713679 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3193,14 +3193,14 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1715327</t>
+          <t>1718803</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3210,24 +3210,24 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>FFO-1715327-HAGAP.pdf</t>
+          <t>FFO 1718803 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>65,98</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1717332</t>
+          <t>1703223</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3237,24 +3237,24 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>FFO-1717332-HAGAP.pdf</t>
+          <t>FFO-1703223-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>176,23</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1719070</t>
+          <t>1708877</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>FFO-1719070-HAGAP.pdf</t>
+          <t>FFO-1708877-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3274,14 +3274,14 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1719881</t>
+          <t>1710116</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>FFO-1719881-HAGAP.pdf</t>
+          <t>FFO-1710116-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3301,14 +3301,14 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1708066</t>
+          <t>1712547</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>FFO.-1708066-HAGAP.pdf</t>
+          <t>FFO-1712547-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3328,14 +3328,14 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1712957</t>
+          <t>1713044C</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>FFO.-1712957-HAGAP.pdf</t>
+          <t>FFO-1713044C.-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3355,14 +3355,14 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1718442</t>
+          <t>1713044I</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>FFO´1718442-HAGAP.pdf</t>
+          <t>FFO-1713044II-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3382,32 +3382,275 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
+          <t>1713262</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>FFO-1713262-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>1714909</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>FFO-1714909-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>1715327</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>FFO-1715327-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>65,98</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>1717332</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>FFO-1717332-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>176,23</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>1719070</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>FFO-1719070-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>1719881</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>FFO-1719881-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>1708066</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>FFO.-1708066-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>1712957</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>FFO.-1712957-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>1718442</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>FFO´1718442-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
           <t>1703223</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>BMD</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
         <is>
           <t>MULTA-1703223-HAGAP.pdf</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr">
+      <c r="D120" t="inlineStr">
         <is>
           <t>0,00</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr"/>
+      <c r="E120" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/medicoes.xlsx
+++ b/medicoes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E120"/>
+  <dimension ref="A1:E126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -986,7 +986,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1704867</t>
+          <t>1688115C</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -996,24 +996,24 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BMD - 1704867 - ASP.pdf</t>
+          <t>BMD - 1688115C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>23.915,48</t>
+          <t>6,65</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1712538</t>
+          <t>1688115I</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1023,24 +1023,24 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>BMD - 1712538 - HAGAP.pdf</t>
+          <t>BMD - 1688115I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>387,36</t>
+          <t>2.670,64</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1713240</t>
+          <t>1704867</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1050,24 +1050,24 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BMD - 1713240 - HAGAP - 20-05-2026.pdf</t>
+          <t>BMD - 1704867 - ASP.pdf</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>5.108,11</t>
+          <t>23.915,48</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1713933</t>
+          <t>1711384</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1077,24 +1077,24 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BMD - 1713933 - HAGAP - 20-05-2026.pdf</t>
+          <t>BMD - 1711384 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>5.530,92</t>
+          <t>122,95</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1715878</t>
+          <t>1712538</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1104,24 +1104,24 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BMD - 1715878 - HAGAP - 20-05-2026.pdf</t>
+          <t>BMD - 1712538 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1.786,71</t>
+          <t>387,36</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1718435</t>
+          <t>1713240</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1131,24 +1131,24 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>BMD - 1718435 - HAGAP - 20-05-2026.pdf</t>
+          <t>BMD - 1713240 - HAGAP - 20-05-2026.pdf</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>17.153,90</t>
+          <t>5.108,11</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1520612</t>
+          <t>1713933</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1158,24 +1158,24 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>BMD 1520612 HAGAP.pdf</t>
+          <t>BMD - 1713933 - HAGAP - 20-05-2026.pdf</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>53.357,33</t>
+          <t>5.530,92</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1520615</t>
+          <t>1715878</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>BMD 1520615 HAGAP.pdf</t>
+          <t>BMD - 1715878 - HAGAP - 20-05-2026.pdf</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>22.840,59</t>
+          <t>1.786,71</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1202,7 +1202,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1671139I</t>
+          <t>1718435</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1212,24 +1212,24 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>BMD 1671139I HAGAP.pdf</t>
+          <t>BMD - 1718435 - HAGAP - 20-05-2026.pdf</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>6.138,54</t>
+          <t>17.153,90</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1692636</t>
+          <t>1520612</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1239,24 +1239,24 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>BMD 1692636 ASP.pdf</t>
+          <t>BMD 1520612 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>19.387,05</t>
+          <t>53.357,33</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1699516</t>
+          <t>1520615</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>BMD 1699516 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1520615 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>3.388,62</t>
+          <t>22.840,59</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1704525</t>
+          <t>1671139I</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1293,24 +1293,24 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>BMD 1704525 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1671139I HAGAP.pdf</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>15.365,48</t>
+          <t>6.138,54</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1710937</t>
+          <t>1692636</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1320,24 +1320,24 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>BMD 1710937 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1692636 ASP.pdf</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>19.387,05</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1711525</t>
+          <t>1699516</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1347,24 +1347,24 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>BMD 1711525 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1699516 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1.998,42</t>
+          <t>3.388,62</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1712624</t>
+          <t>1704525</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1374,24 +1374,24 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>BMD 1712624 HAGAP.pdf</t>
+          <t>BMD 1704525 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>3.073,90</t>
+          <t>15.365,48</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1713679</t>
+          <t>1710937</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1401,12 +1401,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>BMD 1713679 HAGAP.pdf</t>
+          <t>BMD 1710937 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>3.574,44</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1418,7 +1418,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1713719</t>
+          <t>1711525</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1428,24 +1428,24 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>BMD 1713719 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1711525 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>3.385,92</t>
+          <t>1.998,42</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1715920</t>
+          <t>1712624</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1455,12 +1455,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>BMD 1715920 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1712624 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1.031,94</t>
+          <t>3.073,90</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1472,7 +1472,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1718803</t>
+          <t>1713679</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1482,24 +1482,24 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>BMD 1718803 HAGAP.pdf</t>
+          <t>BMD 1713679 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>3.825,18</t>
+          <t>3.574,44</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1719097</t>
+          <t>1713719</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1509,24 +1509,24 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>BMD 1719097 HAGAP.pdf</t>
+          <t>BMD 1713719 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>7.450,28</t>
+          <t>3.385,92</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1719155</t>
+          <t>1715920</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1536,12 +1536,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>BMD 1719155 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1715920 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2.223,15</t>
+          <t>1.031,94</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1553,7 +1553,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1720920</t>
+          <t>1718803</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1563,39 +1563,39 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>BMD 1720920 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1718803 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>555,60</t>
+          <t>3.825,18</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1702776C</t>
+          <t>1719097</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>BMD FINAL - 1702776C - HAGAP.pdf</t>
+          <t>BMD 1719097 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>7.450,28</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1607,49 +1607,49 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1702776I</t>
+          <t>1719155</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>BMD FINAL - 1702776I - HAGAP.pdf</t>
+          <t>BMD 1719155 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>18.098,87</t>
+          <t>2.223,15</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1713262</t>
+          <t>1720920</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>BMD FINAL-1713262-HAGAP.pdf</t>
+          <t>BMD 1720920 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>55,90</t>
+          <t>555,60</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1661,7 +1661,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1719135</t>
+          <t>1702776C</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>BMD FINAL-1719135-HAGAP.pdf</t>
+          <t>BMD FINAL - 1702776C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>47,08</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1688,88 +1688,88 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1677314</t>
+          <t>1702776I</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1677314 - HAGAP.pdf</t>
+          <t>BMD FINAL - 1702776I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>46.760,40</t>
+          <t>18.098,87</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1677316</t>
+          <t>1713262</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1677316 HAGAP.pdf</t>
+          <t>BMD FINAL-1713262-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>51.623,62</t>
+          <t>55,90</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1688115C</t>
+          <t>1719135</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1688115C - HAGAP.pdf</t>
+          <t>BMD FINAL-1719135-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>6,36</t>
+          <t>47,08</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1688115I</t>
+          <t>1677314</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1779,24 +1779,24 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1688115I - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1677314 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>18.752,84</t>
+          <t>46.760,40</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1694258</t>
+          <t>1677316</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1806,24 +1806,24 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1694258 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1677316 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>127.751,38</t>
+          <t>51.623,62</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1695716</t>
+          <t>1688115C</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1833,24 +1833,24 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1695716 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1688115C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>74.647,17</t>
+          <t>6,36</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1710735</t>
+          <t>1688115I</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1860,24 +1860,24 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1710735 HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1688115I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>9.153,35</t>
+          <t>18.752,84</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1711384</t>
+          <t>1694258</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1887,24 +1887,24 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1711384 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1694258 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2.127,38</t>
+          <t>127.751,38</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1712538</t>
+          <t>1695716</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1914,24 +1914,24 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1712538 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1695716 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>3.568,05</t>
+          <t>74.647,17</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1715688</t>
+          <t>1710735</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1715688 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1710735 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>9.669,94</t>
+          <t>9.153,35</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -1958,7 +1958,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1712530</t>
+          <t>1711384</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1968,24 +1968,24 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>BMD PARCIAL -1712530-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1711384 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>5.393,72</t>
+          <t>2.127,38</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1563492</t>
+          <t>1712538</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1995,24 +1995,24 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>BMD PARCIAL CIANORTE - 1563492 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1712538 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>80.240,76</t>
+          <t>3.568,05</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1563492</t>
+          <t>1715688</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2022,24 +2022,24 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>BMD PARCIAL JUSSARA - 1563492 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1715688 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>64.923,56</t>
+          <t>9.669,94</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1708877I</t>
+          <t>1712530</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2049,24 +2049,24 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1708877I-HAGAP.pdf</t>
+          <t>BMD PARCIAL -1712530-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2.132,72</t>
+          <t>5.393,72</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1713226</t>
+          <t>1563492</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2076,24 +2076,24 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1713226-HAGAP.pdf</t>
+          <t>BMD PARCIAL CIANORTE - 1563492 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>3.049,11</t>
+          <t>80.240,76</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1715668</t>
+          <t>1563492</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2103,24 +2103,24 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1715668-HAGAP.pdf</t>
+          <t>BMD PARCIAL JUSSARA - 1563492 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2.070,47</t>
+          <t>64.923,56</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1717332</t>
+          <t>1708877I</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1717332-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1708877I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2.320,28</t>
+          <t>2.132,72</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2147,7 +2147,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1718442</t>
+          <t>1713226</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2157,24 +2157,24 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1718442-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1713226-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>3.160,96</t>
+          <t>3.049,11</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1718555I</t>
+          <t>1715668</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2184,24 +2184,24 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1718555I-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1715668-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2.781,60</t>
+          <t>2.070,47</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1713221</t>
+          <t>1717332</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>BMD parcial - 1713221 - HAGAP.pdf</t>
+          <t>BMD PARCIAL-1717332-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>18.794,09</t>
+          <t>2.320,28</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1703223</t>
+          <t>1718442</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2238,24 +2238,24 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>BMD-1703223-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1718442-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>1.471,15</t>
+          <t>3.160,96</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1708066</t>
+          <t>1718555I</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2265,24 +2265,24 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>BMD-1708066-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1718555I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>3.419,06</t>
+          <t>2.781,60</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1712547</t>
+          <t>1713221</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2292,24 +2292,24 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>BMD-1712547-HAGAP.pdf</t>
+          <t>BMD parcial - 1713221 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>117,63</t>
+          <t>18.794,09</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1712766</t>
+          <t>1703223</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2319,24 +2319,24 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>BMD-1712766-HAGAP.pdf</t>
+          <t>BMD-1703223-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>705,45</t>
+          <t>1.471,15</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1713044I</t>
+          <t>1708066</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2346,24 +2346,24 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>BMD-1713044II-HAGAP.pdf</t>
+          <t>BMD-1708066-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>1.528,53</t>
+          <t>3.419,06</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1714909</t>
+          <t>1712547</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2373,24 +2373,24 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>BMD-1714909-HAGAP.pdf</t>
+          <t>BMD-1712547-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>107,93</t>
+          <t>117,63</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1718442</t>
+          <t>1712766</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2400,24 +2400,24 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>BMD-1718442-HAGAP.pdf</t>
+          <t>BMD-1712766-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>45,19</t>
+          <t>705,45</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1719070</t>
+          <t>1713044I</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2427,24 +2427,24 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>BMD-1719070-HAGAP.pdf</t>
+          <t>BMD-1713044II-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>333,14</t>
+          <t>1.528,53</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1719881</t>
+          <t>1714909</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2454,24 +2454,24 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>BMD-1719881-HAGAP.pdf</t>
+          <t>BMD-1714909-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>3.239,73</t>
+          <t>107,93</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1719881H</t>
+          <t>1718442</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2481,24 +2481,24 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>BMD-1719881HAGAP.pdf</t>
+          <t>BMD-1718442-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>38.258,42</t>
+          <t>45,19</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1720116</t>
+          <t>1719070</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2508,24 +2508,24 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>BMD-1720116-HAGAP.pdf</t>
+          <t>BMD-1719070-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>168,95</t>
+          <t>333,14</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1713044C</t>
+          <t>1719881</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2535,24 +2535,24 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>BMD.-1713044C.-HAGAP.pdf</t>
+          <t>BMD-1719881-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>21,11</t>
+          <t>3.239,73</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1715327</t>
+          <t>1719881H</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2562,88 +2562,88 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>BMD.1715327-HAGAP.pdf</t>
+          <t>BMD-1719881HAGAP.pdf</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>38.258,42</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1708877</t>
+          <t>1720116</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>BMDFINAL-1708877-HAGAP.pdf</t>
+          <t>BMD-1720116-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>3,54</t>
+          <t>168,95</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1712957</t>
+          <t>1713044C</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>BMDFINAL-1712957-HAGAP.pdf</t>
+          <t>BMD.-1713044C.-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>45,19</t>
+          <t>21,11</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1717332</t>
+          <t>1715327</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>BMDFINAL-1717332-HAGAP.pdf</t>
+          <t>BMD.1715327-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2660,88 +2660,88 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1703223</t>
+          <t>1708877</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1703223-HAGAP.pdf</t>
+          <t>BMDFINAL-1708877-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>18.169,34</t>
+          <t>3,54</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1712547</t>
+          <t>1712957</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1712547-HAGAP.pdf</t>
+          <t>BMDFINAL-1712957-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>6.951,82</t>
+          <t>45,19</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1712957</t>
+          <t>1717332</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1712957-HAGAP.pdf</t>
+          <t>BMDFINAL-1717332-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2.177,64</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1713262</t>
+          <t>1703223</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2751,24 +2751,24 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1713262-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1703223-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2.619,71</t>
+          <t>18.169,34</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1714909</t>
+          <t>1712547</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2778,24 +2778,24 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1714909-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1712547-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>954,64</t>
+          <t>6.951,82</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1715127</t>
+          <t>1712957</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2805,24 +2805,24 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1715127-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1712957-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>4.418,94</t>
+          <t>2.177,64</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1715327</t>
+          <t>1713262</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1715327-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1713262-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>5.417,39</t>
+          <t>2.619,71</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -2849,7 +2849,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1719070</t>
+          <t>1714909</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2859,24 +2859,24 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1719070-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1714909-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2.744,71</t>
+          <t>954,64</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1719135</t>
+          <t>1715127</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2886,24 +2886,24 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1719135-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1715127-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>913,84</t>
+          <t>4.418,94</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1720116</t>
+          <t>1715327</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2913,12 +2913,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1720116-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1715327-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>1.675,57</t>
+          <t>5.417,39</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -2930,27 +2930,27 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1712766</t>
+          <t>1719070</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>FF0-1712766-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1719070-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.744,71</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -2962,44 +2962,44 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>FFO  -1719135-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1719135-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>913,84</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1702776C</t>
+          <t>1720116</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>FFO - 1702776C - HAGAP.pdf</t>
+          <t>BMDPARCIAL-1720116-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>1.675,57</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -3011,7 +3011,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1702776I</t>
+          <t>1712766</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>FFO - 1702776I - HAGAP.pdf</t>
+          <t>FF0-1712766-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3031,14 +3031,14 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1704867</t>
+          <t>1719135</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>FFO - 1704867 - ASP.pdf</t>
+          <t>FFO  -1719135-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3058,14 +3058,14 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1712538</t>
+          <t>1688115C</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>FFO - 1712538 - HAGAP.pdf</t>
+          <t>FFO - 1688115C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3085,14 +3085,14 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1713240</t>
+          <t>1688115I</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>FFO - 1713240 - HAGAP - 20-05-2026.pdf</t>
+          <t>FFO - 1688115I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3112,14 +3112,14 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1715878</t>
+          <t>1702776C</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3129,7 +3129,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>FFO - 1715878 - HAGAP - 20-05-2026.pdf</t>
+          <t>FFO - 1702776C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3139,14 +3139,14 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1641139I</t>
+          <t>1702776I</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>FFO 1641139I HAGAP.pdf</t>
+          <t>FFO - 1702776I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3166,14 +3166,14 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1713679</t>
+          <t>1704867</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>FFO 1713679 HAGAP.pdf</t>
+          <t>FFO - 1704867 - ASP.pdf</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3193,14 +3193,14 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1718803</t>
+          <t>1711384</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>FFO 1718803 HAGAP.pdf</t>
+          <t>FFO - 1711384 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3220,14 +3220,14 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1703223</t>
+          <t>1712538</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>FFO-1703223-HAGAP.pdf</t>
+          <t>FFO - 1712538 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3247,14 +3247,14 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1708877</t>
+          <t>1713240</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>FFO-1708877-HAGAP.pdf</t>
+          <t>FFO - 1713240 - HAGAP - 20-05-2026.pdf</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3274,14 +3274,14 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1710116</t>
+          <t>1715878</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>FFO-1710116-HAGAP.pdf</t>
+          <t>FFO - 1715878 - HAGAP - 20-05-2026.pdf</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3301,14 +3301,14 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1712547</t>
+          <t>1641139I</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>FFO-1712547-HAGAP.pdf</t>
+          <t>FFO 1641139I HAGAP.pdf</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3328,14 +3328,14 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1713044C</t>
+          <t>1713679</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>FFO-1713044C.-HAGAP.pdf</t>
+          <t>FFO 1713679 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3362,7 +3362,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1713044I</t>
+          <t>1718803</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>FFO-1713044II-HAGAP.pdf</t>
+          <t>FFO 1718803 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3382,14 +3382,14 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1713262</t>
+          <t>1703223</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3399,7 +3399,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>FFO-1713262-HAGAP.pdf</t>
+          <t>FFO-1703223-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -3409,14 +3409,14 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1714909</t>
+          <t>1708877</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>FFO-1714909-HAGAP.pdf</t>
+          <t>FFO-1708877-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -3436,14 +3436,14 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1715327</t>
+          <t>1710116</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3453,24 +3453,24 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>FFO-1715327-HAGAP.pdf</t>
+          <t>FFO-1710116-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>65,98</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1717332</t>
+          <t>1712547</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3480,24 +3480,24 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>FFO-1717332-HAGAP.pdf</t>
+          <t>FFO-1712547-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>176,23</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1719070</t>
+          <t>1713044C</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>FFO-1719070-HAGAP.pdf</t>
+          <t>FFO-1713044C.-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -3517,14 +3517,14 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1719881</t>
+          <t>1713044I</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>FFO-1719881-HAGAP.pdf</t>
+          <t>FFO-1713044II-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -3544,14 +3544,14 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1708066</t>
+          <t>1713262</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>FFO.-1708066-HAGAP.pdf</t>
+          <t>FFO-1713262-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -3571,14 +3571,14 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1712957</t>
+          <t>1714909</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>FFO.-1712957-HAGAP.pdf</t>
+          <t>FFO-1714909-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3598,14 +3598,14 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1718442</t>
+          <t>1715327</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3615,42 +3615,204 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>FFO´1718442-HAGAP.pdf</t>
+          <t>FFO-1715327-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>65,98</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
+          <t>1717332</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>FFO-1717332-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>176,23</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>1719070</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>FFO-1719070-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>1719881</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>FFO-1719881-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>1708066</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>FFO.-1708066-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>1712957</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>FFO.-1712957-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>1718442</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>FFO´1718442-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
           <t>1703223</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>BMD</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
         <is>
           <t>MULTA-1703223-HAGAP.pdf</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr">
+      <c r="D126" t="inlineStr">
         <is>
           <t>0,00</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr"/>
+      <c r="E126" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/medicoes.xlsx
+++ b/medicoes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E126"/>
+  <dimension ref="A1:E145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -743,7 +743,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1704476</t>
+          <t>1683861I</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -753,17 +753,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1704476 BMD.pdf</t>
+          <t>1683861i BMD.pdf</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>111,28</t>
+          <t>20.224,44</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
     </row>
@@ -775,56 +775,56 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1704476 FFO.pdf</t>
+          <t>1704476 BMD.pdf</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>111,28</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1704891</t>
+          <t>1704476</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1704891 - BMD PARC - HAGAP.pdf</t>
+          <t>1704476 FFO.pdf</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>100.528,77</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1704968</t>
+          <t>1704891</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -834,17 +834,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1704968 - BMD - HAGAP.pdf</t>
+          <t>1704891 - BMD PARC - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2.808,15</t>
+          <t>100.528,77</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1704968 - FFO - HAGAP.pdf</t>
+          <t>1704968 - BMD - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.808,15</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -878,27 +878,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1710937</t>
+          <t>1704968</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1710937 - bmd - hagap.pdf</t>
+          <t>1704968 - FFO - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>4.234,81</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
@@ -910,17 +910,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1710937 - ffo - hagap.pdf</t>
+          <t>1710937 - bmd - hagap.pdf</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>4.234,81</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -932,34 +932,34 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1724341</t>
+          <t>1710937</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1724341 - BMD PARC - ASP.pdf</t>
+          <t>1710937 - ffo - hagap.pdf</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>40.758,00</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1510407</t>
+          <t>1724341</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -969,24 +969,24 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BMD - 1510407 - HAGAP - 26-05-2026.pdf</t>
+          <t>1724341 - BMD PARC - ASP.pdf</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>28.642,47</t>
+          <t>40.758,00</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1688115C</t>
+          <t>1510407</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -996,24 +996,24 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BMD - 1688115C - HAGAP.pdf</t>
+          <t>BMD - 1510407 - HAGAP - 26-05-2026.pdf</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>6,65</t>
+          <t>28.642,47</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1688115I</t>
+          <t>1688115C</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1023,12 +1023,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>BMD - 1688115I - HAGAP.pdf</t>
+          <t>BMD - 1688115C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2.670,64</t>
+          <t>6,65</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1040,7 +1040,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1704867</t>
+          <t>1688115I</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1050,24 +1050,24 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BMD - 1704867 - ASP.pdf</t>
+          <t>BMD - 1688115I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>23.915,48</t>
+          <t>2.670,64</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1711384</t>
+          <t>1704867</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1077,24 +1077,24 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BMD - 1711384 - HAGAP.pdf</t>
+          <t>BMD - 1704867 - ASP.pdf</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>122,95</t>
+          <t>23.915,48</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1712538</t>
+          <t>1711384</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1104,24 +1104,24 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BMD - 1712538 - HAGAP.pdf</t>
+          <t>BMD - 1711384 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>387,36</t>
+          <t>122,95</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1713240</t>
+          <t>1712538</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1131,24 +1131,24 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>BMD - 1713240 - HAGAP - 20-05-2026.pdf</t>
+          <t>BMD - 1712538 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>5.108,11</t>
+          <t>387,36</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1713933</t>
+          <t>1713240</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1158,24 +1158,24 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>BMD - 1713933 - HAGAP - 20-05-2026.pdf</t>
+          <t>BMD - 1713240 - HAGAP - 20-05-2026.pdf</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>5.530,92</t>
+          <t>5.108,11</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1715878</t>
+          <t>1713933</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1185,24 +1185,24 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>BMD - 1715878 - HAGAP - 20-05-2026.pdf</t>
+          <t>BMD - 1713933 - HAGAP - 20-05-2026.pdf</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.786,71</t>
+          <t>5.530,92</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1718435</t>
+          <t>1715878</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1212,24 +1212,24 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>BMD - 1718435 - HAGAP - 20-05-2026.pdf</t>
+          <t>BMD - 1715878 - HAGAP - 20-05-2026.pdf</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>17.153,90</t>
+          <t>1.786,71</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1520612</t>
+          <t>1718435</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1239,24 +1239,24 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>BMD 1520612 HAGAP.pdf</t>
+          <t>BMD - 1718435 - HAGAP - 20-05-2026.pdf</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>53.357,33</t>
+          <t>17.153,90</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1520615</t>
+          <t>1725738C</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>BMD 1520615 HAGAP.pdf</t>
+          <t>BMD - 1725738C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>22.840,59</t>
+          <t>140,91</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1671139I</t>
+          <t>1725738I</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1293,24 +1293,24 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>BMD 1671139I HAGAP.pdf</t>
+          <t>BMD - 1725738I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>6.138,54</t>
+          <t>15.544,67</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1692636</t>
+          <t>1520612</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1320,24 +1320,24 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>BMD 1692636 ASP.pdf</t>
+          <t>BMD 1520612 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>19.387,05</t>
+          <t>53.357,33</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1699516</t>
+          <t>1520615</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1347,24 +1347,24 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>BMD 1699516 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1520615 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>3.388,62</t>
+          <t>22.840,59</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1704525</t>
+          <t>1671139I</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1374,24 +1374,24 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>BMD 1704525 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1671139I HAGAP.pdf</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>15.365,48</t>
+          <t>6.138,54</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1710937</t>
+          <t>1692636</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1401,24 +1401,24 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>BMD 1710937 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1692636 ASP.pdf</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>19.387,05</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1711525</t>
+          <t>1699516</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1428,24 +1428,24 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>BMD 1711525 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1699516 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1.998,42</t>
+          <t>3.388,62</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1712624</t>
+          <t>1704525</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1455,24 +1455,24 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>BMD 1712624 HAGAP.pdf</t>
+          <t>BMD 1704525 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>3.073,90</t>
+          <t>15.365,48</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1713679</t>
+          <t>1710937</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>BMD 1713679 HAGAP.pdf</t>
+          <t>BMD 1710937 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>3.574,44</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1713719</t>
+          <t>1711525</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1509,24 +1509,24 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>BMD 1713719 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1711525 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>3.385,92</t>
+          <t>1.998,42</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1715920</t>
+          <t>1712624</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1536,12 +1536,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>BMD 1715920 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1712624 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1.031,94</t>
+          <t>3.073,90</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1553,7 +1553,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1718803</t>
+          <t>1713679</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1563,24 +1563,24 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>BMD 1718803 HAGAP.pdf</t>
+          <t>BMD 1713679 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>3.825,18</t>
+          <t>3.574,44</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1719097</t>
+          <t>1713719</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1590,24 +1590,24 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>BMD 1719097 HAGAP.pdf</t>
+          <t>BMD 1713719 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>7.450,28</t>
+          <t>3.385,92</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1719155</t>
+          <t>1715920</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>BMD 1719155 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1715920 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2.223,15</t>
+          <t>1.031,94</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1634,7 +1634,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1720920</t>
+          <t>1718803</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1644,39 +1644,39 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>BMD 1720920 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1718803 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>555,60</t>
+          <t>3.825,18</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1702776C</t>
+          <t>1719097</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>BMD FINAL - 1702776C - HAGAP.pdf</t>
+          <t>BMD 1719097 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>7.450,28</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1688,49 +1688,49 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1702776I</t>
+          <t>1719155</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>BMD FINAL - 1702776I - HAGAP.pdf</t>
+          <t>BMD 1719155 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>18.098,87</t>
+          <t>2.223,15</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1713262</t>
+          <t>1720920</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>BMD FINAL-1713262-HAGAP.pdf</t>
+          <t>BMD 1720920 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>55,90</t>
+          <t>555,60</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1742,7 +1742,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1719135</t>
+          <t>1702776C</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1752,12 +1752,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>BMD FINAL-1719135-HAGAP.pdf</t>
+          <t>BMD FINAL - 1702776C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>47,08</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1769,88 +1769,88 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1677314</t>
+          <t>1702776I</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1677314 - HAGAP.pdf</t>
+          <t>BMD FINAL - 1702776I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>46.760,40</t>
+          <t>18.098,87</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1677316</t>
+          <t>1713262</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1677316 HAGAP.pdf</t>
+          <t>BMD FINAL-1713262-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>51.623,62</t>
+          <t>55,90</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1688115C</t>
+          <t>1719135</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1688115C - HAGAP.pdf</t>
+          <t>BMD FINAL-1719135-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>6,36</t>
+          <t>47,08</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1688115I</t>
+          <t>1677314</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1860,24 +1860,24 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1688115I - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1677314 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>18.752,84</t>
+          <t>46.760,40</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1694258</t>
+          <t>1677316</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1887,24 +1887,24 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1694258 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1677316 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>127.751,38</t>
+          <t>51.623,62</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1695716</t>
+          <t>1688115C</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1914,24 +1914,24 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1695716 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1688115C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>74.647,17</t>
+          <t>6,36</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1710735</t>
+          <t>1688115I</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1941,24 +1941,24 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1710735 HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1688115I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>9.153,35</t>
+          <t>18.752,84</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1711384</t>
+          <t>1694258</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1968,24 +1968,24 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1711384 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1694258 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2.127,38</t>
+          <t>127.751,38</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1712538</t>
+          <t>1695716</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1995,24 +1995,24 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1712538 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1695716 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>3.568,05</t>
+          <t>74.647,17</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1715688</t>
+          <t>1710735</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1715688 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1710735 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>9.669,94</t>
+          <t>9.153,35</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2039,7 +2039,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1712530</t>
+          <t>1711384</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2049,24 +2049,24 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>BMD PARCIAL -1712530-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1711384 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>5.393,72</t>
+          <t>2.127,38</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1563492</t>
+          <t>1712538</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2076,24 +2076,24 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>BMD PARCIAL CIANORTE - 1563492 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1712538 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>80.240,76</t>
+          <t>3.568,05</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1563492</t>
+          <t>1715278</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2103,24 +2103,24 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>BMD PARCIAL JUSSARA - 1563492 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1715278 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>64.923,56</t>
+          <t>2.654,77</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1708877I</t>
+          <t>1715688</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1708877I-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1715688 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2.132,72</t>
+          <t>9.669,94</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2147,7 +2147,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1713226</t>
+          <t>1712530</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2157,24 +2157,24 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1713226-HAGAP.pdf</t>
+          <t>BMD PARCIAL -1712530-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>3.049,11</t>
+          <t>5.393,72</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1715668</t>
+          <t>1563492</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2184,24 +2184,24 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1715668-HAGAP.pdf</t>
+          <t>BMD PARCIAL CIANORTE - 1563492 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2.070,47</t>
+          <t>80.240,76</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1717332</t>
+          <t>1563492</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1717332-HAGAP.pdf</t>
+          <t>BMD PARCIAL JUSSARA - 1563492 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2.320,28</t>
+          <t>64.923,56</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1718442</t>
+          <t>1667141</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2238,24 +2238,24 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1718442-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1667141-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>3.160,96</t>
+          <t>509,47</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1718555I</t>
+          <t>1708877I</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1718555I-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1708877I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2.781,60</t>
+          <t>2.132,72</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2282,7 +2282,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1713221</t>
+          <t>1713226</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2292,24 +2292,24 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>BMD parcial - 1713221 - HAGAP.pdf</t>
+          <t>BMD PARCIAL-1713226-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>18.794,09</t>
+          <t>3.049,11</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1703223</t>
+          <t>1715668</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2319,12 +2319,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>BMD-1703223-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1715668-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>1.471,15</t>
+          <t>2.070,47</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2336,7 +2336,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1708066</t>
+          <t>1717332</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2346,24 +2346,24 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>BMD-1708066-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1717332-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>3.419,06</t>
+          <t>2.320,28</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1712547</t>
+          <t>1718442</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2373,24 +2373,24 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>BMD-1712547-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1718442-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>117,63</t>
+          <t>3.160,96</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1712766</t>
+          <t>1718555I</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2400,24 +2400,24 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>BMD-1712766-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1718555I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>705,45</t>
+          <t>2.781,60</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1713044I</t>
+          <t>1713221</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2427,24 +2427,24 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>BMD-1713044II-HAGAP.pdf</t>
+          <t>BMD parcial - 1713221 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>1.528,53</t>
+          <t>18.794,09</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1714909</t>
+          <t>1667141</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2454,24 +2454,24 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>BMD-1714909-HAGAP.pdf</t>
+          <t>BMD-1667141-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>107,93</t>
+          <t>152,42</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1718442</t>
+          <t>1675389</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2481,24 +2481,24 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>BMD-1718442-HAGAP.pdf</t>
+          <t>BMD-1675389-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>45,19</t>
+          <t>389,52</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1719070</t>
+          <t>1703223</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2508,24 +2508,24 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>BMD-1719070-HAGAP.pdf</t>
+          <t>BMD-1703223-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>333,14</t>
+          <t>1.471,15</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1719881</t>
+          <t>1708066</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2535,24 +2535,24 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>BMD-1719881-HAGAP.pdf</t>
+          <t>BMD-1708066-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>3.239,73</t>
+          <t>3.419,06</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1719881H</t>
+          <t>1712547</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2562,24 +2562,24 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>BMD-1719881HAGAP.pdf</t>
+          <t>BMD-1712547-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>38.258,42</t>
+          <t>117,63</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1720116</t>
+          <t>1712766</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2589,24 +2589,24 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>BMD-1720116-HAGAP.pdf</t>
+          <t>BMD-1712766-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>168,95</t>
+          <t>705,45</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1713044C</t>
+          <t>1713044I</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2616,24 +2616,24 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>BMD.-1713044C.-HAGAP.pdf</t>
+          <t>BMD-1713044II-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>21,11</t>
+          <t>1.528,53</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1715327</t>
+          <t>1713226</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2643,105 +2643,105 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>BMD.1715327-HAGAP.pdf</t>
+          <t>BMD-1713226-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>237,93</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1708877</t>
+          <t>1714909</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>BMDFINAL-1708877-HAGAP.pdf</t>
+          <t>BMD-1714909-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>3,54</t>
+          <t>107,93</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1712957</t>
+          <t>1715127</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>BMDFINAL-1712957-HAGAP.pdf</t>
+          <t>BMD-1715127-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>45,19</t>
+          <t>128,31</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1717332</t>
+          <t>1715131</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>BMDFINAL-1717332-HAGAP.pdf</t>
+          <t>BMD-1715131-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.220,22</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1703223</t>
+          <t>1715257I</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2751,24 +2751,24 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1703223-HAGAP.pdf</t>
+          <t>BMD-1715257I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>18.169,34</t>
+          <t>6.765,65</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1712547</t>
+          <t>1715668</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2778,24 +2778,24 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1712547-HAGAP.pdf</t>
+          <t>BMD-1715668-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>6.951,82</t>
+          <t>249,06</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1712957</t>
+          <t>1718442</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2805,24 +2805,24 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1712957-HAGAP.pdf</t>
+          <t>BMD-1718442-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2.177,64</t>
+          <t>45,19</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1713262</t>
+          <t>1719070</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2832,24 +2832,24 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1713262-HAGAP.pdf</t>
+          <t>BMD-1719070-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2.619,71</t>
+          <t>333,14</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1714909</t>
+          <t>1719881</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2859,24 +2859,24 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1714909-HAGAP.pdf</t>
+          <t>BMD-1719881-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>954,64</t>
+          <t>3.239,73</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1715127</t>
+          <t>1719881H</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2886,24 +2886,24 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1715127-HAGAP.pdf</t>
+          <t>BMD-1719881HAGAP.pdf</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>4.418,94</t>
+          <t>38.258,42</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1715327</t>
+          <t>1720116</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2913,12 +2913,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1715327-HAGAP.pdf</t>
+          <t>BMD-1720116-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>5.417,39</t>
+          <t>168,95</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -2930,7 +2930,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1719070</t>
+          <t>1713044C</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2940,24 +2940,24 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1719070-HAGAP.pdf</t>
+          <t>BMD.-1713044C.-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2.744,71</t>
+          <t>21,11</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1719135</t>
+          <t>1715327</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2967,51 +2967,51 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1719135-HAGAP.pdf</t>
+          <t>BMD.1715327-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>913,84</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1720116</t>
+          <t>1708877</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1720116-HAGAP.pdf</t>
+          <t>BMDFINAL-1708877-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>1.675,57</t>
+          <t>3,54</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1712766</t>
+          <t>1712957</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3021,24 +3021,24 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>FF0-1712766-HAGAP.pdf</t>
+          <t>BMDFINAL-1712957-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>45,19</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1719135</t>
+          <t>1717332</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>FFO  -1719135-HAGAP.pdf</t>
+          <t>BMDFINAL-1717332-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3065,76 +3065,76 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1688115C</t>
+          <t>1703223</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>FFO - 1688115C - HAGAP.pdf</t>
+          <t>BMDPARCIAL-1703223-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>18.169,34</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1688115I</t>
+          <t>1712547</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>FFO - 1688115I - HAGAP.pdf</t>
+          <t>BMDPARCIAL-1712547-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>6.951,82</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1702776C</t>
+          <t>1712957</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>FFO - 1702776C - HAGAP.pdf</t>
+          <t>BMDPARCIAL-1712957-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.177,64</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -3146,22 +3146,22 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1702776I</t>
+          <t>1713262</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>FFO - 1702776I - HAGAP.pdf</t>
+          <t>BMDPARCIAL-1713262-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.619,71</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -3173,22 +3173,22 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1704867</t>
+          <t>1714909</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>FFO - 1704867 - ASP.pdf</t>
+          <t>BMDPARCIAL-1714909-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>954,64</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -3200,142 +3200,142 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1711384</t>
+          <t>1715127</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>FFO - 1711384 - HAGAP.pdf</t>
+          <t>BMDPARCIAL-1715127-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>4.418,94</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1712538</t>
+          <t>1715327</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>FFO - 1712538 - HAGAP.pdf</t>
+          <t>BMDPARCIAL-1715327-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>5.417,39</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1713240</t>
+          <t>1719070</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>FFO - 1713240 - HAGAP - 20-05-2026.pdf</t>
+          <t>BMDPARCIAL-1719070-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.744,71</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1715878</t>
+          <t>1719135</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>FFO - 1715878 - HAGAP - 20-05-2026.pdf</t>
+          <t>BMDPARCIAL-1719135-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>913,84</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1641139I</t>
+          <t>1720116</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>FFO 1641139I HAGAP.pdf</t>
+          <t>BMDPARCIAL-1720116-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>1.675,57</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1713679</t>
+          <t>1712766</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>FFO 1713679 HAGAP.pdf</t>
+          <t>FF0-1712766-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3355,14 +3355,14 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1718803</t>
+          <t>1719135</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>FFO 1718803 HAGAP.pdf</t>
+          <t>FFO  -1719135-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3382,14 +3382,14 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1703223</t>
+          <t>1688115C</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3399,7 +3399,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>FFO-1703223-HAGAP.pdf</t>
+          <t>FFO - 1688115C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -3409,14 +3409,14 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1708877</t>
+          <t>1688115I</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>FFO-1708877-HAGAP.pdf</t>
+          <t>FFO - 1688115I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -3436,14 +3436,14 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1710116</t>
+          <t>1702776C</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>FFO-1710116-HAGAP.pdf</t>
+          <t>FFO - 1702776C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3463,14 +3463,14 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1712547</t>
+          <t>1702776I</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>FFO-1712547-HAGAP.pdf</t>
+          <t>FFO - 1702776I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3490,14 +3490,14 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1713044C</t>
+          <t>1704867</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>FFO-1713044C.-HAGAP.pdf</t>
+          <t>FFO - 1704867 - ASP.pdf</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -3517,14 +3517,14 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1713044I</t>
+          <t>1711384</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>FFO-1713044II-HAGAP.pdf</t>
+          <t>FFO - 1711384 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -3544,14 +3544,14 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1713262</t>
+          <t>1712538</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>FFO-1713262-HAGAP.pdf</t>
+          <t>FFO - 1712538 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -3571,14 +3571,14 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1714909</t>
+          <t>1713240</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>FFO-1714909-HAGAP.pdf</t>
+          <t>FFO - 1713240 - HAGAP - 20-05-2026.pdf</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3598,14 +3598,14 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1715327</t>
+          <t>1715878</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3615,24 +3615,24 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>FFO-1715327-HAGAP.pdf</t>
+          <t>FFO - 1715878 - HAGAP - 20-05-2026.pdf</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>65,98</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1717332</t>
+          <t>1641139I</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3642,24 +3642,24 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>FFO-1717332-HAGAP.pdf</t>
+          <t>FFO 1641139I HAGAP.pdf</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>176,23</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1719070</t>
+          <t>1713679</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>FFO-1719070-HAGAP.pdf</t>
+          <t>FFO 1713679 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -3679,14 +3679,14 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1719881</t>
+          <t>1718803</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>FFO-1719881-HAGAP.pdf</t>
+          <t>FFO 1718803 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -3706,14 +3706,14 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1708066</t>
+          <t>1667141</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>FFO.-1708066-HAGAP.pdf</t>
+          <t>FFO-1667141-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -3733,14 +3733,14 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1712957</t>
+          <t>1675389</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>FFO.-1712957-HAGAP.pdf</t>
+          <t>FFO-1675389-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -3760,14 +3760,14 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1718442</t>
+          <t>1703223</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>FFO´1718442-HAGAP.pdf</t>
+          <t>FFO-1703223-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -3787,32 +3787,545 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
+          <t>1708877</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>FFO-1708877-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>1710116</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>FFO-1710116-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>1712531</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>FFO-1712531-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>1712547</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>FFO-1712547-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>1713044C</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>FFO-1713044C.-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>1713044I</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>FFO-1713044II-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>1713226</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>FFO-1713226-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>1713262</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>FFO-1713262-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>1714909</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>FFO-1714909-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>1715127</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>FFO-1715127-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>1715257I</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>FFO-1715257I-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>1715327</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>FFO-1715327-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>65,98</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>1715668</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>FFO-1715668-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>1717332</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>FFO-1717332-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>176,23</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>1719070</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>FFO-1719070-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>1719881</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>FFO-1719881-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>1708066</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>FFO.-1708066-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>1712957</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>FFO.-1712957-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>1718442</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>FFO´1718442-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
           <t>1703223</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>BMD</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
         <is>
           <t>MULTA-1703223-HAGAP.pdf</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/medicoes.xlsx
+++ b/medicoes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E145"/>
+  <dimension ref="A1:E184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,61 +446,61 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1648254</t>
+          <t>1564187</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1648254- FFO - asp.pdf</t>
+          <t>1564187 BMD PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>107.041,70</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1657710</t>
+          <t>1648254</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1657710 BMD PARCIAL ASP.pdf</t>
+          <t>1648254- FFO - asp.pdf</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>59.714,14</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1657713</t>
+          <t>1657710</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1657713 BMD PARCIAL.pdf</t>
+          <t>1657710 BMD PARCIAL ASP.pdf</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>45.658,12</t>
+          <t>59.714,14</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -537,12 +537,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1657713 parcial 1.pdf</t>
+          <t>1657713 BMD PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>37.609,02</t>
+          <t>45.658,12</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -554,7 +554,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1658452</t>
+          <t>1657713</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -564,17 +564,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1658452 -BMD -HAGAP.pdf</t>
+          <t>1657713 parcial 1.pdf</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7.792,10</t>
+          <t>37.609,02</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
@@ -586,49 +586,49 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1658452 -FFO -HAGAP.pdf</t>
+          <t>1658452 -BMD -HAGAP.pdf</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>7.792,10</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1663556</t>
+          <t>1658452</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1663556 - BMD - HAGAP.pdf</t>
+          <t>1658452 -FFO -HAGAP.pdf</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2.470,38</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
     </row>
@@ -640,29 +640,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1663556 - FFO - HAGAP.pdf</t>
+          <t>1663556 - BMD - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.470,38</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1667593</t>
+          <t>1663556</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1667593 - FFO - asp.pdf</t>
+          <t>1663556 - FFO - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -682,34 +682,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1676605</t>
+          <t>1667593</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1676605 - BMD PARCIAL - HAGAP.pdf</t>
+          <t>1667593 - FFO - asp.pdf</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>39.199,95</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1676605 - BMD PARCIAL - HAGAP1.pdf</t>
+          <t>1676605 - BMD PARCIAL - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -743,7 +743,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1683861I</t>
+          <t>1676605</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -753,24 +753,24 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1683861i BMD.pdf</t>
+          <t>1676605 - BMD PARCIAL - HAGAP1.pdf</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>20.224,44</t>
+          <t>39.199,95</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1704476</t>
+          <t>1683861I</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -780,17 +780,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1704476 BMD.pdf</t>
+          <t>1683861i BMD.pdf</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>111,28</t>
+          <t>20.224,44</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
     </row>
@@ -802,56 +802,56 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1704476 FFO.pdf</t>
+          <t>1704476 BMD.pdf</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>111,28</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1704891</t>
+          <t>1704476</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1704891 - BMD PARC - HAGAP.pdf</t>
+          <t>1704476 FFO.pdf</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>100.528,77</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1704968</t>
+          <t>1704891</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -861,17 +861,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1704968 - BMD - HAGAP.pdf</t>
+          <t>1704891 - BMD PARC - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2.808,15</t>
+          <t>100.528,77</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
@@ -883,17 +883,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1704968 - FFO - HAGAP.pdf</t>
+          <t>1704968 - BMD - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.808,15</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -905,27 +905,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1710937</t>
+          <t>1704968</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1710937 - bmd - hagap.pdf</t>
+          <t>1704968 - FFO - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>4.234,81</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
@@ -937,17 +937,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1710937 - ffo - hagap.pdf</t>
+          <t>1710937 - bmd - hagap.pdf</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>4.234,81</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -959,34 +959,34 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1724341</t>
+          <t>1710937</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1724341 - BMD PARC - ASP.pdf</t>
+          <t>1710937 - ffo - hagap.pdf</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>40.758,00</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1510407</t>
+          <t>1724341</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -996,24 +996,24 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BMD - 1510407 - HAGAP - 26-05-2026.pdf</t>
+          <t>1724341 - BMD PARC - ASP.pdf</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>28.642,47</t>
+          <t>40.758,00</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1688115C</t>
+          <t>1510407</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1023,24 +1023,24 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>BMD - 1688115C - HAGAP.pdf</t>
+          <t>BMD - 1510407 - HAGAP - 26-05-2026.pdf</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>6,65</t>
+          <t>28.642,47</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1688115I</t>
+          <t>1688115C</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1050,12 +1050,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BMD - 1688115I - HAGAP.pdf</t>
+          <t>BMD - 1688115C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2.670,64</t>
+          <t>6,65</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1067,7 +1067,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1704867</t>
+          <t>1688115I</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1077,24 +1077,24 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BMD - 1704867 - ASP.pdf</t>
+          <t>BMD - 1688115I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>23.915,48</t>
+          <t>2.670,64</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1711384</t>
+          <t>1704867</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1104,24 +1104,24 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BMD - 1711384 - HAGAP.pdf</t>
+          <t>BMD - 1704867 - ASP.pdf</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>122,95</t>
+          <t>23.915,48</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1712538</t>
+          <t>1711384</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1131,24 +1131,24 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>BMD - 1712538 - HAGAP.pdf</t>
+          <t>BMD - 1711384 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>387,36</t>
+          <t>122,95</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1713240</t>
+          <t>1712538</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1158,24 +1158,24 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>BMD - 1713240 - HAGAP - 20-05-2026.pdf</t>
+          <t>BMD - 1712538 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>5.108,11</t>
+          <t>387,36</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1713933</t>
+          <t>1713240</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1185,24 +1185,24 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>BMD - 1713933 - HAGAP - 20-05-2026.pdf</t>
+          <t>BMD - 1713240 - HAGAP - 20-05-2026.pdf</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>5.530,92</t>
+          <t>5.108,11</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1715878</t>
+          <t>1713933</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1212,24 +1212,24 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>BMD - 1715878 - HAGAP - 20-05-2026.pdf</t>
+          <t>BMD - 1713933 - HAGAP - 20-05-2026.pdf</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.786,71</t>
+          <t>5.530,92</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1718435</t>
+          <t>1715878</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1239,24 +1239,24 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>BMD - 1718435 - HAGAP - 20-05-2026.pdf</t>
+          <t>BMD - 1715878 - HAGAP - 20-05-2026.pdf</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>17.153,90</t>
+          <t>1.786,71</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1725738C</t>
+          <t>1718435</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>BMD - 1725738C - HAGAP.pdf</t>
+          <t>BMD - 1718435 - HAGAP - 20-05-2026.pdf</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>140,91</t>
+          <t>17.153,90</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1725738I</t>
+          <t>1725738C</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1293,12 +1293,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>BMD - 1725738I - HAGAP.pdf</t>
+          <t>BMD - 1725738C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>15.544,67</t>
+          <t>140,91</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1310,7 +1310,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1520612</t>
+          <t>1725738I</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1320,24 +1320,24 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>BMD 1520612 HAGAP.pdf</t>
+          <t>BMD - 1725738I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>53.357,33</t>
+          <t>15.544,67</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1520615</t>
+          <t>1520612</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>BMD 1520615 HAGAP.pdf</t>
+          <t>BMD 1520612 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>22.840,59</t>
+          <t>53.357,33</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1364,7 +1364,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1671139I</t>
+          <t>1520615</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1374,24 +1374,24 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>BMD 1671139I HAGAP.pdf</t>
+          <t>BMD 1520615 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>6.138,54</t>
+          <t>22.840,59</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1692636</t>
+          <t>1671139I</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1401,24 +1401,24 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>BMD 1692636 ASP.pdf</t>
+          <t>BMD 1671139I HAGAP.pdf</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>19.387,05</t>
+          <t>6.138,54</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1699516</t>
+          <t>1692636</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1428,24 +1428,24 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>BMD 1699516 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1692636 ASP.pdf</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>3.388,62</t>
+          <t>19.387,05</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1704525</t>
+          <t>1699516</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1455,24 +1455,24 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>BMD 1704525 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1699516 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>15.365,48</t>
+          <t>3.388,62</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1710937</t>
+          <t>1704525</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1482,24 +1482,24 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>BMD 1710937 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1704525 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>15.365,48</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1711525</t>
+          <t>1705074</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1509,24 +1509,24 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>BMD 1711525 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1705074 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1.998,42</t>
+          <t>150.312,87</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1712624</t>
+          <t>1710937</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1536,12 +1536,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>BMD 1712624 HAGAP.pdf</t>
+          <t>BMD 1710937 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>3.073,90</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1553,7 +1553,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1713679</t>
+          <t>1711525</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1563,24 +1563,24 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>BMD 1713679 HAGAP.pdf</t>
+          <t>BMD 1711525 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>3.574,44</t>
+          <t>1.998,42</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1713719</t>
+          <t>1712624</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1590,24 +1590,24 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>BMD 1713719 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1712624 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>3.385,92</t>
+          <t>3.073,90</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1715920</t>
+          <t>1713223</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1617,24 +1617,24 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>BMD 1715920 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1713223 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1.031,94</t>
+          <t>9.773,21</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1718803</t>
+          <t>1713679</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1644,24 +1644,24 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>BMD 1718803 HAGAP.pdf</t>
+          <t>BMD 1713679 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>3.825,18</t>
+          <t>3.574,44</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1719097</t>
+          <t>1713719</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1671,24 +1671,24 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>BMD 1719097 HAGAP.pdf</t>
+          <t>BMD 1713719 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>7.450,28</t>
+          <t>3.385,92</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1719155</t>
+          <t>1714729</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1698,24 +1698,24 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>BMD 1719155 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1714729 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2.223,15</t>
+          <t>6.722,61</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1720920</t>
+          <t>1715920</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1725,132 +1725,132 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>BMD 1720920 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1715920 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>555,60</t>
+          <t>1.031,94</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1702776C</t>
+          <t>1718803</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>BMD FINAL - 1702776C - HAGAP.pdf</t>
+          <t>BMD 1718803 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>3.825,18</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1702776I</t>
+          <t>1719097</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>BMD FINAL - 1702776I - HAGAP.pdf</t>
+          <t>BMD 1719097 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>18.098,87</t>
+          <t>7.450,28</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1713262</t>
+          <t>1719155</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>BMD FINAL-1713262-HAGAP.pdf</t>
+          <t>BMD 1719155 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>55,90</t>
+          <t>2.223,15</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1719135</t>
+          <t>1720721</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>BMD FINAL-1719135-HAGAP.pdf</t>
+          <t>BMD 1720721 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>47,08</t>
+          <t>2.015,45</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1677314</t>
+          <t>1720920</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1860,12 +1860,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1677314 - HAGAP.pdf</t>
+          <t>BMD 1720920 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>46.760,40</t>
+          <t>555,60</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1877,7 +1877,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1677316</t>
+          <t>1724356</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1887,24 +1887,24 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1677316 HAGAP.pdf</t>
+          <t>BMD 1724356 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>51.623,62</t>
+          <t>7.614,80</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1688115C</t>
+          <t>1728163</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1914,132 +1914,132 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1688115C - HAGAP.pdf</t>
+          <t>BMD 1728163 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>6,36</t>
+          <t>7.914,69</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1688115I</t>
+          <t>1702776C</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1688115I - HAGAP.pdf</t>
+          <t>BMD FINAL - 1702776C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>18.752,84</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1694258</t>
+          <t>1702776I</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1694258 - HAGAP.pdf</t>
+          <t>BMD FINAL - 1702776I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>127.751,38</t>
+          <t>18.098,87</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1695716</t>
+          <t>1713262</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1695716 - HAGAP.pdf</t>
+          <t>BMD FINAL-1713262-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>74.647,17</t>
+          <t>55,90</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1710735</t>
+          <t>1719135</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1710735 HAGAP.pdf</t>
+          <t>BMD FINAL-1719135-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>9.153,35</t>
+          <t>47,08</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1711384</t>
+          <t>1712550</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2049,24 +2049,24 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1711384 - HAGAP.pdf</t>
+          <t>BMD PARCAIL-1712550-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2.127,38</t>
+          <t>4.585,98</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1712538</t>
+          <t>1677314</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2076,12 +2076,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1712538 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1677314 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>3.568,05</t>
+          <t>46.760,40</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2093,7 +2093,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1715278</t>
+          <t>1677316</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2103,24 +2103,24 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1715278 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1677316 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2.654,77</t>
+          <t>51.623,62</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1715688</t>
+          <t>1688115C</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2130,24 +2130,24 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1715688 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1688115C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>9.669,94</t>
+          <t>6,36</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1712530</t>
+          <t>1688115I</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2157,24 +2157,24 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>BMD PARCIAL -1712530-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1688115I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>5.393,72</t>
+          <t>18.752,84</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1563492</t>
+          <t>1691534</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2184,24 +2184,24 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>BMD PARCIAL CIANORTE - 1563492 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1691534 - HAGAP - 19-06-2026.pdf</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>80.240,76</t>
+          <t>20.334,45</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1563492</t>
+          <t>1694258</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>BMD PARCIAL JUSSARA - 1563492 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1694258 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>64.923,56</t>
+          <t>127.751,38</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1667141</t>
+          <t>1695716</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2238,24 +2238,24 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1667141-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1695716 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>509,47</t>
+          <t>74.647,17</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1708877I</t>
+          <t>1698056</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2265,24 +2265,24 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1708877I-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1698056 - HAGAP - 22-06-2026.pdf</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2.132,72</t>
+          <t>8.966,25</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1713226</t>
+          <t>1710735</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2292,24 +2292,24 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1713226-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1710735 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>3.049,11</t>
+          <t>9.153,35</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1715668</t>
+          <t>1711384</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2319,24 +2319,24 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1715668-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1711384 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2.070,47</t>
+          <t>2.127,38</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1717332</t>
+          <t>1712538</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2346,24 +2346,24 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1717332-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1712538 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2.320,28</t>
+          <t>3.568,05</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1718442</t>
+          <t>1715278</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2373,24 +2373,24 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1718442-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1715278 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>3.160,96</t>
+          <t>2.654,77</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1718555I</t>
+          <t>1715688</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2400,12 +2400,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1718555I-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1715688 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2.781,60</t>
+          <t>9.669,94</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2417,7 +2417,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1713221</t>
+          <t>1720914</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2427,24 +2427,24 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>BMD parcial - 1713221 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1720914 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>18.794,09</t>
+          <t>13.736,92</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1667141</t>
+          <t>1721887</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2454,24 +2454,24 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>BMD-1667141-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1721887 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>152,42</t>
+          <t>15.229,27</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1675389</t>
+          <t>1722169</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2481,24 +2481,24 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>BMD-1675389-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1722169 - HAGAP - 19-06-2026.pdf</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>389,52</t>
+          <t>38.238,91</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1703223</t>
+          <t>1712530</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2508,24 +2508,24 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>BMD-1703223-HAGAP.pdf</t>
+          <t>BMD PARCIAL -1712530-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>1.471,15</t>
+          <t>5.393,72</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1708066</t>
+          <t>1713626I</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2535,24 +2535,24 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>BMD-1708066-HAGAP.pdf</t>
+          <t>BMD PARCIAL -1713626I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>3.419,06</t>
+          <t>5.318,80</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1712547</t>
+          <t>1713260</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2562,24 +2562,24 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>BMD-1712547-HAGAP.pdf</t>
+          <t>BMD PARCIAL 1713260 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>117,63</t>
+          <t>8.854,04</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1712766</t>
+          <t>1563492</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2589,24 +2589,24 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>BMD-1712766-HAGAP.pdf</t>
+          <t>BMD PARCIAL CIANORTE - 1563492 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>705,45</t>
+          <t>80.240,76</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1713044I</t>
+          <t>1563492</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2616,24 +2616,24 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>BMD-1713044II-HAGAP.pdf</t>
+          <t>BMD PARCIAL JUSSARA - 1563492 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>1.528,53</t>
+          <t>64.923,56</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1713226</t>
+          <t>1667141</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2643,24 +2643,24 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>BMD-1713226-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1667141-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>237,93</t>
+          <t>509,47</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1714909</t>
+          <t>1694841</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2670,24 +2670,24 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>BMD-1714909-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1694841-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>107,93</t>
+          <t>4.476,57</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1715127</t>
+          <t>1708877I</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2697,24 +2697,24 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>BMD-1715127-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1708877I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>128,31</t>
+          <t>2.132,72</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1715131</t>
+          <t>1709486</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2724,24 +2724,24 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>BMD-1715131-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1709486-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2.220,22</t>
+          <t>4.402,38</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1715257I</t>
+          <t>1711775</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2751,24 +2751,24 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>BMD-1715257I-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1711775-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>6.765,65</t>
+          <t>1.928,86</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1715668</t>
+          <t>1713226</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2778,24 +2778,24 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>BMD-1715668-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1713226-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>249,06</t>
+          <t>3.049,11</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1718442</t>
+          <t>1713656</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2805,24 +2805,24 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>BMD-1718442-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1713656-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>45,19</t>
+          <t>4.315,58</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1719070</t>
+          <t>1714342</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2832,24 +2832,24 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>BMD-1719070-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1714342-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>333,14</t>
+          <t>1.949,56</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1719881</t>
+          <t>1714699</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2859,24 +2859,24 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>BMD-1719881-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1714699-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>3.239,73</t>
+          <t>18.624,62</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1719881H</t>
+          <t>1715201</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2886,24 +2886,24 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>BMD-1719881HAGAP.pdf</t>
+          <t>BMD PARCIAL-1715201-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>38.258,42</t>
+          <t>6.987,28</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1720116</t>
+          <t>1715668</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2913,12 +2913,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>BMD-1720116-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1715668-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>168,95</t>
+          <t>2.070,47</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -2930,7 +2930,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1713044C</t>
+          <t>1715955I</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2940,24 +2940,24 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>BMD.-1713044C.-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1715955I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>21,11</t>
+          <t>2.970,68</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1715327</t>
+          <t>1717168</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2967,105 +2967,105 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>BMD.1715327-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1717168-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.528,74</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1708877</t>
+          <t>1717332</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>BMDFINAL-1708877-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1717332-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>3,54</t>
+          <t>2.320,28</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1712957</t>
+          <t>1718442</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>BMDFINAL-1712957-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1718442-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>45,19</t>
+          <t>3.160,96</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1717332</t>
+          <t>1718555I</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>BMDFINAL-1717332-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1718555I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.781,60</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1703223</t>
+          <t>1721869</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3075,24 +3075,24 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1703223-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1721869-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>18.169,34</t>
+          <t>807,18</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1712547</t>
+          <t>1725260</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3102,24 +3102,24 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1712547-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1725260-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>6.951,82</t>
+          <t>4.716,47</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1712957</t>
+          <t>1713221</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3129,12 +3129,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1712957-HAGAP.pdf</t>
+          <t>BMD parcial - 1713221 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2.177,64</t>
+          <t>18.794,09</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -3146,7 +3146,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1713262</t>
+          <t>1667141</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1713262-HAGAP.pdf</t>
+          <t>BMD-1667141-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2.619,71</t>
+          <t>152,42</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1714909</t>
+          <t>1675389</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3183,24 +3183,24 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1714909-HAGAP.pdf</t>
+          <t>BMD-1675389-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>954,64</t>
+          <t>389,52</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1715127</t>
+          <t>1703223</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3210,24 +3210,24 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1715127-HAGAP.pdf</t>
+          <t>BMD-1703223-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>4.418,94</t>
+          <t>1.471,15</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1715327</t>
+          <t>1708066</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3237,24 +3237,24 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1715327-HAGAP.pdf</t>
+          <t>BMD-1708066-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>5.417,39</t>
+          <t>3.419,06</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1719070</t>
+          <t>1712547</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3264,24 +3264,24 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1719070-HAGAP.pdf</t>
+          <t>BMD-1712547-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2.744,71</t>
+          <t>117,63</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1719135</t>
+          <t>1712766</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3291,24 +3291,24 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1719135-HAGAP.pdf</t>
+          <t>BMD-1712766-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>913,84</t>
+          <t>705,45</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1720116</t>
+          <t>1713044I</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3318,584 +3318,584 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1720116-HAGAP.pdf</t>
+          <t>BMD-1713044II-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>1.675,57</t>
+          <t>1.528,53</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1712766</t>
+          <t>1713226</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>FF0-1712766-HAGAP.pdf</t>
+          <t>BMD-1713226-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>237,93</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1719135</t>
+          <t>1714909</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>FFO  -1719135-HAGAP.pdf</t>
+          <t>BMD-1714909-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>107,93</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1688115C</t>
+          <t>1715127</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>FFO - 1688115C - HAGAP.pdf</t>
+          <t>BMD-1715127-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>128,31</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1688115I</t>
+          <t>1715131</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>FFO - 1688115I - HAGAP.pdf</t>
+          <t>BMD-1715131-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.220,22</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1702776C</t>
+          <t>1715257I</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>FFO - 1702776C - HAGAP.pdf</t>
+          <t>BMD-1715257I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>6.765,65</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1702776I</t>
+          <t>1715668</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>FFO - 1702776I - HAGAP.pdf</t>
+          <t>BMD-1715668-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>249,06</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1704867</t>
+          <t>1715816C</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>FFO - 1704867 - ASP.pdf</t>
+          <t>BMD-1715816C-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>30,22</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1711384</t>
+          <t>1715816I</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>FFO - 1711384 - HAGAP.pdf</t>
+          <t>BMD-1715816I-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>3.168,40</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1712538</t>
+          <t>1715899</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>FFO - 1712538 - HAGAP.pdf</t>
+          <t>BMD-1715899-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>3.389,65</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1713240</t>
+          <t>1717166</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>FFO - 1713240 - HAGAP - 20-05-2026.pdf</t>
+          <t>BMD-1717166-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>22.116,83</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1715878</t>
+          <t>1718442</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>FFO - 1715878 - HAGAP - 20-05-2026.pdf</t>
+          <t>BMD-1718442-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>45,19</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1641139I</t>
+          <t>1718561</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>FFO 1641139I HAGAP.pdf</t>
+          <t>BMD-1718561-HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>13.683,99</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1713679</t>
+          <t>1719070</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>FFO 1713679 HAGAP.pdf</t>
+          <t>BMD-1719070-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>333,14</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1718803</t>
+          <t>1719213</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>FFO 1718803 HAGAP.pdf</t>
+          <t>BMD-1719213-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>5.951,32</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1667141</t>
+          <t>1719214</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>FFO-1667141-HAGAP.pdf</t>
+          <t>BMD-1719214-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>6.124,60</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1675389</t>
+          <t>1719881</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>FFO-1675389-HAGAP.pdf</t>
+          <t>BMD-1719881-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>3.239,73</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1703223</t>
+          <t>1719881H</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>FFO-1703223-HAGAP.pdf</t>
+          <t>BMD-1719881HAGAP.pdf</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>38.258,42</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1708877</t>
+          <t>1720116</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>FFO-1708877-HAGAP.pdf</t>
+          <t>BMD-1720116-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>168,95</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1710116</t>
+          <t>1721631</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>FFO-1710116-HAGAP.pdf</t>
+          <t>BMD-1721631-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>12.649,43</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1712531</t>
+          <t>1721631C</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>FFO-1712531-HAGAP.pdf</t>
+          <t>BMD-1721631C-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>100,65</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>1712547</t>
+          <t>1721886</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>FFO-1712547-HAGAP.pdf</t>
+          <t>BMD-1721886 - HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>14.551,70</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
@@ -3907,39 +3907,39 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>FFO-1713044C.-HAGAP.pdf</t>
+          <t>BMD.-1713044C.-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>21,11</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1713044I</t>
+          <t>1715327</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>FFO-1713044II-HAGAP.pdf</t>
+          <t>BMD.1715327-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -3949,14 +3949,14 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>1713226</t>
+          <t>1708877</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3966,24 +3966,24 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>FFO-1713226-HAGAP.pdf</t>
+          <t>BMDFINAL-1708877-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>3,54</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1713262</t>
+          <t>1712957</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3993,24 +3993,24 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>FFO-1713262-HAGAP.pdf</t>
+          <t>BMDFINAL-1712957-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>45,19</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1714909</t>
+          <t>1717332</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>FFO-1714909-HAGAP.pdf</t>
+          <t>BMDFINAL-1717332-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -4030,83 +4030,83 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1715127</t>
+          <t>1703223</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>FFO-1715127-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1703223-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>18.169,34</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1715257I</t>
+          <t>1712547</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>FFO-1715257I-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1712547-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>6.951,82</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1715327</t>
+          <t>1712957</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>FFO-1715327-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1712957-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>65,98</t>
+          <t>2.177,64</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -4118,49 +4118,49 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1715668</t>
+          <t>1713262</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>FFO-1715668-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1713262-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.619,71</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1717332</t>
+          <t>1714909</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>FFO-1717332-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1714909-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>176,23</t>
+          <t>954,64</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -4172,160 +4172,1213 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1719070</t>
+          <t>1715127</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>FFO-1719070-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1715127-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>4.418,94</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1719881</t>
+          <t>1715327</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>FFO-1719881-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1715327-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>5.417,39</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1708066</t>
+          <t>1719070</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>FFO.-1708066-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1719070-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.744,71</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1712957</t>
+          <t>1719135</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>FFO.-1712957-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1719135-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>913,84</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1718442</t>
+          <t>1720116</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>FFO´1718442-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1720116-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>1.675,57</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
+          <t>1724491</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>BMDPARCIAL-1724491-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>14.377,51</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>1712766</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>FF0-1712766-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>1719135</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>FFO  -1719135-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>1688115C</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>FFO - 1688115C - HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>1688115I</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>FFO - 1688115I - HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>1702776C</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>FFO - 1702776C - HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>1702776I</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>FFO - 1702776I - HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>1704867</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>FFO - 1704867 - ASP.pdf</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>1711384</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>FFO - 1711384 - HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>1712538</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>FFO - 1712538 - HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>1713240</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>FFO - 1713240 - HAGAP - 20-05-2026.pdf</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>1715878</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>FFO - 1715878 - HAGAP - 20-05-2026.pdf</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>1641139I</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>FFO 1641139I HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>1713679</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>FFO 1713679 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>1714729</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>FFO 1714729 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>1718803</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>FFO 1718803 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>1720721</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>FFO 1720721 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>1667141</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>FFO-1667141-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>1675389</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>FFO-1675389-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
           <t>1703223</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>BMD</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>FFO-1703223-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>1708877</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>FFO-1708877-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>1710116</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>FFO-1710116-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>1712531</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>FFO-1712531-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>1712547</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>FFO-1712547-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>1713044C</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>FFO-1713044C.-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>1713044I</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>FFO-1713044II-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>1713226</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>FFO-1713226-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>1713262</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>FFO-1713262-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>1714909</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>FFO-1714909-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>1715127</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>FFO-1715127-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>1715257I</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>FFO-1715257I-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>1715327</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>FFO-1715327-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>65,98</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>1715668</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>FFO-1715668-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>1717332</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>FFO-1717332-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>176,23</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>1719070</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>FFO-1719070-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>1719881</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>FFO-1719881-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>1708066</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>FFO.-1708066-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>1712957</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>FFO.-1712957-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>1718442</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>FFO´1718442-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>1703223</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
         <is>
           <t>MULTA-1703223-HAGAP.pdf</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr">
+      <c r="D184" t="inlineStr">
         <is>
           <t>0,00</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr"/>
+      <c r="E184" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/medicoes.xlsx
+++ b/medicoes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E184"/>
+  <dimension ref="A1:E193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -878,7 +878,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1704968</t>
+          <t>1704920</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -888,17 +888,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1704968 - BMD - HAGAP.pdf</t>
+          <t>1704920 BMD PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2.808,15</t>
+          <t>58.137,43</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
@@ -910,17 +910,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1704968 - FFO - HAGAP.pdf</t>
+          <t>1704968 - BMD - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.808,15</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -932,61 +932,61 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1710937</t>
+          <t>1704968</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1710937 - bmd - hagap.pdf</t>
+          <t>1704968 - FFO - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>4.234,81</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1710937</t>
+          <t>1707817</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1710937 - ffo - hagap.pdf</t>
+          <t>1707817 BMD PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>138.680,75</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1724341</t>
+          <t>1710937</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -996,51 +996,51 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1724341 - BMD PARC - ASP.pdf</t>
+          <t>1710937 - bmd - hagap.pdf</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>40.758,00</t>
+          <t>4.234,81</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1510407</t>
+          <t>1710937</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>BMD - 1510407 - HAGAP - 26-05-2026.pdf</t>
+          <t>1710937 - ffo - hagap.pdf</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>28.642,47</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1688115C</t>
+          <t>1724341</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1050,24 +1050,24 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BMD - 1688115C - HAGAP.pdf</t>
+          <t>1724341 - BMD PARC - ASP.pdf</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>6,65</t>
+          <t>40.758,00</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1688115I</t>
+          <t>1510407</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1077,24 +1077,24 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BMD - 1688115I - HAGAP.pdf</t>
+          <t>BMD - 1510407 - HAGAP - 26-05-2026.pdf</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2.670,64</t>
+          <t>28.642,47</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1704867</t>
+          <t>1658892</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1104,24 +1104,24 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BMD - 1704867 - ASP.pdf</t>
+          <t>BMD - 1658892 - HAGAP - 22-06-2026.pdf</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>23.915,48</t>
+          <t>38.435,91</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1711384</t>
+          <t>1688115C</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>BMD - 1711384 - HAGAP.pdf</t>
+          <t>BMD - 1688115C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>122,95</t>
+          <t>6,65</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1148,7 +1148,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1712538</t>
+          <t>1688115I</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1158,24 +1158,24 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>BMD - 1712538 - HAGAP.pdf</t>
+          <t>BMD - 1688115I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>387,36</t>
+          <t>2.670,64</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1713240</t>
+          <t>1704867</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1185,24 +1185,24 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>BMD - 1713240 - HAGAP - 20-05-2026.pdf</t>
+          <t>BMD - 1704867 - ASP.pdf</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>5.108,11</t>
+          <t>23.915,48</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1713933</t>
+          <t>1711384</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1212,24 +1212,24 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>BMD - 1713933 - HAGAP - 20-05-2026.pdf</t>
+          <t>BMD - 1711384 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>5.530,92</t>
+          <t>122,95</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1715878</t>
+          <t>1712538</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1239,24 +1239,24 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>BMD - 1715878 - HAGAP - 20-05-2026.pdf</t>
+          <t>BMD - 1712538 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.786,71</t>
+          <t>387,36</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1718435</t>
+          <t>1713240</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>BMD - 1718435 - HAGAP - 20-05-2026.pdf</t>
+          <t>BMD - 1713240 - HAGAP - 20-05-2026.pdf</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>17.153,90</t>
+          <t>5.108,11</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1725738C</t>
+          <t>1713933</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1293,24 +1293,24 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>BMD - 1725738C - HAGAP.pdf</t>
+          <t>BMD - 1713933 - HAGAP - 20-05-2026.pdf</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>140,91</t>
+          <t>5.530,92</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1725738I</t>
+          <t>1715878</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1320,24 +1320,24 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>BMD - 1725738I - HAGAP.pdf</t>
+          <t>BMD - 1715878 - HAGAP - 20-05-2026.pdf</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>15.544,67</t>
+          <t>1.786,71</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1520612</t>
+          <t>1718435</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1347,24 +1347,24 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>BMD 1520612 HAGAP.pdf</t>
+          <t>BMD - 1718435 - HAGAP - 20-05-2026.pdf</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>53.357,33</t>
+          <t>17.153,90</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1520615</t>
+          <t>1718783</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1374,24 +1374,24 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>BMD 1520615 HAGAP.pdf</t>
+          <t>BMD - 1718783 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>22.840,59</t>
+          <t>16.983,02</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1671139I</t>
+          <t>1725738C</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1401,24 +1401,24 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>BMD 1671139I HAGAP.pdf</t>
+          <t>BMD - 1725738C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>6.138,54</t>
+          <t>140,91</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1692636</t>
+          <t>1725738I</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1428,24 +1428,24 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>BMD 1692636 ASP.pdf</t>
+          <t>BMD - 1725738I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>19.387,05</t>
+          <t>15.544,67</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1699516</t>
+          <t>1520612</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1455,24 +1455,24 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>BMD 1699516 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1520612 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>3.388,62</t>
+          <t>53.357,33</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1704525</t>
+          <t>1520615</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1482,24 +1482,24 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>BMD 1704525 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1520615 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>15.365,48</t>
+          <t>22.840,59</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1705074</t>
+          <t>1671139I</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1509,24 +1509,24 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>BMD 1705074 HAGAP.pdf</t>
+          <t>BMD 1671139I HAGAP.pdf</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>150.312,87</t>
+          <t>6.138,54</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1710937</t>
+          <t>1692636</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1536,24 +1536,24 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>BMD 1710937 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1692636 ASP.pdf</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>19.387,05</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1711525</t>
+          <t>1699516</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1563,24 +1563,24 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>BMD 1711525 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1699516 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1.998,42</t>
+          <t>3.388,62</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1712624</t>
+          <t>1704525</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1590,24 +1590,24 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>BMD 1712624 HAGAP.pdf</t>
+          <t>BMD 1704525 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>3.073,90</t>
+          <t>15.365,48</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1713223</t>
+          <t>1704891</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1617,24 +1617,24 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>BMD 1713223 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1704891 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>9.773,21</t>
+          <t>41.477,99</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1713679</t>
+          <t>1705074</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1644,24 +1644,24 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>BMD 1713679 HAGAP.pdf</t>
+          <t>BMD 1705074 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>3.574,44</t>
+          <t>150.312,87</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1713719</t>
+          <t>1710329</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1671,24 +1671,24 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>BMD 1713719 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1710329 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>3.385,92</t>
+          <t>24.209,42</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1714729</t>
+          <t>1710937</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1698,24 +1698,24 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>BMD 1714729 HAGAP.pdf</t>
+          <t>BMD 1710937 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>6.722,61</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1715920</t>
+          <t>1711525</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1725,24 +1725,24 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>BMD 1715920 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1711525 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1.031,94</t>
+          <t>1.998,42</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1718803</t>
+          <t>1712624</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1752,24 +1752,24 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>BMD 1718803 HAGAP.pdf</t>
+          <t>BMD 1712624 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>3.825,18</t>
+          <t>3.073,90</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1719097</t>
+          <t>1713223</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1779,24 +1779,24 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>BMD 1719097 HAGAP.pdf</t>
+          <t>BMD 1713223 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>7.450,28</t>
+          <t>9.773,21</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1719155</t>
+          <t>1713679</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>BMD 1719155 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1713679 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2.223,15</t>
+          <t>3.574,44</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1823,7 +1823,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1720721</t>
+          <t>1713719</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1833,24 +1833,24 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>BMD 1720721 HAGAP.pdf</t>
+          <t>BMD 1713719 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2.015,45</t>
+          <t>3.385,92</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1720920</t>
+          <t>1714729</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1860,24 +1860,24 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>BMD 1720920 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1714729 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>555,60</t>
+          <t>6.722,61</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1724356</t>
+          <t>1715920</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1887,24 +1887,24 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>BMD 1724356 HAGAP.pdf</t>
+          <t>BMD 1715920 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>7.614,80</t>
+          <t>1.031,94</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1728163</t>
+          <t>1718803</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1914,39 +1914,39 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>BMD 1728163 HAGAP.pdf</t>
+          <t>BMD 1718803 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>7.914,69</t>
+          <t>3.825,18</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1702776C</t>
+          <t>1719097</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>BMD FINAL - 1702776C - HAGAP.pdf</t>
+          <t>BMD 1719097 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>7.450,28</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -1958,76 +1958,76 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1702776I</t>
+          <t>1719155</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>BMD FINAL - 1702776I - HAGAP.pdf</t>
+          <t>BMD 1719155 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>18.098,87</t>
+          <t>2.223,15</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1713262</t>
+          <t>1720721</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>BMD FINAL-1713262-HAGAP.pdf</t>
+          <t>BMD 1720721 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>55,90</t>
+          <t>2.015,45</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1719135</t>
+          <t>1720920</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>BMD FINAL-1719135-HAGAP.pdf</t>
+          <t>BMD 1720920 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>47,08</t>
+          <t>555,60</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2039,7 +2039,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1712550</t>
+          <t>1724356</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2049,24 +2049,24 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>BMD PARCAIL-1712550-HAGAP.pdf</t>
+          <t>BMD 1724356 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>4.585,98</t>
+          <t>7.614,80</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1677314</t>
+          <t>1728163</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2076,132 +2076,132 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1677314 - HAGAP.pdf</t>
+          <t>BMD 1728163 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>46.760,40</t>
+          <t>7.914,69</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1677316</t>
+          <t>1702776C</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1677316 HAGAP.pdf</t>
+          <t>BMD FINAL - 1702776C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>51.623,62</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1688115C</t>
+          <t>1702776I</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1688115C - HAGAP.pdf</t>
+          <t>BMD FINAL - 1702776I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>6,36</t>
+          <t>18.098,87</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1688115I</t>
+          <t>1713262</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1688115I - HAGAP.pdf</t>
+          <t>BMD FINAL-1713262-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>18.752,84</t>
+          <t>55,90</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1691534</t>
+          <t>1719135</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1691534 - HAGAP - 19-06-2026.pdf</t>
+          <t>BMD FINAL-1719135-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>20.334,45</t>
+          <t>47,08</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1694258</t>
+          <t>1712550</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1694258 - HAGAP.pdf</t>
+          <t>BMD PARCAIL-1712550-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>127.751,38</t>
+          <t>4.585,98</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1695716</t>
+          <t>1677314</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2238,24 +2238,24 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1695716 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1677314 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>74.647,17</t>
+          <t>46.760,40</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1698056</t>
+          <t>1677316</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2265,24 +2265,24 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1698056 - HAGAP - 22-06-2026.pdf</t>
+          <t>BMD PARCIAL - 1677316 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>8.966,25</t>
+          <t>51.623,62</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1710735</t>
+          <t>1688115C</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2292,24 +2292,24 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1710735 HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1688115C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>9.153,35</t>
+          <t>6,36</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1711384</t>
+          <t>1688115I</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2319,24 +2319,24 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1711384 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1688115I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2.127,38</t>
+          <t>18.752,84</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1712538</t>
+          <t>1691534</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2346,24 +2346,24 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1712538 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1691534 - HAGAP - 19-06-2026.pdf</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>3.568,05</t>
+          <t>20.334,45</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1715278</t>
+          <t>1694258</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2373,24 +2373,24 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1715278 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1694258 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2.654,77</t>
+          <t>127.751,38</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1715688</t>
+          <t>1695716</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2400,12 +2400,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1715688 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1695716 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>9.669,94</t>
+          <t>74.647,17</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2417,7 +2417,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1720914</t>
+          <t>1698056</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2427,12 +2427,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1720914 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1698056 - HAGAP - 22-06-2026.pdf</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>13.736,92</t>
+          <t>8.966,25</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2444,7 +2444,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1721887</t>
+          <t>1710735</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2454,24 +2454,24 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1721887 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1710735 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>15.229,27</t>
+          <t>9.153,35</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1722169</t>
+          <t>1711384</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2481,24 +2481,24 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1722169 - HAGAP - 19-06-2026.pdf</t>
+          <t>BMD PARCIAL - 1711384 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>38.238,91</t>
+          <t>2.127,38</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1712530</t>
+          <t>1712538</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2508,24 +2508,24 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>BMD PARCIAL -1712530-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1712538 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>5.393,72</t>
+          <t>3.568,05</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1713626I</t>
+          <t>1715278</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2535,24 +2535,24 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>BMD PARCIAL -1713626I-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1715278 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>5.318,80</t>
+          <t>2.654,77</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1713260</t>
+          <t>1715688</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2562,24 +2562,24 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>BMD PARCIAL 1713260 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1715688 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>8.854,04</t>
+          <t>9.669,94</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1563492</t>
+          <t>1720914</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2589,24 +2589,24 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>BMD PARCIAL CIANORTE - 1563492 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1720914 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>80.240,76</t>
+          <t>13.736,92</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1563492</t>
+          <t>1721887</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2616,24 +2616,24 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>BMD PARCIAL JUSSARA - 1563492 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1721887 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>64.923,56</t>
+          <t>15.229,27</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1667141</t>
+          <t>1722169</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2643,24 +2643,24 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1667141-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1722169 - HAGAP - 19-06-2026.pdf</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>509,47</t>
+          <t>38.238,91</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1694841</t>
+          <t>1722779</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2670,24 +2670,24 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1694841-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1722779 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>4.476,57</t>
+          <t>14.090,54</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1708877I</t>
+          <t>1712530</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2697,24 +2697,24 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1708877I-HAGAP.pdf</t>
+          <t>BMD PARCIAL -1712530-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2.132,72</t>
+          <t>5.393,72</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1709486</t>
+          <t>1713626I</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2724,24 +2724,24 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1709486-HAGAP.pdf</t>
+          <t>BMD PARCIAL -1713626I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>4.402,38</t>
+          <t>5.318,80</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1711775</t>
+          <t>1713260</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2751,24 +2751,24 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1711775-HAGAP.pdf</t>
+          <t>BMD PARCIAL 1713260 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>1.928,86</t>
+          <t>8.854,04</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1713226</t>
+          <t>1563492</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2778,24 +2778,24 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1713226-HAGAP.pdf</t>
+          <t>BMD PARCIAL CIANORTE - 1563492 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>3.049,11</t>
+          <t>80.240,76</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1713656</t>
+          <t>1563492</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2805,24 +2805,24 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1713656-HAGAP.pdf</t>
+          <t>BMD PARCIAL JUSSARA - 1563492 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>4.315,58</t>
+          <t>64.923,56</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1714342</t>
+          <t>1667141</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2832,24 +2832,24 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1714342-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1667141-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>1.949,56</t>
+          <t>509,47</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1714699</t>
+          <t>1694841</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1714699-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1694841-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>18.624,62</t>
+          <t>4.476,57</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -2876,7 +2876,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1715201</t>
+          <t>1704877</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2886,24 +2886,24 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1715201-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1704877-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>6.987,28</t>
+          <t>158.642,45</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1715668</t>
+          <t>1708877I</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2913,24 +2913,24 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1715668-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1708877I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2.070,47</t>
+          <t>2.132,72</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1715955I</t>
+          <t>1709486</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2940,24 +2940,24 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1715955I-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1709486-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2.970,68</t>
+          <t>4.402,38</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1717168</t>
+          <t>1711507</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2967,24 +2967,24 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1717168-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1711507-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2.528,74</t>
+          <t>14.415,50</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1717332</t>
+          <t>1711775</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2994,24 +2994,24 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1717332-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1711775-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2.320,28</t>
+          <t>1.928,86</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1718442</t>
+          <t>1713226</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3021,24 +3021,24 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1718442-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1713226-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>3.160,96</t>
+          <t>3.049,11</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1718555I</t>
+          <t>1713656</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3048,24 +3048,24 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1718555I-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1713656-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2.781,60</t>
+          <t>4.315,58</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1721869</t>
+          <t>1714342</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3075,24 +3075,24 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1721869-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1714342-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>807,18</t>
+          <t>1.949,56</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1725260</t>
+          <t>1714699</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3102,24 +3102,24 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1725260-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1714699-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>4.716,47</t>
+          <t>18.624,62</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1713221</t>
+          <t>1715201</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3129,24 +3129,24 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>BMD parcial - 1713221 - HAGAP.pdf</t>
+          <t>BMD PARCIAL-1715201-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>18.794,09</t>
+          <t>6.987,28</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1667141</t>
+          <t>1715668</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>BMD-1667141-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1715668-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>152,42</t>
+          <t>2.070,47</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1675389</t>
+          <t>1715955I</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3183,24 +3183,24 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>BMD-1675389-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1715955I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>389,52</t>
+          <t>2.970,68</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1703223</t>
+          <t>1717168</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3210,24 +3210,24 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>BMD-1703223-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1717168-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>1.471,15</t>
+          <t>2.528,74</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1708066</t>
+          <t>1717332</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3237,24 +3237,24 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>BMD-1708066-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1717332-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>3.419,06</t>
+          <t>2.320,28</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1712547</t>
+          <t>1718442</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3264,24 +3264,24 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>BMD-1712547-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1718442-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>117,63</t>
+          <t>3.160,96</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1712766</t>
+          <t>1718555I</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3291,24 +3291,24 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>BMD-1712766-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1718555I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>705,45</t>
+          <t>2.781,60</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1713044I</t>
+          <t>1721869</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3318,24 +3318,24 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>BMD-1713044II-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1721869-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>1.528,53</t>
+          <t>807,18</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1713226</t>
+          <t>1725260</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3345,24 +3345,24 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>BMD-1713226-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1725260-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>237,93</t>
+          <t>4.716,47</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1714909</t>
+          <t>1713221</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>BMD-1714909-HAGAP.pdf</t>
+          <t>BMD parcial - 1713221 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>107,93</t>
+          <t>18.794,09</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -3389,7 +3389,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1715127</t>
+          <t>1667141</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3399,24 +3399,24 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>BMD-1715127-HAGAP.pdf</t>
+          <t>BMD-1667141-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>128,31</t>
+          <t>152,42</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1715131</t>
+          <t>1675389</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3426,24 +3426,24 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>BMD-1715131-HAGAP.pdf</t>
+          <t>BMD-1675389-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2.220,22</t>
+          <t>389,52</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1715257I</t>
+          <t>1703223</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3453,24 +3453,24 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>BMD-1715257I-HAGAP.pdf</t>
+          <t>BMD-1703223-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>6.765,65</t>
+          <t>1.471,15</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1715668</t>
+          <t>1708066</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3480,24 +3480,24 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>BMD-1715668-HAGAP.pdf</t>
+          <t>BMD-1708066-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>249,06</t>
+          <t>3.419,06</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1715816C</t>
+          <t>1712547</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3507,24 +3507,24 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>BMD-1715816C-HAGAP  PARCIAL.pdf</t>
+          <t>BMD-1712547-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>30,22</t>
+          <t>117,63</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1715816I</t>
+          <t>1712766</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3534,24 +3534,24 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>BMD-1715816I-HAGAP  PARCIAL.pdf</t>
+          <t>BMD-1712766-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>3.168,40</t>
+          <t>705,45</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1715899</t>
+          <t>1713044I</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3561,24 +3561,24 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>BMD-1715899-HAGAP  PARCIAL.pdf</t>
+          <t>BMD-1713044II-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>3.389,65</t>
+          <t>1.528,53</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1717166</t>
+          <t>1713226</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3588,24 +3588,24 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>BMD-1717166-HAGAP  PARCIAL.pdf</t>
+          <t>BMD-1713226-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>22.116,83</t>
+          <t>237,93</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1718442</t>
+          <t>1714909</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3615,24 +3615,24 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>BMD-1718442-HAGAP.pdf</t>
+          <t>BMD-1714909-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>45,19</t>
+          <t>107,93</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1718561</t>
+          <t>1715127</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3642,24 +3642,24 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>BMD-1718561-HAGAP PARCIAL.pdf</t>
+          <t>BMD-1715127-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>13.683,99</t>
+          <t>128,31</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1719070</t>
+          <t>1715131</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3669,24 +3669,24 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>BMD-1719070-HAGAP.pdf</t>
+          <t>BMD-1715131-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>333,14</t>
+          <t>2.220,22</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1719213</t>
+          <t>1715257I</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3696,12 +3696,12 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>BMD-1719213-HAGAP  PARCIAL.pdf</t>
+          <t>BMD-1715257I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>5.951,32</t>
+          <t>6.765,65</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -3713,7 +3713,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1719214</t>
+          <t>1715668</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3723,24 +3723,24 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>BMD-1719214-HAGAP  PARCIAL.pdf</t>
+          <t>BMD-1715668-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>6.124,60</t>
+          <t>249,06</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1719881</t>
+          <t>1715816C</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3750,24 +3750,24 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>BMD-1719881-HAGAP.pdf</t>
+          <t>BMD-1715816C-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>3.239,73</t>
+          <t>30,22</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1719881H</t>
+          <t>1715816I</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3777,24 +3777,24 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>BMD-1719881HAGAP.pdf</t>
+          <t>BMD-1715816I-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>38.258,42</t>
+          <t>3.168,40</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1720116</t>
+          <t>1715899</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3804,24 +3804,24 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>BMD-1720116-HAGAP.pdf</t>
+          <t>BMD-1715899-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>168,95</t>
+          <t>3.389,65</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1721631</t>
+          <t>1717166</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3831,24 +3831,24 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>BMD-1721631-HAGAP  PARCIAL.pdf</t>
+          <t>BMD-1717166-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>12.649,43</t>
+          <t>22.116,83</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1721631C</t>
+          <t>1718442</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3858,24 +3858,24 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>BMD-1721631C-HAGAP  PARCIAL.pdf</t>
+          <t>BMD-1718442-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>100,65</t>
+          <t>45,19</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>1721886</t>
+          <t>1718561</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3885,24 +3885,24 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>BMD-1721886 - HAGAP PARCIAL.pdf</t>
+          <t>BMD-1718561-HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>14.551,70</t>
+          <t>13.683,99</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1713044C</t>
+          <t>1719070</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3912,24 +3912,24 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>BMD.-1713044C.-HAGAP.pdf</t>
+          <t>BMD-1719070-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>21,11</t>
+          <t>333,14</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1715327</t>
+          <t>1719213</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3939,105 +3939,105 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>BMD.1715327-HAGAP.pdf</t>
+          <t>BMD-1719213-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>5.951,32</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>1708877</t>
+          <t>1719214</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>BMDFINAL-1708877-HAGAP.pdf</t>
+          <t>BMD-1719214-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>3,54</t>
+          <t>6.124,60</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1712957</t>
+          <t>1719881</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>BMDFINAL-1712957-HAGAP.pdf</t>
+          <t>BMD-1719881-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>45,19</t>
+          <t>3.239,73</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1717332</t>
+          <t>1719881H</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>BMDFINAL-1717332-HAGAP.pdf</t>
+          <t>BMD-1719881HAGAP.pdf</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>38.258,42</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1703223</t>
+          <t>1720116</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4047,24 +4047,24 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1703223-HAGAP.pdf</t>
+          <t>BMD-1720116-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>18.169,34</t>
+          <t>168,95</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1712547</t>
+          <t>1721631</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4074,24 +4074,24 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1712547-HAGAP.pdf</t>
+          <t>BMD-1721631-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>6.951,82</t>
+          <t>12.649,43</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1712957</t>
+          <t>1721631C</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1712957-HAGAP.pdf</t>
+          <t>BMD-1721631C-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2.177,64</t>
+          <t>100,65</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1713262</t>
+          <t>1721886</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4128,24 +4128,24 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1713262-HAGAP.pdf</t>
+          <t>BMD-1721886 - HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2.619,71</t>
+          <t>14.551,70</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1714909</t>
+          <t>1713044C</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4155,24 +4155,24 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1714909-HAGAP.pdf</t>
+          <t>BMD.-1713044C.-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>954,64</t>
+          <t>21,11</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1715127</t>
+          <t>1715327</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -4182,105 +4182,105 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1715127-HAGAP.pdf</t>
+          <t>BMD.1715327-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>4.418,94</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1715327</t>
+          <t>1708877</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1715327-HAGAP.pdf</t>
+          <t>BMDFINAL-1708877-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>5.417,39</t>
+          <t>3,54</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1719070</t>
+          <t>1712957</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1719070-HAGAP.pdf</t>
+          <t>BMDFINAL-1712957-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2.744,71</t>
+          <t>45,19</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1719135</t>
+          <t>1717332</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1719135-HAGAP.pdf</t>
+          <t>BMDFINAL-1717332-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>913,84</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1720116</t>
+          <t>1703223</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4290,24 +4290,24 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1720116-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1703223-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>1.675,57</t>
+          <t>18.169,34</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1724491</t>
+          <t>1712547</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4317,147 +4317,147 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1724491-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1712547-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>14.377,51</t>
+          <t>6.951,82</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>1712766</t>
+          <t>1712957</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>FF0-1712766-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1712957-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.177,64</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1719135</t>
+          <t>1713262</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>FFO  -1719135-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1713262-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.619,71</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1688115C</t>
+          <t>1714909</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>FFO - 1688115C - HAGAP.pdf</t>
+          <t>BMDPARCIAL-1714909-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>954,64</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1688115I</t>
+          <t>1715127</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>FFO - 1688115I - HAGAP.pdf</t>
+          <t>BMDPARCIAL-1715127-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>4.418,94</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>1702776C</t>
+          <t>1715327</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>FFO - 1702776C - HAGAP.pdf</t>
+          <t>BMDPARCIAL-1715327-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>5.417,39</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -4469,49 +4469,49 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>1702776I</t>
+          <t>1719070</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>FFO - 1702776I - HAGAP.pdf</t>
+          <t>BMDPARCIAL-1719070-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.744,71</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>1704867</t>
+          <t>1719135</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>FFO - 1704867 - ASP.pdf</t>
+          <t>BMDPARCIAL-1719135-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>913,84</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -4523,61 +4523,61 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1711384</t>
+          <t>1720116</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>FFO - 1711384 - HAGAP.pdf</t>
+          <t>BMDPARCIAL-1720116-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>1.675,57</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>1712538</t>
+          <t>1724491</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>FFO - 1712538 - HAGAP.pdf</t>
+          <t>BMDPARCIAL-1724491-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>14.377,51</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>1713240</t>
+          <t>1712766</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4587,7 +4587,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>FFO - 1713240 - HAGAP - 20-05-2026.pdf</t>
+          <t>FF0-1712766-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -4597,14 +4597,14 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>1715878</t>
+          <t>1719135</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>FFO - 1715878 - HAGAP - 20-05-2026.pdf</t>
+          <t>FFO  -1719135-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -4624,14 +4624,14 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1641139I</t>
+          <t>1688115C</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>FFO 1641139I HAGAP.pdf</t>
+          <t>FFO - 1688115C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -4651,14 +4651,14 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>1713679</t>
+          <t>1688115I</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>FFO 1713679 HAGAP.pdf</t>
+          <t>FFO - 1688115I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -4678,14 +4678,14 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1714729</t>
+          <t>1702776C</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>FFO 1714729 HAGAP.pdf</t>
+          <t>FFO - 1702776C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -4705,14 +4705,14 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>1718803</t>
+          <t>1702776I</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4722,7 +4722,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>FFO 1718803 HAGAP.pdf</t>
+          <t>FFO - 1702776I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -4732,14 +4732,14 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>1720721</t>
+          <t>1704867</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>FFO 1720721 HAGAP.pdf</t>
+          <t>FFO - 1704867 - ASP.pdf</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -4759,14 +4759,14 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>1667141</t>
+          <t>1711384</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4776,7 +4776,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>FFO-1667141-HAGAP.pdf</t>
+          <t>FFO - 1711384 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -4786,14 +4786,14 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>1675389</t>
+          <t>1712538</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>FFO-1675389-HAGAP.pdf</t>
+          <t>FFO - 1712538 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -4813,14 +4813,14 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>1703223</t>
+          <t>1713240</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>FFO-1703223-HAGAP.pdf</t>
+          <t>FFO - 1713240 - HAGAP - 20-05-2026.pdf</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -4840,14 +4840,14 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>1708877</t>
+          <t>1715878</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>FFO-1708877-HAGAP.pdf</t>
+          <t>FFO - 1715878 - HAGAP - 20-05-2026.pdf</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -4867,14 +4867,14 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>1710116</t>
+          <t>1641139I</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>FFO-1710116-HAGAP.pdf</t>
+          <t>FFO 1641139I HAGAP.pdf</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -4894,14 +4894,14 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1712531</t>
+          <t>1713679</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>FFO-1712531-HAGAP.pdf</t>
+          <t>FFO 1713679 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -4921,14 +4921,14 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1712547</t>
+          <t>1714729</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>FFO-1712547-HAGAP.pdf</t>
+          <t>FFO 1714729 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -4948,14 +4948,14 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>1713044C</t>
+          <t>1718803</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>FFO-1713044C.-HAGAP.pdf</t>
+          <t>FFO 1718803 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -4975,14 +4975,14 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>1713044I</t>
+          <t>1720721</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -4992,7 +4992,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>FFO-1713044II-HAGAP.pdf</t>
+          <t>FFO 1720721 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -5002,14 +5002,14 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>1713226</t>
+          <t>1667141</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>FFO-1713226-HAGAP.pdf</t>
+          <t>FFO-1667141-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -5029,14 +5029,14 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>1713262</t>
+          <t>1675389</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>FFO-1713262-HAGAP.pdf</t>
+          <t>FFO-1675389-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -5056,14 +5056,14 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>1714909</t>
+          <t>1703223</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -5073,7 +5073,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>FFO-1714909-HAGAP.pdf</t>
+          <t>FFO-1703223-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -5083,14 +5083,14 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>1715127</t>
+          <t>1708877</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5100,7 +5100,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>FFO-1715127-HAGAP.pdf</t>
+          <t>FFO-1708877-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -5110,14 +5110,14 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>1715257I</t>
+          <t>1710116</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>FFO-1715257I-HAGAP.pdf</t>
+          <t>FFO-1710116-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -5137,14 +5137,14 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1715327</t>
+          <t>1712531</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5154,24 +5154,24 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>FFO-1715327-HAGAP.pdf</t>
+          <t>FFO-1712531-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>65,98</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>1715668</t>
+          <t>1712547</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>FFO-1715668-HAGAP.pdf</t>
+          <t>FFO-1712547-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -5191,14 +5191,14 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>1717332</t>
+          <t>1713044C</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -5208,24 +5208,24 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>FFO-1717332-HAGAP.pdf</t>
+          <t>FFO-1713044C.-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>176,23</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>1719070</t>
+          <t>1713044I</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -5235,7 +5235,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>FFO-1719070-HAGAP.pdf</t>
+          <t>FFO-1713044II-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -5245,14 +5245,14 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>1719881</t>
+          <t>1713226</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -5262,7 +5262,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>FFO-1719881-HAGAP.pdf</t>
+          <t>FFO-1713226-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -5272,14 +5272,14 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>1708066</t>
+          <t>1713262</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -5289,7 +5289,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>FFO.-1708066-HAGAP.pdf</t>
+          <t>FFO-1713262-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -5299,14 +5299,14 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>1712957</t>
+          <t>1714909</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>FFO.-1712957-HAGAP.pdf</t>
+          <t>FFO-1714909-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -5326,14 +5326,14 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>1718442</t>
+          <t>1715127</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>FFO´1718442-HAGAP.pdf</t>
+          <t>FFO-1715127-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -5353,32 +5353,275 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
+          <t>1715257I</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>FFO-1715257I-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>1715327</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>FFO-1715327-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>65,98</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>1715668</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>FFO-1715668-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>1717332</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>FFO-1717332-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>176,23</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>1719070</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>FFO-1719070-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>1719881</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>FFO-1719881-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>1708066</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>FFO.-1708066-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>1712957</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>FFO.-1712957-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>1718442</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>FFO´1718442-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
           <t>1703223</t>
         </is>
       </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>BMD</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
         <is>
           <t>MULTA-1703223-HAGAP.pdf</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr">
+      <c r="D193" t="inlineStr">
         <is>
           <t>0,00</t>
         </is>
       </c>
-      <c r="E184" t="inlineStr"/>
+      <c r="E193" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/medicoes.xlsx
+++ b/medicoes.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="503">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="959" uniqueCount="503">
   <si>
     <t>Projeto</t>
   </si>
@@ -4165,8 +4165,8 @@
       <c r="D135" t="s">
         <v>414</v>
       </c>
-      <c r="E135" t="s">
-        <v>18</v>
+      <c r="E135" s="1">
+        <v>46181</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">

--- a/medicoes.xlsx
+++ b/medicoes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E196"/>
+  <dimension ref="A1:E233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -662,7 +662,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1663556</t>
+          <t>1659019</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -672,24 +672,24 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1663556 - BMD - HAGAP.pdf</t>
+          <t>1659019 BMD.pdf</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.470,38</t>
+          <t>9.678,68</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1663556</t>
+          <t>1659019</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1663556 - FFO - HAGAP.pdf</t>
+          <t>1659019 FFO.pdf</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -709,95 +709,95 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1667593</t>
+          <t>1663556</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1667593 - FFO - asp.pdf</t>
+          <t>1663556 - BMD - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.470,38</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1675032C</t>
+          <t>1663556</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1675032C - BMD 01.pdf</t>
+          <t>1663556 - FFO - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>23,99</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1675032I</t>
+          <t>1667593</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1675032I - BMD 01.pdf</t>
+          <t>1667593 - FFO - asp.pdf</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>222.884,15</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1676605</t>
+          <t>1675032C</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -807,24 +807,24 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1676605 - BMD PARCIAL - HAGAP.pdf</t>
+          <t>1675032C - BMD 01.pdf</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>39.199,95</t>
+          <t>23,99</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1676605</t>
+          <t>1675032I</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -834,24 +834,24 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1676605 - BMD PARCIAL - HAGAP1.pdf</t>
+          <t>1675032I - BMD 01.pdf</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>39.199,95</t>
+          <t>222.884,15</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1683861I</t>
+          <t>1676605</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -861,24 +861,24 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1683861i BMD.pdf</t>
+          <t>1676605 - BMD PARCIAL - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>20.224,44</t>
+          <t>39.199,95</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1704476</t>
+          <t>1676605</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -888,51 +888,51 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1704476 BMD.pdf</t>
+          <t>1676605 - BMD PARCIAL - HAGAP1.pdf</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>111,28</t>
+          <t>39.199,95</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1704476</t>
+          <t>1683861I</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1704476 FFO.pdf</t>
+          <t>1683861i BMD.pdf</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>20.224,44</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1704891</t>
+          <t>1694202</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -942,51 +942,51 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1704891 - BMD PARC - HAGAP.pdf</t>
+          <t>1694202 BMD.pdf</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>100.528,77</t>
+          <t>4.490,43</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1704920</t>
+          <t>1694202</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1704920 BMD PARCIAL.pdf</t>
+          <t>1694202 FFO.pdf</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>58.137,43</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1704968</t>
+          <t>1698781</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -996,78 +996,78 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1704968 - BMD - HAGAP.pdf</t>
+          <t>1698781 BMD.pdf</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2.808,15</t>
+          <t>914,56</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1704968</t>
+          <t>1700852</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1704968 - FFO - HAGAP.pdf</t>
+          <t>1700852 BMD.pdf</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>12.509,24</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1707817</t>
+          <t>1700852</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1707817 BMD PARCIAL.pdf</t>
+          <t>1700852 FFO.pdf</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>138.680,75</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1710937</t>
+          <t>1704476</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1077,51 +1077,51 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1710937 - bmd - hagap.pdf</t>
+          <t>1704476 - BMD Parcial Peabiru.pdf</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>4.234,81</t>
+          <t>23.713,90</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1710937</t>
+          <t>1704476</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1710937 - ffo - hagap.pdf</t>
+          <t>1704476 - MD PARCIAL - CAMPO MOURÃO.pdf</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>7.938,74</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1724341</t>
+          <t>1704476</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1131,51 +1131,51 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1724341 - BMD PARC - ASP.pdf</t>
+          <t>1704476 BMD.pdf</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>40.758,00</t>
+          <t>111,28</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1510407</t>
+          <t>1704476</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>BMD - 1510407 - HAGAP - 26-05-2026.pdf</t>
+          <t>1704476 FFO.pdf</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>28.642,47</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1658892</t>
+          <t>1704891</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1185,24 +1185,24 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>BMD - 1658892 - HAGAP - 22-06-2026.pdf</t>
+          <t>1704891 - BMD PARC - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>38.435,91</t>
+          <t>100.528,77</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1688115C</t>
+          <t>1704920</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1212,24 +1212,24 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>BMD - 1688115C - HAGAP.pdf</t>
+          <t>1704920 BMD PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>6,65</t>
+          <t>58.137,43</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1688115I</t>
+          <t>1704964</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1239,51 +1239,51 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>BMD - 1688115I - HAGAP.pdf</t>
+          <t>1704964 BMD.pdf</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2.670,64</t>
+          <t>2.692,23</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1704867</t>
+          <t>1704964</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>BMD - 1704867 - ASP.pdf</t>
+          <t>1704964 FFO.pdf</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>23.915,48</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1711384</t>
+          <t>1704968</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1293,51 +1293,51 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>BMD - 1711384 - HAGAP.pdf</t>
+          <t>1704968 - BMD - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>122,95</t>
+          <t>2.808,15</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1712538</t>
+          <t>1704968</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>BMD - 1712538 - HAGAP.pdf</t>
+          <t>1704968 - FFO - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>387,36</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1713240</t>
+          <t>1707817</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1347,24 +1347,24 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>BMD - 1713240 - HAGAP - 20-05-2026.pdf</t>
+          <t>1707817 BMD PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>5.108,11</t>
+          <t>138.680,75</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1713933</t>
+          <t>1710937</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1374,12 +1374,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>BMD - 1713933 - HAGAP - 20-05-2026.pdf</t>
+          <t>1710937 - bmd - hagap.pdf</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>5.530,92</t>
+          <t>4.234,81</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1391,34 +1391,34 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1715878</t>
+          <t>1710937</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>BMD - 1715878 - HAGAP - 20-05-2026.pdf</t>
+          <t>1710937 - ffo - hagap.pdf</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.786,71</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1718435</t>
+          <t>1724341</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1428,24 +1428,24 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>BMD - 1718435 - HAGAP - 20-05-2026.pdf</t>
+          <t>1724341 - BMD PARC - ASP.pdf</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>17.153,90</t>
+          <t>40.758,00</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1718783</t>
+          <t>1510407</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1455,24 +1455,24 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>BMD - 1718783 - HAGAP.pdf</t>
+          <t>BMD - 1510407 - HAGAP - 26-05-2026.pdf</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>16.983,02</t>
+          <t>28.642,47</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1725738C</t>
+          <t>1658892</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1482,24 +1482,24 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>BMD - 1725738C - HAGAP.pdf</t>
+          <t>BMD - 1658892 - HAGAP - 22-06-2026.pdf</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>140,91</t>
+          <t>38.435,91</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1725738I</t>
+          <t>1688115C</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1509,24 +1509,24 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>BMD - 1725738I - HAGAP.pdf</t>
+          <t>BMD - 1688115C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>15.544,67</t>
+          <t>6,65</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1520612</t>
+          <t>1688115I</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1536,24 +1536,24 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>BMD 1520612 HAGAP.pdf</t>
+          <t>BMD - 1688115I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>53.357,33</t>
+          <t>2.670,64</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1520615</t>
+          <t>1698047</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1563,24 +1563,24 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>BMD 1520615 HAGAP.pdf</t>
+          <t>BMD - 1698047 - HAGAP 30-04-2026.pdf</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>22.840,59</t>
+          <t>2.449,89</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1671139I</t>
+          <t>1704867</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1590,12 +1590,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>BMD 1671139I HAGAP.pdf</t>
+          <t>BMD - 1704867 - ASP.pdf</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>6.138,54</t>
+          <t>23.915,48</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1607,7 +1607,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1692636</t>
+          <t>1709995</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1617,24 +1617,24 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>BMD 1692636 ASP.pdf</t>
+          <t>BMD - 1709995 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>19.387,05</t>
+          <t>2.410,16</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1699516</t>
+          <t>1711384</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1644,24 +1644,24 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>BMD 1699516 HAGAP PARCIAL.pdf</t>
+          <t>BMD - 1711384 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>3.388,62</t>
+          <t>122,95</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1704525</t>
+          <t>1712538</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1671,24 +1671,24 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>BMD 1704525 HAGAP PARCIAL.pdf</t>
+          <t>BMD - 1712538 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>15.365,48</t>
+          <t>387,36</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1704891</t>
+          <t>1713240</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1698,24 +1698,24 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>BMD 1704891 HAGAP PARCIAL.pdf</t>
+          <t>BMD - 1713240 - HAGAP - 20-05-2026.pdf</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>41.477,99</t>
+          <t>5.108,11</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1705074</t>
+          <t>1713933</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1725,24 +1725,24 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>BMD 1705074 HAGAP.pdf</t>
+          <t>BMD - 1713933 - HAGAP - 20-05-2026.pdf</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>150.312,87</t>
+          <t>5.530,92</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1710329</t>
+          <t>1715878</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1752,24 +1752,24 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>BMD 1710329 HAGAP PARCIAL.pdf</t>
+          <t>BMD - 1715878 - HAGAP - 20-05-2026.pdf</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>24.209,42</t>
+          <t>1.786,71</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1710937</t>
+          <t>1718435</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1779,12 +1779,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>BMD 1710937 HAGAP PARCIAL.pdf</t>
+          <t>BMD - 1718435 - HAGAP - 20-05-2026.pdf</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>17.153,90</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1796,7 +1796,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1711525</t>
+          <t>1718783</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1806,24 +1806,24 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>BMD 1711525 HAGAP PARCIAL.pdf</t>
+          <t>BMD - 1718783 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1.998,42</t>
+          <t>16.983,02</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1712624</t>
+          <t>1722169</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1833,24 +1833,24 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>BMD 1712624 HAGAP.pdf</t>
+          <t>BMD - 1722169 - HAGAP - 25-06-2026.pdf</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>3.073,90</t>
+          <t>1.225,38</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1713223</t>
+          <t>1725738C</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1860,24 +1860,24 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>BMD 1713223 HAGAP PARCIAL.pdf</t>
+          <t>BMD - 1725738C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>9.773,21</t>
+          <t>140,91</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1713679</t>
+          <t>1725738I</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1887,24 +1887,24 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>BMD 1713679 HAGAP.pdf</t>
+          <t>BMD - 1725738I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>3.574,44</t>
+          <t>15.544,67</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1713719</t>
+          <t>1520612</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1914,24 +1914,24 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>BMD 1713719 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1520612 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>3.385,92</t>
+          <t>53.357,33</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1714729</t>
+          <t>1520615</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1941,24 +1941,24 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>BMD 1714729 HAGAP.pdf</t>
+          <t>BMD 1520615 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>6.722,61</t>
+          <t>22.840,59</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1715920</t>
+          <t>1660062C</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1968,24 +1968,24 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>BMD 1715920 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1660062C HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>1.031,94</t>
+          <t>100,65</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1718803</t>
+          <t>1660062I</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1995,24 +1995,24 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>BMD 1718803 HAGAP.pdf</t>
+          <t>BMD 1660062I HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>3.825,18</t>
+          <t>11.953,89</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1719097</t>
+          <t>1671139I</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2022,24 +2022,24 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>BMD 1719097 HAGAP.pdf</t>
+          <t>BMD 1671139I HAGAP.pdf</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>7.450,28</t>
+          <t>6.138,54</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1719155</t>
+          <t>1692636</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2049,24 +2049,24 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>BMD 1719155 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1692636 ASP.pdf</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2.223,15</t>
+          <t>19.387,05</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1720721</t>
+          <t>1699516</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2076,24 +2076,24 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>BMD 1720721 HAGAP.pdf</t>
+          <t>BMD 1699516 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2.015,45</t>
+          <t>3.388,62</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1720920</t>
+          <t>1704525</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2103,24 +2103,24 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>BMD 1720920 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1704525 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>555,60</t>
+          <t>15.365,48</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1724356</t>
+          <t>1704891</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2130,24 +2130,24 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>BMD 1724356 HAGAP.pdf</t>
+          <t>BMD 1704891 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>7.614,80</t>
+          <t>41.477,99</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1728163</t>
+          <t>1705074</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2157,132 +2157,132 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>BMD 1728163 HAGAP.pdf</t>
+          <t>BMD 1705074 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>7.914,69</t>
+          <t>150.312,87</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1702776C</t>
+          <t>1708906</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>BMD FINAL - 1702776C - HAGAP.pdf</t>
+          <t>BMD 1708906  30-04-2026 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>7.584,06</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1702776I</t>
+          <t>1710329</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>BMD FINAL - 1702776I - HAGAP.pdf</t>
+          <t>BMD 1710329 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>18.098,87</t>
+          <t>24.209,42</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1713262</t>
+          <t>1710937</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>BMD FINAL-1713262-HAGAP.pdf</t>
+          <t>BMD 1710937 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>55,90</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1719135</t>
+          <t>1710975</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>BMD FINAL-1719135-HAGAP.pdf</t>
+          <t>BMD 1710975 HAGAP FF.pdf</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>47,08</t>
+          <t>913,41</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1712550</t>
+          <t>1711525</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2292,24 +2292,24 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>BMD PARCAIL-1712550-HAGAP.pdf</t>
+          <t>BMD 1711525 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>4.585,98</t>
+          <t>1.998,42</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1677314</t>
+          <t>1712533</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2319,24 +2319,24 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1677314 - HAGAP.pdf</t>
+          <t>BMD 1712533 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>46.760,40</t>
+          <t>2.553,46</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1677316</t>
+          <t>1712624</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2346,12 +2346,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1677316 HAGAP.pdf</t>
+          <t>BMD 1712624 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>51.623,62</t>
+          <t>3.073,90</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2363,7 +2363,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1688115C</t>
+          <t>1713223</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2373,24 +2373,24 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1688115C - HAGAP.pdf</t>
+          <t>BMD 1713223 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>6,36</t>
+          <t>9.773,21</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1688115I</t>
+          <t>1713679</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2400,24 +2400,24 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1688115I - HAGAP.pdf</t>
+          <t>BMD 1713679 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>18.752,84</t>
+          <t>3.574,44</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1691534</t>
+          <t>1713719</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2427,24 +2427,24 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1691534 - HAGAP - 19-06-2026.pdf</t>
+          <t>BMD 1713719 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>20.334,45</t>
+          <t>3.385,92</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1694258</t>
+          <t>1714364</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2454,24 +2454,24 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1694258 - HAGAP.pdf</t>
+          <t>BMD 1714364 HAGAP FF.pdf</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>127.751,38</t>
+          <t>54,64</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1695716</t>
+          <t>1714729</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2481,24 +2481,24 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1695716 - HAGAP.pdf</t>
+          <t>BMD 1714729 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>74.647,17</t>
+          <t>6.722,61</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1698056</t>
+          <t>1715920</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2508,24 +2508,24 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1698056 - HAGAP - 22-06-2026.pdf</t>
+          <t>BMD 1715920 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>8.966,25</t>
+          <t>1.031,94</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1710735</t>
+          <t>1718803</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2535,24 +2535,24 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1710735 HAGAP.pdf</t>
+          <t>BMD 1718803 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>9.153,35</t>
+          <t>3.825,18</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1711384</t>
+          <t>1719097</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2562,24 +2562,24 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1711384 - HAGAP.pdf</t>
+          <t>BMD 1719097 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2.127,38</t>
+          <t>7.450,28</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1712538</t>
+          <t>1719155</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2589,24 +2589,24 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1712538 - HAGAP.pdf</t>
+          <t>BMD 1719155 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>3.568,05</t>
+          <t>2.223,15</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1715278</t>
+          <t>1720721</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1715278 - HAGAP.pdf</t>
+          <t>BMD 1720721 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2.654,77</t>
+          <t>2.015,45</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -2633,7 +2633,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1715688</t>
+          <t>1720920</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2643,24 +2643,24 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1715688 - HAGAP.pdf</t>
+          <t>BMD 1720920 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>9.669,94</t>
+          <t>555,60</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1720914</t>
+          <t>1724356</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2670,24 +2670,24 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1720914 - HAGAP.pdf</t>
+          <t>BMD 1724356 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>13.736,92</t>
+          <t>7.614,80</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1721887</t>
+          <t>1728163</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2697,24 +2697,24 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1721887 - HAGAP.pdf</t>
+          <t>BMD 1728163 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>15.229,27</t>
+          <t>7.914,69</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1722169</t>
+          <t>1712533</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2724,132 +2724,132 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1722169 - HAGAP - 19-06-2026.pdf</t>
+          <t>BMD FF 1712533 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>38.238,91</t>
+          <t>127,40</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1722779</t>
+          <t>1702776C</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1722779 - HAGAP.pdf</t>
+          <t>BMD FINAL - 1702776C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>14.090,54</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1712530</t>
+          <t>1702776I</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>BMD PARCIAL -1712530-HAGAP.pdf</t>
+          <t>BMD FINAL - 1702776I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>5.393,72</t>
+          <t>18.098,87</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1713626I</t>
+          <t>1713262</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>BMD PARCIAL -1713626I-HAGAP.pdf</t>
+          <t>BMD FINAL-1713262-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>5.318,80</t>
+          <t>55,90</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1713260</t>
+          <t>1719135</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>BMD PARCIAL 1713260 - HAGAP.pdf</t>
+          <t>BMD FINAL-1719135-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>8.854,04</t>
+          <t>47,08</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1563492</t>
+          <t>1712550</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2859,24 +2859,24 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>BMD PARCIAL CIANORTE - 1563492 - HAGAP.pdf</t>
+          <t>BMD PARCAIL-1712550-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>80.240,76</t>
+          <t>4.585,98</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1563492</t>
+          <t>1677314</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2886,24 +2886,24 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>BMD PARCIAL JUSSARA - 1563492 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1677314 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>64.923,56</t>
+          <t>46.760,40</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1667141</t>
+          <t>1677316</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2913,24 +2913,24 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1667141-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1677316 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>509,47</t>
+          <t>51.623,62</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1694841</t>
+          <t>1688115C</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2940,24 +2940,24 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1694841-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1688115C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>4.476,57</t>
+          <t>6,36</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1704877</t>
+          <t>1688115I</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2967,24 +2967,24 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1704877-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1688115I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>158.642,45</t>
+          <t>18.752,84</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1708877I</t>
+          <t>1691534</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2994,24 +2994,24 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1708877I-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1691534 - HAGAP - 19-06-2026.pdf</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2.132,72</t>
+          <t>20.334,45</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1709486</t>
+          <t>1694258</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3021,24 +3021,24 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1709486-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1694258 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>4.402,38</t>
+          <t>127.751,38</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1711507</t>
+          <t>1695716</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3048,24 +3048,24 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1711507-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1695716 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>14.415,50</t>
+          <t>74.647,17</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1711775</t>
+          <t>1698056</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3075,24 +3075,24 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1711775-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1698056 - HAGAP - 22-06-2026.pdf</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>1.928,86</t>
+          <t>8.966,25</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1713226</t>
+          <t>1710735</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3102,24 +3102,24 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1713226-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1710735 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>3.049,11</t>
+          <t>9.153,35</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1713656</t>
+          <t>1711384</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3129,24 +3129,24 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1713656-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1711384 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>4.315,58</t>
+          <t>2.127,38</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1714342</t>
+          <t>1712538</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1714342-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1712538 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>1.949,56</t>
+          <t>3.568,05</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1714699</t>
+          <t>1715278</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3183,24 +3183,24 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1714699-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1715278 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>18.624,62</t>
+          <t>2.654,77</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1715201</t>
+          <t>1715688</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3210,24 +3210,24 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1715201-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1715688 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>6.987,28</t>
+          <t>9.669,94</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1715668</t>
+          <t>1720914</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3237,24 +3237,24 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1715668-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1720914 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2.070,47</t>
+          <t>13.736,92</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1715955I</t>
+          <t>1721887</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3264,24 +3264,24 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1715955I-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1721887 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2.970,68</t>
+          <t>15.229,27</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1717168</t>
+          <t>1722169</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3291,24 +3291,24 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1717168-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1722169 - HAGAP - 19-06-2026.pdf</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2.528,74</t>
+          <t>38.238,91</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1717332</t>
+          <t>1722779</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3318,24 +3318,24 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1717332-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1722779 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2.320,28</t>
+          <t>14.090,54</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1718442</t>
+          <t>1712530</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3345,24 +3345,24 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1718442-HAGAP.pdf</t>
+          <t>BMD PARCIAL -1712530-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>3.160,96</t>
+          <t>5.393,72</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1718555I</t>
+          <t>1713626I</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3372,24 +3372,24 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1718555I-HAGAP.pdf</t>
+          <t>BMD PARCIAL -1713626I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2.781,60</t>
+          <t>5.318,80</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1721869</t>
+          <t>1713260</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3399,24 +3399,24 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1721869-HAGAP.pdf</t>
+          <t>BMD PARCIAL 1713260 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>807,18</t>
+          <t>8.854,04</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1725260</t>
+          <t>1563492</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3426,24 +3426,24 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1725260-HAGAP.pdf</t>
+          <t>BMD PARCIAL CIANORTE - 1563492 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>4.716,47</t>
+          <t>80.240,76</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1713221</t>
+          <t>1563492</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3453,17 +3453,17 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>BMD parcial - 1713221 - HAGAP.pdf</t>
+          <t>BMD PARCIAL JUSSARA - 1563492 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>18.794,09</t>
+          <t>64.923,56</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
@@ -3480,24 +3480,24 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>BMD-1667141-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1667141-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>152,42</t>
+          <t>509,47</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1675389</t>
+          <t>1694841</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3507,24 +3507,24 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>BMD-1675389-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1694841-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>389,52</t>
+          <t>4.476,57</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1703223</t>
+          <t>1704877</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3534,24 +3534,24 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>BMD-1703223-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1704877-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>1.471,15</t>
+          <t>158.642,45</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1708066</t>
+          <t>1708877I</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3561,24 +3561,24 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>BMD-1708066-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1708877I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>3.419,06</t>
+          <t>2.132,72</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1712547</t>
+          <t>1709486</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3588,24 +3588,24 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>BMD-1712547-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1709486-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>117,63</t>
+          <t>4.402,38</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1712766</t>
+          <t>1711507</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3615,24 +3615,24 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>BMD-1712766-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1711507-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>705,45</t>
+          <t>14.415,50</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1713044I</t>
+          <t>1711775</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3642,24 +3642,24 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>BMD-1713044II-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1711775-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>1.528,53</t>
+          <t>1.928,86</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1713226</t>
+          <t>1712531</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3669,24 +3669,24 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>BMD-1713226-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1712531-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>237,93</t>
+          <t>5.019,99</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1714909</t>
+          <t>1713226</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3696,24 +3696,24 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>BMD-1714909-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1713226-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>107,93</t>
+          <t>3.049,11</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1715127</t>
+          <t>1713656</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3723,24 +3723,24 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>BMD-1715127-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1713656-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>128,31</t>
+          <t>4.315,58</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1715131</t>
+          <t>1714342</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3750,24 +3750,24 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>BMD-1715131-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1714342-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2.220,22</t>
+          <t>1.949,56</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1715257I</t>
+          <t>1714699</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3777,24 +3777,24 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>BMD-1715257I-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1714699-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>6.765,65</t>
+          <t>18.624,62</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1715668</t>
+          <t>1715201</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3804,24 +3804,24 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>BMD-1715668-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1715201-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>249,06</t>
+          <t>6.987,28</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1715816C</t>
+          <t>1715668</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3831,24 +3831,24 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>BMD-1715816C-HAGAP  PARCIAL.pdf</t>
+          <t>BMD PARCIAL-1715668-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>30,22</t>
+          <t>2.070,47</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1715816I</t>
+          <t>1715955I</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3858,24 +3858,24 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>BMD-1715816I-HAGAP  PARCIAL.pdf</t>
+          <t>BMD PARCIAL-1715955I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>3.168,40</t>
+          <t>2.970,68</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>1715899</t>
+          <t>1717168</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3885,24 +3885,24 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>BMD-1715899-HAGAP  PARCIAL.pdf</t>
+          <t>BMD PARCIAL-1717168-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>3.389,65</t>
+          <t>2.528,74</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1717166</t>
+          <t>1717332</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3912,17 +3912,17 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>BMD-1717166-HAGAP  PARCIAL.pdf</t>
+          <t>BMD PARCIAL-1717332-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>22.116,83</t>
+          <t>2.320,28</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
@@ -3939,24 +3939,24 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>BMD-1718442-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1718442-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>45,19</t>
+          <t>3.160,96</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>1718561</t>
+          <t>1718555I</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3966,24 +3966,24 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>BMD-1718561-HAGAP PARCIAL.pdf</t>
+          <t>BMD PARCIAL-1718555I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>13.683,99</t>
+          <t>2.781,60</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1719070</t>
+          <t>1721869</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3993,24 +3993,24 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>BMD-1719070-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1721869-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>333,14</t>
+          <t>807,18</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1719213</t>
+          <t>1725260</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4020,24 +4020,24 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>BMD-1719213-HAGAP  PARCIAL.pdf</t>
+          <t>BMD PARCIAL-1725260-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>5.951,32</t>
+          <t>4.716,47</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1719214</t>
+          <t>1713221</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4047,24 +4047,24 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>BMD-1719214-HAGAP  PARCIAL.pdf</t>
+          <t>BMD parcial - 1713221 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>6.124,60</t>
+          <t>18.794,09</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1719881</t>
+          <t>1667141</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4074,24 +4074,24 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>BMD-1719881-HAGAP.pdf</t>
+          <t>BMD-1667141-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>3.239,73</t>
+          <t>152,42</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1719881H</t>
+          <t>1675389</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>BMD-1719881HAGAP.pdf</t>
+          <t>BMD-1675389-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>38.258,42</t>
+          <t>389,52</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1720116</t>
+          <t>1691390</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4128,24 +4128,24 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>BMD-1720116-HAGAP.pdf</t>
+          <t>BMD-1691390-HAGAP..pdf</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>168,95</t>
+          <t>457,30</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1721631</t>
+          <t>1703223</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4155,24 +4155,24 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>BMD-1721631-HAGAP  PARCIAL.pdf</t>
+          <t>BMD-1703223-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>12.649,43</t>
+          <t>1.471,15</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1721631C</t>
+          <t>1708066</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -4182,24 +4182,24 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>BMD-1721631C-HAGAP  PARCIAL.pdf</t>
+          <t>BMD-1708066-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>100,65</t>
+          <t>3.419,06</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1721886</t>
+          <t>1712547</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -4209,24 +4209,24 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>BMD-1721886 - HAGAP PARCIAL.pdf</t>
+          <t>BMD-1712547-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>14.551,70</t>
+          <t>117,63</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1713044C</t>
+          <t>1712550</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4236,24 +4236,24 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>BMD.-1713044C.-HAGAP.pdf</t>
+          <t>BMD-1712550-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>21,11</t>
+          <t>421,10</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1715327</t>
+          <t>1712766</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4263,105 +4263,105 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>BMD.1715327-HAGAP.pdf</t>
+          <t>BMD-1712766-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>705,45</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1708877</t>
+          <t>1713044I</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>BMDFINAL-1708877-HAGAP.pdf</t>
+          <t>BMD-1713044II-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>3,54</t>
+          <t>1.528,53</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1712957</t>
+          <t>1713226</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>BMDFINAL-1712957-HAGAP.pdf</t>
+          <t>BMD-1713226-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>45,19</t>
+          <t>237,93</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>1717332</t>
+          <t>1714909</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>BMDFINAL-1717332-HAGAP.pdf</t>
+          <t>BMD-1714909-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>107,93</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1703223</t>
+          <t>1715127</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4371,24 +4371,24 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1703223-HAGAP.pdf</t>
+          <t>BMD-1715127-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>18.169,34</t>
+          <t>128,31</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1712547</t>
+          <t>1715131</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1712547-HAGAP.pdf</t>
+          <t>BMD-1715131-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>6.951,82</t>
+          <t>2.220,22</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -4415,7 +4415,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1712957</t>
+          <t>1715257I</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4425,24 +4425,24 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1712957-HAGAP.pdf</t>
+          <t>BMD-1715257I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2.177,64</t>
+          <t>6.765,65</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>1713262</t>
+          <t>1715668</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4452,24 +4452,24 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1713262-HAGAP.pdf</t>
+          <t>BMD-1715668-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2.619,71</t>
+          <t>249,06</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>1714909</t>
+          <t>1715816C</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4479,24 +4479,24 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1714909-HAGAP.pdf</t>
+          <t>BMD-1715816C-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>954,64</t>
+          <t>30,22</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>1715127</t>
+          <t>1715816I</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4506,24 +4506,24 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1715127-HAGAP.pdf</t>
+          <t>BMD-1715816I-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>4.418,94</t>
+          <t>3.168,40</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1715327</t>
+          <t>1715899</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4533,24 +4533,24 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1715327-HAGAP.pdf</t>
+          <t>BMD-1715899-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>5.417,39</t>
+          <t>3.389,65</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>1719070</t>
+          <t>1717166</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4560,24 +4560,24 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1719070-HAGAP.pdf</t>
+          <t>BMD-1717166-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2.744,71</t>
+          <t>22.116,83</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>1719135</t>
+          <t>1717168</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4587,24 +4587,24 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1719135-HAGAP.pdf</t>
+          <t>BMD-1717168-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>913,84</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>1720116</t>
+          <t>1718442</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4614,24 +4614,24 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1720116-HAGAP.pdf</t>
+          <t>BMD-1718442-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>1.675,57</t>
+          <t>45,19</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1724491</t>
+          <t>1718561</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4641,174 +4641,174 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1724491-HAGAP.pdf</t>
+          <t>BMD-1718561-HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>14.377,51</t>
+          <t>13.683,99</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>1712766</t>
+          <t>1719070</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>FF0-1712766-HAGAP.pdf</t>
+          <t>BMD-1719070-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>333,14</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1719135</t>
+          <t>1719213</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>FFO  -1719135-HAGAP.pdf</t>
+          <t>BMD-1719213-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>5.951,32</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>1688115C</t>
+          <t>1719214</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>FFO - 1688115C - HAGAP.pdf</t>
+          <t>BMD-1719214-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>6.124,60</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>1688115I</t>
+          <t>1719881</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>FFO - 1688115I - HAGAP.pdf</t>
+          <t>BMD-1719881-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>3.239,73</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>1702776C</t>
+          <t>1719881H</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>FFO - 1702776C - HAGAP.pdf</t>
+          <t>BMD-1719881HAGAP.pdf</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>38.258,42</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>1702776I</t>
+          <t>1720116</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>FFO - 1702776I - HAGAP.pdf</t>
+          <t>BMD-1720116-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>168,95</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -4820,49 +4820,49 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>1704867</t>
+          <t>1721631</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>FFO - 1704867 - ASP.pdf</t>
+          <t>BMD-1721631-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>12.649,43</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>1711384</t>
+          <t>1721631C</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>FFO - 1711384 - HAGAP.pdf</t>
+          <t>BMD-1721631C-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>100,65</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -4874,98 +4874,98 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>1712538</t>
+          <t>1721869</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>FFO - 1712538 - HAGAP.pdf</t>
+          <t>BMD-1721869-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>133,09</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1713240</t>
+          <t>1721886</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>FFO - 1713240 - HAGAP - 20-05-2026.pdf</t>
+          <t>BMD-1721886 - HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>14.551,70</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1715878</t>
+          <t>1713044C</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>FFO - 1715878 - HAGAP - 20-05-2026.pdf</t>
+          <t>BMD.-1713044C.-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>21,11</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>1641139I</t>
+          <t>1715327</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>FFO 1641139I HAGAP.pdf</t>
+          <t>BMD.1715327-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -4982,7 +4982,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>1713679</t>
+          <t>1708877</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -4992,24 +4992,24 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>FFO 1713679 HAGAP.pdf</t>
+          <t>BMDFINAL-1708877-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>3,54</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>1714729</t>
+          <t>1712957</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5019,24 +5019,24 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>FFO 1714729 HAGAP.pdf</t>
+          <t>BMDFINAL-1712957-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>45,19</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>1718803</t>
+          <t>1717332</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>FFO 1718803 HAGAP.pdf</t>
+          <t>BMDFINAL-1717332-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -5056,311 +5056,311 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>1720721</t>
+          <t>1703223</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>FFO 1720721 HAGAP.pdf</t>
+          <t>BMDPARCIAL-1703223-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>18.169,34</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>1667141</t>
+          <t>1712547</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>FFO-1667141-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1712547-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>6.951,82</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>1675389</t>
+          <t>1712957</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>FFO-1675389-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1712957-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.177,64</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1703223</t>
+          <t>1713262</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>FFO-1703223-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1713262-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.619,71</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>1708877</t>
+          <t>1714909</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>FFO-1708877-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1714909-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>954,64</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>1710116</t>
+          <t>1715127</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>FFO-1710116-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1715127-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>4.418,94</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>1712531</t>
+          <t>1715327</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>FFO-1712531-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1715327-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>5.417,39</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>1712547</t>
+          <t>1719070</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>FFO-1712547-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1719070-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.744,71</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>1713044C</t>
+          <t>1719135</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>FFO-1713044C.-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1719135-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>913,84</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>1713044I</t>
+          <t>1720116</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>FFO-1713044II-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1720116-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>1.675,57</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>1713226</t>
+          <t>1724491</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>FFO-1713226-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1724491-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>14.377,51</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>1713262</t>
+          <t>1712766</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -5370,7 +5370,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>FFO-1713262-HAGAP.pdf</t>
+          <t>FF0-1712766-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -5380,14 +5380,14 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>1714909</t>
+          <t>1719135</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>FFO-1714909-HAGAP.pdf</t>
+          <t>FFO  -1719135-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -5407,14 +5407,14 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>1715127</t>
+          <t>1688115C</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>FFO-1715127-HAGAP.pdf</t>
+          <t>FFO - 1688115C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -5434,14 +5434,14 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>1715257I</t>
+          <t>1688115I</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>FFO-1715257I-HAGAP.pdf</t>
+          <t>FFO - 1688115I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -5461,14 +5461,14 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>1715327</t>
+          <t>1698047</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -5478,24 +5478,24 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>FFO-1715327-HAGAP.pdf</t>
+          <t>FFO - 1698047 - HAGAP - 30-04-2026.pdf</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>65,98</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>1715668</t>
+          <t>1702776C</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -5505,7 +5505,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>FFO-1715668-HAGAP.pdf</t>
+          <t>FFO - 1702776C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -5515,14 +5515,14 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>1717332</t>
+          <t>1702776I</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>FFO-1717332-HAGAP.pdf</t>
+          <t>FFO - 1702776I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>176,23</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -5549,7 +5549,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>1719070</t>
+          <t>1704867</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>FFO-1719070-HAGAP.pdf</t>
+          <t>FFO - 1704867 - ASP.pdf</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -5569,14 +5569,14 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>1719881</t>
+          <t>1709995</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>FFO-1719881-HAGAP.pdf</t>
+          <t>FFO - 1709995 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -5596,14 +5596,14 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>1708066</t>
+          <t>1711384</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -5613,7 +5613,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>FFO.-1708066-HAGAP.pdf</t>
+          <t>FFO - 1711384 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -5623,14 +5623,14 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>1712957</t>
+          <t>1712538</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -5640,7 +5640,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>FFO.-1712957-HAGAP.pdf</t>
+          <t>FFO - 1712538 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -5650,14 +5650,14 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>1718442</t>
+          <t>1713240</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -5667,7 +5667,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>FFO´1718442-HAGAP.pdf</t>
+          <t>FFO - 1713240 - HAGAP - 20-05-2026.pdf</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -5677,32 +5677,1031 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
+          <t>1715878</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>FFO - 1715878 - HAGAP - 20-05-2026.pdf</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>1641139I</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>FFO 1641139I HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>1710975</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>FFO 1710975 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>1712533</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>FFO 1712533 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>1713679</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>FFO 1713679 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>1714364</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>FFO 1714364 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>1714729</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>FFO 1714729 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>1718803</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>FFO 1718803 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>1720721</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>FFO 1720721 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>1667141</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>FFO-1667141-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>1675389</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>FFO-1675389-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>1691390</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>FFO-1691390-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
           <t>1703223</t>
         </is>
       </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>BMD</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>FFO-1703223-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>1708877</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>FFO-1708877-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>1710116</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>FFO-1710116-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>1711110</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>FFO-1711110-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>1712531</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>FFO-1712531-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>1712547</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>FFO-1712547-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>1712550</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>FFO-1712550-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>1713044C</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>FFO-1713044C.-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>1713044I</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>FFO-1713044II-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>1713226</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>FFO-1713226-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>1713262</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>FFO-1713262-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>1714909</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>FFO-1714909-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>1715127</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>FFO-1715127-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>1715257I</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>FFO-1715257I-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>1715327</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>FFO-1715327-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>65,98</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>1715668</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>FFO-1715668-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>1717168</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>FFO-1717168-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>87,00</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>1717332</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>FFO-1717332-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>176,23</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>1719070</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>FFO-1719070-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>1719881</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>FFO-1719881-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>1721869</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>FFO-1721869-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>1708066</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>FFO.-1708066-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>1712957</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>FFO.-1712957-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>1691380</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>FFO_1691380.pdf</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>1718442</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>FFO´1718442-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>1703223</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
         <is>
           <t>MULTA-1703223-HAGAP.pdf</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr">
+      <c r="D233" t="inlineStr">
         <is>
           <t>0,00</t>
         </is>
       </c>
-      <c r="E196" t="inlineStr"/>
+      <c r="E233" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/medicoes.xlsx
+++ b/medicoes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E233"/>
+  <dimension ref="A1:E244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2498,7 +2498,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1715920</t>
+          <t>1715154</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2508,24 +2508,24 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>BMD 1715920 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1715154 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>1.031,94</t>
+          <t>2.658,74</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1718803</t>
+          <t>1715920</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2535,24 +2535,24 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>BMD 1718803 HAGAP.pdf</t>
+          <t>BMD 1715920 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>3.825,18</t>
+          <t>1.031,94</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1719097</t>
+          <t>1718803</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2562,24 +2562,24 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>BMD 1719097 HAGAP.pdf</t>
+          <t>BMD 1718803 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>7.450,28</t>
+          <t>3.825,18</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1719155</t>
+          <t>1719097</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2589,24 +2589,24 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>BMD 1719155 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1719097 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2.223,15</t>
+          <t>7.450,28</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1720721</t>
+          <t>1719155</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2616,24 +2616,24 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>BMD 1720721 HAGAP.pdf</t>
+          <t>BMD 1719155 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2.015,45</t>
+          <t>2.223,15</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1720920</t>
+          <t>1720721</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2643,24 +2643,24 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>BMD 1720920 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1720721 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>555,60</t>
+          <t>2.015,45</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1724356</t>
+          <t>1720920</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2670,24 +2670,24 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>BMD 1724356 HAGAP.pdf</t>
+          <t>BMD 1720920 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>7.614,80</t>
+          <t>555,60</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1728163</t>
+          <t>1724356</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2697,12 +2697,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>BMD 1728163 HAGAP.pdf</t>
+          <t>BMD 1724356 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>7.914,69</t>
+          <t>7.614,80</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -2714,7 +2714,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1712533</t>
+          <t>1728163</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2724,51 +2724,51 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>BMD FF 1712533 HAGAP.pdf</t>
+          <t>BMD 1728163 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>127,40</t>
+          <t>7.914,69</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1702776C</t>
+          <t>1712533</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>BMD FINAL - 1702776C - HAGAP.pdf</t>
+          <t>BMD FF 1712533 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>127,40</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1702776I</t>
+          <t>1702776C</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2778,24 +2778,24 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>BMD FINAL - 1702776I - HAGAP.pdf</t>
+          <t>BMD FINAL - 1702776C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>18.098,87</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1713262</t>
+          <t>1702776I</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2805,24 +2805,24 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>BMD FINAL-1713262-HAGAP.pdf</t>
+          <t>BMD FINAL - 1702776I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>55,90</t>
+          <t>18.098,87</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1719135</t>
+          <t>1713262</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>BMD FINAL-1719135-HAGAP.pdf</t>
+          <t>BMD FINAL-1713262-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>47,08</t>
+          <t>55,90</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -2849,34 +2849,34 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1712550</t>
+          <t>1719135</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>BMD PARCAIL-1712550-HAGAP.pdf</t>
+          <t>BMD FINAL-1719135-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>4.585,98</t>
+          <t>47,08</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1677314</t>
+          <t>1712550</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2886,24 +2886,24 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1677314 - HAGAP.pdf</t>
+          <t>BMD PARCAIL-1712550-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>46.760,40</t>
+          <t>4.585,98</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1677316</t>
+          <t>1677314</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2913,24 +2913,24 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1677316 HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1677314 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>51.623,62</t>
+          <t>46.760,40</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1688115C</t>
+          <t>1677316</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2940,24 +2940,24 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1688115C - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1677316 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>6,36</t>
+          <t>51.623,62</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1688115I</t>
+          <t>1688115C</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2967,12 +2967,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1688115I - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1688115C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>18.752,84</t>
+          <t>6,36</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -2984,7 +2984,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1691534</t>
+          <t>1688115I</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2994,24 +2994,24 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1691534 - HAGAP - 19-06-2026.pdf</t>
+          <t>BMD PARCIAL - 1688115I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>20.334,45</t>
+          <t>18.752,84</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1694258</t>
+          <t>1691534</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3021,24 +3021,24 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1694258 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1691534 - HAGAP - 19-06-2026.pdf</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>127.751,38</t>
+          <t>20.334,45</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1695716</t>
+          <t>1694258</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3048,24 +3048,24 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1695716 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1694258 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>74.647,17</t>
+          <t>127.751,38</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1698056</t>
+          <t>1695716</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3075,24 +3075,24 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1698056 - HAGAP - 22-06-2026.pdf</t>
+          <t>BMD PARCIAL - 1695716 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>8.966,25</t>
+          <t>74.647,17</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1710735</t>
+          <t>1698056</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3102,24 +3102,24 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1710735 HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1698056 - HAGAP - 22-06-2026.pdf</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>9.153,35</t>
+          <t>8.966,25</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1711384</t>
+          <t>1710735</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3129,24 +3129,24 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1711384 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1710735 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2.127,38</t>
+          <t>9.153,35</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1712538</t>
+          <t>1711384</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1712538 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1711384 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>3.568,05</t>
+          <t>2.127,38</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1715278</t>
+          <t>1712538</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3183,24 +3183,24 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1715278 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1712538 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2.654,77</t>
+          <t>3.568,05</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1715688</t>
+          <t>1715278</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3210,24 +3210,24 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1715688 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1715278 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>9.669,94</t>
+          <t>2.654,77</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1720914</t>
+          <t>1715688</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3237,24 +3237,24 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1720914 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1715688 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>13.736,92</t>
+          <t>9.669,94</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1721887</t>
+          <t>1720914</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3264,24 +3264,24 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1721887 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1720914 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>15.229,27</t>
+          <t>13.736,92</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1722169</t>
+          <t>1721887</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3291,24 +3291,24 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1722169 - HAGAP - 19-06-2026.pdf</t>
+          <t>BMD PARCIAL - 1721887 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>38.238,91</t>
+          <t>15.229,27</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1722779</t>
+          <t>1722169</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3318,24 +3318,24 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1722779 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1722169 - HAGAP - 19-06-2026.pdf</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>14.090,54</t>
+          <t>38.238,91</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1712530</t>
+          <t>1722779</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3345,24 +3345,24 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>BMD PARCIAL -1712530-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1722779 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>5.393,72</t>
+          <t>14.090,54</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1713626I</t>
+          <t>1712530</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3372,24 +3372,24 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>BMD PARCIAL -1713626I-HAGAP.pdf</t>
+          <t>BMD PARCIAL -1712530-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>5.318,80</t>
+          <t>5.393,72</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1713260</t>
+          <t>1713626I</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3399,24 +3399,24 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>BMD PARCIAL 1713260 - HAGAP.pdf</t>
+          <t>BMD PARCIAL -1713626I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>8.854,04</t>
+          <t>5.318,80</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1563492</t>
+          <t>1713260</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3426,17 +3426,17 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>BMD PARCIAL CIANORTE - 1563492 - HAGAP.pdf</t>
+          <t>BMD PARCIAL 1713260 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>80.240,76</t>
+          <t>8.854,04</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
@@ -3453,12 +3453,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>BMD PARCIAL JUSSARA - 1563492 - HAGAP.pdf</t>
+          <t>BMD PARCIAL CIANORTE - 1563492 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>64.923,56</t>
+          <t>80.240,76</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -3470,7 +3470,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1667141</t>
+          <t>1563492</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3480,24 +3480,24 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1667141-HAGAP.pdf</t>
+          <t>BMD PARCIAL JUSSARA - 1563492 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>509,47</t>
+          <t>64.923,56</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1694841</t>
+          <t>1667141</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3507,24 +3507,24 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1694841-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1667141-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>4.476,57</t>
+          <t>509,47</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1704877</t>
+          <t>1694841</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3534,24 +3534,24 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1704877-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1694841-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>158.642,45</t>
+          <t>4.476,57</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1708877I</t>
+          <t>1704877</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3561,24 +3561,24 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1708877I-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1704877-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2.132,72</t>
+          <t>158.642,45</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1709486</t>
+          <t>1708877I</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3588,24 +3588,24 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1709486-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1708877I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>4.402,38</t>
+          <t>2.132,72</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1711507</t>
+          <t>1709486</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3615,12 +3615,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1711507-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1709486-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>14.415,50</t>
+          <t>4.402,38</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -3632,7 +3632,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1711775</t>
+          <t>1711507</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3642,24 +3642,24 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1711775-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1711507-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>1.928,86</t>
+          <t>14.415,50</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1712531</t>
+          <t>1711775</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3669,24 +3669,24 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1712531-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1711775-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>5.019,99</t>
+          <t>1.928,86</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1713226</t>
+          <t>1712531</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3696,24 +3696,24 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1713226-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1712531-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>3.049,11</t>
+          <t>5.019,99</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1713656</t>
+          <t>1713226</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3723,24 +3723,24 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1713656-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1713226-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>4.315,58</t>
+          <t>3.049,11</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1714342</t>
+          <t>1713656</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1714342-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1713656-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>1.949,56</t>
+          <t>4.315,58</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -3767,7 +3767,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1714699</t>
+          <t>1714342</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3777,24 +3777,24 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1714699-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1714342-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>18.624,62</t>
+          <t>1.949,56</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1715201</t>
+          <t>1714699</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3804,24 +3804,24 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1715201-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1714699-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>6.987,28</t>
+          <t>18.624,62</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1715668</t>
+          <t>1715201</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3831,24 +3831,24 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1715668-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1715201-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2.070,47</t>
+          <t>6.987,28</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1715955I</t>
+          <t>1715668</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3858,24 +3858,24 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1715955I-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1715668-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2.970,68</t>
+          <t>2.070,47</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>1717168</t>
+          <t>1715955I</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3885,24 +3885,24 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1717168-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1715955I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2.528,74</t>
+          <t>2.970,68</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1717332</t>
+          <t>1717168</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3912,24 +3912,24 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1717332-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1717168-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2.320,28</t>
+          <t>2.528,74</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1718442</t>
+          <t>1717332</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3939,12 +3939,12 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1718442-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1717332-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>3.160,96</t>
+          <t>2.320,28</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -3956,7 +3956,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>1718555I</t>
+          <t>1718442</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1718555I-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1718442-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2.781,60</t>
+          <t>3.160,96</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -3983,7 +3983,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1721869</t>
+          <t>1718555I</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3993,24 +3993,24 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1721869-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1718555I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>807,18</t>
+          <t>2.781,60</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1725260</t>
+          <t>1721869</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4020,24 +4020,24 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1725260-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1721869-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>4.716,47</t>
+          <t>807,18</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1713221</t>
+          <t>1725260</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4047,24 +4047,24 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>BMD parcial - 1713221 - HAGAP.pdf</t>
+          <t>BMD PARCIAL-1725260-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>18.794,09</t>
+          <t>4.716,47</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1667141</t>
+          <t>1713221</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4074,24 +4074,24 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>BMD-1667141-HAGAP.pdf</t>
+          <t>BMD parcial - 1713221 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>152,42</t>
+          <t>18.794,09</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1675389</t>
+          <t>1667141</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>BMD-1675389-HAGAP.pdf</t>
+          <t>BMD-1667141-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>389,52</t>
+          <t>152,42</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1691390</t>
+          <t>1675389</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4128,24 +4128,24 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>BMD-1691390-HAGAP..pdf</t>
+          <t>BMD-1675389-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>457,30</t>
+          <t>389,52</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1703223</t>
+          <t>1691390</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4155,24 +4155,24 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>BMD-1703223-HAGAP.pdf</t>
+          <t>BMD-1691390-HAGAP..pdf</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>1.471,15</t>
+          <t>457,30</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1708066</t>
+          <t>1703223</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -4182,24 +4182,24 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>BMD-1708066-HAGAP.pdf</t>
+          <t>BMD-1703223-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>3.419,06</t>
+          <t>1.471,15</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1712547</t>
+          <t>1708066</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -4209,24 +4209,24 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>BMD-1712547-HAGAP.pdf</t>
+          <t>BMD-1708066-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>117,63</t>
+          <t>3.419,06</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1712550</t>
+          <t>1712547</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4236,24 +4236,24 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>BMD-1712550-HAGAP.pdf</t>
+          <t>BMD-1712547-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>421,10</t>
+          <t>117,63</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1712766</t>
+          <t>1712550</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4263,24 +4263,24 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>BMD-1712766-HAGAP.pdf</t>
+          <t>BMD-1712550-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>705,45</t>
+          <t>421,10</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1713044I</t>
+          <t>1712766</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>BMD-1713044II-HAGAP.pdf</t>
+          <t>BMD-1712766-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>1.528,53</t>
+          <t>705,45</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -4307,7 +4307,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1713226</t>
+          <t>1713044I</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4317,24 +4317,24 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>BMD-1713226-HAGAP.pdf</t>
+          <t>BMD-1713044II-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>237,93</t>
+          <t>1.528,53</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>1714909</t>
+          <t>1713226</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4344,24 +4344,24 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>BMD-1714909-HAGAP.pdf</t>
+          <t>BMD-1713226-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>107,93</t>
+          <t>237,93</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1715127</t>
+          <t>1714909</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4371,24 +4371,24 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>BMD-1715127-HAGAP.pdf</t>
+          <t>BMD-1714909-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>128,31</t>
+          <t>107,93</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1715131</t>
+          <t>1715127</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4398,24 +4398,24 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>BMD-1715131-HAGAP.pdf</t>
+          <t>BMD-1715127-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2.220,22</t>
+          <t>128,31</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1715257I</t>
+          <t>1715131</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4425,24 +4425,24 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>BMD-1715257I-HAGAP.pdf</t>
+          <t>BMD-1715131-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>6.765,65</t>
+          <t>2.220,22</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>1715668</t>
+          <t>1715257I</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4452,24 +4452,24 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>BMD-1715668-HAGAP.pdf</t>
+          <t>BMD-1715257I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>249,06</t>
+          <t>6.765,65</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>1715816C</t>
+          <t>1715668</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4479,24 +4479,24 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>BMD-1715816C-HAGAP  PARCIAL.pdf</t>
+          <t>BMD-1715668-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>30,22</t>
+          <t>249,06</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>1715816I</t>
+          <t>1715816C</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>BMD-1715816I-HAGAP  PARCIAL.pdf</t>
+          <t>BMD-1715816C-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>3.168,40</t>
+          <t>30,22</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -4523,7 +4523,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1715899</t>
+          <t>1715816I</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>BMD-1715899-HAGAP  PARCIAL.pdf</t>
+          <t>BMD-1715816I-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>3.389,65</t>
+          <t>3.168,40</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -4550,7 +4550,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>1717166</t>
+          <t>1715899</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4560,24 +4560,24 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>BMD-1717166-HAGAP  PARCIAL.pdf</t>
+          <t>BMD-1715899-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>22.116,83</t>
+          <t>3.389,65</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>1717168</t>
+          <t>1717166</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4587,24 +4587,24 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>BMD-1717168-HAGAP.pdf</t>
+          <t>BMD-1717166-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>22.116,83</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>1718442</t>
+          <t>1717168</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4614,24 +4614,24 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>BMD-1718442-HAGAP.pdf</t>
+          <t>BMD-1717168-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>45,19</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1718561</t>
+          <t>1718442</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4641,24 +4641,24 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>BMD-1718561-HAGAP PARCIAL.pdf</t>
+          <t>BMD-1718442-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>13.683,99</t>
+          <t>45,19</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>1719070</t>
+          <t>1718561</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4668,24 +4668,24 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>BMD-1719070-HAGAP.pdf</t>
+          <t>BMD-1718561-HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>333,14</t>
+          <t>13.683,99</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1719213</t>
+          <t>1719070</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4695,24 +4695,24 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>BMD-1719213-HAGAP  PARCIAL.pdf</t>
+          <t>BMD-1719070-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>5.951,32</t>
+          <t>333,14</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>1719214</t>
+          <t>1719213</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4722,24 +4722,24 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>BMD-1719214-HAGAP  PARCIAL.pdf</t>
+          <t>BMD-1719213-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>6.124,60</t>
+          <t>5.951,32</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>1719881</t>
+          <t>1719214</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4749,24 +4749,24 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>BMD-1719881-HAGAP.pdf</t>
+          <t>BMD-1719214-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>3.239,73</t>
+          <t>6.124,60</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>1719881H</t>
+          <t>1719881</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4776,24 +4776,24 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>BMD-1719881HAGAP.pdf</t>
+          <t>BMD-1719881-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>38.258,42</t>
+          <t>3.239,73</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>1720116</t>
+          <t>1719881H</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4803,24 +4803,24 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>BMD-1720116-HAGAP.pdf</t>
+          <t>BMD-1719881HAGAP.pdf</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>168,95</t>
+          <t>38.258,42</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>1721631</t>
+          <t>1720116</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4830,24 +4830,24 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>BMD-1721631-HAGAP  PARCIAL.pdf</t>
+          <t>BMD-1720116-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>12.649,43</t>
+          <t>168,95</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>1721631C</t>
+          <t>1721631</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>BMD-1721631C-HAGAP  PARCIAL.pdf</t>
+          <t>BMD-1721631-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>100,65</t>
+          <t>12.649,43</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -4874,7 +4874,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>1721869</t>
+          <t>1721631C</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4884,24 +4884,24 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>BMD-1721869-HAGAP.pdf</t>
+          <t>BMD-1721631C-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>133,09</t>
+          <t>100,65</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1721886</t>
+          <t>1721869</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4911,24 +4911,24 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>BMD-1721886 - HAGAP PARCIAL.pdf</t>
+          <t>BMD-1721869-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>14.551,70</t>
+          <t>133,09</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1713044C</t>
+          <t>1721886</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4938,24 +4938,24 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>BMD.-1713044C.-HAGAP.pdf</t>
+          <t>BMD-1721886 - HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>21,11</t>
+          <t>14.551,70</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>1715327</t>
+          <t>1713044C</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4965,51 +4965,51 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>BMD.1715327-HAGAP.pdf</t>
+          <t>BMD.-1713044C.-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>21,11</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>1708877</t>
+          <t>1715327</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>BMDFINAL-1708877-HAGAP.pdf</t>
+          <t>BMD.1715327-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>3,54</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>1712957</t>
+          <t>1708877</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5019,24 +5019,24 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>BMDFINAL-1712957-HAGAP.pdf</t>
+          <t>BMDFINAL-1708877-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>45,19</t>
+          <t>3,54</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>1717332</t>
+          <t>1712957</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5046,51 +5046,51 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>BMDFINAL-1717332-HAGAP.pdf</t>
+          <t>BMDFINAL-1712957-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>45,19</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>1703223</t>
+          <t>1717332</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1703223-HAGAP.pdf</t>
+          <t>BMDFINAL-1717332-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>18.169,34</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>1712547</t>
+          <t>1703223</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5100,24 +5100,24 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1712547-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1703223-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>6.951,82</t>
+          <t>18.169,34</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>1712957</t>
+          <t>1712547</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5127,24 +5127,24 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1712957-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1712547-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2.177,64</t>
+          <t>6.951,82</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1713262</t>
+          <t>1712957</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1713262-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1712957-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2.619,71</t>
+          <t>2.177,64</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -5171,7 +5171,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>1714909</t>
+          <t>1713262</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -5181,12 +5181,12 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1714909-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1713262-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>954,64</t>
+          <t>2.619,71</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -5198,7 +5198,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>1715127</t>
+          <t>1714909</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -5208,24 +5208,24 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1715127-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1714909-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>4.418,94</t>
+          <t>954,64</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>1715327</t>
+          <t>1715127</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -5235,24 +5235,24 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1715327-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1715127-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>5.417,39</t>
+          <t>4.418,94</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>1719070</t>
+          <t>1715327</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -5262,24 +5262,24 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1719070-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1715327-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2.744,71</t>
+          <t>5.417,39</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>1719135</t>
+          <t>1719070</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -5289,24 +5289,24 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1719135-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1719070-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>913,84</t>
+          <t>2.744,71</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>1720116</t>
+          <t>1719135</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1720116-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1719135-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>1.675,57</t>
+          <t>913,84</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -5333,7 +5333,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>1724491</t>
+          <t>1720116</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -5343,51 +5343,51 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1724491-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1720116-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>14.377,51</t>
+          <t>1.675,57</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>1712766</t>
+          <t>1724491</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>FF0-1712766-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1724491-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>14.377,51</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>1719135</t>
+          <t>1712766</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>FFO  -1719135-HAGAP.pdf</t>
+          <t>FF0-1712766-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -5407,14 +5407,14 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>1688115C</t>
+          <t>1719135</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>FFO - 1688115C - HAGAP.pdf</t>
+          <t>FFO  -1719135-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -5434,14 +5434,14 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>1688115I</t>
+          <t>1688115C</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>FFO - 1688115I - HAGAP.pdf</t>
+          <t>FFO - 1688115C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -5468,7 +5468,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>1698047</t>
+          <t>1688115I</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -5478,7 +5478,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>FFO - 1698047 - HAGAP - 30-04-2026.pdf</t>
+          <t>FFO - 1688115I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -5488,14 +5488,14 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>1702776C</t>
+          <t>1692174</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -5505,7 +5505,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>FFO - 1702776C - HAGAP.pdf</t>
+          <t>FFO - 1692174 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -5515,14 +5515,14 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>1702776I</t>
+          <t>1698047</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>FFO - 1702776I - HAGAP.pdf</t>
+          <t>FFO - 1698047 - HAGAP - 30-04-2026.pdf</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -5542,14 +5542,14 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>1704867</t>
+          <t>1702127</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>FFO - 1704867 - ASP.pdf</t>
+          <t>FFO - 1702127 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -5569,14 +5569,14 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>1709995</t>
+          <t>1702776C</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>FFO - 1709995 - HAGAP.pdf</t>
+          <t>FFO - 1702776C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -5596,14 +5596,14 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>1711384</t>
+          <t>1702776I</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -5613,7 +5613,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>FFO - 1711384 - HAGAP.pdf</t>
+          <t>FFO - 1702776I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -5623,14 +5623,14 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>1712538</t>
+          <t>1704867</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -5640,7 +5640,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>FFO - 1712538 - HAGAP.pdf</t>
+          <t>FFO - 1704867 - ASP.pdf</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -5650,14 +5650,14 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>1713240</t>
+          <t>1705802I</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -5667,7 +5667,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>FFO - 1713240 - HAGAP - 20-05-2026.pdf</t>
+          <t>FFO - 1705802I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -5677,14 +5677,14 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>1715878</t>
+          <t>1709419</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>FFO - 1715878 - HAGAP - 20-05-2026.pdf</t>
+          <t>FFO - 1709419 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -5704,14 +5704,14 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>1641139I</t>
+          <t>1709995</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -5721,7 +5721,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>FFO 1641139I HAGAP.pdf</t>
+          <t>FFO - 1709995 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -5731,14 +5731,14 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>1710975</t>
+          <t>1711384</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -5748,7 +5748,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>FFO 1710975 HAGAP.pdf</t>
+          <t>FFO - 1711384 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -5758,14 +5758,14 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>1712533</t>
+          <t>1712538</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>FFO 1712533 HAGAP.pdf</t>
+          <t>FFO - 1712538 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -5785,14 +5785,14 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>1713679</t>
+          <t>1713221</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>FFO 1713679 HAGAP.pdf</t>
+          <t>FFO - 1713221 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -5812,14 +5812,14 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>1714364</t>
+          <t>1713240</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -5829,7 +5829,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>FFO 1714364 HAGAP.pdf</t>
+          <t>FFO - 1713240 - HAGAP - 20-05-2026.pdf</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -5839,14 +5839,14 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>1714729</t>
+          <t>1715878</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>FFO 1714729 HAGAP.pdf</t>
+          <t>FFO - 1715878 - HAGAP - 20-05-2026.pdf</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -5866,14 +5866,14 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>1718803</t>
+          <t>1641139I</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -5883,7 +5883,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>FFO 1718803 HAGAP.pdf</t>
+          <t>FFO 1641139I HAGAP.pdf</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -5893,14 +5893,14 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>1720721</t>
+          <t>1710736</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -5910,7 +5910,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>FFO 1720721 HAGAP.pdf</t>
+          <t>FFO 1710736 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -5920,14 +5920,14 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>1667141</t>
+          <t>1710975</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -5937,7 +5937,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>FFO-1667141-HAGAP.pdf</t>
+          <t>FFO 1710975 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -5947,14 +5947,14 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>1675389</t>
+          <t>1712533</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>FFO-1675389-HAGAP.pdf</t>
+          <t>FFO 1712533 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -5974,14 +5974,14 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>1691390</t>
+          <t>1713435I</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>FFO-1691390-HAGAP.pdf</t>
+          <t>FFO 1713435I HAGAP.pdf</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -6001,14 +6001,14 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>1703223</t>
+          <t>1713679</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>FFO-1703223-HAGAP.pdf</t>
+          <t>FFO 1713679 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -6028,14 +6028,14 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>1708877</t>
+          <t>1714364</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -6045,7 +6045,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>FFO-1708877-HAGAP.pdf</t>
+          <t>FFO 1714364 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -6055,14 +6055,14 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>1710116</t>
+          <t>1714729</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>FFO-1710116-HAGAP.pdf</t>
+          <t>FFO 1714729 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -6082,14 +6082,14 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>1711110</t>
+          <t>1715154</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -6099,7 +6099,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>FFO-1711110-HAGAP.pdf</t>
+          <t>FFO 1715154 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -6109,14 +6109,14 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>1712531</t>
+          <t>1718803</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>FFO-1712531-HAGAP.pdf</t>
+          <t>FFO 1718803 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -6136,14 +6136,14 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>1712547</t>
+          <t>1720721</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>FFO-1712547-HAGAP.pdf</t>
+          <t>FFO 1720721 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -6163,14 +6163,14 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>1712550</t>
+          <t>1667141</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>FFO-1712550-HAGAP.pdf</t>
+          <t>FFO-1667141-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -6190,14 +6190,14 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>1713044C</t>
+          <t>1675389</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -6207,7 +6207,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>FFO-1713044C.-HAGAP.pdf</t>
+          <t>FFO-1675389-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -6217,14 +6217,14 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>1713044I</t>
+          <t>1691390</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -6234,7 +6234,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>FFO-1713044II-HAGAP.pdf</t>
+          <t>FFO-1691390-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -6244,14 +6244,14 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>1713226</t>
+          <t>1703223</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>FFO-1713226-HAGAP.pdf</t>
+          <t>FFO-1703223-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -6271,14 +6271,14 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>1713262</t>
+          <t>1708877</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -6288,7 +6288,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>FFO-1713262-HAGAP.pdf</t>
+          <t>FFO-1708877-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -6305,7 +6305,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>1714909</t>
+          <t>1710116</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -6315,7 +6315,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>FFO-1714909-HAGAP.pdf</t>
+          <t>FFO-1710116-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -6325,14 +6325,14 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>1715127</t>
+          <t>1711110</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -6342,7 +6342,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>FFO-1715127-HAGAP.pdf</t>
+          <t>FFO-1711110-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -6352,14 +6352,14 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>1715257I</t>
+          <t>1712531</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>FFO-1715257I-HAGAP.pdf</t>
+          <t>FFO-1712531-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -6379,14 +6379,14 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>1715327</t>
+          <t>1712547</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -6396,24 +6396,24 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>FFO-1715327-HAGAP.pdf</t>
+          <t>FFO-1712547-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>65,98</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>1715668</t>
+          <t>1712550</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -6423,7 +6423,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>FFO-1715668-HAGAP.pdf</t>
+          <t>FFO-1712550-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -6433,14 +6433,14 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>1717168</t>
+          <t>1713044C</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -6450,24 +6450,24 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>FFO-1717168-HAGAP.pdf</t>
+          <t>FFO-1713044C.-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>87,00</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>1717332</t>
+          <t>1713044I</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -6477,24 +6477,24 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>FFO-1717332-HAGAP.pdf</t>
+          <t>FFO-1713044II-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>176,23</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>1719070</t>
+          <t>1713226</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -6504,7 +6504,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>FFO-1719070-HAGAP.pdf</t>
+          <t>FFO-1713226-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -6514,14 +6514,14 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>1719881</t>
+          <t>1713262</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -6531,7 +6531,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>FFO-1719881-HAGAP.pdf</t>
+          <t>FFO-1713262-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -6541,14 +6541,14 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>1721869</t>
+          <t>1714909</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>FFO-1721869-HAGAP.pdf</t>
+          <t>FFO-1714909-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -6568,14 +6568,14 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>1708066</t>
+          <t>1715127</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -6585,7 +6585,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>FFO.-1708066-HAGAP.pdf</t>
+          <t>FFO-1715127-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -6595,14 +6595,14 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>1712957</t>
+          <t>1715257I</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>FFO.-1712957-HAGAP.pdf</t>
+          <t>FFO-1715257I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -6622,14 +6622,14 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>1691380</t>
+          <t>1715327</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -6639,24 +6639,24 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>FFO_1691380.pdf</t>
+          <t>FFO-1715327-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>65,98</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>1718442</t>
+          <t>1715668</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -6666,7 +6666,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>FFO´1718442-HAGAP.pdf</t>
+          <t>FFO-1715668-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -6676,32 +6676,321 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
+          <t>1717168</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>FFO-1717168-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>87,00</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>1717332</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>FFO-1717332-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>176,23</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>1719070</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>FFO-1719070-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>1719881</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>FFO-1719881-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>1721869</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>FFO-1721869-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>1708066</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>FFO.-1708066-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>1712957</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>FFO.-1712957-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>1691380</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>FFO_1691380.pdf</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>1718442</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>FFO´1718442-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
           <t>1703223</t>
         </is>
       </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>BMD</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
         <is>
           <t>MULTA-1703223-HAGAP.pdf</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
-      </c>
-      <c r="E233" t="inlineStr"/>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>1713044I</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>MULTA-1713044I-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>1715327</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>MULTA-1715327-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/medicoes.xlsx
+++ b/medicoes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E244"/>
+  <dimension ref="A1:E306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -716,7 +716,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1663556</t>
+          <t>1663544</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -726,24 +726,24 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1663556 - BMD - HAGAP.pdf</t>
+          <t>1663544 - BMD - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2.470,38</t>
+          <t>1.065,14</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1663556</t>
+          <t>1663544</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1663556 - FFO - HAGAP.pdf</t>
+          <t>1663544 - FFO - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -763,68 +763,68 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1667593</t>
+          <t>1663556</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1667593 - FFO - asp.pdf</t>
+          <t>1663556 - BMD - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.470,38</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1675032C</t>
+          <t>1663556</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1675032C - BMD 01.pdf</t>
+          <t>1663556 - FFO - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>23,99</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1675032I</t>
+          <t>1667134</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -834,78 +834,78 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1675032I - BMD 01.pdf</t>
+          <t>1667134 - BMD - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>222.884,15</t>
+          <t>1.273,55</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1676605</t>
+          <t>1667134</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1676605 - BMD PARCIAL - HAGAP.pdf</t>
+          <t>1667134 - FFO - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>39.199,95</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1676605</t>
+          <t>1667593</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1676605 - BMD PARCIAL - HAGAP1.pdf</t>
+          <t>1667593 - FFO - asp.pdf</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>39.199,95</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1683861I</t>
+          <t>1675032C</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -915,24 +915,24 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1683861i BMD.pdf</t>
+          <t>1675032C - BMD 01.pdf</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>20.224,44</t>
+          <t>23,99</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1694202</t>
+          <t>1675032I</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -942,51 +942,51 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1694202 BMD.pdf</t>
+          <t>1675032I - BMD 01.pdf</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>4.490,43</t>
+          <t>222.884,15</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1694202</t>
+          <t>1676605</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1694202 FFO.pdf</t>
+          <t>1676605 - BMD PARCIAL - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>39.199,95</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1698781</t>
+          <t>1676605</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -996,24 +996,24 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1698781 BMD.pdf</t>
+          <t>1676605 - BMD PARCIAL - HAGAP1.pdf</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>914,56</t>
+          <t>39.199,95</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1700852</t>
+          <t>1683861I</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1023,78 +1023,78 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1700852 BMD.pdf</t>
+          <t>1683861i BMD.pdf</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>12.509,24</t>
+          <t>20.224,44</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1700852</t>
+          <t>1694202</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1700852 FFO.pdf</t>
+          <t>1694202 BMD.pdf</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>4.490,43</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1704476</t>
+          <t>1694202</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1704476 - BMD Parcial Peabiru.pdf</t>
+          <t>1694202 FFO.pdf</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>23.713,90</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1704476</t>
+          <t>1698781</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1104,24 +1104,24 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1704476 - MD PARCIAL - CAMPO MOURÃO.pdf</t>
+          <t>1698781 BMD.pdf</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>7.938,74</t>
+          <t>914,56</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1704476</t>
+          <t>1700852</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1704476 BMD.pdf</t>
+          <t>1700852 BMD.pdf</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>111,28</t>
+          <t>12.509,24</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1148,7 +1148,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1704476</t>
+          <t>1700852</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1704476 FFO.pdf</t>
+          <t>1700852 FFO.pdf</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1168,14 +1168,14 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1704891</t>
+          <t>1704476</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1185,24 +1185,24 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1704891 - BMD PARC - HAGAP.pdf</t>
+          <t>1704476 - BMD Parcial Peabiru.pdf</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>100.528,77</t>
+          <t>23.713,90</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1704920</t>
+          <t>1704476</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1212,24 +1212,24 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1704920 BMD PARCIAL.pdf</t>
+          <t>1704476 - MD PARCIAL - CAMPO MOURÃO.pdf</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>58.137,43</t>
+          <t>7.938,74</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1704964</t>
+          <t>1704476</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1239,24 +1239,24 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1704964 BMD.pdf</t>
+          <t>1704476 BMD.pdf</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2.692,23</t>
+          <t>111,28</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1704964</t>
+          <t>1704476</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1704964 FFO.pdf</t>
+          <t>1704476 FFO.pdf</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1276,14 +1276,14 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1704968</t>
+          <t>1704891</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1293,51 +1293,51 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1704968 - BMD - HAGAP.pdf</t>
+          <t>1704891 - BMD PARC - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2.808,15</t>
+          <t>100.528,77</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1704968</t>
+          <t>1704920</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1704968 - FFO - HAGAP.pdf</t>
+          <t>1704920 BMD PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>58.137,43</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1707817</t>
+          <t>1704964</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1347,105 +1347,105 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1707817 BMD PARCIAL.pdf</t>
+          <t>1704964 BMD.pdf</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>138.680,75</t>
+          <t>2.692,23</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1710937</t>
+          <t>1704964</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1710937 - bmd - hagap.pdf</t>
+          <t>1704964 FFO.pdf</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>4.234,81</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1710937</t>
+          <t>1704968</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1710937 - ffo - hagap.pdf</t>
+          <t>1704968 - BMD - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.808,15</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1724341</t>
+          <t>1704968</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1724341 - BMD PARC - ASP.pdf</t>
+          <t>1704968 - FFO - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>40.758,00</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1510407</t>
+          <t>1707817</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1455,24 +1455,24 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>BMD - 1510407 - HAGAP - 26-05-2026.pdf</t>
+          <t>1707817 BMD PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>28.642,47</t>
+          <t>138.680,75</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1658892</t>
+          <t>1710937</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1482,51 +1482,51 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>BMD - 1658892 - HAGAP - 22-06-2026.pdf</t>
+          <t>1710937 - bmd - hagap.pdf</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>38.435,91</t>
+          <t>4.234,81</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1688115C</t>
+          <t>1710937</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>BMD - 1688115C - HAGAP.pdf</t>
+          <t>1710937 - ffo - hagap.pdf</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>6,65</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1688115I</t>
+          <t>1722165</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1536,51 +1536,51 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>BMD - 1688115I - HAGAP.pdf</t>
+          <t>1722165 BMD HAGAP.pdf</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2.670,64</t>
+          <t>23.880,34</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1698047</t>
+          <t>1722165</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>BMD - 1698047 - HAGAP 30-04-2026.pdf</t>
+          <t>1722165 FFO.pdf</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2.449,89</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1704867</t>
+          <t>1724341</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1590,24 +1590,24 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>BMD - 1704867 - ASP.pdf</t>
+          <t>1724341 - BMD PARC - ASP.pdf</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>23.915,48</t>
+          <t>40.758,00</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1709995</t>
+          <t>1726042</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1617,24 +1617,24 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>BMD - 1709995 - HAGAP.pdf</t>
+          <t>1726042 - BMD PARCIAL - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2.410,16</t>
+          <t>52.831,30</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1711384</t>
+          <t>1726044</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1644,24 +1644,24 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>BMD - 1711384 - HAGAP.pdf</t>
+          <t>1726044 - BMD PARCIAL - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>122,95</t>
+          <t>68.094,35</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1712538</t>
+          <t>1726045</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1671,24 +1671,24 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>BMD - 1712538 - HAGAP.pdf</t>
+          <t>1726045 BMD PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>387,36</t>
+          <t>59.559,30</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1713240</t>
+          <t>1726057</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1698,24 +1698,24 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>BMD - 1713240 - HAGAP - 20-05-2026.pdf</t>
+          <t>1726057 BMD PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>5.108,11</t>
+          <t>98.316,97</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1713933</t>
+          <t>1726058</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1725,24 +1725,24 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>BMD - 1713933 - HAGAP - 20-05-2026.pdf</t>
+          <t>1726058 BMD PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>5.530,92</t>
+          <t>28.638,24</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1715878</t>
+          <t>1510407</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1752,24 +1752,24 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>BMD - 1715878 - HAGAP - 20-05-2026.pdf</t>
+          <t>BMD - 1510407 - HAGAP - 26-05-2026.pdf</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1.786,71</t>
+          <t>28.642,47</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1718435</t>
+          <t>1658892</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1779,24 +1779,24 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>BMD - 1718435 - HAGAP - 20-05-2026.pdf</t>
+          <t>BMD - 1658892 - HAGAP - 22-06-2026.pdf</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>17.153,90</t>
+          <t>38.435,91</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1718783</t>
+          <t>1677314</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1806,24 +1806,24 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>BMD - 1718783 - HAGAP.pdf</t>
+          <t>BMD - 1677314 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>16.983,02</t>
+          <t>4.880,14</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1722169</t>
+          <t>1688115C</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1833,24 +1833,24 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>BMD - 1722169 - HAGAP - 25-06-2026.pdf</t>
+          <t>BMD - 1688115C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1.225,38</t>
+          <t>6,65</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1725738C</t>
+          <t>1688115I</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1860,24 +1860,24 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>BMD - 1725738C - HAGAP.pdf</t>
+          <t>BMD - 1688115I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>140,91</t>
+          <t>2.670,64</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1725738I</t>
+          <t>1691534</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1887,24 +1887,24 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>BMD - 1725738I - HAGAP.pdf</t>
+          <t>BMD - 1691534 - HAGAP - 03-07-2026.pdf</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>15.544,67</t>
+          <t>996,86</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1520612</t>
+          <t>1698047</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1914,24 +1914,24 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>BMD 1520612 HAGAP.pdf</t>
+          <t>BMD - 1698047 - HAGAP 30-04-2026.pdf</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>53.357,33</t>
+          <t>2.449,89</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1520615</t>
+          <t>1702640</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1941,24 +1941,24 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>BMD 1520615 HAGAP.pdf</t>
+          <t>BMD - 1702640 - HAGAP - 10-07-2026.pdf</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>22.840,59</t>
+          <t>2.963,92</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1660062C</t>
+          <t>1704867</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1968,24 +1968,24 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>BMD 1660062C HAGAP PARCIAL.pdf</t>
+          <t>BMD - 1704867 - ASP.pdf</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>100,65</t>
+          <t>23.915,48</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1660062I</t>
+          <t>1709995</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1995,24 +1995,24 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>BMD 1660062I HAGAP PARCIAL.pdf</t>
+          <t>BMD - 1709995 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>11.953,89</t>
+          <t>2.410,16</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1671139I</t>
+          <t>1711384</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2022,24 +2022,24 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>BMD 1671139I HAGAP.pdf</t>
+          <t>BMD - 1711384 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>6.138,54</t>
+          <t>122,95</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1692636</t>
+          <t>1712538</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2049,24 +2049,24 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>BMD 1692636 ASP.pdf</t>
+          <t>BMD - 1712538 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>19.387,05</t>
+          <t>387,36</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1699516</t>
+          <t>1713240</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2076,24 +2076,24 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>BMD 1699516 HAGAP PARCIAL.pdf</t>
+          <t>BMD - 1713240 - HAGAP - 20-05-2026.pdf</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>3.388,62</t>
+          <t>5.108,11</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1704525</t>
+          <t>1713933</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2103,24 +2103,24 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>BMD 1704525 HAGAP PARCIAL.pdf</t>
+          <t>BMD - 1713933 - HAGAP - 20-05-2026.pdf</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>15.365,48</t>
+          <t>5.530,92</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1704891</t>
+          <t>1715878</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2130,24 +2130,24 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>BMD 1704891 HAGAP PARCIAL.pdf</t>
+          <t>BMD - 1715878 - HAGAP - 20-05-2026.pdf</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>41.477,99</t>
+          <t>1.786,71</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1705074</t>
+          <t>1718435</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2157,24 +2157,24 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>BMD 1705074 HAGAP.pdf</t>
+          <t>BMD - 1718435 - HAGAP - 20-05-2026.pdf</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>150.312,87</t>
+          <t>17.153,90</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1708906</t>
+          <t>1718783</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2184,24 +2184,24 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>BMD 1708906  30-04-2026 HAGAP.pdf</t>
+          <t>BMD - 1718783 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>7.584,06</t>
+          <t>16.983,02</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1710329</t>
+          <t>1718783C</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>BMD 1710329 HAGAP PARCIAL.pdf</t>
+          <t>BMD - 1718783C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>24.209,42</t>
+          <t>7,32</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1710937</t>
+          <t>1722169</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2238,24 +2238,24 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>BMD 1710937 HAGAP PARCIAL.pdf</t>
+          <t>BMD - 1722169 - HAGAP - 25-06-2026.pdf</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>1.225,38</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1710975</t>
+          <t>1725738C</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2265,24 +2265,24 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>BMD 1710975 HAGAP FF.pdf</t>
+          <t>BMD - 1725738C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>913,41</t>
+          <t>140,91</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1711525</t>
+          <t>1725738I</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2292,24 +2292,24 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>BMD 1711525 HAGAP PARCIAL.pdf</t>
+          <t>BMD - 1725738I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>1.998,42</t>
+          <t>15.544,67</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1712533</t>
+          <t>1520612</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2319,24 +2319,24 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>BMD 1712533 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1520612 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2.553,46</t>
+          <t>53.357,33</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1712624</t>
+          <t>1520615</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2346,24 +2346,24 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>BMD 1712624 HAGAP.pdf</t>
+          <t>BMD 1520615 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>3.073,90</t>
+          <t>22.840,59</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1713223</t>
+          <t>1660062C</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2373,24 +2373,24 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>BMD 1713223 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1660062C HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>9.773,21</t>
+          <t>100,65</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1713679</t>
+          <t>1660062I</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2400,24 +2400,24 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>BMD 1713679 HAGAP.pdf</t>
+          <t>BMD 1660062I HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>3.574,44</t>
+          <t>11.953,89</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1713719</t>
+          <t>1671139I</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2427,24 +2427,24 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>BMD 1713719 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1671139I HAGAP.pdf</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>3.385,92</t>
+          <t>6.138,54</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1714364</t>
+          <t>1692636</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>BMD 1714364 HAGAP FF.pdf</t>
+          <t>BMD 1692636 ASP.pdf</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>54,64</t>
+          <t>19.387,05</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -2471,7 +2471,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1714729</t>
+          <t>1699516</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2481,24 +2481,24 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>BMD 1714729 HAGAP.pdf</t>
+          <t>BMD 1699516 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>6.722,61</t>
+          <t>3.388,62</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1715154</t>
+          <t>1704525</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2508,24 +2508,24 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>BMD 1715154 HAGAP.pdf</t>
+          <t>BMD 1704525 FF HAGAP.pdf</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2.658,74</t>
+          <t>86,77</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1715920</t>
+          <t>1704525</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2535,24 +2535,24 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>BMD 1715920 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1704525 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>1.031,94</t>
+          <t>15.365,48</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1718803</t>
+          <t>1704891</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2562,24 +2562,24 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>BMD 1718803 HAGAP.pdf</t>
+          <t>BMD 1704891 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>3.825,18</t>
+          <t>41.477,99</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1719097</t>
+          <t>1705074</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2589,24 +2589,24 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>BMD 1719097 HAGAP.pdf</t>
+          <t>BMD 1705074 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>7.450,28</t>
+          <t>150.312,87</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1719155</t>
+          <t>1708906</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2616,24 +2616,24 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>BMD 1719155 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1708906  30-04-2026 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2.223,15</t>
+          <t>7.584,06</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1720721</t>
+          <t>1710329</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2643,24 +2643,24 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>BMD 1720721 HAGAP.pdf</t>
+          <t>BMD 1710329 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2.015,45</t>
+          <t>24.209,42</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1720920</t>
+          <t>1710937</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2670,24 +2670,24 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>BMD 1720920 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1710937 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>555,60</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1724356</t>
+          <t>1710975</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2697,24 +2697,24 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>BMD 1724356 HAGAP.pdf</t>
+          <t>BMD 1710975 HAGAP FF.pdf</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>7.614,80</t>
+          <t>913,41</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1728163</t>
+          <t>1711525</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2724,24 +2724,24 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>BMD 1728163 HAGAP.pdf</t>
+          <t>BMD 1711525 FF HAGAP.pdf</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>7.914,69</t>
+          <t>126,93</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1712533</t>
+          <t>1711525</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2751,132 +2751,132 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>BMD FF 1712533 HAGAP.pdf</t>
+          <t>BMD 1711525 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>127,40</t>
+          <t>1.998,42</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1702776C</t>
+          <t>1712533</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>BMD FINAL - 1702776C - HAGAP.pdf</t>
+          <t>BMD 1712533 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.553,46</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1702776I</t>
+          <t>1712624</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>BMD FINAL - 1702776I - HAGAP.pdf</t>
+          <t>BMD 1712624 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>18.098,87</t>
+          <t>3.073,90</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1713262</t>
+          <t>1713223</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>BMD FINAL-1713262-HAGAP.pdf</t>
+          <t>BMD 1713223 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>55,90</t>
+          <t>9.773,21</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1719135</t>
+          <t>1713679</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>BMD FINAL-1719135-HAGAP.pdf</t>
+          <t>BMD 1713679 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>47,08</t>
+          <t>3.574,44</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1712550</t>
+          <t>1713719</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2886,24 +2886,24 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>BMD PARCAIL-1712550-HAGAP.pdf</t>
+          <t>BMD 1713719 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>4.585,98</t>
+          <t>3.385,92</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1677314</t>
+          <t>1714364</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2913,24 +2913,24 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1677314 - HAGAP.pdf</t>
+          <t>BMD 1714364 HAGAP FF.pdf</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>46.760,40</t>
+          <t>54,64</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1677316</t>
+          <t>1714729</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2940,24 +2940,24 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1677316 HAGAP.pdf</t>
+          <t>BMD 1714729 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>51.623,62</t>
+          <t>6.722,61</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1688115C</t>
+          <t>1715154</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2967,24 +2967,24 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1688115C - HAGAP.pdf</t>
+          <t>BMD 1715154 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>6,36</t>
+          <t>2.658,74</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1688115I</t>
+          <t>1715920</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2994,24 +2994,24 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1688115I - HAGAP.pdf</t>
+          <t>BMD 1715920 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>18.752,84</t>
+          <t>1.031,94</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1691534</t>
+          <t>1718561</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3021,24 +3021,24 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1691534 - HAGAP - 19-06-2026.pdf</t>
+          <t>BMD 1718561 FF HAGAP.pdf</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>20.334,45</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1694258</t>
+          <t>1718803</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3048,24 +3048,24 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1694258 - HAGAP.pdf</t>
+          <t>BMD 1718803 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>127.751,38</t>
+          <t>3.825,18</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1695716</t>
+          <t>1719097</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3075,24 +3075,24 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1695716 - HAGAP.pdf</t>
+          <t>BMD 1719097 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>74.647,17</t>
+          <t>7.450,28</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1698056</t>
+          <t>1719155</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3102,24 +3102,24 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1698056 - HAGAP - 22-06-2026.pdf</t>
+          <t>BMD 1719155 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>8.966,25</t>
+          <t>2.223,15</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1710735</t>
+          <t>1719213</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3129,24 +3129,24 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1710735 HAGAP.pdf</t>
+          <t>BMD 1719213 FF HAGAP.pdf</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>9.153,35</t>
+          <t>1.371,87</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1711384</t>
+          <t>1720721</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1711384 - HAGAP.pdf</t>
+          <t>BMD 1720721 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2.127,38</t>
+          <t>2.015,45</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1712538</t>
+          <t>1720909</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3183,24 +3183,24 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1712538 - HAGAP.pdf</t>
+          <t>BMD 1720909 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>3.568,05</t>
+          <t>2.851,89</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1715278</t>
+          <t>1720920</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3210,24 +3210,24 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1715278 - HAGAP.pdf</t>
+          <t>BMD 1720920 FF HAGAP.pdf</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2.654,77</t>
+          <t>89,29</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1715688</t>
+          <t>1720920</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3237,24 +3237,24 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1715688 - HAGAP.pdf</t>
+          <t>BMD 1720920 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>9.669,94</t>
+          <t>555,60</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1720914</t>
+          <t>1722904</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3264,24 +3264,24 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1720914 - HAGAP.pdf</t>
+          <t>BMD 1722904 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>13.736,92</t>
+          <t>2.417,20</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1721887</t>
+          <t>1724356</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3291,24 +3291,24 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1721887 - HAGAP.pdf</t>
+          <t>BMD 1724356 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>15.229,27</t>
+          <t>7.614,80</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1722169</t>
+          <t>1728163</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3318,12 +3318,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1722169 - HAGAP - 19-06-2026.pdf</t>
+          <t>BMD 1728163 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>38.238,91</t>
+          <t>7.914,69</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -3335,7 +3335,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1722779</t>
+          <t>1682195</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3345,24 +3345,24 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1722779 - HAGAP.pdf</t>
+          <t>BMD FF 1682195 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>14.090,54</t>
+          <t>8,36</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1712530</t>
+          <t>1693027</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3372,24 +3372,24 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>BMD PARCIAL -1712530-HAGAP.pdf</t>
+          <t>BMD FF 1693027 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>5.393,72</t>
+          <t>2.215,91</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1713626I</t>
+          <t>1712533</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3399,24 +3399,24 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>BMD PARCIAL -1713626I-HAGAP.pdf</t>
+          <t>BMD FF 1712533 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>5.318,80</t>
+          <t>127,40</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1713260</t>
+          <t>1719155</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3426,213 +3426,213 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>BMD PARCIAL 1713260 - HAGAP.pdf</t>
+          <t>BMD FF 1719155 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>8.854,04</t>
+          <t>145,82</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1563492</t>
+          <t>1677316</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>BMD PARCIAL CIANORTE - 1563492 - HAGAP.pdf</t>
+          <t>BMD FINAL - 1677316 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>80.240,76</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1563492</t>
+          <t>1702776C</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>BMD PARCIAL JUSSARA - 1563492 - HAGAP.pdf</t>
+          <t>BMD FINAL - 1702776C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>64.923,56</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1667141</t>
+          <t>1702776I</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1667141-HAGAP.pdf</t>
+          <t>BMD FINAL - 1702776I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>509,47</t>
+          <t>18.098,87</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1694841</t>
+          <t>1715278</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1694841-HAGAP.pdf</t>
+          <t>BMD FINAL - 1715278 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>4.476,57</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1704877</t>
+          <t>1715688</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1704877-HAGAP.pdf</t>
+          <t>BMD FINAL - 1715688 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>158.642,45</t>
+          <t>1.425,04</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1708877I</t>
+          <t>1713262</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1708877I-HAGAP.pdf</t>
+          <t>BMD FINAL-1713262-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2.132,72</t>
+          <t>55,90</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1709486</t>
+          <t>1719135</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1709486-HAGAP.pdf</t>
+          <t>BMD FINAL-1719135-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>4.402,38</t>
+          <t>47,08</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1711507</t>
+          <t>1712550</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3642,24 +3642,24 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1711507-HAGAP.pdf</t>
+          <t>BMD PARCAIL-1712550-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>14.415,50</t>
+          <t>4.585,98</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1711775</t>
+          <t>1677314</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3669,24 +3669,24 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1711775-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1677314 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>1.928,86</t>
+          <t>46.760,40</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1712531</t>
+          <t>1677316</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3696,24 +3696,24 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1712531-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1677316 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>5.019,99</t>
+          <t>51.623,62</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1713226</t>
+          <t>1688115C</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3723,24 +3723,24 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1713226-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1688115C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>3.049,11</t>
+          <t>6,36</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1713656</t>
+          <t>1688115I</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3750,24 +3750,24 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1713656-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1688115I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>4.315,58</t>
+          <t>18.752,84</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1714342</t>
+          <t>1691534</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1714342-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1691534 - HAGAP - 19-06-2026.pdf</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>1.949,56</t>
+          <t>20.334,45</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -3794,7 +3794,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1714699</t>
+          <t>1694258</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3804,24 +3804,24 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1714699-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1694258 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>18.624,62</t>
+          <t>127.751,38</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1715201</t>
+          <t>1695716</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3831,24 +3831,24 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1715201-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1695716 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>6.987,28</t>
+          <t>74.647,17</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1715668</t>
+          <t>1698056</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3858,24 +3858,24 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1715668-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1698056 - HAGAP - 22-06-2026.pdf</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2.070,47</t>
+          <t>8.966,25</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>1715955I</t>
+          <t>1710735</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3885,24 +3885,24 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1715955I-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1710735 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2.970,68</t>
+          <t>9.153,35</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1717168</t>
+          <t>1711384</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3912,24 +3912,24 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1717168-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1711384 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2.528,74</t>
+          <t>2.127,38</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1717332</t>
+          <t>1712538</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3939,24 +3939,24 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1717332-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1712538 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2.320,28</t>
+          <t>3.568,05</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>1718442</t>
+          <t>1715278</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3966,24 +3966,24 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1718442-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1715278 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>3.160,96</t>
+          <t>2.654,77</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1718555I</t>
+          <t>1715688</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1718555I-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1715688 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2.781,60</t>
+          <t>9.669,94</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -4010,7 +4010,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1721869</t>
+          <t>1720914</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4020,24 +4020,24 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1721869-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1720914 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>807,18</t>
+          <t>13.736,92</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1725260</t>
+          <t>1721887</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4047,24 +4047,24 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1725260-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1721887 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>4.716,47</t>
+          <t>15.229,27</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1713221</t>
+          <t>1722169</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4074,24 +4074,24 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>BMD parcial - 1713221 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1722169 - HAGAP - 19-06-2026.pdf</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>18.794,09</t>
+          <t>38.238,91</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1667141</t>
+          <t>1722779</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>BMD-1667141-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1722779 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>152,42</t>
+          <t>14.090,54</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1675389</t>
+          <t>1712530</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4128,24 +4128,24 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>BMD-1675389-HAGAP.pdf</t>
+          <t>BMD PARCIAL -1712530-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>389,52</t>
+          <t>5.393,72</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1691390</t>
+          <t>1713626I</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4155,24 +4155,24 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>BMD-1691390-HAGAP..pdf</t>
+          <t>BMD PARCIAL -1713626I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>457,30</t>
+          <t>5.318,80</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1703223</t>
+          <t>1713260</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -4182,24 +4182,24 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>BMD-1703223-HAGAP.pdf</t>
+          <t>BMD PARCIAL 1713260 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>1.471,15</t>
+          <t>8.854,04</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1708066</t>
+          <t>1563492</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -4209,24 +4209,24 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>BMD-1708066-HAGAP.pdf</t>
+          <t>BMD PARCIAL CIANORTE - 1563492 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>3.419,06</t>
+          <t>80.240,76</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1712547</t>
+          <t>1563492</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4236,24 +4236,24 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>BMD-1712547-HAGAP.pdf</t>
+          <t>BMD PARCIAL JUSSARA - 1563492 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>117,63</t>
+          <t>64.923,56</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1712550</t>
+          <t>1667141</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4263,24 +4263,24 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>BMD-1712550-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1667141-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>421,10</t>
+          <t>509,47</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1712766</t>
+          <t>1694841</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4290,24 +4290,24 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>BMD-1712766-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1694841-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>705,45</t>
+          <t>4.476,57</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1713044I</t>
+          <t>1704877</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4317,24 +4317,24 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>BMD-1713044II-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1704877-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>1.528,53</t>
+          <t>158.642,45</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>1713226</t>
+          <t>1708877I</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4344,24 +4344,24 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>BMD-1713226-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1708877I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>237,93</t>
+          <t>2.132,72</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1714909</t>
+          <t>1709486</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4371,24 +4371,24 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>BMD-1714909-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1709486-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>107,93</t>
+          <t>4.402,38</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1715127</t>
+          <t>1711507</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4398,24 +4398,24 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>BMD-1715127-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1711507-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>128,31</t>
+          <t>14.415,50</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1715131</t>
+          <t>1711775</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4425,24 +4425,24 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>BMD-1715131-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1711775-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2.220,22</t>
+          <t>1.928,86</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>1715257I</t>
+          <t>1712531</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4452,24 +4452,24 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>BMD-1715257I-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1712531-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>6.765,65</t>
+          <t>5.019,99</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>1715668</t>
+          <t>1713226</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4479,24 +4479,24 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>BMD-1715668-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1713226-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>249,06</t>
+          <t>3.049,11</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>1715816C</t>
+          <t>1713656</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4506,24 +4506,24 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>BMD-1715816C-HAGAP  PARCIAL.pdf</t>
+          <t>BMD PARCIAL-1713656-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>30,22</t>
+          <t>4.315,58</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1715816I</t>
+          <t>1714342</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4533,24 +4533,24 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>BMD-1715816I-HAGAP  PARCIAL.pdf</t>
+          <t>BMD PARCIAL-1714342-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>3.168,40</t>
+          <t>1.949,56</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>1715899</t>
+          <t>1714699</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4560,24 +4560,24 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>BMD-1715899-HAGAP  PARCIAL.pdf</t>
+          <t>BMD PARCIAL-1714699-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>3.389,65</t>
+          <t>18.624,62</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>1717166</t>
+          <t>1715201</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4587,24 +4587,24 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>BMD-1717166-HAGAP  PARCIAL.pdf</t>
+          <t>BMD PARCIAL-1715201-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>22.116,83</t>
+          <t>6.987,28</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>1717168</t>
+          <t>1715668</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4614,24 +4614,24 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>BMD-1717168-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1715668-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.070,47</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1718442</t>
+          <t>1715955I</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4641,24 +4641,24 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>BMD-1718442-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1715955I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>45,19</t>
+          <t>2.970,68</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>1718561</t>
+          <t>1717168</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4668,24 +4668,24 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>BMD-1718561-HAGAP PARCIAL.pdf</t>
+          <t>BMD PARCIAL-1717168-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>13.683,99</t>
+          <t>2.528,74</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1719070</t>
+          <t>1717332</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4695,24 +4695,24 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>BMD-1719070-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1717332-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>333,14</t>
+          <t>2.320,28</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>1719213</t>
+          <t>1718442</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4722,24 +4722,24 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>BMD-1719213-HAGAP  PARCIAL.pdf</t>
+          <t>BMD PARCIAL-1718442-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>5.951,32</t>
+          <t>3.160,96</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>1719214</t>
+          <t>1718555I</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4749,24 +4749,24 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>BMD-1719214-HAGAP  PARCIAL.pdf</t>
+          <t>BMD PARCIAL-1718555I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>6.124,60</t>
+          <t>2.781,60</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>1719881</t>
+          <t>1721869</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4776,24 +4776,24 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>BMD-1719881-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1721869-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>3.239,73</t>
+          <t>807,18</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>1719881H</t>
+          <t>1725260</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4803,24 +4803,24 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>BMD-1719881HAGAP.pdf</t>
+          <t>BMD PARCIAL-1725260-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>38.258,42</t>
+          <t>4.716,47</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>1720116</t>
+          <t>1713221</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4830,12 +4830,12 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>BMD-1720116-HAGAP.pdf</t>
+          <t>BMD parcial - 1713221 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>168,95</t>
+          <t>18.794,09</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -4847,7 +4847,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>1721631</t>
+          <t>1667141</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4857,24 +4857,24 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>BMD-1721631-HAGAP  PARCIAL.pdf</t>
+          <t>BMD-1667141-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>12.649,43</t>
+          <t>152,42</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>1721631C</t>
+          <t>1675389</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4884,24 +4884,24 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>BMD-1721631C-HAGAP  PARCIAL.pdf</t>
+          <t>BMD-1675389-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>100,65</t>
+          <t>389,52</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1721869</t>
+          <t>1691390</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4911,24 +4911,24 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>BMD-1721869-HAGAP.pdf</t>
+          <t>BMD-1691390-HAGAP..pdf</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>133,09</t>
+          <t>457,30</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1721886</t>
+          <t>1703223</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4938,24 +4938,24 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>BMD-1721886 - HAGAP PARCIAL.pdf</t>
+          <t>BMD-1703223-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>14.551,70</t>
+          <t>1.471,15</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>1713044C</t>
+          <t>1708066</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4965,24 +4965,24 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>BMD.-1713044C.-HAGAP.pdf</t>
+          <t>BMD-1708066-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>21,11</t>
+          <t>3.419,06</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>1715327</t>
+          <t>1709486</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -4992,105 +4992,105 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>BMD.1715327-HAGAP.pdf</t>
+          <t>BMD-1709486-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>1.889,02</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>1708877</t>
+          <t>1711775</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>BMDFINAL-1708877-HAGAP.pdf</t>
+          <t>BMD-1711775-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>3,54</t>
+          <t>4,07</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>1712957</t>
+          <t>1712547</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>BMDFINAL-1712957-HAGAP.pdf</t>
+          <t>BMD-1712547-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>45,19</t>
+          <t>117,63</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>1717332</t>
+          <t>1712550</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>BMDFINAL-1717332-HAGAP.pdf</t>
+          <t>BMD-1712550-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>421,10</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>1703223</t>
+          <t>1712766</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5100,24 +5100,24 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1703223-HAGAP.pdf</t>
+          <t>BMD-1712766-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>18.169,34</t>
+          <t>705,45</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>1712547</t>
+          <t>1713044I</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5127,24 +5127,24 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1712547-HAGAP.pdf</t>
+          <t>BMD-1713044II-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>6.951,82</t>
+          <t>1.528,53</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1712957</t>
+          <t>1713226</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5154,24 +5154,24 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1712957-HAGAP.pdf</t>
+          <t>BMD-1713226-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2.177,64</t>
+          <t>237,93</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>1713262</t>
+          <t>1713626</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -5181,24 +5181,24 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1713262-HAGAP.pdf</t>
+          <t>BMD-1713626-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2.619,71</t>
+          <t>161,42</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>1714909</t>
+          <t>1713656I</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -5208,24 +5208,24 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1714909-HAGAP.pdf</t>
+          <t>BMD-1713656I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>954,64</t>
+          <t>161,74</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>1715127</t>
+          <t>1713660</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -5235,24 +5235,24 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1715127-HAGAP.pdf</t>
+          <t>BMD-1713660-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>4.418,94</t>
+          <t>161,11</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>1715327</t>
+          <t>1714857</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -5262,24 +5262,24 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1715327-HAGAP.pdf</t>
+          <t>BMD-1714857-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>5.417,39</t>
+          <t>185,07</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>1719070</t>
+          <t>1714909</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -5289,24 +5289,24 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1719070-HAGAP.pdf</t>
+          <t>BMD-1714909-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2.744,71</t>
+          <t>107,93</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>1719135</t>
+          <t>1715127</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -5316,24 +5316,24 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1719135-HAGAP.pdf</t>
+          <t>BMD-1715127-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>913,84</t>
+          <t>128,31</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>1720116</t>
+          <t>1715131</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -5343,24 +5343,24 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1720116-HAGAP.pdf</t>
+          <t>BMD-1715131-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>1.675,57</t>
+          <t>2.220,22</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>1724491</t>
+          <t>1715201</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -5370,39 +5370,39 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1724491-HAGAP.pdf</t>
+          <t>BMD-1715201-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>14.377,51</t>
+          <t>3,29</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>1712766</t>
+          <t>1715257I</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>FF0-1712766-HAGAP.pdf</t>
+          <t>BMD-1715257I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>6.765,65</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -5414,152 +5414,152 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>1719135</t>
+          <t>1715668</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>FFO  -1719135-HAGAP.pdf</t>
+          <t>BMD-1715668-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>249,06</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>1688115C</t>
+          <t>1715816C</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>FFO - 1688115C - HAGAP.pdf</t>
+          <t>BMD-1715816C-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>30,22</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>1688115I</t>
+          <t>1715816I</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>FFO - 1688115I - HAGAP.pdf</t>
+          <t>BMD-1715816I-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>3.168,40</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>1692174</t>
+          <t>1715899</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>FFO - 1692174 - HAGAP.pdf</t>
+          <t>BMD-1715899-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>3.389,65</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>1698047</t>
+          <t>1717166</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>FFO - 1698047 - HAGAP - 30-04-2026.pdf</t>
+          <t>BMD-1717166-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>22.116,83</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>1702127</t>
+          <t>1717168</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>FFO - 1702127 - HAGAP.pdf</t>
+          <t>BMD-1717168-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -5569,375 +5569,375 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>1702776C</t>
+          <t>1718442</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>FFO - 1702776C - HAGAP.pdf</t>
+          <t>BMD-1718442-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>45,19</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>1702776I</t>
+          <t>1718561</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>FFO - 1702776I - HAGAP.pdf</t>
+          <t>BMD-1718561-HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>13.683,99</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>1704867</t>
+          <t>1719070</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>FFO - 1704867 - ASP.pdf</t>
+          <t>BMD-1719070-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>333,14</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>1705802I</t>
+          <t>1719213</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>FFO - 1705802I - HAGAP.pdf</t>
+          <t>BMD-1719213-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>5.951,32</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>1709419</t>
+          <t>1719214</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>FFO - 1709419 - HAGAP.pdf</t>
+          <t>BMD-1719214-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>6.124,60</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>1709995</t>
+          <t>1719881</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>FFO - 1709995 - HAGAP.pdf</t>
+          <t>BMD-1719881-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>3.239,73</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>1711384</t>
+          <t>1719881H</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>FFO - 1711384 - HAGAP.pdf</t>
+          <t>BMD-1719881HAGAP.pdf</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>38.258,42</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>1712538</t>
+          <t>1720116</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>FFO - 1712538 - HAGAP.pdf</t>
+          <t>BMD-1720116-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>168,95</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>1713221</t>
+          <t>1721631</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>FFO - 1713221 - HAGAP.pdf</t>
+          <t>BMD-1721631-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>12.649,43</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>1713240</t>
+          <t>1721631C</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>FFO - 1713240 - HAGAP - 20-05-2026.pdf</t>
+          <t>BMD-1721631C-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>100,65</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>1715878</t>
+          <t>1721869</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>FFO - 1715878 - HAGAP - 20-05-2026.pdf</t>
+          <t>BMD-1721869-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>133,09</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>1641139I</t>
+          <t>1721886</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>FFO 1641139I HAGAP.pdf</t>
+          <t>BMD-1721886 - HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>14.551,70</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>1710736</t>
+          <t>1713044C</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>FFO 1710736 HAGAP.pdf</t>
+          <t>BMD.-1713044C.-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>21,11</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>1710975</t>
+          <t>1715327</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>FFO 1710975 HAGAP.pdf</t>
+          <t>BMD.1715327-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -5947,14 +5947,14 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>1712533</t>
+          <t>1708877</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -5964,24 +5964,24 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>FFO 1712533 HAGAP.pdf</t>
+          <t>BMDFINAL-1708877-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>3,54</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>1713435I</t>
+          <t>1712957</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -5991,24 +5991,24 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>FFO 1713435I HAGAP.pdf</t>
+          <t>BMDFINAL-1712957-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>45,19</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>1713679</t>
+          <t>1717332</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>FFO 1713679 HAGAP.pdf</t>
+          <t>BMDFINAL-1717332-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -6028,348 +6028,348 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>1714364</t>
+          <t>1703223</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>FFO 1714364 HAGAP.pdf</t>
+          <t>BMDPARCIAL-1703223-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>18.169,34</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>1714729</t>
+          <t>1712547</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>FFO 1714729 HAGAP.pdf</t>
+          <t>BMDPARCIAL-1712547-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>6.951,82</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>1715154</t>
+          <t>1712957</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>FFO 1715154 HAGAP.pdf</t>
+          <t>BMDPARCIAL-1712957-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.177,64</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>1718803</t>
+          <t>1713262</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>FFO 1718803 HAGAP.pdf</t>
+          <t>BMDPARCIAL-1713262-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.619,71</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>1720721</t>
+          <t>1714909</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>FFO 1720721 HAGAP.pdf</t>
+          <t>BMDPARCIAL-1714909-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>954,64</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>1667141</t>
+          <t>1715127</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>FFO-1667141-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1715127-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>4.418,94</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>1675389</t>
+          <t>1715327</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>FFO-1675389-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1715327-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>5.417,39</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>1691390</t>
+          <t>1719070</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>FFO-1691390-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1719070-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.744,71</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>1703223</t>
+          <t>1719135</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>FFO-1703223-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1719135-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>913,84</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>1708877</t>
+          <t>1720116</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>FFO-1708877-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1720116-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>1.675,57</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>1710116</t>
+          <t>1724491</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>FFO-1710116-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1724491-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>14.377,51</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>1711110</t>
+          <t>1717315</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>FFO-1711110-HAGAP.pdf</t>
+          <t>BMD_1717315_HAGAP.pdf</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>13.183,29</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>1712531</t>
+          <t>1725869</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>FFO-1712531-HAGAP.pdf</t>
+          <t>BMD_1725869_HAGAP.pdf</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -6379,14 +6379,14 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>1712547</t>
+          <t>1712766</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>FFO-1712547-HAGAP.pdf</t>
+          <t>FF0-1712766-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -6406,14 +6406,14 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>1712550</t>
+          <t>1719135</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -6423,7 +6423,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>FFO-1712550-HAGAP.pdf</t>
+          <t>FFO  -1719135-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -6433,14 +6433,14 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>1713044C</t>
+          <t>1677314</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -6450,7 +6450,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>FFO-1713044C.-HAGAP.pdf</t>
+          <t>FFO - 1677314 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -6460,14 +6460,14 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>1713044I</t>
+          <t>1677316</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>FFO-1713044II-HAGAP.pdf</t>
+          <t>FFO - 1677316 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -6487,14 +6487,14 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>1713226</t>
+          <t>1688115C</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -6504,7 +6504,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>FFO-1713226-HAGAP.pdf</t>
+          <t>FFO - 1688115C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -6514,14 +6514,14 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>1713262</t>
+          <t>1688115I</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -6531,7 +6531,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>FFO-1713262-HAGAP.pdf</t>
+          <t>FFO - 1688115I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -6541,14 +6541,14 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>1714909</t>
+          <t>1691534</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>FFO-1714909-HAGAP.pdf</t>
+          <t>FFO - 1691534 - HAGAP - 03-07-2026.pdf</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -6568,14 +6568,14 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>1715127</t>
+          <t>1692174</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -6585,7 +6585,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>FFO-1715127-HAGAP.pdf</t>
+          <t>FFO - 1692174 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -6595,14 +6595,14 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>1715257I</t>
+          <t>1698047</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>FFO-1715257I-HAGAP.pdf</t>
+          <t>FFO - 1698047 - HAGAP - 30-04-2026.pdf</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -6622,14 +6622,14 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>1715327</t>
+          <t>1702127</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -6639,24 +6639,24 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>FFO-1715327-HAGAP.pdf</t>
+          <t>FFO - 1702127 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>65,98</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>1715668</t>
+          <t>1702640</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -6666,7 +6666,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>FFO-1715668-HAGAP.pdf</t>
+          <t>FFO - 1702640 - HAGAP - 10-07-2026.pdf</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -6676,14 +6676,14 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>1717168</t>
+          <t>1702776C</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -6693,24 +6693,24 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>FFO-1717168-HAGAP.pdf</t>
+          <t>FFO - 1702776C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>87,00</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>1717332</t>
+          <t>1702776I</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>FFO-1717332-HAGAP.pdf</t>
+          <t>FFO - 1702776I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>176,23</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -6737,7 +6737,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>1719070</t>
+          <t>1704867</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>FFO-1719070-HAGAP.pdf</t>
+          <t>FFO - 1704867 - ASP.pdf</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -6757,14 +6757,14 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>1719881</t>
+          <t>1705802I</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -6774,7 +6774,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>FFO-1719881-HAGAP.pdf</t>
+          <t>FFO - 1705802I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -6784,14 +6784,14 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>1721869</t>
+          <t>1709419</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>FFO-1721869-HAGAP.pdf</t>
+          <t>FFO - 1709419 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -6811,14 +6811,14 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>1708066</t>
+          <t>1709995</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -6828,7 +6828,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>FFO.-1708066-HAGAP.pdf</t>
+          <t>FFO - 1709995 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -6838,14 +6838,14 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>1712957</t>
+          <t>1711384</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>FFO.-1712957-HAGAP.pdf</t>
+          <t>FFO - 1711384 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -6865,14 +6865,14 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>1691380</t>
+          <t>1712538</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -6882,7 +6882,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>FFO_1691380.pdf</t>
+          <t>FFO - 1712538 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -6892,14 +6892,14 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>1718442</t>
+          <t>1713221</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -6909,7 +6909,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>FFO´1718442-HAGAP.pdf</t>
+          <t>FFO - 1713221 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -6919,24 +6919,24 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>1703223</t>
+          <t>1713240</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>MULTA-1703223-HAGAP.pdf</t>
+          <t>FFO - 1713240 - HAGAP - 20-05-2026.pdf</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -6944,53 +6944,1727 @@
           <t>0,00</t>
         </is>
       </c>
-      <c r="E242" t="inlineStr"/>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>1713044I</t>
+          <t>1715278</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>MULTA-1713044I-HAGAP.pdf</t>
+          <t>FFO - 1715278 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>0,00</t>
-        </is>
-      </c>
-      <c r="E243" t="inlineStr"/>
+          <t>306,36</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
+          <t>1715688</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>FFO - 1715688 - HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>1715878</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>FFO - 1715878 - HAGAP - 20-05-2026.pdf</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>1520615</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>FFO 1520615 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>1641139I</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>FFO 1641139I HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>1682195</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>FFO 1682195 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>1693027</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>FFO 1693027 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>1704525</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>FFO 1704525 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>1710736</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>FFO 1710736 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>1710975</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>FFO 1710975 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>1711525</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>FFO 1711525 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>1712533</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>FFO 1712533 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>1713435I</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>FFO 1713435I HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>1713679</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>FFO 1713679 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>1714364</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>FFO 1714364 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>1714729</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>FFO 1714729 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>1715154</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>FFO 1715154 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>1718561</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>FFO 1718561 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>1.543,28</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>1718803</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>FFO 1718803 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>1719155</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>FFO 1719155 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>1720721</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>FFO 1720721 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>1720909</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>FFO 1720909 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>1720920</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>FFO 1720920 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>1722904</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>FFO 1722904 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>1667141</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>FFO-1667141-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>1675389</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>FFO-1675389-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>1691390</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>FFO-1691390-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>1703223</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>FFO-1703223-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>1708877</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>FFO-1708877-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>1709486</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>FFO-1709486-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>1710116</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>FFO-1710116-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>1711110</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>FFO-1711110-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>1711775</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>FFO-1711775-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>1712531</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>FFO-1712531-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>1712547</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>FFO-1712547-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>1712550</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>FFO-1712550-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>1713044C</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>FFO-1713044C.-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>1713044I</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>FFO-1713044II-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>1713226</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>FFO-1713226-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>1713262</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>FFO-1713262-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>1713626</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>FFO-1713626-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>1713656I</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>FFO-1713656I-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>1714857</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>FFO-1714857-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>1714909</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>FFO-1714909-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>1715127</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>FFO-1715127-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>1715201</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>FFO-1715201-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>1715257I</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>FFO-1715257I-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
           <t>1715327</t>
         </is>
       </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>BMD</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr">
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>FFO-1715327-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>65,98</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>1715668</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>FFO-1715668-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>1717168</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>FFO-1717168-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>87,00</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>1717332</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>FFO-1717332-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>176,23</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>1719070</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>FFO-1719070-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>1719881</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>FFO-1719881-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>1721869</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>FFO-1721869-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>1708066</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>FFO.-1708066-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>1712957</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>FFO.-1712957-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>1713660</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>FFO.-1713660-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>1691380</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>FFO_1691380.pdf</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>1717315</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>FFO_1717315_HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>1725869</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>FFO_1725869_HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>2.488,83</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>1718442</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>FFO´1718442-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>1703223</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>MULTA-1703223-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr"/>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>1713044I</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>MULTA-1713044I-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr"/>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>1715327</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
         <is>
           <t>MULTA-1715327-HAGAP.pdf</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
-      </c>
-      <c r="E244" t="inlineStr"/>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/medicoes.xlsx
+++ b/medicoes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E306"/>
+  <dimension ref="A1:E363"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1779,24 +1779,24 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>BMD - 1658892 - HAGAP - 22-06-2026.pdf</t>
+          <t>BMD - 1658892 - HAGAP - 15-07-2026.pdf</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>38.435,91</t>
+          <t>2.353,51</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1677314</t>
+          <t>1658892</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1806,24 +1806,24 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>BMD - 1677314 - HAGAP.pdf</t>
+          <t>BMD - 1658892 - HAGAP - 22-06-2026.pdf</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>4.880,14</t>
+          <t>38.435,91</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1688115C</t>
+          <t>1677314</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1833,24 +1833,24 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>BMD - 1688115C - HAGAP.pdf</t>
+          <t>BMD - 1677314 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>6,65</t>
+          <t>4.880,14</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1688115I</t>
+          <t>1688115C</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1860,12 +1860,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>BMD - 1688115I - HAGAP.pdf</t>
+          <t>BMD - 1688115C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2.670,64</t>
+          <t>6,65</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1877,7 +1877,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1691534</t>
+          <t>1688115I</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1887,24 +1887,24 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>BMD - 1691534 - HAGAP - 03-07-2026.pdf</t>
+          <t>BMD - 1688115I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>996,86</t>
+          <t>2.670,64</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1698047</t>
+          <t>1691534</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1914,24 +1914,24 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>BMD - 1698047 - HAGAP 30-04-2026.pdf</t>
+          <t>BMD - 1691534 - HAGAP - 03-07-2026.pdf</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2.449,89</t>
+          <t>996,86</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1702640</t>
+          <t>1698047</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1941,24 +1941,24 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>BMD - 1702640 - HAGAP - 10-07-2026.pdf</t>
+          <t>BMD - 1698047 - HAGAP 30-04-2026.pdf</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2.963,92</t>
+          <t>2.449,89</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1704867</t>
+          <t>1698056</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1968,24 +1968,24 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>BMD - 1704867 - ASP.pdf</t>
+          <t>BMD - 1698056 - HAGAP - 17-07-2026.pdf</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>23.915,48</t>
+          <t>692,14</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1709995</t>
+          <t>1702640</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1995,24 +1995,24 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>BMD - 1709995 - HAGAP.pdf</t>
+          <t>BMD - 1702640 - HAGAP - 10-07-2026.pdf</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2.410,16</t>
+          <t>2.963,92</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1711384</t>
+          <t>1704867</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2022,24 +2022,24 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>BMD - 1711384 - HAGAP.pdf</t>
+          <t>BMD - 1704867 - ASP.pdf</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>122,95</t>
+          <t>23.915,48</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1712538</t>
+          <t>1707174</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2049,24 +2049,24 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>BMD - 1712538 - HAGAP.pdf</t>
+          <t>BMD - 1707174 - HAGAP - 17-07-2026.pdf</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>387,36</t>
+          <t>1.924,94</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1713240</t>
+          <t>1709995</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2076,24 +2076,24 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>BMD - 1713240 - HAGAP - 20-05-2026.pdf</t>
+          <t>BMD - 1709995 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>5.108,11</t>
+          <t>2.410,16</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1713933</t>
+          <t>1711384</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2103,24 +2103,24 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>BMD - 1713933 - HAGAP - 20-05-2026.pdf</t>
+          <t>BMD - 1711384 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>5.530,92</t>
+          <t>122,95</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1715878</t>
+          <t>1712538</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2130,24 +2130,24 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>BMD - 1715878 - HAGAP - 20-05-2026.pdf</t>
+          <t>BMD - 1712538 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>1.786,71</t>
+          <t>387,36</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1718435</t>
+          <t>1713240</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2157,24 +2157,24 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>BMD - 1718435 - HAGAP - 20-05-2026.pdf</t>
+          <t>BMD - 1713240 - HAGAP - 20-05-2026.pdf</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>17.153,90</t>
+          <t>5.108,11</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1718783</t>
+          <t>1713933</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2184,24 +2184,24 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>BMD - 1718783 - HAGAP.pdf</t>
+          <t>BMD - 1713933 - HAGAP - 20-05-2026.pdf</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>16.983,02</t>
+          <t>5.530,92</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1718783C</t>
+          <t>1715878</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>BMD - 1718783C - HAGAP.pdf</t>
+          <t>BMD - 1715878 - HAGAP - 20-05-2026.pdf</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>7,32</t>
+          <t>1.786,71</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1722169</t>
+          <t>1718435</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2238,24 +2238,24 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>BMD - 1722169 - HAGAP - 25-06-2026.pdf</t>
+          <t>BMD - 1718435 - HAGAP - 20-05-2026.pdf</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>1.225,38</t>
+          <t>17.153,90</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1725738C</t>
+          <t>1718783</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2265,24 +2265,24 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>BMD - 1725738C - HAGAP.pdf</t>
+          <t>BMD - 1718783 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>140,91</t>
+          <t>16.983,02</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1725738I</t>
+          <t>1718783C</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2292,24 +2292,24 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>BMD - 1725738I - HAGAP.pdf</t>
+          <t>BMD - 1718783C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>15.544,67</t>
+          <t>7,32</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1520612</t>
+          <t>1722169</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2319,24 +2319,24 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>BMD 1520612 HAGAP.pdf</t>
+          <t>BMD - 1722169 - HAGAP - 25-06-2026.pdf</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>53.357,33</t>
+          <t>1.225,38</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1520615</t>
+          <t>1722321</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2346,24 +2346,24 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>BMD 1520615 HAGAP.pdf</t>
+          <t>BMD - 1722321 - HAGAP - 15-07-2026.pdf</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>22.840,59</t>
+          <t>8.119,58</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1660062C</t>
+          <t>1724051I</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2373,24 +2373,24 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>BMD 1660062C HAGAP PARCIAL.pdf</t>
+          <t>BMD - 1724051I - HAGAP - 15-07-2026.pdf</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>100,65</t>
+          <t>2.432,48</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1660062I</t>
+          <t>1725738C</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2400,24 +2400,24 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>BMD 1660062I HAGAP PARCIAL.pdf</t>
+          <t>BMD - 1725738C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>11.953,89</t>
+          <t>140,91</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1671139I</t>
+          <t>1725738I</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2427,24 +2427,24 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>BMD 1671139I HAGAP.pdf</t>
+          <t>BMD - 1725738I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>6.138,54</t>
+          <t>15.544,67</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1692636</t>
+          <t>1520612</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2454,24 +2454,24 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>BMD 1692636 ASP.pdf</t>
+          <t>BMD 1520612 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>19.387,05</t>
+          <t>53.357,33</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1699516</t>
+          <t>1520615</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2481,24 +2481,24 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>BMD 1699516 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1520615 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>3.388,62</t>
+          <t>22.840,59</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1704525</t>
+          <t>1536912</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2508,24 +2508,24 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>BMD 1704525 FF HAGAP.pdf</t>
+          <t>BMD 1536912 PARCIAL HAGAP.pdf</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>86,77</t>
+          <t>2.474,56</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1704525</t>
+          <t>1660062C</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2535,24 +2535,24 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>BMD 1704525 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1660062C HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>15.365,48</t>
+          <t>100,65</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1704891</t>
+          <t>1660062I</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2562,24 +2562,24 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>BMD 1704891 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1660062I HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>41.477,99</t>
+          <t>11.953,89</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1705074</t>
+          <t>1671139I</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2589,24 +2589,24 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>BMD 1705074 HAGAP.pdf</t>
+          <t>BMD 1671139I HAGAP.pdf</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>150.312,87</t>
+          <t>6.138,54</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1708906</t>
+          <t>1692636</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2616,24 +2616,24 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>BMD 1708906  30-04-2026 HAGAP.pdf</t>
+          <t>BMD 1692636 ASP.pdf</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>7.584,06</t>
+          <t>19.387,05</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1710329</t>
+          <t>1699516</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2643,24 +2643,24 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>BMD 1710329 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1699516 FF HAGAP.pdf</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>24.209,42</t>
+          <t>287,85</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1710937</t>
+          <t>1699516</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2670,12 +2670,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>BMD 1710937 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1699516 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>3.388,62</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -2687,7 +2687,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1710975</t>
+          <t>1704525</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2697,24 +2697,24 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>BMD 1710975 HAGAP FF.pdf</t>
+          <t>BMD 1704525 FF HAGAP.pdf</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>913,41</t>
+          <t>86,77</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1711525</t>
+          <t>1704525</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2724,24 +2724,24 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>BMD 1711525 FF HAGAP.pdf</t>
+          <t>BMD 1704525 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>126,93</t>
+          <t>15.365,48</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1711525</t>
+          <t>1704891</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2751,24 +2751,24 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>BMD 1711525 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1704891 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>1.998,42</t>
+          <t>41.477,99</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1712533</t>
+          <t>1705074</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2778,24 +2778,24 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>BMD 1712533 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1705074 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2.553,46</t>
+          <t>150.312,87</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1712624</t>
+          <t>1708906</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2805,24 +2805,24 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>BMD 1712624 HAGAP.pdf</t>
+          <t>BMD 1708906  30-04-2026 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>3.073,90</t>
+          <t>7.584,06</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1713223</t>
+          <t>1710329</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2832,24 +2832,24 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>BMD 1713223 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1710329 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>9.773,21</t>
+          <t>24.209,42</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1713679</t>
+          <t>1710937</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>BMD 1713679 HAGAP.pdf</t>
+          <t>BMD 1710937 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>3.574,44</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -2876,7 +2876,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1713719</t>
+          <t>1710975</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2886,24 +2886,24 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>BMD 1713719 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1710975 HAGAP FF.pdf</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>3.385,92</t>
+          <t>913,41</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1714364</t>
+          <t>1711525</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2913,24 +2913,24 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>BMD 1714364 HAGAP FF.pdf</t>
+          <t>BMD 1711525 FF HAGAP.pdf</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>54,64</t>
+          <t>126,93</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1714729</t>
+          <t>1711525</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2940,24 +2940,24 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>BMD 1714729 HAGAP.pdf</t>
+          <t>BMD 1711525 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>6.722,61</t>
+          <t>1.998,42</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1715154</t>
+          <t>1711629</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2967,24 +2967,24 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>BMD 1715154 HAGAP.pdf</t>
+          <t>BMD 1711629 PARCIAL HAGAP.pdf</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2.658,74</t>
+          <t>4.201,07</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1715920</t>
+          <t>1712533</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2994,24 +2994,24 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>BMD 1715920 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1712533 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>1.031,94</t>
+          <t>2.553,46</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1718561</t>
+          <t>1712624</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3021,24 +3021,24 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>BMD 1718561 FF HAGAP.pdf</t>
+          <t>BMD 1712624 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>3.073,90</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1718803</t>
+          <t>1713223</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3048,24 +3048,24 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>BMD 1718803 HAGAP.pdf</t>
+          <t>BMD 1713223 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>3.825,18</t>
+          <t>9.773,21</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1719097</t>
+          <t>1713351</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3075,24 +3075,24 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>BMD 1719097 HAGAP.pdf</t>
+          <t>BMD 1713351 HAGAPP.pdf</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>7.450,28</t>
+          <t>622,97</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1719155</t>
+          <t>1713679</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3102,12 +3102,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>BMD 1719155 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1713679 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2.223,15</t>
+          <t>3.574,44</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -3119,7 +3119,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1719213</t>
+          <t>1713719</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3129,24 +3129,24 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>BMD 1719213 FF HAGAP.pdf</t>
+          <t>BMD 1713719 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>1.371,87</t>
+          <t>3.385,92</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1720721</t>
+          <t>1714364</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>BMD 1720721 HAGAP.pdf</t>
+          <t>BMD 1714364 HAGAP FF.pdf</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2.015,45</t>
+          <t>54,64</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1720909</t>
+          <t>1714729</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3183,24 +3183,24 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>BMD 1720909 HAGAP.pdf</t>
+          <t>BMD 1714729 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2.851,89</t>
+          <t>6.722,61</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1720920</t>
+          <t>1715154</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3210,24 +3210,24 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>BMD 1720920 FF HAGAP.pdf</t>
+          <t>BMD 1715154 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>89,29</t>
+          <t>2.658,74</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1720920</t>
+          <t>1715920</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3237,24 +3237,24 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>BMD 1720920 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1715920 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>555,60</t>
+          <t>1.031,94</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1722904</t>
+          <t>1718561</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3264,24 +3264,24 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>BMD 1722904 HAGAP.pdf</t>
+          <t>BMD 1718561 FF HAGAP.pdf</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2.417,20</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1724356</t>
+          <t>1718803</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3291,24 +3291,24 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>BMD 1724356 HAGAP.pdf</t>
+          <t>BMD 1718803 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>7.614,80</t>
+          <t>3.825,18</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1728163</t>
+          <t>1719097</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3318,24 +3318,24 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>BMD 1728163 HAGAP.pdf</t>
+          <t>BMD 1719097 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>7.914,69</t>
+          <t>7.450,28</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1682195</t>
+          <t>1719155</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3345,24 +3345,24 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>BMD FF 1682195 HAGAP.pdf</t>
+          <t>BMD 1719155 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>8,36</t>
+          <t>2.223,15</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1693027</t>
+          <t>1719159</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3372,24 +3372,24 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>BMD FF 1693027 HAGAP.pdf</t>
+          <t>BMD 1719159 PARCIAL HAGAP.pdf</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2.215,91</t>
+          <t>2.240,81</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1712533</t>
+          <t>1719213</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3399,24 +3399,24 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>BMD FF 1712533 HAGAP.pdf</t>
+          <t>BMD 1719213 FF HAGAP.pdf</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>127,40</t>
+          <t>1.371,87</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1719155</t>
+          <t>1720721</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3426,213 +3426,213 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>BMD FF 1719155 HAGAP.pdf</t>
+          <t>BMD 1720721 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>145,82</t>
+          <t>2.015,45</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1677316</t>
+          <t>1720909</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>BMD FINAL - 1677316 HAGAP.pdf</t>
+          <t>BMD 1720909 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.851,89</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1702776C</t>
+          <t>1720920</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>BMD FINAL - 1702776C - HAGAP.pdf</t>
+          <t>BMD 1720920 FF HAGAP.pdf</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>89,29</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1702776I</t>
+          <t>1720920</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>BMD FINAL - 1702776I - HAGAP.pdf</t>
+          <t>BMD 1720920 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>18.098,87</t>
+          <t>555,60</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1715278</t>
+          <t>1721175</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>BMD FINAL - 1715278 - HAGAP.pdf</t>
+          <t>BMD 1721175 PARCIAL HAGAP.pdf</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>1.191,73</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1715688</t>
+          <t>1721595</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>BMD FINAL - 1715688 - HAGAP.pdf</t>
+          <t>BMD 1721595 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>1.425,04</t>
+          <t>2.704,41</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1713262</t>
+          <t>1721884</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>BMD FINAL-1713262-HAGAP.pdf</t>
+          <t>BMD 1721884 PARCIAL HAGAP.pdf</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>55,90</t>
+          <t>41.481,66</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1719135</t>
+          <t>1722320</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>BMD FINAL-1719135-HAGAP.pdf</t>
+          <t>BMD 1722320 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>47,08</t>
+          <t>12.790,83</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1712550</t>
+          <t>1722904</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>BMD PARCAIL-1712550-HAGAP.pdf</t>
+          <t>BMD 1722904 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>4.585,98</t>
+          <t>2.417,20</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -3659,7 +3659,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1677314</t>
+          <t>1724172</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3669,24 +3669,24 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1677314 - HAGAP.pdf</t>
+          <t>BMD 1724172 PARCIAL HAGAP.pdf</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>46.760,40</t>
+          <t>23.068,97</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1677316</t>
+          <t>1724356</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3696,24 +3696,24 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1677316 HAGAP.pdf</t>
+          <t>BMD 1724356 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>51.623,62</t>
+          <t>7.614,80</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1688115C</t>
+          <t>1725686</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3723,24 +3723,24 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1688115C - HAGAP.pdf</t>
+          <t>BMD 1725686 PARCIAL HAGAP.pdf</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>6,36</t>
+          <t>11.172,87</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1688115I</t>
+          <t>1726332</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3750,24 +3750,24 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1688115I - HAGAP.pdf</t>
+          <t>BMD 1726332 PARCIAL HAGAP.pdf</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>18.752,84</t>
+          <t>5.722,23</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1691534</t>
+          <t>1728055</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3777,24 +3777,24 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1691534 - HAGAP - 19-06-2026.pdf</t>
+          <t>BMD 1728055 PARCIAL HAGAP.pdf</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>20.334,45</t>
+          <t>12.947,91</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1694258</t>
+          <t>1728163</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3804,24 +3804,24 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1694258 - HAGAP.pdf</t>
+          <t>BMD 1728163 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>127.751,38</t>
+          <t>7.914,69</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1695716</t>
+          <t>1682195</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3831,24 +3831,24 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1695716 - HAGAP.pdf</t>
+          <t>BMD FF 1682195 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>74.647,17</t>
+          <t>8,36</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1698056</t>
+          <t>1693027</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3858,24 +3858,24 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1698056 - HAGAP - 22-06-2026.pdf</t>
+          <t>BMD FF 1693027 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>8.966,25</t>
+          <t>2.215,91</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>1710735</t>
+          <t>1710329</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3885,24 +3885,24 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1710735 HAGAP.pdf</t>
+          <t>BMD FF 1710329 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>9.153,35</t>
+          <t>2,44</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1711384</t>
+          <t>1712533</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3912,24 +3912,24 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1711384 - HAGAP.pdf</t>
+          <t>BMD FF 1712533 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2.127,38</t>
+          <t>127,40</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1712538</t>
+          <t>1719155</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3939,213 +3939,213 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1712538 - HAGAP.pdf</t>
+          <t>BMD FF 1719155 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>3.568,05</t>
+          <t>145,82</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>1715278</t>
+          <t>1677316</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1715278 - HAGAP.pdf</t>
+          <t>BMD FINAL - 1677316 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2.654,77</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1715688</t>
+          <t>1702776C</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1715688 - HAGAP.pdf</t>
+          <t>BMD FINAL - 1702776C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>9.669,94</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1720914</t>
+          <t>1702776I</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1720914 - HAGAP.pdf</t>
+          <t>BMD FINAL - 1702776I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>13.736,92</t>
+          <t>18.098,87</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1721887</t>
+          <t>1715278</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1721887 - HAGAP.pdf</t>
+          <t>BMD FINAL - 1715278 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>15.229,27</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1722169</t>
+          <t>1715688</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1722169 - HAGAP - 19-06-2026.pdf</t>
+          <t>BMD FINAL - 1715688 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>38.238,91</t>
+          <t>1.425,04</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1722779</t>
+          <t>1713262</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1722779 - HAGAP.pdf</t>
+          <t>BMD FINAL-1713262-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>14.090,54</t>
+          <t>55,90</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1712530</t>
+          <t>1719135</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>BMD PARCIAL -1712530-HAGAP.pdf</t>
+          <t>BMD FINAL-1719135-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>5.393,72</t>
+          <t>47,08</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1713626I</t>
+          <t>1712550</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4155,24 +4155,24 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>BMD PARCIAL -1713626I-HAGAP.pdf</t>
+          <t>BMD PARCAIL-1712550-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>5.318,80</t>
+          <t>4.585,98</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1713260</t>
+          <t>1677314</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -4182,24 +4182,24 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>BMD PARCIAL 1713260 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1677314 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>8.854,04</t>
+          <t>46.760,40</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1563492</t>
+          <t>1677316</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -4209,24 +4209,24 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>BMD PARCIAL CIANORTE - 1563492 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1677316 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>80.240,76</t>
+          <t>51.623,62</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1563492</t>
+          <t>1688115C</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4236,24 +4236,24 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>BMD PARCIAL JUSSARA - 1563492 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1688115C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>64.923,56</t>
+          <t>6,36</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1667141</t>
+          <t>1688115I</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4263,24 +4263,24 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1667141-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1688115I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>509,47</t>
+          <t>18.752,84</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1694841</t>
+          <t>1691534</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4290,24 +4290,24 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1694841-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1691534 - HAGAP - 19-06-2026.pdf</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>4.476,57</t>
+          <t>20.334,45</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1704877</t>
+          <t>1694258</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4317,24 +4317,24 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1704877-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1694258 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>158.642,45</t>
+          <t>127.751,38</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>1708877I</t>
+          <t>1695716</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1708877I-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1695716 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2.132,72</t>
+          <t>74.647,17</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -4361,7 +4361,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1709486</t>
+          <t>1698056</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4371,24 +4371,24 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1709486-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1698056 - HAGAP - 22-06-2026.pdf</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>4.402,38</t>
+          <t>8.966,25</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1711507</t>
+          <t>1710735</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4398,24 +4398,24 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1711507-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1710735 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>14.415,50</t>
+          <t>9.153,35</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1711775</t>
+          <t>1711384</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4425,24 +4425,24 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1711775-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1711384 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>1.928,86</t>
+          <t>2.127,38</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>1712531</t>
+          <t>1712538</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4452,24 +4452,24 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1712531-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1712538 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>5.019,99</t>
+          <t>3.568,05</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>1713226</t>
+          <t>1715278</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4479,24 +4479,24 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1713226-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1715278 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>3.049,11</t>
+          <t>2.654,77</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>1713656</t>
+          <t>1715688</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4506,24 +4506,24 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1713656-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1715688 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>4.315,58</t>
+          <t>9.669,94</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1714342</t>
+          <t>1720914</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4533,24 +4533,24 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1714342-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1720914 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>1.949,56</t>
+          <t>13.736,92</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>1714699</t>
+          <t>1721887</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4560,24 +4560,24 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1714699-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1721887 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>18.624,62</t>
+          <t>15.229,27</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>1715201</t>
+          <t>1722169</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4587,24 +4587,24 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1715201-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1722169 - HAGAP - 19-06-2026.pdf</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>6.987,28</t>
+          <t>38.238,91</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>1715668</t>
+          <t>1722779</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4614,24 +4614,24 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1715668-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1722779 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2.070,47</t>
+          <t>14.090,54</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1715955I</t>
+          <t>1712530</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4641,24 +4641,24 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1715955I-HAGAP.pdf</t>
+          <t>BMD PARCIAL -1712530-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2.970,68</t>
+          <t>5.393,72</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>1717168</t>
+          <t>1713626I</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4668,24 +4668,24 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1717168-HAGAP.pdf</t>
+          <t>BMD PARCIAL -1713626I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2.528,74</t>
+          <t>5.318,80</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1717332</t>
+          <t>1713260</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4695,24 +4695,24 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1717332-HAGAP.pdf</t>
+          <t>BMD PARCIAL 1713260 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2.320,28</t>
+          <t>8.854,04</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>1718442</t>
+          <t>1563492</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4722,24 +4722,24 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1718442-HAGAP.pdf</t>
+          <t>BMD PARCIAL CIANORTE - 1563492 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>3.160,96</t>
+          <t>80.240,76</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>1718555I</t>
+          <t>1563492</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4749,24 +4749,24 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1718555I-HAGAP.pdf</t>
+          <t>BMD PARCIAL JUSSARA - 1563492 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2.781,60</t>
+          <t>64.923,56</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>1721869</t>
+          <t>1667141</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4776,24 +4776,24 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1721869-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1667141-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>807,18</t>
+          <t>509,47</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>1725260</t>
+          <t>1694841</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4803,24 +4803,24 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1725260-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1694841-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>4.716,47</t>
+          <t>4.476,57</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>1713221</t>
+          <t>1704877</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4830,24 +4830,24 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>BMD parcial - 1713221 - HAGAP.pdf</t>
+          <t>BMD PARCIAL-1704877-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>18.794,09</t>
+          <t>158.642,45</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>1667141</t>
+          <t>1708877I</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4857,24 +4857,24 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>BMD-1667141-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1708877I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>152,42</t>
+          <t>2.132,72</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>1675389</t>
+          <t>1709486</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4884,24 +4884,24 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>BMD-1675389-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1709486-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>389,52</t>
+          <t>4.402,38</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1691390</t>
+          <t>1711507</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4911,24 +4911,24 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>BMD-1691390-HAGAP..pdf</t>
+          <t>BMD PARCIAL-1711507-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>457,30</t>
+          <t>14.415,50</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1703223</t>
+          <t>1711775</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4938,24 +4938,24 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>BMD-1703223-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1711775-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>1.471,15</t>
+          <t>1.928,86</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>1708066</t>
+          <t>1712531</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4965,24 +4965,24 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>BMD-1708066-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1712531-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>3.419,06</t>
+          <t>5.019,99</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>1709486</t>
+          <t>1712963I</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -4992,24 +4992,24 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>BMD-1709486-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1712963I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>1.889,02</t>
+          <t>12.285,61</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>1711775</t>
+          <t>1713226</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5019,24 +5019,24 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>BMD-1711775-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1713226-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>4,07</t>
+          <t>3.049,11</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>1712547</t>
+          <t>1713656</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>BMD-1712547-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1713656-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>117,63</t>
+          <t>4.315,58</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>1712550</t>
+          <t>1714342</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -5073,24 +5073,24 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>BMD-1712550-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1714342-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>421,10</t>
+          <t>1.949,56</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>1712766</t>
+          <t>1714699</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5100,24 +5100,24 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>BMD-1712766-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1714699-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>705,45</t>
+          <t>18.624,62</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>1713044I</t>
+          <t>1715201</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5127,24 +5127,24 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>BMD-1713044II-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1715201-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>1.528,53</t>
+          <t>6.987,28</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1713226</t>
+          <t>1715668</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5154,24 +5154,24 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>BMD-1713226-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1715668-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>237,93</t>
+          <t>2.070,47</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>1713626</t>
+          <t>1715955I</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -5181,24 +5181,24 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>BMD-1713626-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1715955I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>161,42</t>
+          <t>2.970,68</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>1713656I</t>
+          <t>1717168</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -5208,24 +5208,24 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>BMD-1713656I-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1717168-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>161,74</t>
+          <t>2.528,74</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>1713660</t>
+          <t>1717332</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -5235,24 +5235,24 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>BMD-1713660-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1717332-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>161,11</t>
+          <t>2.320,28</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>1714857</t>
+          <t>1718442</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -5262,24 +5262,24 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>BMD-1714857-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1718442-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>185,07</t>
+          <t>3.160,96</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>1714909</t>
+          <t>1718555I</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -5289,24 +5289,24 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>BMD-1714909-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1718555I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>107,93</t>
+          <t>2.781,60</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>1715127</t>
+          <t>1721869</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -5316,24 +5316,24 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>BMD-1715127-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1721869-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>128,31</t>
+          <t>807,18</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>1715131</t>
+          <t>1724551</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -5343,24 +5343,24 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>BMD-1715131-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1724551-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2.220,22</t>
+          <t>7.181,35</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>1715201</t>
+          <t>1725260</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -5370,24 +5370,24 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>BMD-1715201-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1725260-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>3,29</t>
+          <t>4.716,47</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>1715257I</t>
+          <t>1730763</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -5397,24 +5397,24 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>BMD-1715257I-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1730763-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>6.765,65</t>
+          <t>4.243,92</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>1715668</t>
+          <t>1713221</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -5424,24 +5424,24 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>BMD-1715668-HAGAP.pdf</t>
+          <t>BMD parcial - 1713221 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>249,06</t>
+          <t>18.794,09</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>1715816C</t>
+          <t>1715710</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -5451,24 +5451,24 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>BMD-1715816C-HAGAP  PARCIAL.pdf</t>
+          <t>BMD,-1715710-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>30,22</t>
+          <t>326,74</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>1715816I</t>
+          <t>1667141</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>BMD-1715816I-HAGAP  PARCIAL.pdf</t>
+          <t>BMD-1667141-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>3.168,40</t>
+          <t>152,42</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -5495,7 +5495,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>1715899</t>
+          <t>1675389</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -5505,24 +5505,24 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>BMD-1715899-HAGAP  PARCIAL.pdf</t>
+          <t>BMD-1675389-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>3.389,65</t>
+          <t>389,52</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>1717166</t>
+          <t>1691390</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -5532,24 +5532,24 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>BMD-1717166-HAGAP  PARCIAL.pdf</t>
+          <t>BMD-1691390-HAGAP..pdf</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>22.116,83</t>
+          <t>457,30</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>1717168</t>
+          <t>1694841</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -5559,24 +5559,24 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>BMD-1717168-HAGAP.pdf</t>
+          <t>BMD-1694841-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>1.163,67</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>1718442</t>
+          <t>1703223</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -5586,24 +5586,24 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>BMD-1718442-HAGAP.pdf</t>
+          <t>BMD-1703223-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>45,19</t>
+          <t>1.471,15</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>1718561</t>
+          <t>1704877</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -5613,24 +5613,24 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>BMD-1718561-HAGAP PARCIAL.pdf</t>
+          <t>BMD-1704877-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>13.683,99</t>
+          <t>1.223,97</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>1719070</t>
+          <t>1704953</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -5640,24 +5640,24 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>BMD-1719070-HAGAP.pdf</t>
+          <t>BMD-1704953-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>333,14</t>
+          <t>9.260,98</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>1719213</t>
+          <t>1708066</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -5667,24 +5667,24 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>BMD-1719213-HAGAP  PARCIAL.pdf</t>
+          <t>BMD-1708066-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>5.951,32</t>
+          <t>3.419,06</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>1719214</t>
+          <t>1709486</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -5694,24 +5694,24 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>BMD-1719214-HAGAP  PARCIAL.pdf</t>
+          <t>BMD-1709486-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>6.124,60</t>
+          <t>1.889,02</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>1719881</t>
+          <t>1711775</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -5721,24 +5721,24 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>BMD-1719881-HAGAP.pdf</t>
+          <t>BMD-1711775-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>3.239,73</t>
+          <t>4,07</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>1719881H</t>
+          <t>1712547</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -5748,24 +5748,24 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>BMD-1719881HAGAP.pdf</t>
+          <t>BMD-1712547-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>38.258,42</t>
+          <t>117,63</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>1720116</t>
+          <t>1712550</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -5775,24 +5775,24 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>BMD-1720116-HAGAP.pdf</t>
+          <t>BMD-1712550-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>168,95</t>
+          <t>421,10</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>1721631</t>
+          <t>1712766</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -5802,24 +5802,24 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>BMD-1721631-HAGAP  PARCIAL.pdf</t>
+          <t>BMD-1712766-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>12.649,43</t>
+          <t>705,45</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>1721631C</t>
+          <t>1713044I</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -5829,24 +5829,24 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>BMD-1721631C-HAGAP  PARCIAL.pdf</t>
+          <t>BMD-1713044II-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>100,65</t>
+          <t>1.528,53</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>1721869</t>
+          <t>1713226</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -5856,24 +5856,24 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>BMD-1721869-HAGAP.pdf</t>
+          <t>BMD-1713226-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>133,09</t>
+          <t>237,93</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>1721886</t>
+          <t>1713626</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -5883,24 +5883,24 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>BMD-1721886 - HAGAP PARCIAL.pdf</t>
+          <t>BMD-1713626-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>14.551,70</t>
+          <t>161,42</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>1713044C</t>
+          <t>1713656I</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -5910,24 +5910,24 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>BMD.-1713044C.-HAGAP.pdf</t>
+          <t>BMD-1713656I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>21,11</t>
+          <t>161,74</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>1715327</t>
+          <t>1713660</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -5937,105 +5937,105 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>BMD.1715327-HAGAP.pdf</t>
+          <t>BMD-1713660-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>161,11</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>1708877</t>
+          <t>1714342</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>BMDFINAL-1708877-HAGAP.pdf</t>
+          <t>BMD-1714342-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>3,54</t>
+          <t>62,40</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>1712957</t>
+          <t>1714857</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>BMDFINAL-1712957-HAGAP.pdf</t>
+          <t>BMD-1714857-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>45,19</t>
+          <t>185,07</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>1717332</t>
+          <t>1714909</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>BMDFINAL-1717332-HAGAP.pdf</t>
+          <t>BMD-1714909-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>107,93</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>1703223</t>
+          <t>1715127</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -6045,24 +6045,24 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1703223-HAGAP.pdf</t>
+          <t>BMD-1715127-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>18.169,34</t>
+          <t>128,31</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>1712547</t>
+          <t>1715131</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -6072,12 +6072,12 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1712547-HAGAP.pdf</t>
+          <t>BMD-1715131-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>6.951,82</t>
+          <t>2.220,22</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -6089,7 +6089,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>1712957</t>
+          <t>1715201</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -6099,24 +6099,24 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1712957-HAGAP.pdf</t>
+          <t>BMD-1715201-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2.177,64</t>
+          <t>3,29</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>1713262</t>
+          <t>1715257I</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -6126,24 +6126,24 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1713262-HAGAP.pdf</t>
+          <t>BMD-1715257I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2.619,71</t>
+          <t>6.765,65</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>1714909</t>
+          <t>1715668</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -6153,24 +6153,24 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1714909-HAGAP.pdf</t>
+          <t>BMD-1715668-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>954,64</t>
+          <t>249,06</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>1715127</t>
+          <t>1715816C</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -6180,24 +6180,24 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1715127-HAGAP.pdf</t>
+          <t>BMD-1715816C-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>4.418,94</t>
+          <t>30,22</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>1715327</t>
+          <t>1715816I</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -6207,24 +6207,24 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1715327-HAGAP.pdf</t>
+          <t>BMD-1715816I-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>5.417,39</t>
+          <t>3.168,40</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>1719070</t>
+          <t>1715899</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -6234,24 +6234,24 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1719070-HAGAP.pdf</t>
+          <t>BMD-1715899-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2.744,71</t>
+          <t>3.389,65</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>1719135</t>
+          <t>1717166</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -6261,24 +6261,24 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1719135-HAGAP.pdf</t>
+          <t>BMD-1717166-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>913,84</t>
+          <t>22.116,83</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>1720116</t>
+          <t>1717168</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -6288,24 +6288,24 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1720116-HAGAP.pdf</t>
+          <t>BMD-1717168-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>1.675,57</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>1724491</t>
+          <t>1718019</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -6315,24 +6315,24 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1724491-HAGAP.pdf</t>
+          <t>BMD-1718019-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>14.377,51</t>
+          <t>4.408,31</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>1717315</t>
+          <t>1718442</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -6342,24 +6342,24 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>BMD_1717315_HAGAP.pdf</t>
+          <t>BMD-1718442-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>13.183,29</t>
+          <t>45,19</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>1725869</t>
+          <t>1718561</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -6369,439 +6369,439 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>BMD_1725869_HAGAP.pdf</t>
+          <t>BMD-1718561-HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>13.683,99</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>1712766</t>
+          <t>1719070</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>FF0-1712766-HAGAP.pdf</t>
+          <t>BMD-1719070-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>333,14</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>1719135</t>
+          <t>1719213</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>FFO  -1719135-HAGAP.pdf</t>
+          <t>BMD-1719213-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>5.951,32</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>1677314</t>
+          <t>1719214</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>FFO - 1677314 - HAGAP.pdf</t>
+          <t>BMD-1719214-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>6.124,60</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>1677316</t>
+          <t>1719881</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>FFO - 1677316 HAGAP.pdf</t>
+          <t>BMD-1719881-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>3.239,73</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>1688115C</t>
+          <t>1719881H</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>FFO - 1688115C - HAGAP.pdf</t>
+          <t>BMD-1719881HAGAP.pdf</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>38.258,42</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>1688115I</t>
+          <t>1720116</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>FFO - 1688115I - HAGAP.pdf</t>
+          <t>BMD-1720116-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>168,95</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>1691534</t>
+          <t>1721631</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>FFO - 1691534 - HAGAP - 03-07-2026.pdf</t>
+          <t>BMD-1721631-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>12.649,43</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>1692174</t>
+          <t>1721631C</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>FFO - 1692174 - HAGAP.pdf</t>
+          <t>BMD-1721631C-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>100,65</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>1698047</t>
+          <t>1721869</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>FFO - 1698047 - HAGAP - 30-04-2026.pdf</t>
+          <t>BMD-1721869-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>133,09</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>1702127</t>
+          <t>1721886</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>FFO - 1702127 - HAGAP.pdf</t>
+          <t>BMD-1721886 - HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>14.551,70</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>1702640</t>
+          <t>1724491</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>FFO - 1702640 - HAGAP - 10-07-2026.pdf</t>
+          <t>BMD-1724491-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>33,42</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>1702776C</t>
+          <t>1726890</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>FFO - 1702776C - HAGAP.pdf</t>
+          <t>BMD-1726890-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>3.252,02</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>1702776I</t>
+          <t>1727335</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>FFO - 1702776I - HAGAP.pdf</t>
+          <t>BMD-1727335-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>5.053,73</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>1704867</t>
+          <t>1727808I</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>FFO - 1704867 - ASP.pdf</t>
+          <t>BMD-1727808I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.562,33</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>1705802I</t>
+          <t>1713044C</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>FFO - 1705802I - HAGAP.pdf</t>
+          <t>BMD.-1713044C.-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>21,11</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>1709419</t>
+          <t>1715327</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>FFO - 1709419 - HAGAP.pdf</t>
+          <t>BMD.1715327-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -6811,14 +6811,14 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>1709995</t>
+          <t>1708877</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -6828,24 +6828,24 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>FFO - 1709995 - HAGAP.pdf</t>
+          <t>BMDFINAL-1708877-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>3,54</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>1711384</t>
+          <t>1712957</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -6855,24 +6855,24 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>FFO - 1711384 - HAGAP.pdf</t>
+          <t>BMDFINAL-1712957-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>45,19</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>1712538</t>
+          <t>1717332</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -6882,7 +6882,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>FFO - 1712538 - HAGAP.pdf</t>
+          <t>BMDFINAL-1717332-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -6892,348 +6892,348 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>1713221</t>
+          <t>1703223</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>FFO - 1713221 - HAGAP.pdf</t>
+          <t>BMDPARCIAL-1703223-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>18.169,34</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>1713240</t>
+          <t>1712547</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>FFO - 1713240 - HAGAP - 20-05-2026.pdf</t>
+          <t>BMDPARCIAL-1712547-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>6.951,82</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>1715278</t>
+          <t>1712957</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>FFO - 1715278 - HAGAP.pdf</t>
+          <t>BMDPARCIAL-1712957-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>306,36</t>
+          <t>2.177,64</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>1715688</t>
+          <t>1713262</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>FFO - 1715688 - HAGAP.pdf</t>
+          <t>BMDPARCIAL-1713262-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.619,71</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>1715878</t>
+          <t>1714909</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>FFO - 1715878 - HAGAP - 20-05-2026.pdf</t>
+          <t>BMDPARCIAL-1714909-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>954,64</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>1520615</t>
+          <t>1715127</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>FFO 1520615 HAGAP.pdf</t>
+          <t>BMDPARCIAL-1715127-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>4.418,94</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>1641139I</t>
+          <t>1715327</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>FFO 1641139I HAGAP.pdf</t>
+          <t>BMDPARCIAL-1715327-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>5.417,39</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>1682195</t>
+          <t>1719070</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>FFO 1682195 HAGAP.pdf</t>
+          <t>BMDPARCIAL-1719070-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.744,71</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>1693027</t>
+          <t>1719135</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>FFO 1693027 HAGAP.pdf</t>
+          <t>BMDPARCIAL-1719135-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>913,84</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>1704525</t>
+          <t>1720116</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>FFO 1704525 HAGAP.pdf</t>
+          <t>BMDPARCIAL-1720116-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>1.675,57</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>1710736</t>
+          <t>1724491</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>FFO 1710736 HAGAP.pdf</t>
+          <t>BMDPARCIAL-1724491-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>14.377,51</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>1710975</t>
+          <t>1717315</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>FFO 1710975 HAGAP.pdf</t>
+          <t>BMD_1717315_HAGAP.pdf</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>13.183,29</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>1711525</t>
+          <t>1725869</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>FFO 1711525 HAGAP.pdf</t>
+          <t>BMD_1725869_HAGAP.pdf</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -7243,14 +7243,14 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>1712533</t>
+          <t>1712766</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -7260,7 +7260,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>FFO 1712533 HAGAP.pdf</t>
+          <t>FF0-1712766-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -7270,14 +7270,14 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>1713435I</t>
+          <t>1719135</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>FFO 1713435I HAGAP.pdf</t>
+          <t>FFO  -1719135-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -7297,14 +7297,14 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>1713679</t>
+          <t>1658892</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>FFO 1713679 HAGAP.pdf</t>
+          <t>FFO - 1658892 - HAGAP - 15-07-2026.pdf</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -7324,14 +7324,14 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>1714364</t>
+          <t>1677314</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>FFO 1714364 HAGAP.pdf</t>
+          <t>FFO - 1677314 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -7351,14 +7351,14 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>1714729</t>
+          <t>1677316</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>FFO 1714729 HAGAP.pdf</t>
+          <t>FFO - 1677316 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -7378,14 +7378,14 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>1715154</t>
+          <t>1688115C</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -7395,7 +7395,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>FFO 1715154 HAGAP.pdf</t>
+          <t>FFO - 1688115C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -7405,14 +7405,14 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>1718561</t>
+          <t>1688115I</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -7422,24 +7422,24 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>FFO 1718561 HAGAP.pdf</t>
+          <t>FFO - 1688115I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>1.543,28</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>1718803</t>
+          <t>1691534</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -7449,7 +7449,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>FFO 1718803 HAGAP.pdf</t>
+          <t>FFO - 1691534 - HAGAP - 03-07-2026.pdf</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -7459,14 +7459,14 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>1719155</t>
+          <t>1692174</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -7476,7 +7476,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>FFO 1719155 HAGAP.pdf</t>
+          <t>FFO - 1692174 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -7486,14 +7486,14 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>1720721</t>
+          <t>1698047</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>FFO 1720721 HAGAP.pdf</t>
+          <t>FFO - 1698047 - HAGAP - 30-04-2026.pdf</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -7513,14 +7513,14 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>1720909</t>
+          <t>1698056</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -7530,7 +7530,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>FFO 1720909 HAGAP.pdf</t>
+          <t>FFO - 1698056 - HAGAP - 17-07-2026.pdf</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -7540,14 +7540,14 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>1720920</t>
+          <t>1702127</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -7557,7 +7557,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>FFO 1720920 HAGAP.pdf</t>
+          <t>FFO - 1702127 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -7567,14 +7567,14 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>1722904</t>
+          <t>1702640</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -7584,7 +7584,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>FFO 1722904 HAGAP.pdf</t>
+          <t>FFO - 1702640 - HAGAP - 10-07-2026.pdf</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -7594,14 +7594,14 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>1667141</t>
+          <t>1702776C</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -7611,7 +7611,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>FFO-1667141-HAGAP.pdf</t>
+          <t>FFO - 1702776C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -7621,14 +7621,14 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>1675389</t>
+          <t>1702776I</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -7638,7 +7638,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>FFO-1675389-HAGAP.pdf</t>
+          <t>FFO - 1702776I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -7648,14 +7648,14 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>1691390</t>
+          <t>1704867</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -7665,7 +7665,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>FFO-1691390-HAGAP.pdf</t>
+          <t>FFO - 1704867 - ASP.pdf</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -7675,14 +7675,14 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>1703223</t>
+          <t>1705802I</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -7692,7 +7692,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>FFO-1703223-HAGAP.pdf</t>
+          <t>FFO - 1705802I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -7702,14 +7702,14 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>1708877</t>
+          <t>1707174</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -7719,7 +7719,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>FFO-1708877-HAGAP.pdf</t>
+          <t>FFO - 1707174 - HAGAP - 17-07-2026.pdf</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -7729,14 +7729,14 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>1709486</t>
+          <t>1709419</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>FFO-1709486-HAGAP.pdf</t>
+          <t>FFO - 1709419 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -7756,14 +7756,14 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>1710116</t>
+          <t>1709995</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>FFO-1710116-HAGAP.pdf</t>
+          <t>FFO - 1709995 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -7783,14 +7783,14 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>1711110</t>
+          <t>1711384</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -7800,7 +7800,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>FFO-1711110-HAGAP.pdf</t>
+          <t>FFO - 1711384 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -7810,14 +7810,14 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>1711775</t>
+          <t>1712538</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>FFO-1711775-HAGAP.pdf</t>
+          <t>FFO - 1712538 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -7837,14 +7837,14 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>1712531</t>
+          <t>1713221</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>FFO-1712531-HAGAP.pdf</t>
+          <t>FFO - 1713221 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -7864,14 +7864,14 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>1712547</t>
+          <t>1713240</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>FFO-1712547-HAGAP.pdf</t>
+          <t>FFO - 1713240 - HAGAP - 20-05-2026.pdf</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -7891,14 +7891,14 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>1712550</t>
+          <t>1715278</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -7908,24 +7908,24 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>FFO-1712550-HAGAP.pdf</t>
+          <t>FFO - 1715278 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>306,36</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>1713044C</t>
+          <t>1715688</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -7935,7 +7935,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>FFO-1713044C.-HAGAP.pdf</t>
+          <t>FFO - 1715688 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -7945,14 +7945,14 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>1713044I</t>
+          <t>1715878</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -7962,7 +7962,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>FFO-1713044II-HAGAP.pdf</t>
+          <t>FFO - 1715878 - HAGAP - 20-05-2026.pdf</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -7979,7 +7979,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>1713226</t>
+          <t>1722321</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -7989,7 +7989,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>FFO-1713226-HAGAP.pdf</t>
+          <t>FFO - 1722321 - HAGAP - 15-07-2026.pdf</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -7999,14 +7999,14 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>1713262</t>
+          <t>1724051I</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -8016,7 +8016,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>FFO-1713262-HAGAP.pdf</t>
+          <t>FFO - 1724051I - HAGAP - 15-07-2026.pdf</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -8026,14 +8026,14 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>1713626</t>
+          <t>1520615</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -8043,7 +8043,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>FFO-1713626-HAGAP.pdf</t>
+          <t>FFO 1520615 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -8053,14 +8053,14 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>1713656I</t>
+          <t>1641139I</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>FFO-1713656I-HAGAP.pdf</t>
+          <t>FFO 1641139I HAGAP.pdf</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -8080,14 +8080,14 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>1714857</t>
+          <t>1682195</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -8097,7 +8097,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>FFO-1714857-HAGAP.pdf</t>
+          <t>FFO 1682195 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -8107,14 +8107,14 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>1714909</t>
+          <t>1693027</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -8124,7 +8124,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>FFO-1714909-HAGAP.pdf</t>
+          <t>FFO 1693027 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -8134,14 +8134,14 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>1715127</t>
+          <t>1699516</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>FFO-1715127-HAGAP.pdf</t>
+          <t>FFO 1699516 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -8161,14 +8161,14 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>1715201</t>
+          <t>1704525</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>FFO-1715201-HAGAP.pdf</t>
+          <t>FFO 1704525 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -8195,7 +8195,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>1715257I</t>
+          <t>1710329</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -8205,7 +8205,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>FFO-1715257I-HAGAP.pdf</t>
+          <t>FFO 1710329 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -8215,14 +8215,14 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>1715327</t>
+          <t>1710736</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -8232,24 +8232,24 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>FFO-1715327-HAGAP.pdf</t>
+          <t>FFO 1710736 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>65,98</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>1715668</t>
+          <t>1710975</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -8259,7 +8259,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>FFO-1715668-HAGAP.pdf</t>
+          <t>FFO 1710975 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -8269,14 +8269,14 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>1717168</t>
+          <t>1711525</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -8286,24 +8286,24 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>FFO-1717168-HAGAP.pdf</t>
+          <t>FFO 1711525 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>87,00</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>1717332</t>
+          <t>1712533</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -8313,24 +8313,24 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>FFO-1717332-HAGAP.pdf</t>
+          <t>FFO 1712533 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>176,23</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>1719070</t>
+          <t>1713351</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -8340,7 +8340,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>FFO-1719070-HAGAP.pdf</t>
+          <t>FFO 1713351 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -8350,14 +8350,14 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>1719881</t>
+          <t>1713435I</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -8367,7 +8367,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>FFO-1719881-HAGAP.pdf</t>
+          <t>FFO 1713435I HAGAP.pdf</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -8377,14 +8377,14 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>1721869</t>
+          <t>1713679</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -8394,7 +8394,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>FFO-1721869-HAGAP.pdf</t>
+          <t>FFO 1713679 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -8404,14 +8404,14 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>1708066</t>
+          <t>1714364</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -8421,7 +8421,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>FFO.-1708066-HAGAP.pdf</t>
+          <t>FFO 1714364 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -8431,14 +8431,14 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>1712957</t>
+          <t>1714729</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -8448,7 +8448,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>FFO.-1712957-HAGAP.pdf</t>
+          <t>FFO 1714729 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -8458,14 +8458,14 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>1713660</t>
+          <t>1715154</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -8475,7 +8475,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>FFO.-1713660-HAGAP.pdf</t>
+          <t>FFO 1715154 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -8485,14 +8485,14 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>1691380</t>
+          <t>1718561</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -8502,24 +8502,24 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>FFO_1691380.pdf</t>
+          <t>FFO 1718561 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>1.543,28</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>1717315</t>
+          <t>1718803</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -8529,7 +8529,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>FFO_1717315_HAGAP.pdf</t>
+          <t>FFO 1718803 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -8539,14 +8539,14 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>1725869</t>
+          <t>1719155</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -8556,24 +8556,24 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>FFO_1725869_HAGAP.pdf</t>
+          <t>FFO 1719155 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>2.488,83</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>1718442</t>
+          <t>1719213</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>FFO´1718442-HAGAP.pdf</t>
+          <t>FFO 1719213 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -8593,24 +8593,24 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>1703223</t>
+          <t>1720721</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>MULTA-1703223-HAGAP.pdf</t>
+          <t>FFO 1720721 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -8618,22 +8618,26 @@
           <t>0,00</t>
         </is>
       </c>
-      <c r="E304" t="inlineStr"/>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>1713044I</t>
+          <t>1720909</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>MULTA-1713044I-HAGAP.pdf</t>
+          <t>FFO 1720909 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -8641,30 +8645,1549 @@
           <t>0,00</t>
         </is>
       </c>
-      <c r="E305" t="inlineStr"/>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
+          <t>1720920</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>FFO 1720920 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>1721595</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>FFO 1721595 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>1722320</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>FFO 1722320 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>1722904</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>FFO 1722904 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>1667141</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>FFO-1667141-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>1675389</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>FFO-1675389-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>1691390</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>FFO-1691390-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>1694841</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>FFO-1694841-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>1703223</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>FFO-1703223-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>1704877</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>FFO-1704877-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>16/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>1704953</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>FFO-1704953-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>1708877</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>FFO-1708877-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>1709486</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>FFO-1709486-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>1710116</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>FFO-1710116-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>1711110</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>FFO-1711110-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>1711775</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>FFO-1711775-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>1712531</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>FFO-1712531-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>1712547</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>FFO-1712547-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>1712550</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>FFO-1712550-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>1713044C</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>FFO-1713044C.-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>1713044I</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>FFO-1713044II-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>1713226</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>FFO-1713226-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>1713262</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>FFO-1713262-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>1713626</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>FFO-1713626-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>1713656I</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>FFO-1713656I-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>1714342</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>FFO-1714342-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>1714857</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>FFO-1714857-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>1714909</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>FFO-1714909-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>1715127</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>FFO-1715127-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>1715201</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>FFO-1715201-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>1715257I</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>FFO-1715257I-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
           <t>1715327</t>
         </is>
       </c>
-      <c r="B306" t="inlineStr">
-        <is>
-          <t>BMD</t>
-        </is>
-      </c>
-      <c r="C306" t="inlineStr">
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>FFO-1715327-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>65,98</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>1715668</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>FFO-1715668-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>1715710</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>FFO-1715710-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>1717168</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>FFO-1717168-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>87,00</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>1717332</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>FFO-1717332-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>176,23</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>1718019</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>FFO-1718019-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>1719070</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>FFO-1719070-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>1719881</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>FFO-1719881-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>1721869</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>FFO-1721869-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>1724491</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>FFO-1724491-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>1726890</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>FFO-1726890-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>1727335</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>FFO-1727335-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>1727808</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>FFO-1727808-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>1708066</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>FFO.-1708066-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>1712957</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>FFO.-1712957-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>1713660</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>FFO.-1713660-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>1691380</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>FFO_1691380.pdf</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>1717315</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>FFO_1717315_HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>1725869</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>FFO_1725869_HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>2.488,83</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>1718442</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>FFO´1718442-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>1694841</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>MULTA-1694841-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr"/>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>1703223</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>MULTA-1703223-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr"/>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>1704877</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>MULTA-1704877-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr"/>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>1713044I</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>MULTA-1713044I-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr"/>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>1715327</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
         <is>
           <t>MULTA-1715327-HAGAP.pdf</t>
         </is>
       </c>
-      <c r="D306" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
-      </c>
-      <c r="E306" t="inlineStr"/>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr"/>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>1724491</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>MULTA-1724491-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr"/>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>1726890</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>MULTA-1726890-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/medicoes.xlsx
+++ b/medicoes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E363"/>
+  <dimension ref="A1:E372"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1752,24 +1752,24 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>BMD - 1510407 - HAGAP - 26-05-2026.pdf</t>
+          <t>BMD - 1510407 - HAGAP - 20-07-2026.pdf</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>28.642,47</t>
+          <t>27.008,69</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1658892</t>
+          <t>1510407</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1779,17 +1779,17 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>BMD - 1658892 - HAGAP - 15-07-2026.pdf</t>
+          <t>BMD - 1510407 - HAGAP - 26-05-2026.pdf</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2.353,51</t>
+          <t>28.642,47</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
@@ -1806,24 +1806,24 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>BMD - 1658892 - HAGAP - 22-06-2026.pdf</t>
+          <t>BMD - 1658892 - HAGAP - 15-07-2026.pdf</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>38.435,91</t>
+          <t>2.353,51</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1677314</t>
+          <t>1658892</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1833,24 +1833,24 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>BMD - 1677314 - HAGAP.pdf</t>
+          <t>BMD - 1658892 - HAGAP - 22-06-2026.pdf</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>4.880,14</t>
+          <t>38.435,91</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1688115C</t>
+          <t>1677314</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1860,24 +1860,24 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>BMD - 1688115C - HAGAP.pdf</t>
+          <t>BMD - 1677314 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>6,65</t>
+          <t>4.880,14</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1688115I</t>
+          <t>1688115C</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>BMD - 1688115I - HAGAP.pdf</t>
+          <t>BMD - 1688115C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2.670,64</t>
+          <t>6,65</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -1904,7 +1904,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1691534</t>
+          <t>1688115I</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1914,24 +1914,24 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>BMD - 1691534 - HAGAP - 03-07-2026.pdf</t>
+          <t>BMD - 1688115I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>996,86</t>
+          <t>2.670,64</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1698047</t>
+          <t>1691534</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1941,24 +1941,24 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>BMD - 1698047 - HAGAP 30-04-2026.pdf</t>
+          <t>BMD - 1691534 - HAGAP - 03-07-2026.pdf</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2.449,89</t>
+          <t>996,86</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1698056</t>
+          <t>1698047</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1968,24 +1968,24 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>BMD - 1698056 - HAGAP - 17-07-2026.pdf</t>
+          <t>BMD - 1698047 - HAGAP 30-04-2026.pdf</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>692,14</t>
+          <t>2.449,89</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1702640</t>
+          <t>1698056</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1995,24 +1995,24 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>BMD - 1702640 - HAGAP - 10-07-2026.pdf</t>
+          <t>BMD - 1698056 - HAGAP - 17-07-2026.pdf</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2.963,92</t>
+          <t>692,14</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1704867</t>
+          <t>1702640</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2022,24 +2022,24 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>BMD - 1704867 - ASP.pdf</t>
+          <t>BMD - 1702640 - HAGAP - 10-07-2026.pdf</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>23.915,48</t>
+          <t>2.963,92</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1707174</t>
+          <t>1704867</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2049,24 +2049,24 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>BMD - 1707174 - HAGAP - 17-07-2026.pdf</t>
+          <t>BMD - 1704867 - ASP.pdf</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>1.924,94</t>
+          <t>23.915,48</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1709995</t>
+          <t>1707174</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2076,24 +2076,24 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>BMD - 1709995 - HAGAP.pdf</t>
+          <t>BMD - 1707174 - HAGAP - 17-07-2026.pdf</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2.410,16</t>
+          <t>1.924,94</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1711384</t>
+          <t>1709995</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2103,24 +2103,24 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>BMD - 1711384 - HAGAP.pdf</t>
+          <t>BMD - 1709995 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>122,95</t>
+          <t>2.410,16</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1712538</t>
+          <t>1711384</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2130,24 +2130,24 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>BMD - 1712538 - HAGAP.pdf</t>
+          <t>BMD - 1711384 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>387,36</t>
+          <t>122,95</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1713240</t>
+          <t>1712538</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2157,24 +2157,24 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>BMD - 1713240 - HAGAP - 20-05-2026.pdf</t>
+          <t>BMD - 1712538 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>5.108,11</t>
+          <t>387,36</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1713933</t>
+          <t>1713240</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2184,24 +2184,24 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>BMD - 1713933 - HAGAP - 20-05-2026.pdf</t>
+          <t>BMD - 1713240 - HAGAP - 20-05-2026.pdf</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>5.530,92</t>
+          <t>5.108,11</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1715878</t>
+          <t>1713933</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>BMD - 1715878 - HAGAP - 20-05-2026.pdf</t>
+          <t>BMD - 1713933 - HAGAP - 20-05-2026.pdf</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>1.786,71</t>
+          <t>5.530,92</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1718435</t>
+          <t>1715878</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2238,24 +2238,24 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>BMD - 1718435 - HAGAP - 20-05-2026.pdf</t>
+          <t>BMD - 1715878 - HAGAP - 20-05-2026.pdf</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>17.153,90</t>
+          <t>1.786,71</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1718783</t>
+          <t>1718435</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2265,24 +2265,24 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>BMD - 1718783 - HAGAP.pdf</t>
+          <t>BMD - 1718435 - HAGAP - 20-05-2026.pdf</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>16.983,02</t>
+          <t>17.153,90</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1718783C</t>
+          <t>1718783</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>BMD - 1718783C - HAGAP.pdf</t>
+          <t>BMD - 1718783 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>7,32</t>
+          <t>16.983,02</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2309,7 +2309,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1722169</t>
+          <t>1718783C</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2319,24 +2319,24 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>BMD - 1722169 - HAGAP - 25-06-2026.pdf</t>
+          <t>BMD - 1718783C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>1.225,38</t>
+          <t>7,32</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1722321</t>
+          <t>1722169</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2346,24 +2346,24 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>BMD - 1722321 - HAGAP - 15-07-2026.pdf</t>
+          <t>BMD - 1722169 - HAGAP - 25-06-2026.pdf</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>8.119,58</t>
+          <t>1.225,38</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1724051I</t>
+          <t>1722321</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>BMD - 1724051I - HAGAP - 15-07-2026.pdf</t>
+          <t>BMD - 1722321 - HAGAP - 15-07-2026.pdf</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2.432,48</t>
+          <t>8.119,58</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2390,7 +2390,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1725738C</t>
+          <t>1724051I</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2400,24 +2400,24 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>BMD - 1725738C - HAGAP.pdf</t>
+          <t>BMD - 1724051I - HAGAP - 15-07-2026.pdf</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>140,91</t>
+          <t>2.432,48</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1725738I</t>
+          <t>1725738C</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2427,12 +2427,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>BMD - 1725738I - HAGAP.pdf</t>
+          <t>BMD - 1725738C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>15.544,67</t>
+          <t>140,91</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2444,7 +2444,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1520612</t>
+          <t>1725738I</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2454,24 +2454,24 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>BMD 1520612 HAGAP.pdf</t>
+          <t>BMD - 1725738I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>53.357,33</t>
+          <t>15.544,67</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1520615</t>
+          <t>1520612</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>BMD 1520615 HAGAP.pdf</t>
+          <t>BMD 1520612 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>22.840,59</t>
+          <t>53.357,33</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -2498,7 +2498,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1536912</t>
+          <t>1520615</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2508,24 +2508,24 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>BMD 1536912 PARCIAL HAGAP.pdf</t>
+          <t>BMD 1520615 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2.474,56</t>
+          <t>22.840,59</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1660062C</t>
+          <t>1536912</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2535,24 +2535,24 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>BMD 1660062C HAGAP PARCIAL.pdf</t>
+          <t>BMD 1536912 PARCIAL HAGAP.pdf</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>100,65</t>
+          <t>2.474,56</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1660062I</t>
+          <t>1660062C</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>BMD 1660062I HAGAP PARCIAL.pdf</t>
+          <t>BMD 1660062C HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>11.953,89</t>
+          <t>100,65</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -2579,7 +2579,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1671139I</t>
+          <t>1660062I</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2589,24 +2589,24 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>BMD 1671139I HAGAP.pdf</t>
+          <t>BMD 1660062I HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>6.138,54</t>
+          <t>11.953,89</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1692636</t>
+          <t>1671139I</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2616,24 +2616,24 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>BMD 1692636 ASP.pdf</t>
+          <t>BMD 1671139I HAGAP.pdf</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>19.387,05</t>
+          <t>6.138,54</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1699516</t>
+          <t>1692636</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2643,17 +2643,17 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>BMD 1699516 FF HAGAP.pdf</t>
+          <t>BMD 1692636 ASP.pdf</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>287,85</t>
+          <t>19.387,05</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
@@ -2670,24 +2670,24 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>BMD 1699516 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1699516 FF HAGAP.pdf</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>3.388,62</t>
+          <t>287,85</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1704525</t>
+          <t>1699516</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2697,17 +2697,17 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>BMD 1704525 FF HAGAP.pdf</t>
+          <t>BMD 1699516 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>86,77</t>
+          <t>3.388,62</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
@@ -2724,24 +2724,24 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>BMD 1704525 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1704525 FF HAGAP.pdf</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>15.365,48</t>
+          <t>86,77</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1704891</t>
+          <t>1704525</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2751,24 +2751,24 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>BMD 1704891 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1704525 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>41.477,99</t>
+          <t>15.365,48</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1705074</t>
+          <t>1704891</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>BMD 1705074 HAGAP.pdf</t>
+          <t>BMD 1704891 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>150.312,87</t>
+          <t>41.477,99</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -2795,7 +2795,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1708906</t>
+          <t>1705074</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2805,24 +2805,24 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>BMD 1708906  30-04-2026 HAGAP.pdf</t>
+          <t>BMD 1705074 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>7.584,06</t>
+          <t>150.312,87</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1710329</t>
+          <t>1708906</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2832,24 +2832,24 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>BMD 1710329 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1708906  30-04-2026 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>24.209,42</t>
+          <t>7.584,06</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1710937</t>
+          <t>1710329</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2859,24 +2859,24 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>BMD 1710937 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1710329 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>24.209,42</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1710975</t>
+          <t>1710937</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2886,24 +2886,24 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>BMD 1710975 HAGAP FF.pdf</t>
+          <t>BMD 1710937 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>913,41</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1711525</t>
+          <t>1710975</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2913,17 +2913,17 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>BMD 1711525 FF HAGAP.pdf</t>
+          <t>BMD 1710975 HAGAP FF.pdf</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>126,93</t>
+          <t>913,41</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
@@ -2940,24 +2940,24 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>BMD 1711525 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1711525 FF HAGAP.pdf</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>1.998,42</t>
+          <t>126,93</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1711629</t>
+          <t>1711525</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2967,24 +2967,24 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>BMD 1711629 PARCIAL HAGAP.pdf</t>
+          <t>BMD 1711525 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>4.201,07</t>
+          <t>1.998,42</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1712533</t>
+          <t>1711629</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2994,24 +2994,24 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>BMD 1712533 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1711629 PARCIAL HAGAP.pdf</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2.553,46</t>
+          <t>4.201,07</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1712624</t>
+          <t>1712533</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3021,24 +3021,24 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>BMD 1712624 HAGAP.pdf</t>
+          <t>BMD 1712533 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>3.073,90</t>
+          <t>2.553,46</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1713223</t>
+          <t>1712624</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3048,24 +3048,24 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>BMD 1713223 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1712624 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>9.773,21</t>
+          <t>3.073,90</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1713351</t>
+          <t>1713223</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3075,24 +3075,24 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>BMD 1713351 HAGAPP.pdf</t>
+          <t>BMD 1713223 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>622,97</t>
+          <t>9.773,21</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1713679</t>
+          <t>1713351</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3102,24 +3102,24 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>BMD 1713679 HAGAP.pdf</t>
+          <t>BMD 1713351 HAGAPP.pdf</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>3.574,44</t>
+          <t>622,97</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1713719</t>
+          <t>1713679</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3129,24 +3129,24 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>BMD 1713719 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1713679 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>3.385,92</t>
+          <t>3.574,44</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1714364</t>
+          <t>1713719</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>BMD 1714364 HAGAP FF.pdf</t>
+          <t>BMD 1713719 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>54,64</t>
+          <t>3.385,92</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1714729</t>
+          <t>1714364</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3183,24 +3183,24 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>BMD 1714729 HAGAP.pdf</t>
+          <t>BMD 1714364 HAGAP FF.pdf</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>6.722,61</t>
+          <t>54,64</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1715154</t>
+          <t>1714729</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>BMD 1715154 HAGAP.pdf</t>
+          <t>BMD 1714729 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2.658,74</t>
+          <t>6.722,61</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -3227,7 +3227,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1715920</t>
+          <t>1715154</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3237,24 +3237,24 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>BMD 1715920 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1715154 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>1.031,94</t>
+          <t>2.658,74</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1718561</t>
+          <t>1715920</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3264,24 +3264,24 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>BMD 1718561 FF HAGAP.pdf</t>
+          <t>BMD 1715920 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>1.031,94</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1718803</t>
+          <t>1718561</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3291,24 +3291,24 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>BMD 1718803 HAGAP.pdf</t>
+          <t>BMD 1718561 FF HAGAP.pdf</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>3.825,18</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1719097</t>
+          <t>1718803</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3318,24 +3318,24 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>BMD 1719097 HAGAP.pdf</t>
+          <t>BMD 1718803 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>7.450,28</t>
+          <t>3.825,18</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1719155</t>
+          <t>1719097</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3345,24 +3345,24 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>BMD 1719155 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1719097 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2.223,15</t>
+          <t>7.450,28</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1719159</t>
+          <t>1719155</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3372,24 +3372,24 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>BMD 1719159 PARCIAL HAGAP.pdf</t>
+          <t>BMD 1719155 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2.240,81</t>
+          <t>2.223,15</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1719213</t>
+          <t>1719159</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3399,24 +3399,24 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>BMD 1719213 FF HAGAP.pdf</t>
+          <t>BMD 1719159 PARCIAL HAGAP.pdf</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>1.371,87</t>
+          <t>2.240,81</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1720721</t>
+          <t>1719213</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3426,24 +3426,24 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>BMD 1720721 HAGAP.pdf</t>
+          <t>BMD 1719213 FF HAGAP.pdf</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2.015,45</t>
+          <t>1.371,87</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1720909</t>
+          <t>1720721</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3453,24 +3453,24 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>BMD 1720909 HAGAP.pdf</t>
+          <t>BMD 1720721 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2.851,89</t>
+          <t>2.015,45</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1720920</t>
+          <t>1720909</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3480,17 +3480,17 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>BMD 1720920 FF HAGAP.pdf</t>
+          <t>BMD 1720909 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>89,29</t>
+          <t>2.851,89</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
@@ -3507,24 +3507,24 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>BMD 1720920 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1720920 FF HAGAP.pdf</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>555,60</t>
+          <t>89,29</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1721175</t>
+          <t>1720920</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3534,24 +3534,24 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>BMD 1721175 PARCIAL HAGAP.pdf</t>
+          <t>BMD 1720920 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>1.191,73</t>
+          <t>555,60</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1721595</t>
+          <t>1721175</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3561,24 +3561,24 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>BMD 1721595 HAGAP.pdf</t>
+          <t>BMD 1721175 PARCIAL HAGAP.pdf</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2.704,41</t>
+          <t>1.191,73</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1721884</t>
+          <t>1721595</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3588,24 +3588,24 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>BMD 1721884 PARCIAL HAGAP.pdf</t>
+          <t>BMD 1721595 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>41.481,66</t>
+          <t>2.704,41</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1722320</t>
+          <t>1721884</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3615,12 +3615,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>BMD 1722320 HAGAP.pdf</t>
+          <t>BMD 1721884 PARCIAL HAGAP.pdf</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>12.790,83</t>
+          <t>41.481,66</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -3632,7 +3632,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1722904</t>
+          <t>1722320</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3642,24 +3642,24 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>BMD 1722904 HAGAP.pdf</t>
+          <t>BMD 1722320 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2.417,20</t>
+          <t>12.790,83</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1724172</t>
+          <t>1722904</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3669,24 +3669,24 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>BMD 1724172 PARCIAL HAGAP.pdf</t>
+          <t>BMD 1722904 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>23.068,97</t>
+          <t>2.417,20</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1724356</t>
+          <t>1724172</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3696,24 +3696,24 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>BMD 1724356 HAGAP.pdf</t>
+          <t>BMD 1724172 PARCIAL HAGAP.pdf</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>7.614,80</t>
+          <t>23.068,97</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1725686</t>
+          <t>1724356</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3723,24 +3723,24 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>BMD 1725686 PARCIAL HAGAP.pdf</t>
+          <t>BMD 1724356 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>11.172,87</t>
+          <t>7.614,80</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1726332</t>
+          <t>1725686</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3750,24 +3750,24 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>BMD 1726332 PARCIAL HAGAP.pdf</t>
+          <t>BMD 1725686 PARCIAL HAGAP.pdf</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>5.722,23</t>
+          <t>11.172,87</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1728055</t>
+          <t>1726332</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3777,24 +3777,24 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>BMD 1728055 PARCIAL HAGAP.pdf</t>
+          <t>BMD 1726332 PARCIAL HAGAP.pdf</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>12.947,91</t>
+          <t>5.722,23</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1728163</t>
+          <t>1728055</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3804,24 +3804,24 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>BMD 1728163 HAGAP.pdf</t>
+          <t>BMD 1728055 PARCIAL HAGAP.pdf</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>7.914,69</t>
+          <t>12.947,91</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1682195</t>
+          <t>1728163</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3831,24 +3831,24 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>BMD FF 1682195 HAGAP.pdf</t>
+          <t>BMD 1728163 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>8,36</t>
+          <t>7.914,69</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1693027</t>
+          <t>1682195</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3858,24 +3858,24 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>BMD FF 1693027 HAGAP.pdf</t>
+          <t>BMD FF 1682195 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2.215,91</t>
+          <t>8,36</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>1710329</t>
+          <t>1693027</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3885,24 +3885,24 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>BMD FF 1710329 HAGAP.pdf</t>
+          <t>BMD FF 1693027 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2,44</t>
+          <t>2.215,91</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1712533</t>
+          <t>1710329</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3912,24 +3912,24 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>BMD FF 1712533 HAGAP.pdf</t>
+          <t>BMD FF 1710329 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>127,40</t>
+          <t>2,44</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1719155</t>
+          <t>1712533</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3939,51 +3939,51 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>BMD FF 1719155 HAGAP.pdf</t>
+          <t>BMD FF 1712533 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>145,82</t>
+          <t>127,40</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>1677316</t>
+          <t>1719155</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>BMD FINAL - 1677316 HAGAP.pdf</t>
+          <t>BMD FF 1719155 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>145,82</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1702776C</t>
+          <t>1677316</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>BMD FINAL - 1702776C - HAGAP.pdf</t>
+          <t>BMD FINAL - 1677316 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -4003,14 +4003,14 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1702776I</t>
+          <t>1702776C</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4020,24 +4020,24 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>BMD FINAL - 1702776I - HAGAP.pdf</t>
+          <t>BMD FINAL - 1702776C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>18.098,87</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1715278</t>
+          <t>1702776I</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4047,24 +4047,24 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>BMD FINAL - 1715278 - HAGAP.pdf</t>
+          <t>BMD FINAL - 1702776I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>18.098,87</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1715688</t>
+          <t>1715278</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4074,24 +4074,24 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>BMD FINAL - 1715688 - HAGAP.pdf</t>
+          <t>BMD FINAL - 1715278 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>1.425,04</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1713262</t>
+          <t>1715688</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>BMD FINAL-1713262-HAGAP.pdf</t>
+          <t>BMD FINAL - 1715688 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>55,90</t>
+          <t>1.425,04</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1719135</t>
+          <t>1713262</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4128,12 +4128,12 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>BMD FINAL-1719135-HAGAP.pdf</t>
+          <t>BMD FINAL-1713262-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>47,08</t>
+          <t>55,90</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -4145,34 +4145,34 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1712550</t>
+          <t>1719135</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>BMD PARCAIL-1712550-HAGAP.pdf</t>
+          <t>BMD FINAL-1719135-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>4.585,98</t>
+          <t>47,08</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1677314</t>
+          <t>1712550</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -4182,24 +4182,24 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1677314 - HAGAP.pdf</t>
+          <t>BMD PARCAIL-1712550-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>46.760,40</t>
+          <t>4.585,98</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1677316</t>
+          <t>1677314</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -4209,24 +4209,24 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1677316 HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1677314 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>51.623,62</t>
+          <t>46.760,40</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1688115C</t>
+          <t>1677316</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4236,24 +4236,24 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1688115C - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1677316 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>6,36</t>
+          <t>51.623,62</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1688115I</t>
+          <t>1688115C</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4263,12 +4263,12 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1688115I - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1688115C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>18.752,84</t>
+          <t>6,36</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -4280,7 +4280,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1691534</t>
+          <t>1688115I</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4290,24 +4290,24 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1691534 - HAGAP - 19-06-2026.pdf</t>
+          <t>BMD PARCIAL - 1688115I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>20.334,45</t>
+          <t>18.752,84</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1694258</t>
+          <t>1691534</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4317,24 +4317,24 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1694258 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1691534 - HAGAP - 19-06-2026.pdf</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>127.751,38</t>
+          <t>20.334,45</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>1695716</t>
+          <t>1694258</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4344,24 +4344,24 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1695716 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1694258 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>74.647,17</t>
+          <t>127.751,38</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1698056</t>
+          <t>1695716</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4371,24 +4371,24 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1698056 - HAGAP - 22-06-2026.pdf</t>
+          <t>BMD PARCIAL - 1695716 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>8.966,25</t>
+          <t>74.647,17</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1710735</t>
+          <t>1698056</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4398,24 +4398,24 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1710735 HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1698056 - HAGAP - 22-06-2026.pdf</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>9.153,35</t>
+          <t>8.966,25</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1711384</t>
+          <t>1710735</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4425,24 +4425,24 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1711384 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1710735 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2.127,38</t>
+          <t>9.153,35</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>1712538</t>
+          <t>1711384</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4452,24 +4452,24 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1712538 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1711384 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>3.568,05</t>
+          <t>2.127,38</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>1715278</t>
+          <t>1712538</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4479,24 +4479,24 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1715278 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1712538 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2.654,77</t>
+          <t>3.568,05</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>1715688</t>
+          <t>1715278</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4506,24 +4506,24 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1715688 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1715278 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>9.669,94</t>
+          <t>2.654,77</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1720914</t>
+          <t>1715688</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4533,24 +4533,24 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1720914 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1715688 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>13.736,92</t>
+          <t>9.669,94</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>1721887</t>
+          <t>1720914</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4560,24 +4560,24 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1721887 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1720914 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>15.229,27</t>
+          <t>13.736,92</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>1722169</t>
+          <t>1721887</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4587,24 +4587,24 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1722169 - HAGAP - 19-06-2026.pdf</t>
+          <t>BMD PARCIAL - 1721887 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>38.238,91</t>
+          <t>15.229,27</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>1722779</t>
+          <t>1722169</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4614,24 +4614,24 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1722779 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1722169 - HAGAP - 19-06-2026.pdf</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>14.090,54</t>
+          <t>38.238,91</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1712530</t>
+          <t>1722779</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4641,24 +4641,24 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>BMD PARCIAL -1712530-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1722779 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>5.393,72</t>
+          <t>14.090,54</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>1713626I</t>
+          <t>1676605</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4668,24 +4668,24 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>BMD PARCIAL -1713626I-HAGAP.pdf</t>
+          <t>BMD PARCIAL -1676605-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>5.318,80</t>
+          <t>42.204,27</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1713260</t>
+          <t>1712530</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4695,24 +4695,24 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>BMD PARCIAL 1713260 - HAGAP.pdf</t>
+          <t>BMD PARCIAL -1712530-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>8.854,04</t>
+          <t>5.393,72</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>1563492</t>
+          <t>1713626I</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4722,24 +4722,24 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>BMD PARCIAL CIANORTE - 1563492 - HAGAP.pdf</t>
+          <t>BMD PARCIAL -1713626I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>80.240,76</t>
+          <t>5.318,80</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>1563492</t>
+          <t>1713260</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4749,24 +4749,24 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>BMD PARCIAL JUSSARA - 1563492 - HAGAP.pdf</t>
+          <t>BMD PARCIAL 1713260 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>64.923,56</t>
+          <t>8.854,04</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>1667141</t>
+          <t>1563492</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4776,24 +4776,24 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1667141-HAGAP.pdf</t>
+          <t>BMD PARCIAL CIANORTE - 1563492 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>509,47</t>
+          <t>80.240,76</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>1694841</t>
+          <t>1563492</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4803,24 +4803,24 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1694841-HAGAP.pdf</t>
+          <t>BMD PARCIAL JUSSARA - 1563492 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>4.476,57</t>
+          <t>64.923,56</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>1704877</t>
+          <t>1564134</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4830,24 +4830,24 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1704877-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1564134-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>158.642,45</t>
+          <t>44.646,20</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>1708877I</t>
+          <t>1667141</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4857,24 +4857,24 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1708877I-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1667141-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2.132,72</t>
+          <t>509,47</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>1709486</t>
+          <t>1694841</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4884,24 +4884,24 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1709486-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1694841-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>4.402,38</t>
+          <t>4.476,57</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1711507</t>
+          <t>1704877</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4911,24 +4911,24 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1711507-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1704877-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>14.415,50</t>
+          <t>158.642,45</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1711775</t>
+          <t>1708877I</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4938,24 +4938,24 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1711775-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1708877I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>1.928,86</t>
+          <t>2.132,72</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>1712531</t>
+          <t>1709486</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4965,24 +4965,24 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1712531-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1709486-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>5.019,99</t>
+          <t>4.402,38</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>1712963I</t>
+          <t>1711507</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -4992,24 +4992,24 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1712963I-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1711507-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>12.285,61</t>
+          <t>14.415,50</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>1713226</t>
+          <t>1711775</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5019,24 +5019,24 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1713226-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1711775-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>3.049,11</t>
+          <t>1.928,86</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>1713656</t>
+          <t>1712531</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1713656-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1712531-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>4.315,58</t>
+          <t>5.019,99</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>1714342</t>
+          <t>1712963I</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -5073,24 +5073,24 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1714342-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1712963I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>1.949,56</t>
+          <t>12.285,61</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>1714699</t>
+          <t>1713226</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5100,24 +5100,24 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1714699-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1713226-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>18.624,62</t>
+          <t>3.049,11</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>1715201</t>
+          <t>1713656</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1715201-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1713656-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>6.987,28</t>
+          <t>4.315,58</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -5144,7 +5144,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1715668</t>
+          <t>1714342</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5154,24 +5154,24 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1715668-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1714342-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2.070,47</t>
+          <t>1.949,56</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>1715955I</t>
+          <t>1714348</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -5181,24 +5181,24 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1715955I-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1714348-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2.970,68</t>
+          <t>7.890,42</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>1717168</t>
+          <t>1714699</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1717168-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1714699-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2.528,74</t>
+          <t>18.624,62</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -5225,7 +5225,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>1717332</t>
+          <t>1715201</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -5235,24 +5235,24 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1717332-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1715201-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2.320,28</t>
+          <t>6.987,28</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>1718442</t>
+          <t>1715668</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -5262,24 +5262,24 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1718442-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1715668-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>3.160,96</t>
+          <t>2.070,47</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>1718555I</t>
+          <t>1715955I</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -5289,24 +5289,24 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1718555I-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1715955I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2.781,60</t>
+          <t>2.970,68</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>1721869</t>
+          <t>1717168</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1721869-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1717168-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>807,18</t>
+          <t>2.528,74</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -5333,7 +5333,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>1724551</t>
+          <t>1717332</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -5343,24 +5343,24 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1724551-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1717332-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>7.181,35</t>
+          <t>2.320,28</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>1725260</t>
+          <t>1718442</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -5370,24 +5370,24 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1725260-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1718442-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>4.716,47</t>
+          <t>3.160,96</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>1730763</t>
+          <t>1718555I</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -5397,24 +5397,24 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1730763-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1718555I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>4.243,92</t>
+          <t>2.781,60</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>1713221</t>
+          <t>1719077</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -5424,24 +5424,24 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>BMD parcial - 1713221 - HAGAP.pdf</t>
+          <t>BMD PARCIAL-1719077-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>18.794,09</t>
+          <t>9.937,52</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>1715710</t>
+          <t>1721869</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -5451,24 +5451,24 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>BMD,-1715710-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1721869-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>326,74</t>
+          <t>807,18</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>1667141</t>
+          <t>1724537</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -5478,24 +5478,24 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>BMD-1667141-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1724537-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>152,42</t>
+          <t>6.077,43</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>1675389</t>
+          <t>1724551</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -5505,24 +5505,24 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>BMD-1675389-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1724551-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>389,52</t>
+          <t>7.181,35</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>1691390</t>
+          <t>1725260</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -5532,24 +5532,24 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>BMD-1691390-HAGAP..pdf</t>
+          <t>BMD PARCIAL-1725260-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>457,30</t>
+          <t>4.716,47</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>1694841</t>
+          <t>1730222</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -5559,24 +5559,24 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>BMD-1694841-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1730222-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>1.163,67</t>
+          <t>18.608,52</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>1703223</t>
+          <t>1730763</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -5586,24 +5586,24 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>BMD-1703223-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1730763-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>1.471,15</t>
+          <t>4.243,92</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>1704877</t>
+          <t>1713221</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -5613,24 +5613,24 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>BMD-1704877-HAGAP.pdf</t>
+          <t>BMD parcial - 1713221 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>1.223,97</t>
+          <t>18.794,09</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>1704953</t>
+          <t>1715710</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -5640,24 +5640,24 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>BMD-1704953-HAGAP.pdf</t>
+          <t>BMD,-1715710-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>9.260,98</t>
+          <t>326,74</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>1708066</t>
+          <t>1667141</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -5667,24 +5667,24 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>BMD-1708066-HAGAP.pdf</t>
+          <t>BMD-1667141-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>3.419,06</t>
+          <t>152,42</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>1709486</t>
+          <t>1675389</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -5694,24 +5694,24 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>BMD-1709486-HAGAP.pdf</t>
+          <t>BMD-1675389-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>1.889,02</t>
+          <t>389,52</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>1711775</t>
+          <t>1691390</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -5721,24 +5721,24 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>BMD-1711775-HAGAP.pdf</t>
+          <t>BMD-1691390-HAGAP..pdf</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>4,07</t>
+          <t>457,30</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>1712547</t>
+          <t>1694841</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -5748,24 +5748,24 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>BMD-1712547-HAGAP.pdf</t>
+          <t>BMD-1694841-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>117,63</t>
+          <t>1.163,67</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>1712550</t>
+          <t>1703223</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -5775,24 +5775,24 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>BMD-1712550-HAGAP.pdf</t>
+          <t>BMD-1703223-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>421,10</t>
+          <t>1.471,15</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>1712766</t>
+          <t>1704877</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -5802,24 +5802,24 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>BMD-1712766-HAGAP.pdf</t>
+          <t>BMD-1704877-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>705,45</t>
+          <t>1.223,97</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>1713044I</t>
+          <t>1704953</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -5829,24 +5829,24 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>BMD-1713044II-HAGAP.pdf</t>
+          <t>BMD-1704953-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>1.528,53</t>
+          <t>9.260,98</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>1713226</t>
+          <t>1708066</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -5856,24 +5856,24 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>BMD-1713226-HAGAP.pdf</t>
+          <t>BMD-1708066-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>237,93</t>
+          <t>3.419,06</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>1713626</t>
+          <t>1709486</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -5883,12 +5883,12 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>BMD-1713626-HAGAP.pdf</t>
+          <t>BMD-1709486-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>161,42</t>
+          <t>1.889,02</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -5900,7 +5900,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>1713656I</t>
+          <t>1711775</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -5910,12 +5910,12 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>BMD-1713656I-HAGAP.pdf</t>
+          <t>BMD-1711775-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>161,74</t>
+          <t>4,07</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -5927,7 +5927,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>1713660</t>
+          <t>1712547</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -5937,24 +5937,24 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>BMD-1713660-HAGAP.pdf</t>
+          <t>BMD-1712547-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>161,11</t>
+          <t>117,63</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>1714342</t>
+          <t>1712550</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -5964,12 +5964,12 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>BMD-1714342-HAGAP.pdf</t>
+          <t>BMD-1712550-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>62,40</t>
+          <t>421,10</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -5981,7 +5981,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>1714857</t>
+          <t>1712766</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -5991,24 +5991,24 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>BMD-1714857-HAGAP.pdf</t>
+          <t>BMD-1712766-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>185,07</t>
+          <t>705,45</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>1714909</t>
+          <t>1713044I</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -6018,24 +6018,24 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>BMD-1714909-HAGAP.pdf</t>
+          <t>BMD-1713044II-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>107,93</t>
+          <t>1.528,53</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>1715127</t>
+          <t>1713226</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -6045,12 +6045,12 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>BMD-1715127-HAGAP.pdf</t>
+          <t>BMD-1713226-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>128,31</t>
+          <t>237,93</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -6062,7 +6062,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>1715131</t>
+          <t>1713626</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -6072,24 +6072,24 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>BMD-1715131-HAGAP.pdf</t>
+          <t>BMD-1713626-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2.220,22</t>
+          <t>161,42</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>1715201</t>
+          <t>1713656I</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>BMD-1715201-HAGAP.pdf</t>
+          <t>BMD-1713656I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>3,29</t>
+          <t>161,74</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -6116,7 +6116,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>1715257I</t>
+          <t>1713660</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -6126,24 +6126,24 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>BMD-1715257I-HAGAP.pdf</t>
+          <t>BMD-1713660-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>6.765,65</t>
+          <t>161,11</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>1715668</t>
+          <t>1714342</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -6153,24 +6153,24 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>BMD-1715668-HAGAP.pdf</t>
+          <t>BMD-1714342-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>249,06</t>
+          <t>62,40</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>1715816C</t>
+          <t>1714857</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -6180,24 +6180,24 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>BMD-1715816C-HAGAP  PARCIAL.pdf</t>
+          <t>BMD-1714857-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>30,22</t>
+          <t>185,07</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>1715816I</t>
+          <t>1714909</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -6207,24 +6207,24 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>BMD-1715816I-HAGAP  PARCIAL.pdf</t>
+          <t>BMD-1714909-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>3.168,40</t>
+          <t>107,93</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>1715899</t>
+          <t>1715127</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -6234,24 +6234,24 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>BMD-1715899-HAGAP  PARCIAL.pdf</t>
+          <t>BMD-1715127-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>3.389,65</t>
+          <t>128,31</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>1717166</t>
+          <t>1715131</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -6261,24 +6261,24 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>BMD-1717166-HAGAP  PARCIAL.pdf</t>
+          <t>BMD-1715131-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>22.116,83</t>
+          <t>2.220,22</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>1717168</t>
+          <t>1715201</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -6288,24 +6288,24 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>BMD-1717168-HAGAP.pdf</t>
+          <t>BMD-1715201-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>3,29</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>1718019</t>
+          <t>1715257I</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -6315,24 +6315,24 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>BMD-1718019-HAGAP.pdf</t>
+          <t>BMD-1715257I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>4.408,31</t>
+          <t>6.765,65</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>1718442</t>
+          <t>1715668</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -6342,12 +6342,12 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>BMD-1718442-HAGAP.pdf</t>
+          <t>BMD-1715668-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>45,19</t>
+          <t>249,06</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -6359,7 +6359,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>1718561</t>
+          <t>1715816C</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -6369,24 +6369,24 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>BMD-1718561-HAGAP PARCIAL.pdf</t>
+          <t>BMD-1715816C-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>13.683,99</t>
+          <t>30,22</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>1719070</t>
+          <t>1715816I</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -6396,24 +6396,24 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>BMD-1719070-HAGAP.pdf</t>
+          <t>BMD-1715816I-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>333,14</t>
+          <t>3.168,40</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>1719213</t>
+          <t>1715899</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -6423,24 +6423,24 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>BMD-1719213-HAGAP  PARCIAL.pdf</t>
+          <t>BMD-1715899-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>5.951,32</t>
+          <t>3.389,65</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>1719214</t>
+          <t>1717166</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -6450,12 +6450,12 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>BMD-1719214-HAGAP  PARCIAL.pdf</t>
+          <t>BMD-1717166-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>6.124,60</t>
+          <t>22.116,83</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -6467,7 +6467,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>1719881</t>
+          <t>1717168</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -6477,24 +6477,24 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>BMD-1719881-HAGAP.pdf</t>
+          <t>BMD-1717168-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>3.239,73</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>1719881H</t>
+          <t>1718019</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -6504,24 +6504,24 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>BMD-1719881HAGAP.pdf</t>
+          <t>BMD-1718019-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>38.258,42</t>
+          <t>4.408,31</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>1720116</t>
+          <t>1718442</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -6531,24 +6531,24 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>BMD-1720116-HAGAP.pdf</t>
+          <t>BMD-1718442-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>168,95</t>
+          <t>45,19</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>1721631</t>
+          <t>1718561</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -6558,24 +6558,24 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>BMD-1721631-HAGAP  PARCIAL.pdf</t>
+          <t>BMD-1718561-HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>12.649,43</t>
+          <t>13.683,99</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>1721631C</t>
+          <t>1719070</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -6585,24 +6585,24 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>BMD-1721631C-HAGAP  PARCIAL.pdf</t>
+          <t>BMD-1719070-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>100,65</t>
+          <t>333,14</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>1721869</t>
+          <t>1719213</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -6612,24 +6612,24 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>BMD-1721869-HAGAP.pdf</t>
+          <t>BMD-1719213-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>133,09</t>
+          <t>5.951,32</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>1721886</t>
+          <t>1719214</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>BMD-1721886 - HAGAP PARCIAL.pdf</t>
+          <t>BMD-1719214-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>14.551,70</t>
+          <t>6.124,60</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -6656,7 +6656,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>1724491</t>
+          <t>1719881</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -6666,24 +6666,24 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>BMD-1724491-HAGAP.pdf</t>
+          <t>BMD-1719881-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>33,42</t>
+          <t>3.239,73</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>1726890</t>
+          <t>1719881H</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -6693,24 +6693,24 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>BMD-1726890-HAGAP.pdf</t>
+          <t>BMD-1719881HAGAP.pdf</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>3.252,02</t>
+          <t>38.258,42</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>1727335</t>
+          <t>1720116</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -6720,24 +6720,24 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>BMD-1727335-HAGAP.pdf</t>
+          <t>BMD-1720116-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>5.053,73</t>
+          <t>168,95</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>1727808I</t>
+          <t>1721631</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -6747,24 +6747,24 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>BMD-1727808I-HAGAP.pdf</t>
+          <t>BMD-1721631-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2.562,33</t>
+          <t>12.649,43</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>1713044C</t>
+          <t>1721631C</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -6774,24 +6774,24 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>BMD.-1713044C.-HAGAP.pdf</t>
+          <t>BMD-1721631C-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>21,11</t>
+          <t>100,65</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>1715327</t>
+          <t>1721869</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -6801,105 +6801,105 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>BMD.1715327-HAGAP.pdf</t>
+          <t>BMD-1721869-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>133,09</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>1708877</t>
+          <t>1721886</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>BMDFINAL-1708877-HAGAP.pdf</t>
+          <t>BMD-1721886 - HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>3,54</t>
+          <t>14.551,70</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>1712957</t>
+          <t>1724491</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>BMDFINAL-1712957-HAGAP.pdf</t>
+          <t>BMD-1724491-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>45,19</t>
+          <t>33,42</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>1717332</t>
+          <t>1726890</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>BMDFINAL-1717332-HAGAP.pdf</t>
+          <t>BMD-1726890-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>3.252,02</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>1703223</t>
+          <t>1727335</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -6909,24 +6909,24 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1703223-HAGAP.pdf</t>
+          <t>BMD-1727335-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>18.169,34</t>
+          <t>5.053,73</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>1712547</t>
+          <t>1727808I</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -6936,24 +6936,24 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1712547-HAGAP.pdf</t>
+          <t>BMD-1727808I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>6.951,82</t>
+          <t>2.562,33</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>1712957</t>
+          <t>1713044C</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -6963,24 +6963,24 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1712957-HAGAP.pdf</t>
+          <t>BMD.-1713044C.-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2.177,64</t>
+          <t>21,11</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>1713262</t>
+          <t>1715327</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -6990,105 +6990,105 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1713262-HAGAP.pdf</t>
+          <t>BMD.1715327-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2.619,71</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>1714909</t>
+          <t>1708877</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1714909-HAGAP.pdf</t>
+          <t>BMDFINAL-1708877-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>954,64</t>
+          <t>3,54</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>1715127</t>
+          <t>1712957</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1715127-HAGAP.pdf</t>
+          <t>BMDFINAL-1712957-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>4.418,94</t>
+          <t>45,19</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>1715327</t>
+          <t>1717332</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1715327-HAGAP.pdf</t>
+          <t>BMDFINAL-1717332-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>5.417,39</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>1719070</t>
+          <t>1703223</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -7098,24 +7098,24 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1719070-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1703223-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2.744,71</t>
+          <t>18.169,34</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>1719135</t>
+          <t>1712547</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -7125,24 +7125,24 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1719135-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1712547-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>913,84</t>
+          <t>6.951,82</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>1720116</t>
+          <t>1712957</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1720116-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1712957-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>1.675,57</t>
+          <t>2.177,64</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -7169,7 +7169,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>1724491</t>
+          <t>1713262</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -7179,24 +7179,24 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1724491-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1713262-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>14.377,51</t>
+          <t>2.619,71</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>1717315</t>
+          <t>1714909</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -7206,24 +7206,24 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>BMD_1717315_HAGAP.pdf</t>
+          <t>BMDPARCIAL-1714909-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>13.183,29</t>
+          <t>954,64</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>1725869</t>
+          <t>1715127</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -7233,196 +7233,196 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>BMD_1725869_HAGAP.pdf</t>
+          <t>BMDPARCIAL-1715127-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>4.418,94</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>1712766</t>
+          <t>1715327</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>FF0-1712766-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1715327-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>5.417,39</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>1719135</t>
+          <t>1719070</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>FFO  -1719135-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1719070-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.744,71</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>1658892</t>
+          <t>1719135</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>FFO - 1658892 - HAGAP - 15-07-2026.pdf</t>
+          <t>BMDPARCIAL-1719135-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>913,84</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>1677314</t>
+          <t>1720116</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>FFO - 1677314 - HAGAP.pdf</t>
+          <t>BMDPARCIAL-1720116-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>1.675,57</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>1677316</t>
+          <t>1724491</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>FFO - 1677316 HAGAP.pdf</t>
+          <t>BMDPARCIAL-1724491-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>14.377,51</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>1688115C</t>
+          <t>1717315</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>FFO - 1688115C - HAGAP.pdf</t>
+          <t>BMD_1717315_HAGAP.pdf</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>13.183,29</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>1688115I</t>
+          <t>1725869</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>FFO - 1688115I - HAGAP.pdf</t>
+          <t>BMD_1725869_HAGAP.pdf</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -7432,14 +7432,14 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>1691534</t>
+          <t>1712766</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -7449,7 +7449,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>FFO - 1691534 - HAGAP - 03-07-2026.pdf</t>
+          <t>FF0-1712766-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -7459,14 +7459,14 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>1692174</t>
+          <t>1719135</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -7476,7 +7476,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>FFO - 1692174 - HAGAP.pdf</t>
+          <t>FFO  -1719135-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -7486,14 +7486,14 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>1698047</t>
+          <t>1510407</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>FFO - 1698047 - HAGAP - 30-04-2026.pdf</t>
+          <t>FFO - 1510407 - HAGAP - 20-07-2026.pdf</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -7513,14 +7513,14 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>1698056</t>
+          <t>1658892</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -7530,7 +7530,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>FFO - 1698056 - HAGAP - 17-07-2026.pdf</t>
+          <t>FFO - 1658892 - HAGAP - 15-07-2026.pdf</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -7540,14 +7540,14 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>1702127</t>
+          <t>1677314</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -7557,7 +7557,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>FFO - 1702127 - HAGAP.pdf</t>
+          <t>FFO - 1677314 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -7567,14 +7567,14 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>1702640</t>
+          <t>1677316</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -7584,7 +7584,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>FFO - 1702640 - HAGAP - 10-07-2026.pdf</t>
+          <t>FFO - 1677316 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -7594,14 +7594,14 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>1702776C</t>
+          <t>1688115C</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -7611,7 +7611,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>FFO - 1702776C - HAGAP.pdf</t>
+          <t>FFO - 1688115C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -7621,14 +7621,14 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>1702776I</t>
+          <t>1688115I</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -7638,7 +7638,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>FFO - 1702776I - HAGAP.pdf</t>
+          <t>FFO - 1688115I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -7648,14 +7648,14 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>1704867</t>
+          <t>1691534</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -7665,7 +7665,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>FFO - 1704867 - ASP.pdf</t>
+          <t>FFO - 1691534 - HAGAP - 03-07-2026.pdf</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -7675,14 +7675,14 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>1705802I</t>
+          <t>1692174</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -7692,7 +7692,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>FFO - 1705802I - HAGAP.pdf</t>
+          <t>FFO - 1692174 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -7709,7 +7709,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>1707174</t>
+          <t>1698047</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -7719,7 +7719,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>FFO - 1707174 - HAGAP - 17-07-2026.pdf</t>
+          <t>FFO - 1698047 - HAGAP - 30-04-2026.pdf</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -7729,14 +7729,14 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>1709419</t>
+          <t>1698056</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>FFO - 1709419 - HAGAP.pdf</t>
+          <t>FFO - 1698056 - HAGAP - 17-07-2026.pdf</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -7756,14 +7756,14 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>1709995</t>
+          <t>1702127</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>FFO - 1709995 - HAGAP.pdf</t>
+          <t>FFO - 1702127 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -7783,14 +7783,14 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>1711384</t>
+          <t>1702640</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -7800,7 +7800,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>FFO - 1711384 - HAGAP.pdf</t>
+          <t>FFO - 1702640 - HAGAP - 10-07-2026.pdf</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -7810,14 +7810,14 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>1712538</t>
+          <t>1702776C</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>FFO - 1712538 - HAGAP.pdf</t>
+          <t>FFO - 1702776C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -7837,14 +7837,14 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>1713221</t>
+          <t>1702776I</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>FFO - 1713221 - HAGAP.pdf</t>
+          <t>FFO - 1702776I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -7864,14 +7864,14 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>1713240</t>
+          <t>1704867</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>FFO - 1713240 - HAGAP - 20-05-2026.pdf</t>
+          <t>FFO - 1704867 - ASP.pdf</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -7891,14 +7891,14 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>1715278</t>
+          <t>1705802I</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -7908,24 +7908,24 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>FFO - 1715278 - HAGAP.pdf</t>
+          <t>FFO - 1705802I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>306,36</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>1715688</t>
+          <t>1707174</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -7935,7 +7935,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>FFO - 1715688 - HAGAP.pdf</t>
+          <t>FFO - 1707174 - HAGAP - 17-07-2026.pdf</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -7945,14 +7945,14 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>1715878</t>
+          <t>1709419</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -7962,7 +7962,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>FFO - 1715878 - HAGAP - 20-05-2026.pdf</t>
+          <t>FFO - 1709419 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -7972,14 +7972,14 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>1722321</t>
+          <t>1709995</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -7989,7 +7989,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>FFO - 1722321 - HAGAP - 15-07-2026.pdf</t>
+          <t>FFO - 1709995 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -7999,14 +7999,14 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>1724051I</t>
+          <t>1711384</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -8016,7 +8016,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>FFO - 1724051I - HAGAP - 15-07-2026.pdf</t>
+          <t>FFO - 1711384 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -8026,14 +8026,14 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>1520615</t>
+          <t>1712538</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -8043,7 +8043,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>FFO 1520615 HAGAP.pdf</t>
+          <t>FFO - 1712538 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -8053,14 +8053,14 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>1641139I</t>
+          <t>1713221</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>FFO 1641139I HAGAP.pdf</t>
+          <t>FFO - 1713221 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -8080,14 +8080,14 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>1682195</t>
+          <t>1713240</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -8097,7 +8097,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>FFO 1682195 HAGAP.pdf</t>
+          <t>FFO - 1713240 - HAGAP - 20-05-2026.pdf</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -8107,14 +8107,14 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>1693027</t>
+          <t>1715278</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -8124,24 +8124,24 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>FFO 1693027 HAGAP.pdf</t>
+          <t>FFO - 1715278 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>306,36</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>1699516</t>
+          <t>1715688</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>FFO 1699516 HAGAP.pdf</t>
+          <t>FFO - 1715688 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -8161,14 +8161,14 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>1704525</t>
+          <t>1715878</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>FFO 1704525 HAGAP.pdf</t>
+          <t>FFO - 1715878 - HAGAP - 20-05-2026.pdf</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -8188,14 +8188,14 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>1710329</t>
+          <t>1722321</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -8205,7 +8205,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>FFO 1710329 HAGAP.pdf</t>
+          <t>FFO - 1722321 - HAGAP - 15-07-2026.pdf</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -8215,14 +8215,14 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>1710736</t>
+          <t>1724051I</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -8232,7 +8232,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>FFO 1710736 HAGAP.pdf</t>
+          <t>FFO - 1724051I - HAGAP - 15-07-2026.pdf</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -8242,14 +8242,14 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>1710975</t>
+          <t>1520615</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -8259,7 +8259,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>FFO 1710975 HAGAP.pdf</t>
+          <t>FFO 1520615 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -8269,14 +8269,14 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>1711525</t>
+          <t>1641139I</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -8286,7 +8286,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>FFO 1711525 HAGAP.pdf</t>
+          <t>FFO 1641139I HAGAP.pdf</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -8296,14 +8296,14 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>1712533</t>
+          <t>1682195</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -8313,7 +8313,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>FFO 1712533 HAGAP.pdf</t>
+          <t>FFO 1682195 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -8323,14 +8323,14 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>1713351</t>
+          <t>1693027</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -8340,7 +8340,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>FFO 1713351 HAGAP.pdf</t>
+          <t>FFO 1693027 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -8350,14 +8350,14 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>1713435I</t>
+          <t>1699516</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -8367,7 +8367,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>FFO 1713435I HAGAP.pdf</t>
+          <t>FFO 1699516 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -8377,14 +8377,14 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>1713679</t>
+          <t>1704525</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -8394,7 +8394,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>FFO 1713679 HAGAP.pdf</t>
+          <t>FFO 1704525 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -8404,14 +8404,14 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>1714364</t>
+          <t>1710329</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -8421,7 +8421,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>FFO 1714364 HAGAP.pdf</t>
+          <t>FFO 1710329 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -8431,14 +8431,14 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>1714729</t>
+          <t>1710736</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -8448,7 +8448,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>FFO 1714729 HAGAP.pdf</t>
+          <t>FFO 1710736 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -8458,14 +8458,14 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>1715154</t>
+          <t>1710975</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -8475,7 +8475,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>FFO 1715154 HAGAP.pdf</t>
+          <t>FFO 1710975 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -8485,14 +8485,14 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>1718561</t>
+          <t>1711525</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -8502,24 +8502,24 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>FFO 1718561 HAGAP.pdf</t>
+          <t>FFO 1711525 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>1.543,28</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>1718803</t>
+          <t>1712533</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -8529,7 +8529,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>FFO 1718803 HAGAP.pdf</t>
+          <t>FFO 1712533 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -8539,14 +8539,14 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>1719155</t>
+          <t>1713351</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>FFO 1719155 HAGAP.pdf</t>
+          <t>FFO 1713351 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -8566,14 +8566,14 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>1719213</t>
+          <t>1713435I</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>FFO 1719213 HAGAP.pdf</t>
+          <t>FFO 1713435I HAGAP.pdf</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -8593,14 +8593,14 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>1720721</t>
+          <t>1713679</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -8610,7 +8610,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>FFO 1720721 HAGAP.pdf</t>
+          <t>FFO 1713679 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -8620,14 +8620,14 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>1720909</t>
+          <t>1714364</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -8637,7 +8637,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>FFO 1720909 HAGAP.pdf</t>
+          <t>FFO 1714364 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -8647,14 +8647,14 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>1720920</t>
+          <t>1714729</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -8664,7 +8664,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>FFO 1720920 HAGAP.pdf</t>
+          <t>FFO 1714729 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -8674,14 +8674,14 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>1721595</t>
+          <t>1715154</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -8691,7 +8691,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>FFO 1721595 HAGAP.pdf</t>
+          <t>FFO 1715154 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -8701,14 +8701,14 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>1722320</t>
+          <t>1718561</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -8718,24 +8718,24 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>FFO 1722320 HAGAP.pdf</t>
+          <t>FFO 1718561 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>1.543,28</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>1722904</t>
+          <t>1718803</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -8745,7 +8745,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>FFO 1722904 HAGAP.pdf</t>
+          <t>FFO 1718803 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -8755,14 +8755,14 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>1667141</t>
+          <t>1719155</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -8772,7 +8772,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>FFO-1667141-HAGAP.pdf</t>
+          <t>FFO 1719155 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -8782,14 +8782,14 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>1675389</t>
+          <t>1719213</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -8799,7 +8799,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>FFO-1675389-HAGAP.pdf</t>
+          <t>FFO 1719213 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -8809,14 +8809,14 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>1691390</t>
+          <t>1720721</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>FFO-1691390-HAGAP.pdf</t>
+          <t>FFO 1720721 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -8836,14 +8836,14 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>1694841</t>
+          <t>1720909</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -8853,7 +8853,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>FFO-1694841-HAGAP.pdf</t>
+          <t>FFO 1720909 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -8863,14 +8863,14 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>1703223</t>
+          <t>1720920</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -8880,7 +8880,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>FFO-1703223-HAGAP.pdf</t>
+          <t>FFO 1720920 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -8890,14 +8890,14 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>1704877</t>
+          <t>1721595</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -8907,7 +8907,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>FFO-1704877-HAGAP.pdf</t>
+          <t>FFO 1721595 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -8917,14 +8917,14 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>1704953</t>
+          <t>1722320</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>FFO-1704953-HAGAP.pdf</t>
+          <t>FFO 1722320 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -8951,7 +8951,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>1708877</t>
+          <t>1722904</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -8961,7 +8961,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>FFO-1708877-HAGAP.pdf</t>
+          <t>FFO 1722904 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -8971,14 +8971,14 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>1709486</t>
+          <t>1667141</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -8988,7 +8988,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>FFO-1709486-HAGAP.pdf</t>
+          <t>FFO-1667141-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -8998,14 +8998,14 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>1710116</t>
+          <t>1675389</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -9015,7 +9015,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>FFO-1710116-HAGAP.pdf</t>
+          <t>FFO-1675389-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -9025,14 +9025,14 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>1711110</t>
+          <t>1691390</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -9042,7 +9042,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>FFO-1711110-HAGAP.pdf</t>
+          <t>FFO-1691390-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -9052,14 +9052,14 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>1711775</t>
+          <t>1694841</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -9069,7 +9069,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>FFO-1711775-HAGAP.pdf</t>
+          <t>FFO-1694841-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -9079,14 +9079,14 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>1712531</t>
+          <t>1703223</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -9096,7 +9096,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>FFO-1712531-HAGAP.pdf</t>
+          <t>FFO-1703223-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -9106,14 +9106,14 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>1712547</t>
+          <t>1704877</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -9123,7 +9123,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>FFO-1712547-HAGAP.pdf</t>
+          <t>FFO-1704877-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -9133,14 +9133,14 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>1712550</t>
+          <t>1704953</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -9150,7 +9150,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>FFO-1712550-HAGAP.pdf</t>
+          <t>FFO-1704953-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -9160,14 +9160,14 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>1713044C</t>
+          <t>1708877</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -9177,7 +9177,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>FFO-1713044C.-HAGAP.pdf</t>
+          <t>FFO-1708877-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -9187,14 +9187,14 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>1713044I</t>
+          <t>1709486</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -9204,7 +9204,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>FFO-1713044II-HAGAP.pdf</t>
+          <t>FFO-1709486-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -9214,14 +9214,14 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>1713226</t>
+          <t>1710116</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -9231,7 +9231,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>FFO-1713226-HAGAP.pdf</t>
+          <t>FFO-1710116-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -9241,14 +9241,14 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>1713262</t>
+          <t>1711110</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -9258,7 +9258,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>FFO-1713262-HAGAP.pdf</t>
+          <t>FFO-1711110-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -9268,14 +9268,14 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>1713626</t>
+          <t>1711775</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -9285,7 +9285,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>FFO-1713626-HAGAP.pdf</t>
+          <t>FFO-1711775-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -9295,14 +9295,14 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>1713656I</t>
+          <t>1712531</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -9312,7 +9312,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>FFO-1713656I-HAGAP.pdf</t>
+          <t>FFO-1712531-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -9322,14 +9322,14 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>1714342</t>
+          <t>1712547</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -9339,7 +9339,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>FFO-1714342-HAGAP.pdf</t>
+          <t>FFO-1712547-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -9349,14 +9349,14 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>1714857</t>
+          <t>1712550</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>FFO-1714857-HAGAP.pdf</t>
+          <t>FFO-1712550-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -9376,14 +9376,14 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>1714909</t>
+          <t>1713044C</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -9393,7 +9393,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>FFO-1714909-HAGAP.pdf</t>
+          <t>FFO-1713044C.-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -9403,14 +9403,14 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>1715127</t>
+          <t>1713044I</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -9420,7 +9420,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>FFO-1715127-HAGAP.pdf</t>
+          <t>FFO-1713044II-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -9430,14 +9430,14 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>1715201</t>
+          <t>1713226</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -9447,7 +9447,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>FFO-1715201-HAGAP.pdf</t>
+          <t>FFO-1713226-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -9457,14 +9457,14 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>1715257I</t>
+          <t>1713262</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -9474,7 +9474,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>FFO-1715257I-HAGAP.pdf</t>
+          <t>FFO-1713262-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -9484,14 +9484,14 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>1715327</t>
+          <t>1713626</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -9501,24 +9501,24 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>FFO-1715327-HAGAP.pdf</t>
+          <t>FFO-1713626-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>65,98</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>1715668</t>
+          <t>1713656I</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -9528,7 +9528,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>FFO-1715668-HAGAP.pdf</t>
+          <t>FFO-1713656I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -9538,14 +9538,14 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>1715710</t>
+          <t>1714342</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -9555,7 +9555,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>FFO-1715710-HAGAP.pdf</t>
+          <t>FFO-1714342-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -9572,7 +9572,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>1717168</t>
+          <t>1714857</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -9582,24 +9582,24 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>FFO-1717168-HAGAP.pdf</t>
+          <t>FFO-1714857-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>87,00</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>1717332</t>
+          <t>1714909</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -9609,24 +9609,24 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>FFO-1717332-HAGAP.pdf</t>
+          <t>FFO-1714909-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>176,23</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>1718019</t>
+          <t>1715127</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>FFO-1718019-HAGAP.pdf</t>
+          <t>FFO-1715127-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -9646,14 +9646,14 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>1719070</t>
+          <t>1715201</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>FFO-1719070-HAGAP.pdf</t>
+          <t>FFO-1715201-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -9673,14 +9673,14 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>1719881</t>
+          <t>1715257I</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>FFO-1719881-HAGAP.pdf</t>
+          <t>FFO-1715257I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -9700,14 +9700,14 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>1721869</t>
+          <t>1715327</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -9717,24 +9717,24 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>FFO-1721869-HAGAP.pdf</t>
+          <t>FFO-1715327-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>65,98</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>1724491</t>
+          <t>1715668</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>FFO-1724491-HAGAP.pdf</t>
+          <t>FFO-1715668-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -9754,14 +9754,14 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>1726890</t>
+          <t>1715710</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -9771,7 +9771,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>FFO-1726890-HAGAP.pdf</t>
+          <t>FFO-1715710-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -9788,7 +9788,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>1727335</t>
+          <t>1717168</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -9798,24 +9798,24 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>FFO-1727335-HAGAP.pdf</t>
+          <t>FFO-1717168-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>87,00</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>1727808</t>
+          <t>1717332</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -9825,24 +9825,24 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>FFO-1727808-HAGAP.pdf</t>
+          <t>FFO-1717332-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>176,23</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>1708066</t>
+          <t>1718019</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>FFO.-1708066-HAGAP.pdf</t>
+          <t>FFO-1718019-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -9862,14 +9862,14 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>1712957</t>
+          <t>1719070</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -9879,7 +9879,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>FFO.-1712957-HAGAP.pdf</t>
+          <t>FFO-1719070-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -9889,14 +9889,14 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>1713660</t>
+          <t>1719881</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>FFO.-1713660-HAGAP.pdf</t>
+          <t>FFO-1719881-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -9916,14 +9916,14 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>1691380</t>
+          <t>1721869</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -9933,7 +9933,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>FFO_1691380.pdf</t>
+          <t>FFO-1721869-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -9943,14 +9943,14 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>1717315</t>
+          <t>1724491</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -9960,7 +9960,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>FFO_1717315_HAGAP.pdf</t>
+          <t>FFO-1724491-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -9970,14 +9970,14 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>1725869</t>
+          <t>1726890</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -9987,24 +9987,24 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>FFO_1725869_HAGAP.pdf</t>
+          <t>FFO-1726890-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>2.488,83</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>1718442</t>
+          <t>1727335</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -10014,7 +10014,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>FFO´1718442-HAGAP.pdf</t>
+          <t>FFO-1727335-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -10024,24 +10024,24 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>1694841</t>
+          <t>1727808</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>MULTA-1694841-HAGAP.pdf</t>
+          <t>FFO-1727808-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -10049,22 +10049,26 @@
           <t>0,00</t>
         </is>
       </c>
-      <c r="E357" t="inlineStr"/>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>1703223</t>
+          <t>1708066</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>MULTA-1703223-HAGAP.pdf</t>
+          <t>FFO.-1708066-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -10072,22 +10076,26 @@
           <t>0,00</t>
         </is>
       </c>
-      <c r="E358" t="inlineStr"/>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>1704877</t>
+          <t>1712957</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>MULTA-1704877-HAGAP.pdf</t>
+          <t>FFO.-1712957-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -10095,22 +10103,26 @@
           <t>0,00</t>
         </is>
       </c>
-      <c r="E359" t="inlineStr"/>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>1713044I</t>
+          <t>1713660</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>MULTA-1713044I-HAGAP.pdf</t>
+          <t>FFO.-1713660-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -10118,22 +10130,26 @@
           <t>0,00</t>
         </is>
       </c>
-      <c r="E360" t="inlineStr"/>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>1715327</t>
+          <t>1691380</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>MULTA-1715327-HAGAP.pdf</t>
+          <t>FFO_1691380.pdf</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -10141,22 +10157,26 @@
           <t>0,00</t>
         </is>
       </c>
-      <c r="E361" t="inlineStr"/>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>1724491</t>
+          <t>1717315</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>MULTA-1724491-HAGAP.pdf</t>
+          <t>FFO_1717315_HAGAP.pdf</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -10164,30 +10184,253 @@
           <t>0,00</t>
         </is>
       </c>
-      <c r="E362" t="inlineStr"/>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
+          <t>1725869</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>FFO_1725869_HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>2.488,83</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>1718442</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>FFO</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>FFO´1718442-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>1694841</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>MULTA-1694841-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr"/>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>1703223</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>MULTA-1703223-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr"/>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>1704877</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>MULTA-1704877-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr"/>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>1713044I</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>MULTA-1713044I-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr"/>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>1715327</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>MULTA-1715327-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr"/>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>1724491</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>MULTA-1724491-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr"/>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
           <t>1726890</t>
         </is>
       </c>
-      <c r="B363" t="inlineStr">
-        <is>
-          <t>BMD</t>
-        </is>
-      </c>
-      <c r="C363" t="inlineStr">
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
         <is>
           <t>MULTA-1726890-HAGAP.pdf</t>
         </is>
       </c>
-      <c r="D363" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
-      </c>
-      <c r="E363" t="inlineStr"/>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr"/>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>1726324</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>bmd parcial-1726324-hagap.pdf</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>2.048,89</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>15/07/2026</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/medicoes.xlsx
+++ b/medicoes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E406"/>
+  <dimension ref="A1:E416"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2255,7 +2255,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1698047</t>
+          <t>1695716</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2265,24 +2265,24 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>BMD - 1698047 - HAGAP 30-04-2026.pdf</t>
+          <t>BMD - 1695716 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2.449,89</t>
+          <t>12.715,57</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1698056</t>
+          <t>1698047</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2292,24 +2292,24 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>BMD - 1698056 - HAGAP - 17-07-2026.pdf</t>
+          <t>BMD - 1698047 - HAGAP 30-04-2026.pdf</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>692,14</t>
+          <t>2.449,89</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1702640</t>
+          <t>1698056</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2319,24 +2319,24 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>BMD - 1702640 - HAGAP - 10-07-2026.pdf</t>
+          <t>BMD - 1698056 - HAGAP - 17-07-2026.pdf</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2.963,92</t>
+          <t>692,14</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1704867</t>
+          <t>1702212</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2346,24 +2346,24 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>BMD - 1704867 - ASP.pdf</t>
+          <t>BMD - 1702212 - DH - 20-07-2026.pdf</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>23.915,48</t>
+          <t>9.859,97</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1707174</t>
+          <t>1702640</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2373,24 +2373,24 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>BMD - 1707174 - HAGAP - 17-07-2026.pdf</t>
+          <t>BMD - 1702640 - HAGAP - 10-07-2026.pdf</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>1.924,94</t>
+          <t>2.963,92</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1709995</t>
+          <t>1704867</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2400,24 +2400,24 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>BMD - 1709995 - HAGAP.pdf</t>
+          <t>BMD - 1704867 - ASP.pdf</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2.410,16</t>
+          <t>23.915,48</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1711384</t>
+          <t>1707174</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2427,24 +2427,24 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>BMD - 1711384 - HAGAP.pdf</t>
+          <t>BMD - 1707174 - HAGAP - 17-07-2026.pdf</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>122,95</t>
+          <t>1.924,94</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1712538</t>
+          <t>1709995</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2454,24 +2454,24 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>BMD - 1712538 - HAGAP.pdf</t>
+          <t>BMD - 1709995 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>387,36</t>
+          <t>2.410,16</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1713240</t>
+          <t>1711384</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2481,24 +2481,24 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>BMD - 1713240 - HAGAP - 20-05-2026.pdf</t>
+          <t>BMD - 1711384 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>5.108,11</t>
+          <t>122,95</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1713933</t>
+          <t>1711454</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2508,24 +2508,24 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>BMD - 1713933 - HAGAP - 20-05-2026.pdf</t>
+          <t>BMD - 1711454 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>5.530,92</t>
+          <t>10.429,60</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1715878</t>
+          <t>1712538</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2535,24 +2535,24 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>BMD - 1715878 - HAGAP - 20-05-2026.pdf</t>
+          <t>BMD - 1712538 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>1.786,71</t>
+          <t>387,36</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1718435</t>
+          <t>1713240</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2562,24 +2562,24 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>BMD - 1718435 - HAGAP - 20-05-2026.pdf</t>
+          <t>BMD - 1713240 - HAGAP - 20-05-2026.pdf</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>17.153,90</t>
+          <t>5.108,11</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1718783</t>
+          <t>1713933</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2589,24 +2589,24 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>BMD - 1718783 - HAGAP.pdf</t>
+          <t>BMD - 1713933 - HAGAP - 20-05-2026.pdf</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>16.983,02</t>
+          <t>5.530,92</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1718783C</t>
+          <t>1715878</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2616,24 +2616,24 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>BMD - 1718783C - HAGAP.pdf</t>
+          <t>BMD - 1715878 - HAGAP - 20-05-2026.pdf</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>7,32</t>
+          <t>1.786,71</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1718956</t>
+          <t>1718435</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2643,24 +2643,24 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>BMD - 1718956 - HAGAP - 20-07-2026.pdf</t>
+          <t>BMD - 1718435 - HAGAP - 20-05-2026.pdf</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>34.745,40</t>
+          <t>17.153,90</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1718958</t>
+          <t>1718783</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2670,24 +2670,24 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>BMD - 1718958 - HAGAP - 20-07-2026.pdf</t>
+          <t>BMD - 1718783 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>24.975,36</t>
+          <t>16.983,02</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1722169</t>
+          <t>1718783C</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2697,24 +2697,24 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>BMD - 1722169 - HAGAP - 25-06-2026.pdf</t>
+          <t>BMD - 1718783C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>1.225,38</t>
+          <t>7,32</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1722321</t>
+          <t>1718956</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2724,24 +2724,24 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>BMD - 1722321 - HAGAP - 15-07-2026.pdf</t>
+          <t>BMD - 1718956 - HAGAP - 20-07-2026.pdf</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>8.119,58</t>
+          <t>34.745,40</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1724051I</t>
+          <t>1718958</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2751,24 +2751,24 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>BMD - 1724051I - HAGAP - 15-07-2026.pdf</t>
+          <t>BMD - 1718958 - HAGAP - 20-07-2026.pdf</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2.432,48</t>
+          <t>24.975,36</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1725738C</t>
+          <t>1722169</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2778,24 +2778,24 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>BMD - 1725738C - HAGAP.pdf</t>
+          <t>BMD - 1722169 - HAGAP - 25-06-2026.pdf</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>140,91</t>
+          <t>1.225,38</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1725738I</t>
+          <t>1722321</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2805,24 +2805,24 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>BMD - 1725738I - HAGAP.pdf</t>
+          <t>BMD - 1722321 - HAGAP - 15-07-2026.pdf</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>15.544,67</t>
+          <t>8.119,58</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1520612</t>
+          <t>1724051I</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2832,24 +2832,24 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>BMD 1520612 HAGAP.pdf</t>
+          <t>BMD - 1724051I - HAGAP - 15-07-2026.pdf</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>53.357,33</t>
+          <t>2.432,48</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1520615</t>
+          <t>1725738C</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2859,24 +2859,24 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>BMD 1520615 HAGAP.pdf</t>
+          <t>BMD - 1725738C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>22.840,59</t>
+          <t>140,91</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1536912</t>
+          <t>1725738I</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2886,24 +2886,24 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>BMD 1536912 PARCIAL HAGAP.pdf</t>
+          <t>BMD - 1725738I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2.474,56</t>
+          <t>15.544,67</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1660062C</t>
+          <t>1520612</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2913,24 +2913,24 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>BMD 1660062C HAGAP PARCIAL.pdf</t>
+          <t>BMD 1520612 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>100,65</t>
+          <t>53.357,33</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1660062I</t>
+          <t>1520615</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2940,24 +2940,24 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>BMD 1660062I HAGAP PARCIAL.pdf</t>
+          <t>BMD 1520615 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>11.953,89</t>
+          <t>22.840,59</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1671139I</t>
+          <t>1536912</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2967,24 +2967,24 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>BMD 1671139I HAGAP.pdf</t>
+          <t>BMD 1536912 PARCIAL HAGAP.pdf</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>6.138,54</t>
+          <t>2.474,56</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1692636</t>
+          <t>1660062C</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2994,24 +2994,24 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>BMD 1692636 ASP.pdf</t>
+          <t>BMD 1660062C HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>19.387,05</t>
+          <t>100,65</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1699516</t>
+          <t>1660062I</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3021,24 +3021,24 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>BMD 1699516 FF HAGAP.pdf</t>
+          <t>BMD 1660062I HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>287,85</t>
+          <t>11.953,89</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1699516</t>
+          <t>1671139I</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3048,24 +3048,24 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>BMD 1699516 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1671139I HAGAP.pdf</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>3.388,62</t>
+          <t>6.138,54</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1704525</t>
+          <t>1692636</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3075,24 +3075,24 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>BMD 1704525 FF HAGAP.pdf</t>
+          <t>BMD 1692636 ASP.pdf</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>86,77</t>
+          <t>19.387,05</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1704525</t>
+          <t>1699516</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3102,24 +3102,24 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>BMD 1704525 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1699516 FF HAGAP.pdf</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>15.365,48</t>
+          <t>287,85</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1704891</t>
+          <t>1699516</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3129,24 +3129,24 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>BMD 1704891 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1699516 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>41.477,99</t>
+          <t>3.388,62</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1705074</t>
+          <t>1704525</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>BMD 1705074 HAGAP.pdf</t>
+          <t>BMD 1704525 FF HAGAP.pdf</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>150.312,87</t>
+          <t>86,77</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1708906</t>
+          <t>1704525</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3183,24 +3183,24 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>BMD 1708906  30-04-2026 HAGAP.pdf</t>
+          <t>BMD 1704525 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>7.584,06</t>
+          <t>15.365,48</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1710329</t>
+          <t>1704891</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3210,24 +3210,24 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>BMD 1710329 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1704891 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>24.209,42</t>
+          <t>41.477,99</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1710937</t>
+          <t>1705074</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3237,24 +3237,24 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>BMD 1710937 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1705074 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>150.312,87</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1710975</t>
+          <t>1708906</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3264,24 +3264,24 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>BMD 1710975 HAGAP FF.pdf</t>
+          <t>BMD 1708906  30-04-2026 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>913,41</t>
+          <t>7.584,06</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1711525</t>
+          <t>1710329</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3291,24 +3291,24 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>BMD 1711525 FF HAGAP.pdf</t>
+          <t>BMD 1710329 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>126,93</t>
+          <t>24.209,42</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1711525</t>
+          <t>1710937</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3318,24 +3318,24 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>BMD 1711525 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1710937 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>1.998,42</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1711629</t>
+          <t>1710975</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3345,24 +3345,24 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>BMD 1711629 PARCIAL HAGAP.pdf</t>
+          <t>BMD 1710975 HAGAP FF.pdf</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>4.201,07</t>
+          <t>913,41</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1712533</t>
+          <t>1711525</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3372,24 +3372,24 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>BMD 1712533 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1711525 FF HAGAP.pdf</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2.553,46</t>
+          <t>126,93</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1712624</t>
+          <t>1711525</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3399,24 +3399,24 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>BMD 1712624 HAGAP.pdf</t>
+          <t>BMD 1711525 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>3.073,90</t>
+          <t>1.998,42</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1713223</t>
+          <t>1711629</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3426,24 +3426,24 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>BMD 1713223 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1711629 PARCIAL HAGAP.pdf</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>9.773,21</t>
+          <t>4.201,07</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1713351</t>
+          <t>1712533</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3453,24 +3453,24 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>BMD 1713351 HAGAPP.pdf</t>
+          <t>BMD 1712533 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>622,97</t>
+          <t>2.553,46</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1713679</t>
+          <t>1712624</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3480,12 +3480,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>BMD 1713679 HAGAP.pdf</t>
+          <t>BMD 1712624 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>3.574,44</t>
+          <t>3.073,90</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -3497,7 +3497,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1713719</t>
+          <t>1713223</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3507,24 +3507,24 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>BMD 1713719 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1713223 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>3.385,92</t>
+          <t>9.773,21</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1714364</t>
+          <t>1713351</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3534,24 +3534,24 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>BMD 1714364 HAGAP FF.pdf</t>
+          <t>BMD 1713351 HAGAPP.pdf</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>54,64</t>
+          <t>622,97</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1714729</t>
+          <t>1713679</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3561,24 +3561,24 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>BMD 1714729 HAGAP.pdf</t>
+          <t>BMD 1713679 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>6.722,61</t>
+          <t>3.574,44</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1715154</t>
+          <t>1713719</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3588,24 +3588,24 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>BMD 1715154 HAGAP.pdf</t>
+          <t>BMD 1713719 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2.658,74</t>
+          <t>3.385,92</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1715920</t>
+          <t>1714364</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3615,24 +3615,24 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>BMD 1715920 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1714364 HAGAP FF.pdf</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>1.031,94</t>
+          <t>54,64</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1718561</t>
+          <t>1714729</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3642,24 +3642,24 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>BMD 1718561 FF HAGAP.pdf</t>
+          <t>BMD 1714729 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>6.722,61</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1718803</t>
+          <t>1715154</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3669,24 +3669,24 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>BMD 1718803 HAGAP.pdf</t>
+          <t>BMD 1715154 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>3.825,18</t>
+          <t>2.658,74</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1719097</t>
+          <t>1715920</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3696,24 +3696,24 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>BMD 1719097 HAGAP.pdf</t>
+          <t>BMD 1715920 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>7.450,28</t>
+          <t>1.031,94</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1719155</t>
+          <t>1718561</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3723,24 +3723,24 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>BMD 1719155 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1718561 FF HAGAP.pdf</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2.223,15</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1719159</t>
+          <t>1718803</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3750,24 +3750,24 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>BMD 1719159 PARCIAL HAGAP.pdf</t>
+          <t>BMD 1718803 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2.240,81</t>
+          <t>3.825,18</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1719213</t>
+          <t>1719097</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3777,24 +3777,24 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>BMD 1719213 FF HAGAP.pdf</t>
+          <t>BMD 1719097 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>1.371,87</t>
+          <t>7.450,28</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1720721</t>
+          <t>1719155</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3804,24 +3804,24 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>BMD 1720721 HAGAP.pdf</t>
+          <t>BMD 1719155 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2.015,45</t>
+          <t>2.223,15</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1720909</t>
+          <t>1719159</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3831,24 +3831,24 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>BMD 1720909 HAGAP.pdf</t>
+          <t>BMD 1719159 PARCIAL HAGAP.pdf</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2.851,89</t>
+          <t>2.240,81</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1720920</t>
+          <t>1719213</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3858,24 +3858,24 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>BMD 1720920 FF HAGAP.pdf</t>
+          <t>BMD 1719213 FF HAGAP.pdf</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>89,29</t>
+          <t>1.371,87</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>1720920</t>
+          <t>1720721</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3885,24 +3885,24 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>BMD 1720920 HAGAP PARCIAL.pdf</t>
+          <t>BMD 1720721 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>555,60</t>
+          <t>2.015,45</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1721175</t>
+          <t>1720909</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3912,24 +3912,24 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>BMD 1721175 PARCIAL HAGAP.pdf</t>
+          <t>BMD 1720909 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>1.191,73</t>
+          <t>2.851,89</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1721595</t>
+          <t>1720920</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3939,24 +3939,24 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>BMD 1721595 HAGAP.pdf</t>
+          <t>BMD 1720920 FF HAGAP.pdf</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2.704,41</t>
+          <t>89,29</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>1721884</t>
+          <t>1720920</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3966,24 +3966,24 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>BMD 1721884 PARCIAL HAGAP.pdf</t>
+          <t>BMD 1720920 HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>41.481,66</t>
+          <t>555,60</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1722320</t>
+          <t>1721175</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3993,24 +3993,24 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>BMD 1722320 HAGAP.pdf</t>
+          <t>BMD 1721175 PARCIAL HAGAP.pdf</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>12.790,83</t>
+          <t>1.191,73</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1722904</t>
+          <t>1721595</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4020,24 +4020,24 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>BMD 1722904 HAGAP.pdf</t>
+          <t>BMD 1721595 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2.417,20</t>
+          <t>2.704,41</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1723691</t>
+          <t>1721884</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4047,24 +4047,24 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>BMD 1723691 PARCIAL HAGAP.pdf</t>
+          <t>BMD 1721884 PARCIAL HAGAP.pdf</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>19.599,32</t>
+          <t>41.481,66</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1724172</t>
+          <t>1722320</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4074,24 +4074,24 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>BMD 1724172 PARCIAL HAGAP.pdf</t>
+          <t>BMD 1722320 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>23.068,97</t>
+          <t>12.790,83</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1724356</t>
+          <t>1722904</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>BMD 1724356 HAGAP.pdf</t>
+          <t>BMD 1722904 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>7.614,80</t>
+          <t>2.417,20</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1724550</t>
+          <t>1723691</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4128,12 +4128,12 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>BMD 1724550 PARCIAL HAGAP.pdf</t>
+          <t>BMD 1723691 PARCIAL HAGAP.pdf</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>17.067,84</t>
+          <t>19.599,32</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -4145,7 +4145,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1725686</t>
+          <t>1724172</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4155,24 +4155,24 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>BMD 1725686 PARCIAL HAGAP.pdf</t>
+          <t>BMD 1724172 PARCIAL HAGAP.pdf</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>11.172,87</t>
+          <t>23.068,97</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1726332</t>
+          <t>1724356</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -4182,24 +4182,24 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>BMD 1726332 PARCIAL HAGAP.pdf</t>
+          <t>BMD 1724356 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>5.722,23</t>
+          <t>7.614,80</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1728055</t>
+          <t>1724550</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -4209,24 +4209,24 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>BMD 1728055 PARCIAL HAGAP.pdf</t>
+          <t>BMD 1724550 PARCIAL HAGAP.pdf</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>12.947,91</t>
+          <t>17.067,84</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1728163</t>
+          <t>1725686</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4236,24 +4236,24 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>BMD 1728163 HAGAP.pdf</t>
+          <t>BMD 1725686 PARCIAL HAGAP.pdf</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>7.914,69</t>
+          <t>11.172,87</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1730908</t>
+          <t>1726332</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4263,24 +4263,24 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>BMD 1730908 HAGAP-.pdf</t>
+          <t>BMD 1726332 PARCIAL HAGAP.pdf</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>4.386,39</t>
+          <t>5.722,23</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1682195</t>
+          <t>1728055</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4290,24 +4290,24 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>BMD FF 1682195 HAGAP.pdf</t>
+          <t>BMD 1728055 PARCIAL HAGAP.pdf</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>8,36</t>
+          <t>12.947,91</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1693027</t>
+          <t>1728163</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4317,24 +4317,24 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>BMD FF 1693027 HAGAP.pdf</t>
+          <t>BMD 1728163 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2.215,91</t>
+          <t>7.914,69</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>1710329</t>
+          <t>1730908</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4344,24 +4344,24 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>BMD FF 1710329 HAGAP.pdf</t>
+          <t>BMD 1730908 HAGAP-.pdf</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2,44</t>
+          <t>4.386,39</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1712533</t>
+          <t>1682195</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4371,24 +4371,24 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>BMD FF 1712533 HAGAP.pdf</t>
+          <t>BMD FF 1682195 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>127,40</t>
+          <t>8,36</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1719155</t>
+          <t>1693027</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4398,105 +4398,105 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>BMD FF 1719155 HAGAP.pdf</t>
+          <t>BMD FF 1693027 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>145,82</t>
+          <t>2.215,91</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1677316</t>
+          <t>1710329</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>BMD FINAL - 1677316 HAGAP.pdf</t>
+          <t>BMD FF 1710329 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2,44</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>1702776C</t>
+          <t>1712533</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>BMD FINAL - 1702776C - HAGAP.pdf</t>
+          <t>BMD FF 1712533 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>127,40</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>1702776I</t>
+          <t>1719155</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>BMD FINAL - 1702776I - HAGAP.pdf</t>
+          <t>BMD FF 1719155 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>18.098,87</t>
+          <t>145,82</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>1715278</t>
+          <t>1677316</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>BMD FINAL - 1715278 - HAGAP.pdf</t>
+          <t>BMD FINAL - 1677316 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -4516,14 +4516,14 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1715688</t>
+          <t>1702776C</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4533,24 +4533,24 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>BMD FINAL - 1715688 - HAGAP.pdf</t>
+          <t>BMD FINAL - 1702776C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>1.425,04</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>1713262</t>
+          <t>1702776I</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4560,24 +4560,24 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>BMD FINAL-1713262-HAGAP.pdf</t>
+          <t>BMD FINAL - 1702776I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>55,90</t>
+          <t>18.098,87</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>1719135</t>
+          <t>1715278</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4587,39 +4587,39 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>BMD FINAL-1719135-HAGAP.pdf</t>
+          <t>BMD FINAL - 1715278 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>47,08</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>1712550</t>
+          <t>1715688</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>BMD PARCAIL-1712550-HAGAP.pdf</t>
+          <t>BMD FINAL - 1715688 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>4.585,98</t>
+          <t>1.425,04</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -4631,22 +4631,22 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1677314</t>
+          <t>1713262</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1677314 - HAGAP.pdf</t>
+          <t>BMD FINAL-1713262-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>46.760,40</t>
+          <t>55,90</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -4658,34 +4658,34 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>1677316</t>
+          <t>1719135</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1677316 HAGAP.pdf</t>
+          <t>BMD FINAL-1719135-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>51.623,62</t>
+          <t>47,08</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1688115C</t>
+          <t>1712550</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4695,24 +4695,24 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1688115C - HAGAP.pdf</t>
+          <t>BMD PARCAIL-1712550-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>6,36</t>
+          <t>4.585,98</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>1688115I</t>
+          <t>1677314</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4722,24 +4722,24 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1688115I - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1677314 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>18.752,84</t>
+          <t>46.760,40</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>1691534</t>
+          <t>1677316</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4749,24 +4749,24 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1691534 - HAGAP - 19-06-2026.pdf</t>
+          <t>BMD PARCIAL - 1677316 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>20.334,45</t>
+          <t>51.623,62</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>1694258</t>
+          <t>1688115C</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4776,24 +4776,24 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1694258 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1688115C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>127.751,38</t>
+          <t>6,36</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>1695716</t>
+          <t>1688115I</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4803,24 +4803,24 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1695716 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1688115I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>74.647,17</t>
+          <t>18.752,84</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>1698056</t>
+          <t>1691534</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4830,24 +4830,24 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1698056 - HAGAP - 22-06-2026.pdf</t>
+          <t>BMD PARCIAL - 1691534 - HAGAP - 19-06-2026.pdf</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>8.966,25</t>
+          <t>20.334,45</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>1710735</t>
+          <t>1694258</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4857,24 +4857,24 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1710735 HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1694258 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>9.153,35</t>
+          <t>127.751,38</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>1711384</t>
+          <t>1695716</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4884,24 +4884,24 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1711384 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1695716 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2.127,38</t>
+          <t>74.647,17</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1712538</t>
+          <t>1698056</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4911,24 +4911,24 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1712538 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1698056 - HAGAP - 22-06-2026.pdf</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>3.568,05</t>
+          <t>8.966,25</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1715278</t>
+          <t>1710735</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4938,24 +4938,24 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1715278 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1710735 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2.654,77</t>
+          <t>9.153,35</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>1715688</t>
+          <t>1711384</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4965,24 +4965,24 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1715688 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1711384 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>9.669,94</t>
+          <t>2.127,38</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>1720914</t>
+          <t>1712538</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -4992,24 +4992,24 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1720914 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1712538 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>13.736,92</t>
+          <t>3.568,05</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>1721887</t>
+          <t>1715278</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5019,24 +5019,24 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1721887 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1715278 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>15.229,27</t>
+          <t>2.654,77</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>1722169</t>
+          <t>1715688</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1722169 - HAGAP - 19-06-2026.pdf</t>
+          <t>BMD PARCIAL - 1715688 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>38.238,91</t>
+          <t>9.669,94</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>1722779</t>
+          <t>1720914</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -5073,24 +5073,24 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1722779 - HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1720914 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>14.090,54</t>
+          <t>13.736,92</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>1727322</t>
+          <t>1721887</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5100,24 +5100,24 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>BMD PARCIAL - 1727322- HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1721887 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2.998,50</t>
+          <t>15.229,27</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>1676605</t>
+          <t>1722169</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5127,24 +5127,24 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>BMD PARCIAL -1676605-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1722169 - HAGAP - 19-06-2026.pdf</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>42.204,27</t>
+          <t>38.238,91</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1711378</t>
+          <t>1722779</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5154,24 +5154,24 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>BMD PARCIAL -1711378-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1722779 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>9.934,10</t>
+          <t>14.090,54</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>1712530</t>
+          <t>1727322</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -5181,24 +5181,24 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>BMD PARCIAL -1712530-HAGAP.pdf</t>
+          <t>BMD PARCIAL - 1727322- HAGAP.pdf</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>5.393,72</t>
+          <t>2.998,50</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>1713626I</t>
+          <t>1676605</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -5208,24 +5208,24 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>BMD PARCIAL -1713626I-HAGAP.pdf</t>
+          <t>BMD PARCIAL -1676605-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>5.318,80</t>
+          <t>42.204,27</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>1713260</t>
+          <t>1711378</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -5235,24 +5235,24 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>BMD PARCIAL 1713260 - HAGAP.pdf</t>
+          <t>BMD PARCIAL -1711378-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>8.854,04</t>
+          <t>9.934,10</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>1563492</t>
+          <t>1712530</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -5262,24 +5262,24 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>BMD PARCIAL CIANORTE - 1563492 - HAGAP.pdf</t>
+          <t>BMD PARCIAL -1712530-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>80.240,76</t>
+          <t>5.393,72</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>1563492</t>
+          <t>1713626I</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -5289,24 +5289,24 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>BMD PARCIAL JUSSARA - 1563492 - HAGAP.pdf</t>
+          <t>BMD PARCIAL -1713626I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>64.923,56</t>
+          <t>5.318,80</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>1564134</t>
+          <t>1713260</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -5316,24 +5316,24 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1564134-HAGAP.pdf</t>
+          <t>BMD PARCIAL 1713260 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>44.646,20</t>
+          <t>8.854,04</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>1667141</t>
+          <t>1563492</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -5343,24 +5343,24 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1667141-HAGAP.pdf</t>
+          <t>BMD PARCIAL CIANORTE - 1563492 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>509,47</t>
+          <t>80.240,76</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>1694841</t>
+          <t>1563492</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -5370,24 +5370,24 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1694841-HAGAP.pdf</t>
+          <t>BMD PARCIAL JUSSARA - 1563492 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>4.476,57</t>
+          <t>64.923,56</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>1704877</t>
+          <t>1564134</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -5397,24 +5397,24 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1704877-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1564134-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>158.642,45</t>
+          <t>44.646,20</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>1708877I</t>
+          <t>1667141</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -5424,24 +5424,24 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1708877I-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1667141-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2.132,72</t>
+          <t>509,47</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>1708908</t>
+          <t>1694841</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -5451,24 +5451,24 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1708908-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1694841-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>30.599,33</t>
+          <t>4.476,57</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>1709486</t>
+          <t>1704877</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -5478,24 +5478,24 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1709486-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1704877-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>4.402,38</t>
+          <t>158.642,45</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>1711507</t>
+          <t>1708877I</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -5505,24 +5505,24 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1711507-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1708877I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>14.415,50</t>
+          <t>2.132,72</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>1711775</t>
+          <t>1708908</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -5532,24 +5532,24 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1711775-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1708908-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>1.928,86</t>
+          <t>30.599,33</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>1712531</t>
+          <t>1709486</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -5559,24 +5559,24 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1712531-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1709486-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>5.019,99</t>
+          <t>4.402,38</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>1712963I</t>
+          <t>1711507</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -5586,24 +5586,24 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1712963I-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1711507-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>12.285,61</t>
+          <t>14.415,50</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>1713226</t>
+          <t>1711775</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -5613,24 +5613,24 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1713226-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1711775-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>3.049,11</t>
+          <t>1.928,86</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>1713656</t>
+          <t>1712531</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -5640,24 +5640,24 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1713656-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1712531-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>4.315,58</t>
+          <t>5.019,99</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>1713681</t>
+          <t>1712963I</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -5667,24 +5667,24 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1713681-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1712963I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>1.129,23</t>
+          <t>12.285,61</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>1714342</t>
+          <t>1713226</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -5694,24 +5694,24 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1714342-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1713226-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>1.949,56</t>
+          <t>3.049,11</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>1714348</t>
+          <t>1713656</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -5721,24 +5721,24 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1714348-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1713656-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>7.890,42</t>
+          <t>4.315,58</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>1714699</t>
+          <t>1713681</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -5748,24 +5748,24 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1714699-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1713681-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>18.624,62</t>
+          <t>1.129,23</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>1715201</t>
+          <t>1714342</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1715201-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1714342-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>6.987,28</t>
+          <t>1.949,56</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -5792,7 +5792,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>1715668</t>
+          <t>1714348</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -5802,24 +5802,24 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1715668-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1714348-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2.070,47</t>
+          <t>7.890,42</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>1715955I</t>
+          <t>1714699</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -5829,24 +5829,24 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1715955I-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1714699-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2.970,68</t>
+          <t>18.624,62</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>1717168</t>
+          <t>1715201</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -5856,24 +5856,24 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1717168-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1715201-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2.528,74</t>
+          <t>6.987,28</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>1717332</t>
+          <t>1715668</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -5883,24 +5883,24 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1717332-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1715668-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2.320,28</t>
+          <t>2.070,47</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>1718442</t>
+          <t>1715955I</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -5910,24 +5910,24 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1718442-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1715955I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>3.160,96</t>
+          <t>2.970,68</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>1718555I</t>
+          <t>1717168</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -5937,24 +5937,24 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1718555I-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1717168-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2.781,60</t>
+          <t>2.528,74</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>1719077</t>
+          <t>1717332</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -5964,24 +5964,24 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1719077-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1717332-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>9.937,52</t>
+          <t>2.320,28</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>1721869</t>
+          <t>1718442</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -5991,24 +5991,24 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1721869-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1718442-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>807,18</t>
+          <t>3.160,96</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>1724537</t>
+          <t>1718555I</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -6018,24 +6018,24 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1724537-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1718555I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>6.077,43</t>
+          <t>2.781,60</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>1724551</t>
+          <t>1719077</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -6045,24 +6045,24 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1724551-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1719077-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>7.181,35</t>
+          <t>9.937,52</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>1725260</t>
+          <t>1721869</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -6072,24 +6072,24 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1725260-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1721869-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>4.716,47</t>
+          <t>807,18</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>1727187</t>
+          <t>1724537</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -6099,24 +6099,24 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1727187-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1724537-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>4.280,60</t>
+          <t>6.077,43</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>1730222</t>
+          <t>1724551</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -6126,24 +6126,24 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1730222-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1724551-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>18.608,52</t>
+          <t>7.181,35</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>1730763</t>
+          <t>1725260</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -6153,24 +6153,24 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>BMD PARCIAL-1730763-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1725260-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>4.243,92</t>
+          <t>4.716,47</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>1713221</t>
+          <t>1727187</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -6180,24 +6180,24 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>BMD parcial - 1713221 - HAGAP.pdf</t>
+          <t>BMD PARCIAL-1727187-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>18.794,09</t>
+          <t>4.280,60</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>1715710</t>
+          <t>1730222</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -6207,24 +6207,24 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>BMD,-1715710-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1730222-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>326,74</t>
+          <t>18.608,52</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>1667141</t>
+          <t>1730763</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -6234,24 +6234,24 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>BMD-1667141-HAGAP.pdf</t>
+          <t>BMD PARCIAL-1730763-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>152,42</t>
+          <t>4.243,92</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>1675389</t>
+          <t>1713221</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -6261,24 +6261,24 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>BMD-1675389-HAGAP.pdf</t>
+          <t>BMD parcial - 1713221 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>389,52</t>
+          <t>18.794,09</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>1691390</t>
+          <t>1715710</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -6288,24 +6288,24 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>BMD-1691390-HAGAP..pdf</t>
+          <t>BMD,-1715710-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>457,30</t>
+          <t>326,74</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>1694841</t>
+          <t>1667141</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -6315,24 +6315,24 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>BMD-1694841-HAGAP.pdf</t>
+          <t>BMD-1667141-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>1.163,67</t>
+          <t>152,42</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>1703223</t>
+          <t>1675389</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -6342,24 +6342,24 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>BMD-1703223-HAGAP.pdf</t>
+          <t>BMD-1675389-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>1.471,15</t>
+          <t>389,52</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>1704877</t>
+          <t>1691390</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -6369,24 +6369,24 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>BMD-1704877-HAGAP.pdf</t>
+          <t>BMD-1691390-HAGAP..pdf</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>1.223,97</t>
+          <t>457,30</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>1704953</t>
+          <t>1694841</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -6396,24 +6396,24 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>BMD-1704953-HAGAP.pdf</t>
+          <t>BMD-1694841-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>9.260,98</t>
+          <t>1.163,67</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>1708066</t>
+          <t>1703223</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -6423,24 +6423,24 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>BMD-1708066-HAGAP.pdf</t>
+          <t>BMD-1703223-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>3.419,06</t>
+          <t>1.471,15</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>1709486</t>
+          <t>1704877</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -6450,24 +6450,24 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>BMD-1709486-HAGAP.pdf</t>
+          <t>BMD-1704877-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>1.889,02</t>
+          <t>1.223,97</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>1711775</t>
+          <t>1704953</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -6477,24 +6477,24 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>BMD-1711775-HAGAP.pdf</t>
+          <t>BMD-1704953-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>4,07</t>
+          <t>9.260,98</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>1712530</t>
+          <t>1708066</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -6504,24 +6504,24 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>BMD-1712530-HAGAP.pdf</t>
+          <t>BMD-1708066-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>1.529,03</t>
+          <t>3.419,06</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>1712547</t>
+          <t>1709486</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -6531,24 +6531,24 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>BMD-1712547-HAGAP.pdf</t>
+          <t>BMD-1709486-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>117,63</t>
+          <t>1.889,02</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>1712550</t>
+          <t>1711775</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -6558,12 +6558,12 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>BMD-1712550-HAGAP.pdf</t>
+          <t>BMD-1711775-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>421,10</t>
+          <t>4,07</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -6575,7 +6575,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>1712766</t>
+          <t>1712530</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -6585,24 +6585,24 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>BMD-1712766-HAGAP.pdf</t>
+          <t>BMD-1712530-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>705,45</t>
+          <t>1.529,03</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>1713044I</t>
+          <t>1712547</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -6612,24 +6612,24 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>BMD-1713044II-HAGAP.pdf</t>
+          <t>BMD-1712547-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>1.528,53</t>
+          <t>117,63</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>1713226</t>
+          <t>1712550</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -6639,24 +6639,24 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>BMD-1713226-HAGAP.pdf</t>
+          <t>BMD-1712550-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>237,93</t>
+          <t>421,10</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>1713626</t>
+          <t>1712766</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -6666,24 +6666,24 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>BMD-1713626-HAGAP.pdf</t>
+          <t>BMD-1712766-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>161,42</t>
+          <t>705,45</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>1713656I</t>
+          <t>1713044I</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -6693,24 +6693,24 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>BMD-1713656I-HAGAP.pdf</t>
+          <t>BMD-1713044II-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>161,74</t>
+          <t>1.528,53</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>1713660</t>
+          <t>1713226</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -6720,24 +6720,24 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>BMD-1713660-HAGAP.pdf</t>
+          <t>BMD-1713226-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>161,11</t>
+          <t>237,93</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>1713903C</t>
+          <t>1713626</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -6747,24 +6747,24 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>BMD-1713903C-HAGAP.pdf</t>
+          <t>BMD-1713626-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>36,14</t>
+          <t>161,42</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>1713903I</t>
+          <t>1713656I</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -6774,24 +6774,24 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>BMD-1713903I-HAGAP.pdf</t>
+          <t>BMD-1713656I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>972,91</t>
+          <t>161,74</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>1714342</t>
+          <t>1713660</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -6801,12 +6801,12 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>BMD-1714342-HAGAP.pdf</t>
+          <t>BMD-1713660-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>62,40</t>
+          <t>161,11</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -6818,7 +6818,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>1714857</t>
+          <t>1713903C</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -6828,24 +6828,24 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>BMD-1714857-HAGAP.pdf</t>
+          <t>BMD-1713903C-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>185,07</t>
+          <t>36,14</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>1714909</t>
+          <t>1713903I</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -6855,24 +6855,24 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>BMD-1714909-HAGAP.pdf</t>
+          <t>BMD-1713903I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>107,93</t>
+          <t>972,91</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>1715127</t>
+          <t>1714342</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -6882,24 +6882,24 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>BMD-1715127-HAGAP.pdf</t>
+          <t>BMD-1714342-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>128,31</t>
+          <t>62,40</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>1715131</t>
+          <t>1714857</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -6909,24 +6909,24 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>BMD-1715131-HAGAP.pdf</t>
+          <t>BMD-1714857-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2.220,22</t>
+          <t>185,07</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>1715201</t>
+          <t>1714909</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -6936,24 +6936,24 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>BMD-1715201-HAGAP.pdf</t>
+          <t>BMD-1714909-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>3,29</t>
+          <t>107,93</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>1715257I</t>
+          <t>1715127</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -6963,24 +6963,24 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>BMD-1715257I-HAGAP.pdf</t>
+          <t>BMD-1715127-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>6.765,65</t>
+          <t>128,31</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>1715668</t>
+          <t>1715131</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -6990,24 +6990,24 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>BMD-1715668-HAGAP.pdf</t>
+          <t>BMD-1715131-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>249,06</t>
+          <t>2.220,22</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>1715816C</t>
+          <t>1715201</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -7017,24 +7017,24 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>BMD-1715816C-HAGAP  PARCIAL.pdf</t>
+          <t>BMD-1715201-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>30,22</t>
+          <t>3,29</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>1715816I</t>
+          <t>1715257I</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -7044,24 +7044,24 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>BMD-1715816I-HAGAP  PARCIAL.pdf</t>
+          <t>BMD-1715257I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>3.168,40</t>
+          <t>6.765,65</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>1715899</t>
+          <t>1715668</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -7071,24 +7071,24 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>BMD-1715899-HAGAP  PARCIAL.pdf</t>
+          <t>BMD-1715668-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>3.389,65</t>
+          <t>249,06</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>1717166</t>
+          <t>1715816C</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -7098,24 +7098,24 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>BMD-1717166-HAGAP  PARCIAL.pdf</t>
+          <t>BMD-1715816C-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>22.116,83</t>
+          <t>30,22</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>1717168</t>
+          <t>1715816I</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -7125,24 +7125,24 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>BMD-1717168-HAGAP.pdf</t>
+          <t>BMD-1715816I-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>3.168,40</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>1718019</t>
+          <t>1715899</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -7152,24 +7152,24 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>BMD-1718019-HAGAP.pdf</t>
+          <t>BMD-1715899-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>4.408,31</t>
+          <t>3.389,65</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>1718442</t>
+          <t>1717166</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -7179,24 +7179,24 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>BMD-1718442-HAGAP.pdf</t>
+          <t>BMD-1717166-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>45,19</t>
+          <t>22.116,83</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>1718561</t>
+          <t>1717168</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -7206,24 +7206,24 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>BMD-1718561-HAGAP PARCIAL.pdf</t>
+          <t>BMD-1717168-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>13.683,99</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>1719070</t>
+          <t>1718019</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -7233,24 +7233,24 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>BMD-1719070-HAGAP.pdf</t>
+          <t>BMD-1718019-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>333,14</t>
+          <t>4.408,31</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>1719213</t>
+          <t>1718442</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -7260,24 +7260,24 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>BMD-1719213-HAGAP  PARCIAL.pdf</t>
+          <t>BMD-1718442-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>5.951,32</t>
+          <t>45,19</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>1719214</t>
+          <t>1718561</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -7287,24 +7287,24 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>BMD-1719214-HAGAP  PARCIAL.pdf</t>
+          <t>BMD-1718561-HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>6.124,60</t>
+          <t>13.683,99</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>1719881</t>
+          <t>1719070</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -7314,12 +7314,12 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>BMD-1719881-HAGAP.pdf</t>
+          <t>BMD-1719070-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>3.239,73</t>
+          <t>333,14</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -7331,7 +7331,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>1719881H</t>
+          <t>1719213</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -7341,24 +7341,24 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>BMD-1719881HAGAP.pdf</t>
+          <t>BMD-1719213-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>38.258,42</t>
+          <t>5.951,32</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>1720116</t>
+          <t>1719214</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -7368,24 +7368,24 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>BMD-1720116-HAGAP.pdf</t>
+          <t>BMD-1719214-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>168,95</t>
+          <t>6.124,60</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>1721631</t>
+          <t>1719881</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -7395,24 +7395,24 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>BMD-1721631-HAGAP  PARCIAL.pdf</t>
+          <t>BMD-1719881-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>12.649,43</t>
+          <t>3.239,73</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>1721631C</t>
+          <t>1719881H</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -7422,24 +7422,24 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>BMD-1721631C-HAGAP  PARCIAL.pdf</t>
+          <t>BMD-1719881HAGAP.pdf</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>100,65</t>
+          <t>38.258,42</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>1721869</t>
+          <t>1720116</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -7449,24 +7449,24 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>BMD-1721869-HAGAP.pdf</t>
+          <t>BMD-1720116-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>133,09</t>
+          <t>168,95</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>1721886</t>
+          <t>1721631</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -7476,24 +7476,24 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>BMD-1721886 - HAGAP PARCIAL.pdf</t>
+          <t>BMD-1721631-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>14.551,70</t>
+          <t>12.649,43</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>1724491</t>
+          <t>1721631C</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -7503,24 +7503,24 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>BMD-1724491-HAGAP.pdf</t>
+          <t>BMD-1721631C-HAGAP  PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>33,42</t>
+          <t>100,65</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>1725260</t>
+          <t>1721869</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>BMD-1725260-HAGAP.pdf</t>
+          <t>BMD-1721869-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>10,16</t>
+          <t>133,09</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -7547,7 +7547,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>1726890</t>
+          <t>1721886</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -7557,24 +7557,24 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>BMD-1726890-HAGAP.pdf</t>
+          <t>BMD-1721886 - HAGAP PARCIAL.pdf</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>3.252,02</t>
+          <t>14.551,70</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>1727335</t>
+          <t>1724491</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -7584,24 +7584,24 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>BMD-1727335-HAGAP.pdf</t>
+          <t>BMD-1724491-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>5.053,73</t>
+          <t>33,42</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>1727808I</t>
+          <t>1725260</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -7611,24 +7611,24 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>BMD-1727808I-HAGAP.pdf</t>
+          <t>BMD-1725260-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2.562,33</t>
+          <t>10,16</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>1729828</t>
+          <t>1726324</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -7638,24 +7638,24 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>BMD-1729828-HAGAP.pdf</t>
+          <t>BMD-1726324-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>914,81</t>
+          <t>245,31</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>1713044C</t>
+          <t>1726890</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -7665,24 +7665,24 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>BMD.-1713044C.-HAGAP.pdf</t>
+          <t>BMD-1726890-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>21,11</t>
+          <t>3.252,02</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>1715327</t>
+          <t>1727335</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -7692,105 +7692,105 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>BMD.1715327-HAGAP.pdf</t>
+          <t>BMD-1727335-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>5.053,73</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>1708877</t>
+          <t>1727529</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>BMDFINAL-1708877-HAGAP.pdf</t>
+          <t>BMD-1727529-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>3,54</t>
+          <t>4.366,81</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>1712957</t>
+          <t>1727808I</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>BMDFINAL-1712957-HAGAP.pdf</t>
+          <t>BMD-1727808I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>45,19</t>
+          <t>2.562,33</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>1717332</t>
+          <t>1729828</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>BMDFINAL-1717332-HAGAP.pdf</t>
+          <t>BMD-1729828-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>914,81</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>1703223</t>
+          <t>1713044C</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -7800,24 +7800,24 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1703223-HAGAP.pdf</t>
+          <t>BMD.-1713044C.-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>18.169,34</t>
+          <t>21,11</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>1712547</t>
+          <t>1715327</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -7827,66 +7827,66 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1712547-HAGAP.pdf</t>
+          <t>BMD.1715327-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>6.951,82</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>1712957</t>
+          <t>1708877</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1712957-HAGAP.pdf</t>
+          <t>BMDFINAL-1708877-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>2.177,64</t>
+          <t>3,54</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>1713262</t>
+          <t>1712957</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1713262-HAGAP.pdf</t>
+          <t>BMDFINAL-1712957-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>2.619,71</t>
+          <t>45,19</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -7898,34 +7898,34 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>1714909</t>
+          <t>1717332</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1714909-HAGAP.pdf</t>
+          <t>BMDFINAL-1717332-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>954,64</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>1715127</t>
+          <t>1703223</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -7935,24 +7935,24 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1715127-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1703223-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>4.418,94</t>
+          <t>18.169,34</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>1715327</t>
+          <t>1712547</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -7962,24 +7962,24 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1715327-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1712547-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>5.417,39</t>
+          <t>6.951,82</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>1719070</t>
+          <t>1712957</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -7989,24 +7989,24 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1719070-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1712957-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>2.744,71</t>
+          <t>2.177,64</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>1719135</t>
+          <t>1713262</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1719135-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1713262-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>913,84</t>
+          <t>2.619,71</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -8033,7 +8033,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>1720116</t>
+          <t>1714909</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -8043,12 +8043,12 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1720116-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1714909-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>1.675,57</t>
+          <t>954,64</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -8060,7 +8060,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>1724491</t>
+          <t>1715127</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -8070,24 +8070,24 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>BMDPARCIAL-1724491-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1715127-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>14.377,51</t>
+          <t>4.418,94</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>1717315</t>
+          <t>1715327</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -8097,24 +8097,24 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>BMD_1717315_HAGAP.pdf</t>
+          <t>BMDPARCIAL-1715327-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>13.183,29</t>
+          <t>5.417,39</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>1725869</t>
+          <t>1719070</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -8124,142 +8124,142 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>BMD_1725869_HAGAP.pdf</t>
+          <t>BMDPARCIAL-1719070-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.744,71</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>1712766</t>
+          <t>1719135</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>FF0-1712766-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1719135-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>913,84</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>1719135</t>
+          <t>1720116</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>FFO  -1719135-HAGAP.pdf</t>
+          <t>BMDPARCIAL-1720116-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>1.675,57</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>1510407</t>
+          <t>1724491</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>FFO - 1510407 - HAGAP - 20-07-2026.pdf</t>
+          <t>BMDPARCIAL-1724491-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>14.377,51</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>1658892</t>
+          <t>1717315</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>FFO - 1658892 - HAGAP - 15-07-2026.pdf</t>
+          <t>BMD_1717315_HAGAP.pdf</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>13.183,29</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>1677314</t>
+          <t>1725869</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>FFO</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>FFO - 1677314 - HAGAP.pdf</t>
+          <t>BMD_1725869_HAGAP.pdf</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -8276,7 +8276,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>1677316</t>
+          <t>1712766</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -8286,7 +8286,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>FFO - 1677316 HAGAP.pdf</t>
+          <t>FF0-1712766-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -8296,14 +8296,14 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>1688115C</t>
+          <t>1719135</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -8313,7 +8313,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>FFO - 1688115C - HAGAP.pdf</t>
+          <t>FFO  -1719135-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -8323,14 +8323,14 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>1688115I</t>
+          <t>1510407</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -8340,7 +8340,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>FFO - 1688115I - HAGAP.pdf</t>
+          <t>FFO - 1510407 - HAGAP - 20-07-2026.pdf</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -8350,14 +8350,14 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>1691534</t>
+          <t>1658892</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -8367,7 +8367,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>FFO - 1691534 - HAGAP - 03-07-2026.pdf</t>
+          <t>FFO - 1658892 - HAGAP - 15-07-2026.pdf</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -8377,14 +8377,14 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>1692174</t>
+          <t>1677314</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -8394,7 +8394,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>FFO - 1692174 - HAGAP.pdf</t>
+          <t>FFO - 1677314 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -8404,14 +8404,14 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>1698047</t>
+          <t>1677316</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -8421,7 +8421,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>FFO - 1698047 - HAGAP - 30-04-2026.pdf</t>
+          <t>FFO - 1677316 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -8431,14 +8431,14 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>1698056</t>
+          <t>1688115C</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -8448,7 +8448,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>FFO - 1698056 - HAGAP - 17-07-2026.pdf</t>
+          <t>FFO - 1688115C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -8458,14 +8458,14 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>1702127</t>
+          <t>1688115I</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -8475,7 +8475,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>FFO - 1702127 - HAGAP.pdf</t>
+          <t>FFO - 1688115I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -8485,14 +8485,14 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>1702640</t>
+          <t>1691534</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>FFO - 1702640 - HAGAP - 10-07-2026.pdf</t>
+          <t>FFO - 1691534 - HAGAP - 03-07-2026.pdf</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -8512,14 +8512,14 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>1702776C</t>
+          <t>1692174</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -8529,7 +8529,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>FFO - 1702776C - HAGAP.pdf</t>
+          <t>FFO - 1692174 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -8539,14 +8539,14 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>1702776I</t>
+          <t>1695716</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>FFO - 1702776I - HAGAP.pdf</t>
+          <t>FFO - 1695716 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -8566,14 +8566,14 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>1704867</t>
+          <t>1698047</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>FFO - 1704867 - ASP.pdf</t>
+          <t>FFO - 1698047 - HAGAP - 30-04-2026.pdf</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -8593,14 +8593,14 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>1705802I</t>
+          <t>1698056</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -8610,7 +8610,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>FFO - 1705802I - HAGAP.pdf</t>
+          <t>FFO - 1698056 - HAGAP - 17-07-2026.pdf</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -8620,14 +8620,14 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>1707174</t>
+          <t>1702127</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -8637,7 +8637,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>FFO - 1707174 - HAGAP - 17-07-2026.pdf</t>
+          <t>FFO - 1702127 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -8647,14 +8647,14 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>1709419</t>
+          <t>1702640</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -8664,7 +8664,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>FFO - 1709419 - HAGAP.pdf</t>
+          <t>FFO - 1702640 - HAGAP - 10-07-2026.pdf</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -8674,14 +8674,14 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>1709995</t>
+          <t>1702776C</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -8691,7 +8691,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>FFO - 1709995 - HAGAP.pdf</t>
+          <t>FFO - 1702776C - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -8701,14 +8701,14 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>1711384</t>
+          <t>1702776I</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>FFO - 1711384 - HAGAP.pdf</t>
+          <t>FFO - 1702776I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -8728,14 +8728,14 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>1712538</t>
+          <t>1704867</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -8745,7 +8745,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>FFO - 1712538 - HAGAP.pdf</t>
+          <t>FFO - 1704867 - ASP.pdf</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -8755,14 +8755,14 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>1713221</t>
+          <t>1705802I</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -8772,7 +8772,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>FFO - 1713221 - HAGAP.pdf</t>
+          <t>FFO - 1705802I - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -8782,14 +8782,14 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>1713240</t>
+          <t>1707174</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -8799,7 +8799,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>FFO - 1713240 - HAGAP - 20-05-2026.pdf</t>
+          <t>FFO - 1707174 - HAGAP - 17-07-2026.pdf</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -8809,14 +8809,14 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>1715278</t>
+          <t>1709419</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -8826,24 +8826,24 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>FFO - 1715278 - HAGAP.pdf</t>
+          <t>FFO - 1709419 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>306,36</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>1715688</t>
+          <t>1709995</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -8853,7 +8853,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>FFO - 1715688 - HAGAP.pdf</t>
+          <t>FFO - 1709995 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -8863,14 +8863,14 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>1715878</t>
+          <t>1711384</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -8880,7 +8880,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>FFO - 1715878 - HAGAP - 20-05-2026.pdf</t>
+          <t>FFO - 1711384 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -8890,14 +8890,14 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>1722321</t>
+          <t>1711454</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -8907,7 +8907,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>FFO - 1722321 - HAGAP - 15-07-2026.pdf</t>
+          <t>FFO - 1711454 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -8917,14 +8917,14 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>1724051I</t>
+          <t>1712538</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>FFO - 1724051I - HAGAP - 15-07-2026.pdf</t>
+          <t>FFO - 1712538 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -8944,14 +8944,14 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>1520615</t>
+          <t>1713221</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -8961,7 +8961,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>FFO 1520615 HAGAP.pdf</t>
+          <t>FFO - 1713221 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -8971,14 +8971,14 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>1641139I</t>
+          <t>1713240</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -8988,7 +8988,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>FFO 1641139I HAGAP.pdf</t>
+          <t>FFO - 1713240 - HAGAP - 20-05-2026.pdf</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -8998,14 +8998,14 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>1682195</t>
+          <t>1715278</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -9015,24 +9015,24 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>FFO 1682195 HAGAP.pdf</t>
+          <t>FFO - 1715278 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>306,36</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>1693027</t>
+          <t>1715688</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -9042,7 +9042,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>FFO 1693027 HAGAP.pdf</t>
+          <t>FFO - 1715688 - HAGAP.pdf</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -9052,14 +9052,14 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>1699516</t>
+          <t>1715878</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -9069,7 +9069,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>FFO 1699516 HAGAP.pdf</t>
+          <t>FFO - 1715878 - HAGAP - 20-05-2026.pdf</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -9079,14 +9079,14 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>1704525</t>
+          <t>1722321</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -9096,7 +9096,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>FFO 1704525 HAGAP.pdf</t>
+          <t>FFO - 1722321 - HAGAP - 15-07-2026.pdf</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -9106,14 +9106,14 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>1710329</t>
+          <t>1724051I</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -9123,7 +9123,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>FFO 1710329 HAGAP.pdf</t>
+          <t>FFO - 1724051I - HAGAP - 15-07-2026.pdf</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -9133,14 +9133,14 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>1710736</t>
+          <t>1520615</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -9150,7 +9150,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>FFO 1710736 HAGAP.pdf</t>
+          <t>FFO 1520615 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -9160,14 +9160,14 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>1710975</t>
+          <t>1641139I</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -9177,7 +9177,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>FFO 1710975 HAGAP.pdf</t>
+          <t>FFO 1641139I HAGAP.pdf</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -9187,14 +9187,14 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>1711525</t>
+          <t>1682195</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -9204,7 +9204,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>FFO 1711525 HAGAP.pdf</t>
+          <t>FFO 1682195 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -9214,14 +9214,14 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>1712533</t>
+          <t>1693027</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -9231,7 +9231,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>FFO 1712533 HAGAP.pdf</t>
+          <t>FFO 1693027 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -9241,14 +9241,14 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>1713351</t>
+          <t>1699516</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -9258,7 +9258,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>FFO 1713351 HAGAP.pdf</t>
+          <t>FFO 1699516 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -9268,14 +9268,14 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>1713435I</t>
+          <t>1704525</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -9285,7 +9285,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>FFO 1713435I HAGAP.pdf</t>
+          <t>FFO 1704525 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -9295,14 +9295,14 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>1713679</t>
+          <t>1710329</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -9312,7 +9312,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>FFO 1713679 HAGAP.pdf</t>
+          <t>FFO 1710329 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -9322,14 +9322,14 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>1714364</t>
+          <t>1710736</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -9339,7 +9339,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>FFO 1714364 HAGAP.pdf</t>
+          <t>FFO 1710736 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -9349,14 +9349,14 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>1714729</t>
+          <t>1710975</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>FFO 1714729 HAGAP.pdf</t>
+          <t>FFO 1710975 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -9376,14 +9376,14 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>1715154</t>
+          <t>1711525</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -9393,7 +9393,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>FFO 1715154 HAGAP.pdf</t>
+          <t>FFO 1711525 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -9403,14 +9403,14 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>1718561</t>
+          <t>1712533</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -9420,24 +9420,24 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>FFO 1718561 HAGAP.pdf</t>
+          <t>FFO 1712533 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>1.543,28</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>1718803</t>
+          <t>1713351</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -9447,7 +9447,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>FFO 1718803 HAGAP.pdf</t>
+          <t>FFO 1713351 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -9457,14 +9457,14 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>1719155</t>
+          <t>1713435I</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -9474,7 +9474,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>FFO 1719155 HAGAP.pdf</t>
+          <t>FFO 1713435I HAGAP.pdf</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -9484,14 +9484,14 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>1719213</t>
+          <t>1713679</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -9501,7 +9501,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>FFO 1719213 HAGAP.pdf</t>
+          <t>FFO 1713679 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -9511,14 +9511,14 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>1720721</t>
+          <t>1714364</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -9528,7 +9528,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>FFO 1720721 HAGAP.pdf</t>
+          <t>FFO 1714364 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -9538,14 +9538,14 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>1720909</t>
+          <t>1714729</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -9555,7 +9555,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>FFO 1720909 HAGAP.pdf</t>
+          <t>FFO 1714729 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -9565,14 +9565,14 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>1720920</t>
+          <t>1715154</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -9582,7 +9582,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>FFO 1720920 HAGAP.pdf</t>
+          <t>FFO 1715154 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -9592,14 +9592,14 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>1721595</t>
+          <t>1718561</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -9609,24 +9609,24 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>FFO 1721595 HAGAP.pdf</t>
+          <t>FFO 1718561 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>1.543,28</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>1722320</t>
+          <t>1718803</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>FFO 1722320 HAGAP.pdf</t>
+          <t>FFO 1718803 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -9646,14 +9646,14 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>1722904</t>
+          <t>1719155</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>FFO 1722904 HAGAP.pdf</t>
+          <t>FFO 1719155 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -9673,14 +9673,14 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>1730908</t>
+          <t>1719213</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>FFO 1730908 HAGAP.pdf</t>
+          <t>FFO 1719213 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -9700,14 +9700,14 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>1667141</t>
+          <t>1720721</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -9717,7 +9717,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>FFO-1667141-HAGAP.pdf</t>
+          <t>FFO 1720721 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -9727,14 +9727,14 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>1675389</t>
+          <t>1720909</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>FFO-1675389-HAGAP.pdf</t>
+          <t>FFO 1720909 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -9754,14 +9754,14 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>1691390</t>
+          <t>1720920</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -9771,7 +9771,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>FFO-1691390-HAGAP.pdf</t>
+          <t>FFO 1720920 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -9781,14 +9781,14 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>1694841</t>
+          <t>1721595</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -9798,7 +9798,7 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>FFO-1694841-HAGAP.pdf</t>
+          <t>FFO 1721595 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -9808,14 +9808,14 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>1703223</t>
+          <t>1722320</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -9825,7 +9825,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>FFO-1703223-HAGAP.pdf</t>
+          <t>FFO 1722320 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -9835,14 +9835,14 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>1704877</t>
+          <t>1722904</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>FFO-1704877-HAGAP.pdf</t>
+          <t>FFO 1722904 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -9862,14 +9862,14 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>1704953</t>
+          <t>1730908</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -9879,7 +9879,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>FFO-1704953-HAGAP.pdf</t>
+          <t>FFO 1730908 HAGAP.pdf</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -9889,14 +9889,14 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>1708877</t>
+          <t>1667141</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>FFO-1708877-HAGAP.pdf</t>
+          <t>FFO-1667141-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -9916,14 +9916,14 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>1709486</t>
+          <t>1675389</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -9933,7 +9933,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>FFO-1709486-HAGAP.pdf</t>
+          <t>FFO-1675389-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -9943,14 +9943,14 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>1710116</t>
+          <t>1691390</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -9960,7 +9960,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>FFO-1710116-HAGAP.pdf</t>
+          <t>FFO-1691390-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -9970,14 +9970,14 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>1711110</t>
+          <t>1694841</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -9987,7 +9987,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>FFO-1711110-HAGAP.pdf</t>
+          <t>FFO-1694841-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -9997,14 +9997,14 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>1711775</t>
+          <t>1703223</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -10014,7 +10014,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>FFO-1711775-HAGAP.pdf</t>
+          <t>FFO-1703223-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -10024,14 +10024,14 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>1712530</t>
+          <t>1704877</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -10041,7 +10041,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>FFO-1712530=-HAGAP.pdf</t>
+          <t>FFO-1704877-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -10051,14 +10051,14 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>1712531</t>
+          <t>1704953</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -10068,7 +10068,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>FFO-1712531-HAGAP.pdf</t>
+          <t>FFO-1704953-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -10078,14 +10078,14 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>1712547</t>
+          <t>1708877</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -10095,7 +10095,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>FFO-1712547-HAGAP.pdf</t>
+          <t>FFO-1708877-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -10105,14 +10105,14 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>1712550</t>
+          <t>1709486</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -10122,7 +10122,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>FFO-1712550-HAGAP.pdf</t>
+          <t>FFO-1709486-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -10132,14 +10132,14 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>1713044C</t>
+          <t>1710116</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -10149,7 +10149,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>FFO-1713044C.-HAGAP.pdf</t>
+          <t>FFO-1710116-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -10159,14 +10159,14 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>1713044I</t>
+          <t>1711110</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -10176,7 +10176,7 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>FFO-1713044II-HAGAP.pdf</t>
+          <t>FFO-1711110-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -10186,14 +10186,14 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>1713226</t>
+          <t>1711775</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -10203,7 +10203,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>FFO-1713226-HAGAP.pdf</t>
+          <t>FFO-1711775-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -10213,14 +10213,14 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>1713262</t>
+          <t>1712530</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -10230,7 +10230,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>FFO-1713262-HAGAP.pdf</t>
+          <t>FFO-1712530=-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -10240,14 +10240,14 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>1713626</t>
+          <t>1712531</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -10257,7 +10257,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>FFO-1713626-HAGAP.pdf</t>
+          <t>FFO-1712531-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -10267,14 +10267,14 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>1713656I</t>
+          <t>1712547</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -10284,7 +10284,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>FFO-1713656I-HAGAP.pdf</t>
+          <t>FFO-1712547-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -10294,14 +10294,14 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>1713903C</t>
+          <t>1712550</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -10311,7 +10311,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>FFO-1713903C-HAGAP.pdf</t>
+          <t>FFO-1712550-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -10321,14 +10321,14 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>1713903I</t>
+          <t>1713044C</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -10338,7 +10338,7 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>FFO-1713903I-HAGAP.pdf</t>
+          <t>FFO-1713044C.-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -10348,14 +10348,14 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>1714342</t>
+          <t>1713044I</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -10365,7 +10365,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>FFO-1714342-HAGAP.pdf</t>
+          <t>FFO-1713044II-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
@@ -10375,14 +10375,14 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>1714857</t>
+          <t>1713226</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -10392,7 +10392,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>FFO-1714857-HAGAP.pdf</t>
+          <t>FFO-1713226-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
@@ -10402,14 +10402,14 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>1714909</t>
+          <t>1713262</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -10419,7 +10419,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>FFO-1714909-HAGAP.pdf</t>
+          <t>FFO-1713262-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -10429,14 +10429,14 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>1715127</t>
+          <t>1713626</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -10446,7 +10446,7 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>FFO-1715127-HAGAP.pdf</t>
+          <t>FFO-1713626-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
@@ -10456,14 +10456,14 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>1715201</t>
+          <t>1713656I</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -10473,7 +10473,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>FFO-1715201-HAGAP.pdf</t>
+          <t>FFO-1713656I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -10490,7 +10490,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>1715257I</t>
+          <t>1713903C</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>FFO-1715257I-HAGAP.pdf</t>
+          <t>FFO-1713903C-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -10510,14 +10510,14 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>1715327</t>
+          <t>1713903I</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -10527,24 +10527,24 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>FFO-1715327-HAGAP.pdf</t>
+          <t>FFO-1713903I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>65,98</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>1715668</t>
+          <t>1714342</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -10554,7 +10554,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>FFO-1715668-HAGAP.pdf</t>
+          <t>FFO-1714342-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
@@ -10564,14 +10564,14 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>1715710</t>
+          <t>1714857</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -10581,7 +10581,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>FFO-1715710-HAGAP.pdf</t>
+          <t>FFO-1714857-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
@@ -10591,14 +10591,14 @@
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>1717168</t>
+          <t>1714909</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -10608,24 +10608,24 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>FFO-1717168-HAGAP.pdf</t>
+          <t>FFO-1714909-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>87,00</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>1717332</t>
+          <t>1715127</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -10635,24 +10635,24 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>FFO-1717332-HAGAP.pdf</t>
+          <t>FFO-1715127-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>176,23</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>1718019</t>
+          <t>1715201</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -10662,7 +10662,7 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>FFO-1718019-HAGAP.pdf</t>
+          <t>FFO-1715201-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
@@ -10672,14 +10672,14 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>1719070</t>
+          <t>1715257I</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -10689,7 +10689,7 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>FFO-1719070-HAGAP.pdf</t>
+          <t>FFO-1715257I-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
@@ -10699,14 +10699,14 @@
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>1719881</t>
+          <t>1715327</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -10716,24 +10716,24 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>FFO-1719881-HAGAP.pdf</t>
+          <t>FFO-1715327-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>65,98</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>1721869</t>
+          <t>1715668</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -10743,7 +10743,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>FFO-1721869-HAGAP.pdf</t>
+          <t>FFO-1715668-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
@@ -10753,14 +10753,14 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>1724491</t>
+          <t>1715710</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -10770,7 +10770,7 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>FFO-1724491-HAGAP.pdf</t>
+          <t>FFO-1715710-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
@@ -10787,7 +10787,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>1725260</t>
+          <t>1717168</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -10797,24 +10797,24 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>FFO-1725260-HAGAP.pdf</t>
+          <t>FFO-1717168-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>87,00</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>1726890</t>
+          <t>1717332</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -10824,24 +10824,24 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>FFO-1726890-HAGAP.pdf</t>
+          <t>FFO-1717332-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>176,23</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>1727335</t>
+          <t>1718019</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -10851,7 +10851,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>FFO-1727335-HAGAP.pdf</t>
+          <t>FFO-1718019-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
@@ -10868,7 +10868,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>1727808</t>
+          <t>1719070</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -10878,7 +10878,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>FFO-1727808-HAGAP.pdf</t>
+          <t>FFO-1719070-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
@@ -10888,14 +10888,14 @@
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>1729828</t>
+          <t>1719881</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -10905,7 +10905,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>FFO-1729828-HAGAP.pdf</t>
+          <t>FFO-1719881-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
@@ -10915,14 +10915,14 @@
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>1708066</t>
+          <t>1721869</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -10932,7 +10932,7 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>FFO.-1708066-HAGAP.pdf</t>
+          <t>FFO-1721869-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
@@ -10942,14 +10942,14 @@
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>1712957</t>
+          <t>1724491</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -10959,7 +10959,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>FFO.-1712957-HAGAP.pdf</t>
+          <t>FFO-1724491-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
@@ -10969,14 +10969,14 @@
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>1713660</t>
+          <t>1725260</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -10986,7 +10986,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>FFO.-1713660-HAGAP.pdf</t>
+          <t>FFO-1725260-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
@@ -10996,14 +10996,14 @@
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>1691380</t>
+          <t>1726324</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -11013,7 +11013,7 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>FFO_1691380.pdf</t>
+          <t>FFO-1726324-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
@@ -11023,14 +11023,14 @@
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>1717315</t>
+          <t>1726890</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -11040,7 +11040,7 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>FFO_1717315_HAGAP.pdf</t>
+          <t>FFO-1726890-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
@@ -11050,14 +11050,14 @@
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>1725869</t>
+          <t>1727335</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -11067,24 +11067,24 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>FFO_1725869_HAGAP.pdf</t>
+          <t>FFO-1727335-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>2.488,83</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>1718442</t>
+          <t>1727529</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -11094,7 +11094,7 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>FFO´1718442-HAGAP.pdf</t>
+          <t>FFO-1727529-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
@@ -11104,24 +11104,24 @@
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>1712530</t>
+          <t>1727808</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>MULT1712530-HAGAP.pdf</t>
+          <t>FFO-1727808-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
@@ -11129,22 +11129,26 @@
           <t>0,00</t>
         </is>
       </c>
-      <c r="E397" t="inlineStr"/>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>1694841</t>
+          <t>1729828</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>MULTA-1694841-HAGAP.pdf</t>
+          <t>FFO-1729828-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
@@ -11152,22 +11156,26 @@
           <t>0,00</t>
         </is>
       </c>
-      <c r="E398" t="inlineStr"/>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>1703223</t>
+          <t>1708066</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>MULTA-1703223-HAGAP.pdf</t>
+          <t>FFO.-1708066-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
@@ -11175,22 +11183,26 @@
           <t>0,00</t>
         </is>
       </c>
-      <c r="E399" t="inlineStr"/>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>1704877</t>
+          <t>1712957</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>MULTA-1704877-HAGAP.pdf</t>
+          <t>FFO.-1712957-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
@@ -11198,22 +11210,26 @@
           <t>0,00</t>
         </is>
       </c>
-      <c r="E400" t="inlineStr"/>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>1713044I</t>
+          <t>1713660</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>MULTA-1713044I-HAGAP.pdf</t>
+          <t>FFO.-1713660-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
@@ -11221,22 +11237,26 @@
           <t>0,00</t>
         </is>
       </c>
-      <c r="E401" t="inlineStr"/>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>1713903I</t>
+          <t>1691380</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>MULTA-1713903I-HAGAP.pdf</t>
+          <t>FFO_1691380.pdf</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
@@ -11244,22 +11264,26 @@
           <t>0,00</t>
         </is>
       </c>
-      <c r="E402" t="inlineStr"/>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>1715327</t>
+          <t>1717315</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>MULTA-1715327-HAGAP.pdf</t>
+          <t>FFO_1717315_HAGAP.pdf</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
@@ -11267,45 +11291,53 @@
           <t>0,00</t>
         </is>
       </c>
-      <c r="E403" t="inlineStr"/>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>1724491</t>
+          <t>1725869</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>MULTA-1724491-HAGAP.pdf</t>
+          <t>FFO_1725869_HAGAP.pdf</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>0,00</t>
-        </is>
-      </c>
-      <c r="E404" t="inlineStr"/>
+          <t>2.488,83</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>1726890</t>
+          <t>1718442</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>FFO</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>MULTA-1726890-HAGAP.pdf</t>
+          <t>FFO´1718442-HAGAP.pdf</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
@@ -11313,30 +11345,264 @@
           <t>0,00</t>
         </is>
       </c>
-      <c r="E405" t="inlineStr"/>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
+          <t>1712530</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>MULT1712530-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr"/>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>1694841</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>MULTA-1694841-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr"/>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>1703223</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>MULTA-1703223-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr"/>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>1704877</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>MULTA-1704877-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr"/>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>1713044I</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>MULTA-1713044I-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr"/>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>1713903I</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>MULTA-1713903I-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr"/>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>1715327</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>MULTA-1715327-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr"/>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>1724491</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>MULTA-1724491-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr"/>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>1726890</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>MULTA-1726890-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr"/>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>1727529</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>MULTA-1727529-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr"/>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
           <t>1726324</t>
         </is>
       </c>
-      <c r="B406" t="inlineStr">
-        <is>
-          <t>BMD</t>
-        </is>
-      </c>
-      <c r="C406" t="inlineStr">
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>BMD</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
         <is>
           <t>bmd parcial-1726324-hagap.pdf</t>
         </is>
       </c>
-      <c r="D406" t="inlineStr">
+      <c r="D416" t="inlineStr">
         <is>
           <t>2.048,89</t>
         </is>
       </c>
-      <c r="E406" t="inlineStr">
+      <c r="E416" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
